--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8394354F-CAEF-4198-ADCC-2B7FE7005493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BF413-071D-4EE1-A690-B3C524437BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="68">
   <si>
     <t>H23</t>
   </si>
@@ -232,10 +232,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>H67</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>H68</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -264,10 +260,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>H74</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>H75</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -281,6 +273,10 @@
   </si>
   <si>
     <t>H78</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H79</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -803,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB58"/>
+  <dimension ref="A1:AB59"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4855,7 +4851,7 @@
         <f t="shared" ref="V42" si="248">ROUND(D42/M42,3)</f>
         <v>25.100999999999999</v>
       </c>
-      <c r="W42" s="18">
+      <c r="W42" s="9">
         <f t="shared" ref="W42" si="249">ROUND(E42/N42,3)</f>
         <v>9.8460000000000001</v>
       </c>
@@ -4952,7 +4948,7 @@
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
         <v>23.690999999999999</v>
       </c>
-      <c r="W43" s="18">
+      <c r="W43" s="9">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
         <v>11.111000000000001</v>
       </c>
@@ -5296,7 +5292,7 @@
         <v>9.27</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K47" s="5">
         <f t="shared" ref="K47" si="307">M$2/M47</f>
@@ -5326,7 +5322,7 @@
         <v>0.33</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47" si="310">ROUND(B47/K47,3)</f>
@@ -5363,7 +5359,7 @@
     </row>
     <row r="48" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2">
         <f t="shared" ref="B48" si="318">D$2/D48</f>
@@ -5393,7 +5389,7 @@
         <v>7</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K48" s="2">
         <f t="shared" ref="K48" si="321">M$2/M48</f>
@@ -5410,7 +5406,7 @@
       <c r="N48" s="9">
         <v>0.08</v>
       </c>
-      <c r="O48" s="9">
+      <c r="O48" s="18">
         <v>0.5</v>
       </c>
       <c r="P48" s="13">
@@ -5423,7 +5419,7 @@
         <v>0.25</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T48" s="2">
         <f t="shared" ref="T48" si="324">ROUND(B48/K48,3)</f>
@@ -5441,7 +5437,7 @@
         <f t="shared" ref="W48" si="327">ROUND(E48/N48,3)</f>
         <v>9.875</v>
       </c>
-      <c r="X48" s="9">
+      <c r="X48" s="18">
         <f t="shared" ref="X48" si="328">ROUND(F48/O48,3)</f>
         <v>17.2</v>
       </c>
@@ -5460,7 +5456,7 @@
     </row>
     <row r="49" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" s="5">
         <f t="shared" ref="B49" si="332">D$2/D49</f>
@@ -5490,7 +5486,7 @@
         <v>7</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K49" s="5">
         <f t="shared" ref="K49" si="335">M$2/M49</f>
@@ -5520,7 +5516,7 @@
         <v>0.24</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T49" s="5">
         <f t="shared" ref="T49" si="338">ROUND(B49/K49,3)</f>
@@ -5538,15 +5534,15 @@
         <f t="shared" ref="W49" si="341">ROUND(E49/N49,3)</f>
         <v>7.75</v>
       </c>
-      <c r="X49" s="18">
+      <c r="X49" s="9">
         <f t="shared" ref="X49" si="342">ROUND(F49/O49,3)</f>
         <v>17.2</v>
       </c>
-      <c r="Y49" s="18">
+      <c r="Y49" s="9">
         <f t="shared" ref="Y49" si="343">ROUND(G49/P49,3)</f>
         <v>37.75</v>
       </c>
-      <c r="Z49" s="18">
+      <c r="Z49" s="9">
         <f t="shared" ref="Z49" si="344">ROUND(H49/Q49,3)</f>
         <v>22</v>
       </c>
@@ -5557,7 +5553,7 @@
     </row>
     <row r="50" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B50" s="2">
         <f t="shared" ref="B50" si="346">D$2/D50</f>
@@ -5587,7 +5583,7 @@
         <v>6.95</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K50" s="2">
         <f t="shared" ref="K50" si="349">M$2/M50</f>
@@ -5617,7 +5613,7 @@
         <v>0.24</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T50" s="2">
         <f t="shared" ref="T50" si="352">ROUND(B50/K50,3)</f>
@@ -5631,7 +5627,7 @@
         <f t="shared" ref="V50" si="354">ROUND(D50/M50,3)</f>
         <v>23.622</v>
       </c>
-      <c r="W50" s="18">
+      <c r="W50" s="9">
         <f t="shared" ref="W50" si="355">ROUND(E50/N50,3)</f>
         <v>9.1430000000000007</v>
       </c>
@@ -5639,22 +5635,22 @@
         <f t="shared" ref="X50" si="356">ROUND(F50/O50,3)</f>
         <v>16.510999999999999</v>
       </c>
-      <c r="Y50" s="18">
+      <c r="Y50" s="9">
         <f t="shared" ref="Y50" si="357">ROUND(G50/P50,3)</f>
         <v>37.832999999999998</v>
       </c>
-      <c r="Z50" s="18">
+      <c r="Z50" s="9">
         <f t="shared" ref="Z50" si="358">ROUND(H50/Q50,3)</f>
         <v>21.332999999999998</v>
       </c>
-      <c r="AA50" s="19">
+      <c r="AA50" s="10">
         <f t="shared" ref="AA50" si="359">ROUND(I50/R50,3)</f>
         <v>28.957999999999998</v>
       </c>
     </row>
     <row r="51" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" s="2">
         <f t="shared" ref="B51" si="360">D$2/D51</f>
@@ -5684,7 +5680,7 @@
         <v>4.96</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K51" s="2">
         <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
@@ -5714,7 +5710,7 @@
         <v>0.18</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T51" s="2">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
@@ -5751,7 +5747,7 @@
     </row>
     <row r="52" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" s="5">
         <f t="shared" ref="B52:B53" si="374">D$2/D52</f>
@@ -5781,7 +5777,7 @@
         <v>4.97</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K52" s="5">
         <f t="shared" si="363"/>
@@ -5811,7 +5807,7 @@
         <v>0.18</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T52" s="5">
         <f t="shared" ref="T52:T53" si="377">ROUND(B52/K52,3)</f>
@@ -5825,19 +5821,19 @@
         <f t="shared" ref="V52:V53" si="379">ROUND(D52/M52,3)</f>
         <v>23.193999999999999</v>
       </c>
-      <c r="W52" s="18">
+      <c r="W52" s="9">
         <f t="shared" ref="W52:W53" si="380">ROUND(E52/N52,3)</f>
         <v>9</v>
       </c>
-      <c r="X52" s="18">
+      <c r="X52" s="9">
         <f t="shared" ref="X52:X53" si="381">ROUND(F52/O52,3)</f>
         <v>16.638000000000002</v>
       </c>
-      <c r="Y52" s="18">
+      <c r="Y52" s="9">
         <f t="shared" ref="Y52:Y53" si="382">ROUND(G52/P52,3)</f>
         <v>41.353000000000002</v>
       </c>
-      <c r="Z52" s="18">
+      <c r="Z52" s="9">
         <f t="shared" ref="Z52:Z53" si="383">ROUND(H52/Q52,3)</f>
         <v>23</v>
       </c>
@@ -5848,7 +5844,7 @@
     </row>
     <row r="53" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B53" s="5">
         <f t="shared" si="374"/>
@@ -5878,7 +5874,7 @@
         <v>4.91</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K53" s="5">
         <f t="shared" si="363"/>
@@ -5908,7 +5904,7 @@
         <v>0.16</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T53" s="5">
         <f t="shared" si="377"/>
@@ -5922,11 +5918,11 @@
         <f t="shared" si="379"/>
         <v>23.277000000000001</v>
       </c>
-      <c r="W53" s="18">
+      <c r="W53" s="9">
         <f t="shared" si="380"/>
         <v>9.5709999999999997</v>
       </c>
-      <c r="X53" s="18">
+      <c r="X53" s="9">
         <f t="shared" si="381"/>
         <v>16.553000000000001</v>
       </c>
@@ -5934,7 +5930,7 @@
         <f t="shared" si="382"/>
         <v>44.533000000000001</v>
       </c>
-      <c r="Z53" s="18">
+      <c r="Z53" s="9">
         <f t="shared" si="383"/>
         <v>22.332999999999998</v>
       </c>
@@ -5945,37 +5941,37 @@
     </row>
     <row r="54" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.34350132625994</v>
+        <v>33.588510354041411</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0033156498673741</v>
+        <v>1.0106880427521709</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.08</v>
+        <v>14.97</v>
       </c>
       <c r="E54" s="13">
         <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.61</v>
+        <v>7.6</v>
       </c>
       <c r="G54" s="9">
-        <v>6.81</v>
+        <v>6.73</v>
       </c>
       <c r="H54" s="9">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="I54" s="10">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
@@ -5990,7 +5986,7 @@
         <v>0.65</v>
       </c>
       <c r="N54" s="13">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O54" s="9">
         <v>0.47</v>
@@ -6005,95 +6001,95 @@
         <v>0.15</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0029999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.2</v>
+        <v>23.030999999999999</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>6.6669999999999998</v>
-      </c>
-      <c r="X54" s="18">
+        <v>4.444</v>
+      </c>
+      <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.190999999999999</v>
-      </c>
-      <c r="Y54" s="18">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.4</v>
-      </c>
-      <c r="Z54" s="18">
+        <v>44.866999999999997</v>
+      </c>
+      <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>22</v>
-      </c>
-      <c r="AA54" s="19">
+        <v>21.332999999999998</v>
+      </c>
+      <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.667000000000002</v>
+        <v>31.466999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>45.79417122040072</v>
+        <v>46.130275229357792</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3734061930783241</v>
+        <v>1.3733944954128441</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.98</v>
+        <v>10.9</v>
       </c>
       <c r="E55" s="9">
         <v>0.4</v>
       </c>
       <c r="F55" s="9">
-        <v>7.4</v>
+        <v>7.33</v>
       </c>
       <c r="G55" s="13">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="H55" s="13">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="I55" s="14">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K55" s="2">
         <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>0.98484848484848486</v>
+        <v>1</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N55" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O55" s="9">
         <v>0.47</v>
       </c>
       <c r="P55" s="13">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q55" s="13">
         <v>0.03</v>
@@ -6102,74 +6098,74 @@
         <v>0.15</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.72499999999999998</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.395</v>
+        <v>1.373</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.635999999999999</v>
+        <v>16.768999999999998</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.744999999999999</v>
+        <v>15.596</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>20.812999999999999</v>
+        <v>22.067</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8.3330000000000002</v>
+        <v>8.6669999999999998</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.399999999999999</v>
+        <v>18.466999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.514338575393147</v>
+        <v>46.172635445362708</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0157261794634598</v>
+        <v>1.0009182736455464</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.81</v>
+        <v>10.89</v>
       </c>
       <c r="E56" s="13">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F56" s="18">
-        <v>7.24</v>
+        <v>7.33</v>
       </c>
       <c r="G56" s="18">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="H56" s="13">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I56" s="19">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="J56" s="20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
@@ -6177,7 +6173,7 @@
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
@@ -6199,11 +6195,11 @@
         <v>0.15</v>
       </c>
       <c r="S56" s="20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.73599999999999999</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
@@ -6211,51 +6207,51 @@
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.379000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>6.5</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.083</v>
+        <v>15.271000000000001</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>20.75</v>
+        <v>20.812999999999999</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
     <row r="57" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>50.031840796019893</v>
+        <v>49.392927308447931</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0756218905472636</v>
+        <v>1.069744597249509</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.050000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="E57" s="9">
         <v>0.39</v>
       </c>
       <c r="F57" s="13">
-        <v>6.64</v>
+        <v>6.77</v>
       </c>
       <c r="G57" s="13">
         <v>3.18</v>
@@ -6264,10 +6260,10 @@
         <v>0.23</v>
       </c>
       <c r="I57" s="14">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K57" s="2">
         <f t="shared" ref="K57:K58" si="424">M$2/M57</f>
@@ -6282,7 +6278,7 @@
         <v>0.64</v>
       </c>
       <c r="N57" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O57" s="13">
         <v>0.47</v>
@@ -6297,27 +6293,27 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.76800000000000002</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0429999999999999</v>
+        <v>1.0369999999999999</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.702999999999999</v>
+        <v>15.906000000000001</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>6.5</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>14.128</v>
+        <v>14.404</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
@@ -6329,60 +6325,60 @@
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.786000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.571282051282047</v>
+        <v>51.413087934560323</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0307692307692309</v>
+        <v>1.0408997955010226</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.75</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E58" s="9">
         <v>0.39</v>
       </c>
       <c r="F58" s="13">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="G58" s="13">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="H58" s="9">
         <v>0.23</v>
       </c>
       <c r="I58" s="14">
-        <v>2.4500000000000002</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K58" s="2">
         <f t="shared" si="424"/>
-        <v>66.206349206349202</v>
+        <v>65.171874999999986</v>
       </c>
       <c r="L58" s="2">
         <f t="shared" si="425"/>
-        <v>1.0158730158730158</v>
+        <v>1</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="426"/>
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="N58" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O58" s="13">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="P58" s="13">
         <v>0.15</v>
@@ -6394,31 +6390,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.77900000000000003</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.0149999999999999</v>
+        <v>1.0409999999999999</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.476000000000001</v>
+        <v>15.281000000000001</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>5.5709999999999997</v>
+        <v>6.5</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>14.151999999999999</v>
+        <v>13.872</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.067</v>
+        <v>20.2</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
@@ -6426,7 +6422,104 @@
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.5</v>
+        <v>17.643000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="2">
+        <f t="shared" ref="B59" si="435">D$2/D59</f>
+        <v>55.376651982378846</v>
+      </c>
+      <c r="C59" s="2">
+        <f t="shared" ref="C59" si="436">D58/D59</f>
+        <v>1.0770925110132157</v>
+      </c>
+      <c r="D59" s="6">
+        <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
+        <v>9.08</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="F59" s="13">
+        <v>6.18</v>
+      </c>
+      <c r="G59" s="13">
+        <v>2.67</v>
+      </c>
+      <c r="H59" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="I59" s="14">
+        <v>2.09</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K59" s="2">
+        <f t="shared" ref="K59" si="438">M$2/M59</f>
+        <v>67.274193548387075</v>
+      </c>
+      <c r="L59" s="2">
+        <f t="shared" ref="L59" si="439">M58/M59</f>
+        <v>1.0322580645161288</v>
+      </c>
+      <c r="M59" s="6">
+        <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="N59" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O59" s="13">
+        <v>0.46</v>
+      </c>
+      <c r="P59" s="13">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R59" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S59" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="T59" s="2">
+        <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="U59" s="2">
+        <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="V59" s="6">
+        <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
+        <v>14.645</v>
+      </c>
+      <c r="W59" s="9">
+        <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
+        <v>6.2859999999999996</v>
+      </c>
+      <c r="X59" s="13">
+        <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
+        <v>13.435</v>
+      </c>
+      <c r="Y59" s="13">
+        <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
+        <v>19.071000000000002</v>
+      </c>
+      <c r="Z59" s="9">
+        <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA59" s="14">
+        <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
+        <v>14.929</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BF413-071D-4EE1-A690-B3C524437BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921974B4-4949-4271-B1EE-9B9399641889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="69">
   <si>
     <t>H23</t>
   </si>
@@ -277,6 +277,10 @@
   </si>
   <si>
     <t>H79</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H80</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -799,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB59"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5945,30 +5949,30 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.588510354041411</v>
+        <v>33.633444816053505</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0106880427521709</v>
+        <v>1.0120401337792642</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>14.97</v>
+        <v>14.950000000000001</v>
       </c>
       <c r="E54" s="13">
         <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.6</v>
+        <v>7.57</v>
       </c>
       <c r="G54" s="9">
         <v>6.73</v>
       </c>
       <c r="H54" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I54" s="10">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
@@ -5986,7 +5990,7 @@
         <v>0.65</v>
       </c>
       <c r="N54" s="13">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O54" s="9">
         <v>0.47</v>
@@ -6005,23 +6009,23 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52300000000000002</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0109999999999999</v>
+        <v>1.012</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.030999999999999</v>
+        <v>23</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>4.444</v>
+        <v>5</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.170000000000002</v>
+        <v>16.106000000000002</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
@@ -6029,11 +6033,11 @@
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.466999999999999</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6042,30 +6046,30 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.130275229357792</v>
+        <v>46.257589696412133</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3733944954128441</v>
+        <v>1.375344986200552</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.9</v>
+        <v>10.870000000000001</v>
       </c>
       <c r="E55" s="9">
         <v>0.4</v>
       </c>
       <c r="F55" s="9">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="G55" s="13">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="H55" s="13">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I55" s="14">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
@@ -6083,7 +6087,7 @@
         <v>0.65</v>
       </c>
       <c r="N55" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O55" s="9">
         <v>0.47</v>
@@ -6102,35 +6106,35 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.71899999999999997</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.373</v>
+        <v>1.375</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.768999999999998</v>
+        <v>16.722999999999999</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.596</v>
+        <v>15.510999999999999</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22.067</v>
+        <v>22.2</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8.6669999999999998</v>
+        <v>8.3330000000000002</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6139,21 +6143,21 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.172635445362708</v>
+        <v>46.342857142857127</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0009182736455464</v>
+        <v>1.0018433179723503</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.89</v>
+        <v>10.850000000000001</v>
       </c>
       <c r="E56" s="13">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F56" s="18">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="G56" s="18">
         <v>3.33</v>
@@ -6162,22 +6166,22 @@
         <v>0.23</v>
       </c>
       <c r="I56" s="19">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>0.98484848484848486</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N56" s="13">
         <v>0.06</v>
@@ -6186,7 +6190,7 @@
         <v>0.48</v>
       </c>
       <c r="P56" s="18">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q56" s="13">
         <v>0.02</v>
@@ -6199,27 +6203,27 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.73099999999999998</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>1.016</v>
+        <v>1.002</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.5</v>
+        <v>16.692</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.271000000000001</v>
+        <v>15.188000000000001</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>20.812999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
@@ -6227,7 +6231,7 @@
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.399999999999999</v>
+        <v>18.466999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6237,30 +6241,30 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>49.392927308447931</v>
+        <v>50.585513078470818</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.069744597249509</v>
+        <v>1.091549295774648</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.18</v>
+        <v>9.94</v>
       </c>
       <c r="E57" s="9">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="F57" s="13">
-        <v>6.77</v>
+        <v>6.55</v>
       </c>
       <c r="G57" s="13">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="H57" s="13">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I57" s="14">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>65</v>
@@ -6271,14 +6275,14 @@
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>1.03125</v>
+        <v>1.015625</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
         <v>0.64</v>
       </c>
       <c r="N57" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O57" s="13">
         <v>0.47</v>
@@ -6297,35 +6301,35 @@
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.75800000000000001</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0369999999999999</v>
+        <v>1.075</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.906000000000001</v>
+        <v>15.531000000000001</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.1669999999999998</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>14.404</v>
+        <v>13.936</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.2</v>
+        <v>21.132999999999999</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>18.786000000000001</v>
+        <v>18.571000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6334,30 +6338,30 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.413087934560323</v>
+        <v>51.308163265306113</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0408997955010226</v>
+        <v>1.0142857142857142</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.7799999999999994</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E58" s="9">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="F58" s="13">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="G58" s="13">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="H58" s="9">
         <v>0.23</v>
       </c>
       <c r="I58" s="14">
-        <v>2.4700000000000002</v>
+        <v>2.46</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
@@ -6394,27 +6398,27 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.78900000000000003</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.0409999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.281000000000001</v>
+        <v>15.313000000000001</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.872</v>
+        <v>13.894</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.2</v>
+        <v>20.266999999999999</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
@@ -6422,7 +6426,7 @@
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.643000000000001</v>
+        <v>17.571000000000002</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6431,27 +6435,27 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>55.376651982378846</v>
+        <v>56.118303571428562</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0770925110132157</v>
+        <v>1.09375</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>9.08</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E59" s="9">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F59" s="13">
-        <v>6.18</v>
+        <v>6.07</v>
       </c>
       <c r="G59" s="13">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="H59" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I59" s="14">
         <v>2.09</v>
@@ -6461,21 +6465,21 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0322580645161288</v>
+        <v>1.0491803278688523</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N59" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O59" s="13">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6484,43 +6488,141 @@
         <v>0.02</v>
       </c>
       <c r="R59" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.82299999999999995</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.0429999999999999</v>
+        <v>1.042</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.645</v>
+        <v>14.689</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>6.2859999999999996</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.435</v>
+        <v>13.489000000000001</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>19.071000000000002</v>
+        <v>18.928999999999998</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>14.929</v>
-      </c>
+        <v>16.077000000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="5">
+        <f t="shared" ref="B60" si="449">D$2/D60</f>
+        <v>56.751693002257333</v>
+      </c>
+      <c r="C60" s="5">
+        <f t="shared" ref="C60" si="450">D59/D60</f>
+        <v>1.0112866817155757</v>
+      </c>
+      <c r="D60" s="4">
+        <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
+        <v>8.86</v>
+      </c>
+      <c r="E60" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="F60" s="18">
+        <v>6.04</v>
+      </c>
+      <c r="G60" s="18">
+        <v>2.59</v>
+      </c>
+      <c r="H60" s="18">
+        <v>0.23</v>
+      </c>
+      <c r="I60" s="19">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="K60" s="5">
+        <f t="shared" ref="K60" si="452">M$2/M60</f>
+        <v>67.274193548387075</v>
+      </c>
+      <c r="L60" s="5">
+        <f t="shared" ref="L60" si="453">M59/M60</f>
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="M60" s="4">
+        <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="N60" s="18">
+        <v>0.08</v>
+      </c>
+      <c r="O60" s="18">
+        <v>0.46</v>
+      </c>
+      <c r="P60" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q60" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R60" s="19">
+        <v>0.13</v>
+      </c>
+      <c r="S60" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="T60" s="5">
+        <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="U60" s="5">
+        <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
+        <v>1.028</v>
+      </c>
+      <c r="V60" s="4">
+        <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
+        <v>14.29</v>
+      </c>
+      <c r="W60" s="18">
+        <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
+        <v>5</v>
+      </c>
+      <c r="X60" s="18">
+        <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
+        <v>13.13</v>
+      </c>
+      <c r="Y60" s="18">
+        <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
+        <v>18.5</v>
+      </c>
+      <c r="Z60" s="18">
+        <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA60" s="19">
+        <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
+        <v>15.615</v>
+      </c>
+      <c r="AB60" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921974B4-4949-4271-B1EE-9B9399641889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B33CA49-26C2-487E-94E4-DF9485646F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
   <si>
     <t>H23</t>
   </si>
@@ -281,6 +281,10 @@
   </si>
   <si>
     <t>H80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H81</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -803,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB60"/>
+  <dimension ref="A1:AB61"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5949,51 +5953,51 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.633444816053505</v>
+        <v>33.476697736351525</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0120401337792642</v>
+        <v>1.0073235685752331</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>14.950000000000001</v>
+        <v>15.020000000000001</v>
       </c>
       <c r="E54" s="13">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F54" s="9">
         <v>7.57</v>
       </c>
       <c r="G54" s="9">
-        <v>6.73</v>
+        <v>6.8</v>
       </c>
       <c r="H54" s="9">
         <v>0.65</v>
       </c>
       <c r="I54" s="10">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>1</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N54" s="13">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O54" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P54" s="9">
         <v>0.15</v>
@@ -6009,27 +6013,27 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52400000000000002</v>
+        <v>0.53</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.012</v>
+        <v>1.0229999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23</v>
+        <v>22.757999999999999</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>5</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.106000000000002</v>
+        <v>15.771000000000001</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>44.866999999999997</v>
+        <v>45.332999999999998</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
@@ -6037,7 +6041,7 @@
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.2</v>
+        <v>31.667000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6046,21 +6050,21 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.257589696412133</v>
+        <v>46.172635445362708</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.375344986200552</v>
+        <v>1.379247015610652</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.870000000000001</v>
+        <v>10.89</v>
       </c>
       <c r="E55" s="9">
         <v>0.4</v>
       </c>
       <c r="F55" s="9">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="G55" s="13">
         <v>3.33</v>
@@ -6080,7 +6084,7 @@
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1</v>
+        <v>1.0153846153846153</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
@@ -6106,15 +6110,15 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.72099999999999997</v>
+        <v>0.72</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.375</v>
+        <v>1.3580000000000001</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.722999999999999</v>
+        <v>16.754000000000001</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
@@ -6122,7 +6126,7 @@
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.510999999999999</v>
+        <v>15.553000000000001</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
@@ -6143,30 +6147,30 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.342857142857127</v>
+        <v>46.385608856088552</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0018433179723503</v>
+        <v>1.0046125461254614</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.850000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="E56" s="13">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F56" s="18">
-        <v>7.29</v>
+        <v>7.27</v>
       </c>
       <c r="G56" s="18">
         <v>3.33</v>
       </c>
       <c r="H56" s="13">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I56" s="19">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
@@ -6203,23 +6207,23 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.72199999999999998</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>1.002</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.692</v>
+        <v>16.677</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>6.5</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.188000000000001</v>
+        <v>15.146000000000001</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
@@ -6227,11 +6231,11 @@
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6241,30 +6245,30 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>50.585513078470818</v>
+        <v>49.882936507936499</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.091549295774648</v>
+        <v>1.0753968253968254</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>9.94</v>
+        <v>10.08</v>
       </c>
       <c r="E57" s="9">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="F57" s="13">
-        <v>6.55</v>
+        <v>6.64</v>
       </c>
       <c r="G57" s="13">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="H57" s="13">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I57" s="14">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>65</v>
@@ -6301,35 +6305,35 @@
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.77600000000000002</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.075</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.531000000000001</v>
+        <v>15.75</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>6.1669999999999998</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>13.936</v>
+        <v>14.128</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.132999999999999</v>
+        <v>21.266999999999999</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.713999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6338,30 +6342,30 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.308163265306113</v>
+        <v>50.687499999999993</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0142857142857142</v>
+        <v>1.0161290322580645</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.8000000000000007</v>
+        <v>9.92</v>
       </c>
       <c r="E58" s="9">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="F58" s="13">
-        <v>6.53</v>
+        <v>6.59</v>
       </c>
       <c r="G58" s="13">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="H58" s="9">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="I58" s="14">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
@@ -6379,7 +6383,7 @@
         <v>0.64</v>
       </c>
       <c r="N58" s="9">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="O58" s="13">
         <v>0.47</v>
@@ -6398,35 +6402,35 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.78700000000000003</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.014</v>
+        <v>1.016</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.313000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.894</v>
+        <v>14.021000000000001</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.266999999999999</v>
+        <v>20.466999999999999</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.571000000000002</v>
+        <v>17.856999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6439,7 +6443,7 @@
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.09375</v>
+        <v>1.107142857142857</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
@@ -6449,13 +6453,13 @@
         <v>0.4</v>
       </c>
       <c r="F59" s="13">
-        <v>6.07</v>
+        <v>6.08</v>
       </c>
       <c r="G59" s="13">
         <v>2.65</v>
       </c>
       <c r="H59" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I59" s="14">
         <v>2.09</v>
@@ -6465,21 +6469,21 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0491803278688523</v>
+        <v>1.0322580645161288</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N59" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O59" s="13">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6495,23 +6499,23 @@
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.82099999999999995</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.042</v>
+        <v>1.073</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.689</v>
+        <v>14.452</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.489000000000001</v>
+        <v>13.217000000000001</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
@@ -6519,7 +6523,7 @@
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
@@ -6532,51 +6536,51 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>56.751693002257333</v>
+        <v>56.369955156950667</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0112866817155757</v>
+        <v>1.0044843049327354</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.86</v>
+        <v>8.92</v>
       </c>
       <c r="E60" s="18">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F60" s="18">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="G60" s="18">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.0299999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
       </c>
       <c r="K60" s="5">
         <f t="shared" ref="K60" si="452">M$2/M60</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L60" s="5">
         <f t="shared" ref="L60" si="453">M59/M60</f>
-        <v>0.9838709677419355</v>
+        <v>1.0163934426229508</v>
       </c>
       <c r="M60" s="4">
         <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N60" s="18">
         <v>0.08</v>
       </c>
       <c r="O60" s="18">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P60" s="18">
         <v>0.14000000000000001</v>
@@ -6592,27 +6596,27 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.84399999999999997</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>1.028</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.29</v>
+        <v>14.622999999999999</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>5</v>
+        <v>5.125</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.13</v>
+        <v>13.444000000000001</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.5</v>
+        <v>18.856999999999999</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6620,9 +6624,106 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
+        <v>15.692</v>
+      </c>
+      <c r="AB60" s="20"/>
+    </row>
+    <row r="61" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="5">
+        <f t="shared" ref="B61" si="463">D$2/D61</f>
+        <v>58.196759259259245</v>
+      </c>
+      <c r="C61" s="5">
+        <f t="shared" ref="C61" si="464">D60/D61</f>
+        <v>1.0324074074074074</v>
+      </c>
+      <c r="D61" s="4">
+        <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
+        <v>8.64</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="F61" s="13">
+        <v>5.78</v>
+      </c>
+      <c r="G61" s="9">
+        <v>2.63</v>
+      </c>
+      <c r="H61" s="18">
+        <v>0.23</v>
+      </c>
+      <c r="I61" s="10">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J61" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K61" s="5">
+        <f t="shared" ref="K61" si="466">M$2/M61</f>
+        <v>67.274193548387075</v>
+      </c>
+      <c r="L61" s="5">
+        <f t="shared" ref="L61" si="467">M60/M61</f>
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="M61" s="4">
+        <f t="shared" ref="M61" si="468">SUM(O61:Q61)</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="N61" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="O61" s="13">
+        <v>0.46</v>
+      </c>
+      <c r="P61" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q61" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="R61" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="S61" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="T61" s="5">
+        <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="U61" s="5">
+        <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="V61" s="4">
+        <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
+        <v>13.935</v>
+      </c>
+      <c r="W61" s="9">
+        <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
+        <v>6.8330000000000002</v>
+      </c>
+      <c r="X61" s="13">
+        <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
+        <v>12.565</v>
+      </c>
+      <c r="Y61" s="9">
+        <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
+        <v>18.786000000000001</v>
+      </c>
+      <c r="Z61" s="18">
+        <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA61" s="10">
+        <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
         <v>15.615</v>
       </c>
-      <c r="AB60" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B33CA49-26C2-487E-94E4-DF9485646F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44D7A8E-C2B2-45FD-8054-68575D400BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="71">
   <si>
     <t>H23</t>
   </si>
@@ -285,6 +285,10 @@
   </si>
   <si>
     <t>H81</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H82</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -807,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB61"/>
+  <dimension ref="A1:AB62"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5953,51 +5957,51 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.476697736351525</v>
+        <v>33.521333333333331</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0073235685752331</v>
+        <v>1.0086666666666668</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.020000000000001</v>
+        <v>15</v>
       </c>
       <c r="E54" s="13">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.57</v>
+        <v>7.55</v>
       </c>
       <c r="G54" s="9">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
       <c r="H54" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I54" s="10">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>0.98484848484848486</v>
+        <v>1</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N54" s="13">
         <v>0.06</v>
       </c>
       <c r="O54" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P54" s="9">
         <v>0.15</v>
@@ -6013,35 +6017,35 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.53</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0229999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>22.757999999999999</v>
+        <v>23.077000000000002</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>6.8330000000000002</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>15.771000000000001</v>
+        <v>16.064</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.332999999999998</v>
+        <v>45.4</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.667000000000002</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6050,27 +6054,27 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.172635445362708</v>
+        <v>45.62794918330308</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.379247015610652</v>
+        <v>1.3611615245009074</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.89</v>
+        <v>11.02</v>
       </c>
       <c r="E55" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F55" s="9">
-        <v>7.31</v>
+        <v>7.43</v>
       </c>
       <c r="G55" s="13">
         <v>3.33</v>
       </c>
       <c r="H55" s="13">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="I55" s="14">
         <v>2.76</v>
@@ -6084,7 +6088,7 @@
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1.0153846153846153</v>
+        <v>1</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
@@ -6110,23 +6114,23 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.72</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.3580000000000001</v>
+        <v>1.361</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.754000000000001</v>
+        <v>16.954000000000001</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>5.7140000000000004</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.553000000000001</v>
+        <v>15.808999999999999</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
@@ -6134,7 +6138,7 @@
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8.3330000000000002</v>
+        <v>8.6669999999999998</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
@@ -6151,47 +6155,47 @@
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0046125461254614</v>
+        <v>1.0166051660516604</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
         <v>10.84</v>
       </c>
       <c r="E56" s="13">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F56" s="18">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="G56" s="18">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="H56" s="13">
         <v>0.24</v>
       </c>
       <c r="I56" s="19">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>64.169230769230751</v>
+        <v>65.171874999999986</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1</v>
+        <v>1.015625</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="N56" s="13">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O56" s="18">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P56" s="18">
         <v>0.15</v>
@@ -6207,27 +6211,27 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.72299999999999998</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>1.0049999999999999</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.677</v>
+        <v>16.937999999999999</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.146000000000001</v>
+        <v>15.446999999999999</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.2</v>
+        <v>22.266999999999999</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
@@ -6235,7 +6239,7 @@
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.399999999999999</v>
+        <v>18.466999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6245,18 +6249,18 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>49.882936507936499</v>
+        <v>49.982107355864805</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0753968253968254</v>
+        <v>1.0775347912524851</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.08</v>
+        <v>10.06</v>
       </c>
       <c r="E57" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F57" s="13">
         <v>6.64</v>
@@ -6265,7 +6269,7 @@
         <v>3.19</v>
       </c>
       <c r="H57" s="13">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I57" s="14">
         <v>2.62</v>
@@ -6279,7 +6283,7 @@
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>1.015625</v>
+        <v>1</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
@@ -6298,26 +6302,26 @@
         <v>0.02</v>
       </c>
       <c r="R57" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.76500000000000001</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0589999999999999</v>
+        <v>1.0780000000000001</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.75</v>
+        <v>15.718999999999999</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
@@ -6329,11 +6333,11 @@
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>18.713999999999999</v>
+        <v>17.466999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6342,30 +6346,30 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>50.687499999999993</v>
+        <v>51.624229979466108</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0161290322580645</v>
+        <v>1.0328542094455853</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.92</v>
+        <v>9.74</v>
       </c>
       <c r="E58" s="9">
         <v>0.39</v>
       </c>
       <c r="F58" s="13">
-        <v>6.59</v>
+        <v>6.51</v>
       </c>
       <c r="G58" s="13">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="H58" s="9">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I58" s="14">
-        <v>2.5</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
@@ -6383,7 +6387,7 @@
         <v>0.64</v>
       </c>
       <c r="N58" s="9">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="O58" s="13">
         <v>0.47</v>
@@ -6402,35 +6406,35 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.77800000000000002</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.016</v>
+        <v>1.0329999999999999</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.5</v>
+        <v>15.218999999999999</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>14.021000000000001</v>
+        <v>13.851000000000001</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.466999999999999</v>
+        <v>20.067</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.856999999999999</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6439,24 +6443,24 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>56.118303571428562</v>
+        <v>55.01312910284463</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.107142857142857</v>
+        <v>1.0656455142231946</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>8.9600000000000009</v>
+        <v>9.14</v>
       </c>
       <c r="E59" s="9">
         <v>0.4</v>
       </c>
       <c r="F59" s="13">
-        <v>6.08</v>
+        <v>6.24</v>
       </c>
       <c r="G59" s="13">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="H59" s="9">
         <v>0.23</v>
@@ -6492,22 +6496,22 @@
         <v>0.02</v>
       </c>
       <c r="R59" s="14">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.83399999999999996</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.073</v>
+        <v>1.032</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.452</v>
+        <v>14.742000000000001</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
@@ -6515,11 +6519,11 @@
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.217000000000001</v>
+        <v>13.565</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>18.928999999999998</v>
+        <v>19.071000000000002</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
@@ -6527,7 +6531,7 @@
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>16.077000000000002</v>
+        <v>14.929</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6536,30 +6540,30 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>56.369955156950667</v>
+        <v>56.751693002257319</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0044843049327354</v>
+        <v>1.0316027088036117</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.92</v>
+        <v>8.8600000000000012</v>
       </c>
       <c r="E60" s="18">
         <v>0.41</v>
       </c>
       <c r="F60" s="18">
-        <v>6.05</v>
+        <v>6.03</v>
       </c>
       <c r="G60" s="18">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.04</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
@@ -6577,7 +6581,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N60" s="18">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O60" s="18">
         <v>0.45</v>
@@ -6596,27 +6600,27 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.82399999999999995</v>
+        <v>0.83</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>0.98799999999999999</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.622999999999999</v>
+        <v>14.525</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>5.125</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.444000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.856999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6624,7 +6628,7 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
-        <v>15.692</v>
+        <v>15.615</v>
       </c>
       <c r="AB60" s="20"/>
     </row>
@@ -6634,24 +6638,24 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>58.196759259259245</v>
+        <v>57.995386389850054</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0324074074074074</v>
+        <v>1.0219146482122261</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.64</v>
+        <v>8.67</v>
       </c>
       <c r="E61" s="9">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="F61" s="13">
-        <v>5.78</v>
+        <v>5.84</v>
       </c>
       <c r="G61" s="9">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="H61" s="18">
         <v>0.23</v>
@@ -6664,21 +6668,21 @@
       </c>
       <c r="K61" s="5">
         <f t="shared" ref="K61" si="466">M$2/M61</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" ref="L61" si="467">M60/M61</f>
-        <v>0.9838709677419355</v>
+        <v>1</v>
       </c>
       <c r="M61" s="4">
         <f t="shared" ref="M61" si="468">SUM(O61:Q61)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N61" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O61" s="13">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P61" s="9">
         <v>0.14000000000000001</v>
@@ -6694,27 +6698,27 @@
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.86499999999999999</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.0489999999999999</v>
+        <v>1.022</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>13.935</v>
+        <v>14.212999999999999</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
-        <v>6.8330000000000002</v>
+        <v>6.7140000000000004</v>
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>12.565</v>
+        <v>12.978</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
-        <v>18.786000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z61" s="18">
         <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
@@ -6722,6 +6726,103 @@
       </c>
       <c r="AA61" s="10">
         <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
+        <v>15.615</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="5">
+        <f t="shared" ref="B62" si="477">D$2/D62</f>
+        <v>58.878220140515211</v>
+      </c>
+      <c r="C62" s="5">
+        <f t="shared" ref="C62" si="478">D61/D62</f>
+        <v>1.0152224824355971</v>
+      </c>
+      <c r="D62" s="4">
+        <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
+        <v>8.5400000000000009</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="F62" s="13">
+        <v>5.7</v>
+      </c>
+      <c r="G62" s="9">
+        <v>2.61</v>
+      </c>
+      <c r="H62" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="I62" s="10">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J62" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="K62" s="5">
+        <f t="shared" ref="K62" si="480">M$2/M62</f>
+        <v>68.377049180327845</v>
+      </c>
+      <c r="L62" s="5">
+        <f t="shared" ref="L62" si="481">M61/M62</f>
+        <v>1</v>
+      </c>
+      <c r="M62" s="4">
+        <f t="shared" ref="M62" si="482">SUM(O62:Q62)</f>
+        <v>0.6100000000000001</v>
+      </c>
+      <c r="N62" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="O62" s="13">
+        <v>0.45</v>
+      </c>
+      <c r="P62" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R62" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="S62" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="T62" s="5">
+        <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="U62" s="5">
+        <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="V62" s="4">
+        <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
+        <v>14</v>
+      </c>
+      <c r="W62" s="9">
+        <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
+        <v>4.875</v>
+      </c>
+      <c r="X62" s="13">
+        <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
+        <v>12.667</v>
+      </c>
+      <c r="Y62" s="9">
+        <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
+        <v>18.643000000000001</v>
+      </c>
+      <c r="Z62" s="18">
+        <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA62" s="10">
+        <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
         <v>15.615</v>
       </c>
     </row>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44D7A8E-C2B2-45FD-8054-68575D400BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0BA930-8E90-4BDA-B602-94B892FF784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="72">
   <si>
     <t>H23</t>
   </si>
@@ -289,6 +289,10 @@
   </si>
   <si>
     <t>H82</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H83</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -811,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB62"/>
+  <dimension ref="A1:AB63"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5957,30 +5961,30 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.521333333333331</v>
+        <v>33.432180851063826</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0086666666666668</v>
+        <v>1.0059840425531914</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15</v>
+        <v>15.040000000000001</v>
       </c>
       <c r="E54" s="13">
         <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.55</v>
+        <v>7.58</v>
       </c>
       <c r="G54" s="9">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="H54" s="9">
         <v>0.64</v>
       </c>
       <c r="I54" s="10">
-        <v>4.71</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
@@ -6017,15 +6021,15 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52200000000000002</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0089999999999999</v>
+        <v>1.006</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.077000000000002</v>
+        <v>23.138000000000002</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
@@ -6033,11 +6037,11 @@
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.064</v>
+        <v>16.128</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.4</v>
+        <v>45.466999999999999</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
@@ -6045,7 +6049,7 @@
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.4</v>
+        <v>32.067</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6054,51 +6058,51 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>45.62794918330308</v>
+        <v>46.428439519852255</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3611615245009074</v>
+        <v>1.3887349953831949</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>11.02</v>
+        <v>10.83</v>
       </c>
       <c r="E55" s="9">
         <v>0.39</v>
       </c>
       <c r="F55" s="9">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="G55" s="13">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="H55" s="13">
         <v>0.26</v>
       </c>
       <c r="I55" s="14">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
       </c>
       <c r="K55" s="2">
         <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N55" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O55" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P55" s="13">
         <v>0.15</v>
@@ -6114,15 +6118,15 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.71099999999999997</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.361</v>
+        <v>1.41</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.954000000000001</v>
+        <v>16.408999999999999</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
@@ -6130,11 +6134,11 @@
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.808999999999999</v>
+        <v>15.103999999999999</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22.2</v>
+        <v>22.132999999999999</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
@@ -6142,7 +6146,7 @@
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.399999999999999</v>
+        <v>18.466999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6151,51 +6155,51 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.385608856088552</v>
+        <v>46.687093779015775</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0166051660516604</v>
+        <v>1.0055710306406684</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.84</v>
+        <v>10.770000000000001</v>
       </c>
       <c r="E56" s="13">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F56" s="18">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="G56" s="18">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="H56" s="13">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="I56" s="19">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>65.171874999999986</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1.015625</v>
+        <v>1.0153846153846153</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="N56" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O56" s="18">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P56" s="18">
         <v>0.15</v>
@@ -6211,35 +6215,35 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.71199999999999997</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>1.0009999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.937999999999999</v>
+        <v>16.568999999999999</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.446999999999999</v>
+        <v>15.083</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.266999999999999</v>
+        <v>22.067</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.266999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6253,7 +6257,7 @@
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0775347912524851</v>
+        <v>1.0705765407554673</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
@@ -6263,10 +6267,10 @@
         <v>0.39</v>
       </c>
       <c r="F57" s="13">
-        <v>6.64</v>
+        <v>6.63</v>
       </c>
       <c r="G57" s="13">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="H57" s="13">
         <v>0.23</v>
@@ -6283,7 +6287,7 @@
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>1</v>
+        <v>1.015625</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
@@ -6313,7 +6317,7 @@
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0780000000000001</v>
+        <v>1.054</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
@@ -6325,11 +6329,11 @@
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>14.128</v>
+        <v>14.106</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.266999999999999</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
@@ -6346,27 +6350,27 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.624229979466108</v>
+        <v>51.890608875128983</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0328542094455853</v>
+        <v>1.0381836945304437</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.74</v>
+        <v>9.6900000000000013</v>
       </c>
       <c r="E58" s="9">
         <v>0.39</v>
       </c>
       <c r="F58" s="13">
-        <v>6.51</v>
+        <v>6.45</v>
       </c>
       <c r="G58" s="13">
         <v>3.01</v>
       </c>
       <c r="H58" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I58" s="14">
         <v>2.4500000000000002</v>
@@ -6406,15 +6410,15 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.79200000000000004</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.0329999999999999</v>
+        <v>1.038</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.218999999999999</v>
+        <v>15.141</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
@@ -6422,7 +6426,7 @@
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.851000000000001</v>
+        <v>13.723000000000001</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
@@ -6430,7 +6434,7 @@
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
@@ -6443,21 +6447,21 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>55.01312910284463</v>
+        <v>55.931034482758612</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0656455142231946</v>
+        <v>1.0778642936596219</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>9.14</v>
+        <v>8.99</v>
       </c>
       <c r="E59" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F59" s="13">
-        <v>6.24</v>
+        <v>6.09</v>
       </c>
       <c r="G59" s="13">
         <v>2.67</v>
@@ -6484,7 +6488,7 @@
         <v>0.62000000000000011</v>
       </c>
       <c r="N59" s="9">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O59" s="13">
         <v>0.46</v>
@@ -6496,30 +6500,30 @@
         <v>0.02</v>
       </c>
       <c r="R59" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.81799999999999995</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.032</v>
+        <v>1.044</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.742000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>6.6669999999999998</v>
+        <v>4.875</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.565</v>
+        <v>13.239000000000001</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
@@ -6531,7 +6535,7 @@
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>14.929</v>
+        <v>16.077000000000002</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6540,24 +6544,24 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>56.751693002257319</v>
+        <v>57.073779795686711</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0316027088036117</v>
+        <v>1.0204313280363224</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.8600000000000012</v>
+        <v>8.81</v>
       </c>
       <c r="E60" s="18">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="F60" s="18">
-        <v>6.03</v>
+        <v>5.99</v>
       </c>
       <c r="G60" s="18">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
@@ -6581,7 +6585,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N60" s="18">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O60" s="18">
         <v>0.45</v>
@@ -6600,27 +6604,27 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.83</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>1.0149999999999999</v>
+        <v>1.004</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.525</v>
+        <v>14.443</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>6.8330000000000002</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.4</v>
+        <v>13.311</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.5</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6638,21 +6642,21 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>57.995386389850054</v>
+        <v>57.729047072330644</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0219146482122261</v>
+        <v>1.0114810562571757</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.67</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="E61" s="9">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="F61" s="13">
-        <v>5.84</v>
+        <v>5.88</v>
       </c>
       <c r="G61" s="9">
         <v>2.6</v>
@@ -6679,7 +6683,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N61" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O61" s="13">
         <v>0.45</v>
@@ -6698,23 +6702,23 @@
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.84799999999999998</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.022</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>14.212999999999999</v>
+        <v>14.279</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
-        <v>6.7140000000000004</v>
+        <v>6.3330000000000002</v>
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>12.978</v>
+        <v>13.067</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
@@ -6735,30 +6739,30 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.878220140515211</v>
+        <v>58.672112018669772</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0152224824355971</v>
+        <v>1.0163360560093349</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.5400000000000009</v>
+        <v>8.57</v>
       </c>
       <c r="E62" s="9">
         <v>0.39</v>
       </c>
       <c r="F62" s="13">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="G62" s="9">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
       </c>
       <c r="I62" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J62" s="20" t="s">
         <v>70</v>
@@ -6776,7 +6780,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6788,34 +6792,34 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.86099999999999999</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>1.0149999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14</v>
+        <v>14.048999999999999</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>4.875</v>
+        <v>6.5</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.667</v>
+        <v>12.778</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6823,6 +6827,103 @@
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
+        <v>14.429</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="5">
+        <f t="shared" ref="B63" si="491">D$2/D63</f>
+        <v>58.947245017584976</v>
+      </c>
+      <c r="C63" s="5">
+        <f t="shared" ref="C63" si="492">D62/D63</f>
+        <v>1.0046893317702226</v>
+      </c>
+      <c r="D63" s="4">
+        <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
+        <v>8.5300000000000011</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="F63" s="9">
+        <v>5.71</v>
+      </c>
+      <c r="G63" s="9">
+        <v>2.59</v>
+      </c>
+      <c r="H63" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="I63" s="10">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="K63" s="5">
+        <f t="shared" ref="K63" si="494">M$2/M63</f>
+        <v>67.274193548387075</v>
+      </c>
+      <c r="L63" s="5">
+        <f t="shared" ref="L63" si="495">M62/M63</f>
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="M63" s="4">
+        <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="N63" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O63" s="9">
+        <v>0.46</v>
+      </c>
+      <c r="P63" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R63" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="S63" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="T63" s="5">
+        <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
+        <v>0.876</v>
+      </c>
+      <c r="U63" s="5">
+        <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
+        <v>1.0209999999999999</v>
+      </c>
+      <c r="V63" s="4">
+        <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
+        <v>13.757999999999999</v>
+      </c>
+      <c r="W63" s="9">
+        <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
+        <v>6</v>
+      </c>
+      <c r="X63" s="18">
+        <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
+        <v>12.413</v>
+      </c>
+      <c r="Y63" s="9">
+        <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
+        <v>18.5</v>
+      </c>
+      <c r="Z63" s="18">
+        <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA63" s="10">
+        <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
         <v>15.615</v>
       </c>
     </row>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0BA930-8E90-4BDA-B602-94B892FF784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE82F48-BD8B-4794-BA42-6FF53BF3F870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -5961,30 +5961,30 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.432180851063826</v>
+        <v>33.543695797198126</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0059840425531914</v>
+        <v>1.0093395597064709</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.040000000000001</v>
+        <v>14.99</v>
       </c>
       <c r="E54" s="13">
         <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.58</v>
+        <v>7.56</v>
       </c>
       <c r="G54" s="9">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="H54" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I54" s="10">
-        <v>4.8099999999999996</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
@@ -6021,15 +6021,15 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52100000000000002</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.006</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.138000000000002</v>
+        <v>23.062000000000001</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
@@ -6037,19 +6037,19 @@
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.128</v>
+        <v>16.085000000000001</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.466999999999999</v>
+        <v>45.2</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>32.067</v>
+        <v>31.533000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6058,30 +6058,30 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.428439519852255</v>
+        <v>46.904850746268657</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3887349953831949</v>
+        <v>1.3983208955223883</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.83</v>
+        <v>10.719999999999999</v>
       </c>
       <c r="E55" s="9">
         <v>0.39</v>
       </c>
       <c r="F55" s="9">
-        <v>7.25</v>
+        <v>7.17</v>
       </c>
       <c r="G55" s="13">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="H55" s="13">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I55" s="14">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
@@ -6099,7 +6099,7 @@
         <v>0.66</v>
       </c>
       <c r="N55" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O55" s="9">
         <v>0.48</v>
@@ -6118,35 +6118,35 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.73499999999999999</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.408999999999999</v>
+        <v>16.242000000000001</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.5</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.103999999999999</v>
+        <v>14.938000000000001</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22.132999999999999</v>
+        <v>22</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8.6669999999999998</v>
+        <v>8.3330000000000002</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6155,45 +6155,45 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.687093779015775</v>
+        <v>46.257589696412133</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0055710306406684</v>
+        <v>0.98620055197792067</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.770000000000001</v>
+        <v>10.870000000000001</v>
       </c>
       <c r="E56" s="13">
         <v>0.4</v>
       </c>
       <c r="F56" s="18">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="G56" s="18">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="H56" s="13">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I56" s="19">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1.0153846153846153</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N56" s="13">
         <v>0.06</v>
@@ -6202,7 +6202,7 @@
         <v>0.48</v>
       </c>
       <c r="P56" s="18">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q56" s="13">
         <v>0.02</v>
@@ -6215,15 +6215,15 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.72799999999999998</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>0.99</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.568999999999999</v>
+        <v>16.47</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
@@ -6231,19 +6231,19 @@
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.083</v>
+        <v>15.228999999999999</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.067</v>
+        <v>20.812999999999999</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.266999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6253,51 +6253,51 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>49.982107355864805</v>
+        <v>50.181636726546905</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0705765407554673</v>
+        <v>1.0848303393213574</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.06</v>
+        <v>10.02</v>
       </c>
       <c r="E57" s="9">
         <v>0.39</v>
       </c>
       <c r="F57" s="13">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="G57" s="13">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="H57" s="13">
         <v>0.23</v>
       </c>
       <c r="I57" s="14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="K57" s="2">
         <f t="shared" ref="K57:K58" si="424">M$2/M57</f>
-        <v>65.171874999999986</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>1.015625</v>
+        <v>1.0153846153846153</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="N57" s="9">
         <v>0.06</v>
       </c>
       <c r="O57" s="13">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P57" s="13">
         <v>0.15</v>
@@ -6313,15 +6313,15 @@
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.76700000000000002</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.054</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.718999999999999</v>
+        <v>15.414999999999999</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
@@ -6329,11 +6329,11 @@
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>14.106</v>
+        <v>13.792</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.132999999999999</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>17.466999999999999</v>
+        <v>17.332999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6350,51 +6350,51 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.890608875128983</v>
+        <v>51.837113402061846</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0381836945304437</v>
+        <v>1.0329896907216494</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.6900000000000013</v>
+        <v>9.7000000000000011</v>
       </c>
       <c r="E58" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F58" s="13">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
       <c r="G58" s="13">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="H58" s="9">
         <v>0.23</v>
       </c>
       <c r="I58" s="14">
-        <v>2.4500000000000002</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
       </c>
       <c r="K58" s="2">
         <f t="shared" si="424"/>
-        <v>65.171874999999986</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L58" s="2">
         <f t="shared" si="425"/>
-        <v>1</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="426"/>
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="N58" s="9">
         <v>0.06</v>
       </c>
       <c r="O58" s="13">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="P58" s="13">
         <v>0.15</v>
@@ -6410,27 +6410,27 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.79600000000000004</v>
+        <v>0.82</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.038</v>
+        <v>1.0489999999999999</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.141</v>
+        <v>14.696999999999999</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>6.5</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.723000000000001</v>
+        <v>13.143000000000001</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.067</v>
+        <v>20.2</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.5</v>
+        <v>17.643000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6447,30 +6447,30 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>55.931034482758612</v>
+        <v>56.560179977502798</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0778642936596219</v>
+        <v>1.0911136107986503</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>8.99</v>
+        <v>8.89</v>
       </c>
       <c r="E59" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F59" s="13">
-        <v>6.09</v>
+        <v>6.02</v>
       </c>
       <c r="G59" s="13">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="H59" s="9">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I59" s="14">
-        <v>2.09</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>67</v>
@@ -6481,14 +6481,14 @@
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0322580645161288</v>
+        <v>1.064516129032258</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
         <v>0.62000000000000011</v>
       </c>
       <c r="N59" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O59" s="13">
         <v>0.46</v>
@@ -6507,35 +6507,35 @@
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.83099999999999996</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.044</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.5</v>
+        <v>14.339</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>4.875</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.239000000000001</v>
+        <v>13.087</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>19.071000000000002</v>
+        <v>18.928999999999998</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>16.077000000000002</v>
+        <v>15.923</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6544,24 +6544,24 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>57.073779795686711</v>
+        <v>57.009070294784571</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0204313280363224</v>
+        <v>1.0079365079365079</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.81</v>
+        <v>8.82</v>
       </c>
       <c r="E60" s="18">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="F60" s="18">
         <v>5.99</v>
       </c>
       <c r="G60" s="18">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
@@ -6585,7 +6585,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N60" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O60" s="18">
         <v>0.45</v>
@@ -6604,19 +6604,19 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.83499999999999996</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>1.004</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.443</v>
+        <v>14.459</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.5</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6642,21 +6642,21 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>57.729047072330644</v>
+        <v>58.129479768786119</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0114810562571757</v>
+        <v>1.0196531791907515</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.7100000000000009</v>
+        <v>8.65</v>
       </c>
       <c r="E61" s="9">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="F61" s="13">
-        <v>5.88</v>
+        <v>5.82</v>
       </c>
       <c r="G61" s="9">
         <v>2.6</v>
@@ -6702,23 +6702,23 @@
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.84399999999999997</v>
+        <v>0.85</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.0109999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>14.279</v>
+        <v>14.18</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
-        <v>6.3330000000000002</v>
+        <v>6.5</v>
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>13.067</v>
+        <v>12.933</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
@@ -6739,30 +6739,30 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.672112018669772</v>
+        <v>59.016431924882625</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0163360560093349</v>
+        <v>1.0152582159624415</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.57</v>
+        <v>8.52</v>
       </c>
       <c r="E62" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F62" s="13">
-        <v>5.75</v>
+        <v>5.68</v>
       </c>
       <c r="G62" s="9">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
       </c>
       <c r="I62" s="10">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J62" s="20" t="s">
         <v>70</v>
@@ -6780,7 +6780,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6792,34 +6792,34 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.85799999999999998</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>1.016</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.048999999999999</v>
+        <v>13.967000000000001</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>6.5</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.778</v>
+        <v>12.622</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.5</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>14.429</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6836,27 +6836,27 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>58.947245017584976</v>
+        <v>58.535506402793942</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.0046893317702226</v>
+        <v>0.99185098952270079</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.5300000000000011</v>
+        <v>8.59</v>
       </c>
       <c r="E63" s="9">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="F63" s="9">
-        <v>5.71</v>
+        <v>5.74</v>
       </c>
       <c r="G63" s="9">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H63" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I63" s="10">
         <v>2.0299999999999998</v>
@@ -6877,7 +6877,7 @@
         <v>0.62000000000000011</v>
       </c>
       <c r="N63" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O63" s="9">
         <v>0.46</v>
@@ -6896,31 +6896,31 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.876</v>
+        <v>0.87</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.0209999999999999</v>
+        <v>1.008</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.757999999999999</v>
+        <v>13.855</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>6</v>
+        <v>5.125</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.413</v>
+        <v>12.478</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.5</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE82F48-BD8B-4794-BA42-6FF53BF3F870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A27CD69-C200-4565-8E38-BE409AF332CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="74">
   <si>
     <t>H23</t>
   </si>
@@ -293,6 +293,14 @@
   </si>
   <si>
     <t>H83</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H84</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H84</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -815,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB63"/>
+  <dimension ref="A1:AB64"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5961,45 +5969,45 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.543695797198126</v>
+        <v>33.387782204515268</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0093395597064709</v>
+        <v>1.0046480743691899</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>14.99</v>
+        <v>15.06</v>
       </c>
       <c r="E54" s="13">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="F54" s="9">
-        <v>7.56</v>
+        <v>7.65</v>
       </c>
       <c r="G54" s="9">
-        <v>6.78</v>
+        <v>6.76</v>
       </c>
       <c r="H54" s="9">
         <v>0.65</v>
       </c>
       <c r="I54" s="10">
-        <v>4.7300000000000004</v>
+        <v>4.74</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>1</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N54" s="13">
         <v>0.06</v>
@@ -6008,7 +6016,7 @@
         <v>0.47</v>
       </c>
       <c r="P54" s="9">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q54" s="9">
         <v>0.03</v>
@@ -6021,27 +6029,27 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52300000000000002</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0089999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.062000000000001</v>
+        <v>22.818000000000001</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>6.6669999999999998</v>
+        <v>8</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.085000000000001</v>
+        <v>16.277000000000001</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.2</v>
+        <v>42.25</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
@@ -6049,7 +6057,7 @@
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.533000000000001</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6058,51 +6066,51 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.904850746268657</v>
+        <v>46.385608856088552</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3983208955223883</v>
+        <v>1.3892988929889301</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.719999999999999</v>
+        <v>10.84</v>
       </c>
       <c r="E55" s="9">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F55" s="9">
-        <v>7.17</v>
+        <v>7.27</v>
       </c>
       <c r="G55" s="13">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="H55" s="13">
         <v>0.25</v>
       </c>
       <c r="I55" s="14">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
       </c>
       <c r="K55" s="2">
         <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>0.98484848484848486</v>
+        <v>1.0153846153846153</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N55" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O55" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P55" s="13">
         <v>0.15</v>
@@ -6118,27 +6126,27 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.74199999999999999</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.42</v>
+        <v>1.3680000000000001</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.242000000000001</v>
+        <v>16.677</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>6.5</v>
+        <v>5.4290000000000003</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>14.938000000000001</v>
+        <v>15.468</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22</v>
+        <v>22.132999999999999</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
@@ -6146,7 +6154,7 @@
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.2</v>
+        <v>18.466999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6155,24 +6163,24 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.257589696412133</v>
+        <v>46.471349353049902</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>0.98620055197792067</v>
+        <v>1.0018484288354899</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.870000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="E56" s="13">
         <v>0.4</v>
       </c>
       <c r="F56" s="18">
-        <v>7.31</v>
+        <v>7.28</v>
       </c>
       <c r="G56" s="18">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="H56" s="13">
         <v>0.23</v>
@@ -6185,24 +6193,24 @@
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>63.196969696969681</v>
+        <v>65.171874999999986</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1</v>
+        <v>1.015625</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="N56" s="13">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O56" s="18">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P56" s="18">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q56" s="13">
         <v>0.02</v>
@@ -6215,7 +6223,7 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.73199999999999998</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
@@ -6223,19 +6231,19 @@
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.47</v>
+        <v>16.905999999999999</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.228999999999999</v>
+        <v>15.489000000000001</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>20.812999999999999</v>
+        <v>22.067</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
@@ -6253,51 +6261,51 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>50.181636726546905</v>
+        <v>49.982107355864812</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0848303393213574</v>
+        <v>1.0755467196819086</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.02</v>
+        <v>10.059999999999999</v>
       </c>
       <c r="E57" s="9">
         <v>0.39</v>
       </c>
       <c r="F57" s="13">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="G57" s="13">
         <v>3.17</v>
       </c>
       <c r="H57" s="13">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I57" s="14">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="K57" s="2">
         <f t="shared" ref="K57:K58" si="424">M$2/M57</f>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>1.0153846153846153</v>
+        <v>0.96969696969696972</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N57" s="9">
         <v>0.06</v>
       </c>
       <c r="O57" s="13">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="P57" s="13">
         <v>0.15</v>
@@ -6306,22 +6314,22 @@
         <v>0.02</v>
       </c>
       <c r="R57" s="14">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.78200000000000003</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0680000000000001</v>
+        <v>1.109</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.414999999999999</v>
+        <v>15.242000000000001</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
@@ -6329,7 +6337,7 @@
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>13.792</v>
+        <v>13.551</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
@@ -6337,11 +6345,11 @@
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>17.332999999999998</v>
+        <v>18.643000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6350,51 +6358,51 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.837113402061846</v>
+        <v>52.051759834368525</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0329896907216494</v>
+        <v>1.0414078674948239</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.7000000000000011</v>
+        <v>9.66</v>
       </c>
       <c r="E58" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F58" s="13">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="G58" s="13">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="H58" s="9">
         <v>0.23</v>
       </c>
       <c r="I58" s="14">
-        <v>2.4700000000000002</v>
+        <v>2.44</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
       </c>
       <c r="K58" s="2">
         <f t="shared" si="424"/>
-        <v>63.196969696969681</v>
+        <v>65.171874999999986</v>
       </c>
       <c r="L58" s="2">
         <f t="shared" si="425"/>
-        <v>0.98484848484848486</v>
+        <v>1.03125</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="426"/>
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="N58" s="9">
         <v>0.06</v>
       </c>
       <c r="O58" s="13">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="P58" s="13">
         <v>0.15</v>
@@ -6410,27 +6418,27 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.82</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.0489999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>14.696999999999999</v>
+        <v>15.093999999999999</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>6.6669999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.143000000000001</v>
+        <v>13.66</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.2</v>
+        <v>20.067</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
@@ -6438,7 +6446,7 @@
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.643000000000001</v>
+        <v>17.428999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6447,24 +6455,24 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>56.560179977502798</v>
+        <v>56.055741360089172</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0911136107986503</v>
+        <v>1.0769230769230769</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>8.89</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="E59" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F59" s="13">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="G59" s="13">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="H59" s="9">
         <v>0.22</v>
@@ -6477,21 +6485,21 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.064516129032258</v>
+        <v>1.0491803278688523</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N59" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O59" s="13">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6507,27 +6515,27 @@
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.84099999999999997</v>
+        <v>0.82</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.0249999999999999</v>
+        <v>1.026</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.339</v>
+        <v>14.705</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.5</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.087</v>
+        <v>13.577999999999999</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>18.928999999999998</v>
+        <v>18.856999999999999</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
@@ -6544,30 +6552,30 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>57.009070294784571</v>
+        <v>56.055741360089172</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0079365079365079</v>
+        <v>1</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.82</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="E60" s="18">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="F60" s="18">
-        <v>5.99</v>
+        <v>6.16</v>
       </c>
       <c r="G60" s="18">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
@@ -6578,7 +6586,7 @@
       </c>
       <c r="L60" s="5">
         <f t="shared" ref="L60" si="453">M59/M60</f>
-        <v>1.0163934426229508</v>
+        <v>1</v>
       </c>
       <c r="M60" s="4">
         <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
@@ -6604,27 +6612,27 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.83399999999999996</v>
+        <v>0.82</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>0.99199999999999999</v>
+        <v>1</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.459</v>
+        <v>14.705</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>6.8330000000000002</v>
+        <v>6.3330000000000002</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.311</v>
+        <v>13.689</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.428999999999998</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6632,7 +6640,7 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
-        <v>15.615</v>
+        <v>15.538</v>
       </c>
       <c r="AB60" s="20"/>
     </row>
@@ -6642,27 +6650,27 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>58.129479768786119</v>
+        <v>57.995386389850054</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0196531791907515</v>
+        <v>1.0346020761245676</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="E61" s="9">
         <v>0.39</v>
       </c>
       <c r="F61" s="13">
-        <v>5.82</v>
+        <v>5.85</v>
       </c>
       <c r="G61" s="9">
         <v>2.6</v>
       </c>
       <c r="H61" s="18">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I61" s="10">
         <v>2.0299999999999998</v>
@@ -6672,21 +6680,21 @@
       </c>
       <c r="K61" s="5">
         <f t="shared" ref="K61" si="466">M$2/M61</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" ref="L61" si="467">M60/M61</f>
-        <v>1</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="M61" s="4">
         <f t="shared" ref="M61" si="468">SUM(O61:Q61)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N61" s="9">
         <v>0.06</v>
       </c>
       <c r="O61" s="13">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P61" s="9">
         <v>0.14000000000000001</v>
@@ -6702,15 +6710,15 @@
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.85</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.02</v>
+        <v>1.052</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>14.18</v>
+        <v>13.984</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
@@ -6718,7 +6726,7 @@
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>12.933</v>
+        <v>12.717000000000001</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
@@ -6726,7 +6734,7 @@
       </c>
       <c r="Z61" s="18">
         <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA61" s="10">
         <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
@@ -6739,24 +6747,24 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>59.016431924882625</v>
+        <v>58.740654205607463</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0152582159624415</v>
+        <v>1.0128504672897196</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.52</v>
+        <v>8.56</v>
       </c>
       <c r="E62" s="9">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F62" s="13">
-        <v>5.68</v>
+        <v>5.73</v>
       </c>
       <c r="G62" s="9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
@@ -6773,14 +6781,14 @@
       </c>
       <c r="L62" s="5">
         <f t="shared" ref="L62" si="481">M61/M62</f>
-        <v>1</v>
+        <v>1.0163934426229508</v>
       </c>
       <c r="M62" s="4">
         <f t="shared" ref="M62" si="482">SUM(O62:Q62)</f>
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6799,27 +6807,27 @@
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.86299999999999999</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>1.0149999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>13.967000000000001</v>
+        <v>14.032999999999999</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>5.7140000000000004</v>
+        <v>5.125</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.622</v>
+        <v>12.733000000000001</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6836,51 +6844,51 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>58.535506402793942</v>
+        <v>59.364817001180626</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>0.99185098952270079</v>
+        <v>1.0106257378984651</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.59</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="E63" s="9">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="F63" s="9">
-        <v>5.74</v>
+        <v>5.64</v>
       </c>
       <c r="G63" s="9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H63" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I63" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J63" s="20" t="s">
         <v>71</v>
       </c>
       <c r="K63" s="5">
         <f t="shared" ref="K63" si="494">M$2/M63</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>0.9838709677419355</v>
+        <v>1</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N63" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O63" s="9">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P63" s="9">
         <v>0.14000000000000001</v>
@@ -6896,34 +6904,131 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.87</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.008</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.855</v>
+        <v>13.885</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>5.125</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.478</v>
+        <v>12.532999999999999</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
+        <v>15.538</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="2">
+        <f t="shared" ref="B64" si="505">D$2/D64</f>
+        <v>65.132124352331587</v>
+      </c>
+      <c r="C64" s="2">
+        <f t="shared" ref="C64" si="506">D63/D64</f>
+        <v>1.0971502590673574</v>
+      </c>
+      <c r="D64" s="6">
+        <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
+        <v>7.7200000000000006</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="F64" s="13">
+        <v>4.88</v>
+      </c>
+      <c r="G64" s="9">
+        <v>2.61</v>
+      </c>
+      <c r="H64" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="I64" s="10">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="K64" s="2">
+        <f t="shared" ref="K64" si="508">M$2/M64</f>
+        <v>77.240740740740719</v>
+      </c>
+      <c r="L64" s="2">
+        <f t="shared" ref="L64" si="509">M63/M64</f>
+        <v>1.1296296296296298</v>
+      </c>
+      <c r="M64" s="6">
+        <f t="shared" ref="M64" si="510">SUM(O64:Q64)</f>
+        <v>0.54</v>
+      </c>
+      <c r="N64" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O64" s="13">
+        <v>0.38</v>
+      </c>
+      <c r="P64" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R64" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="S64" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="T64" s="2">
+        <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="U64" s="2">
+        <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="V64" s="6">
+        <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
+        <v>14.295999999999999</v>
+      </c>
+      <c r="W64" s="9">
+        <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
+        <v>5.5709999999999997</v>
+      </c>
+      <c r="X64" s="13">
+        <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
+        <v>12.842000000000001</v>
+      </c>
+      <c r="Y64" s="9">
+        <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
+        <v>18.643000000000001</v>
+      </c>
+      <c r="Z64" s="9">
+        <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA64" s="10">
+        <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
         <v>15.615</v>
       </c>
     </row>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A27CD69-C200-4565-8E38-BE409AF332CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F970EA5B-2345-458A-9596-3A288852717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="75">
   <si>
     <t>H23</t>
   </si>
@@ -301,6 +301,10 @@
   </si>
   <si>
     <t>H84</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H85</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -823,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB64"/>
+  <dimension ref="A1:AB65"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5969,27 +5973,27 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.387782204515268</v>
+        <v>33.255291005290999</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0046480743691899</v>
+        <v>1.0006613756613758</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.06</v>
+        <v>15.12</v>
       </c>
       <c r="E54" s="13">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.65</v>
+        <v>7.63</v>
       </c>
       <c r="G54" s="9">
-        <v>6.76</v>
+        <v>6.8</v>
       </c>
       <c r="H54" s="9">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="I54" s="10">
         <v>4.74</v>
@@ -5999,15 +6003,15 @@
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>0.98484848484848486</v>
+        <v>1</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N54" s="13">
         <v>0.06</v>
@@ -6016,7 +6020,7 @@
         <v>0.47</v>
       </c>
       <c r="P54" s="9">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q54" s="9">
         <v>0.03</v>
@@ -6029,31 +6033,31 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52800000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.02</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>22.818000000000001</v>
+        <v>23.262</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>8</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.277000000000001</v>
+        <v>16.234000000000002</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>42.25</v>
+        <v>45.332999999999998</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.667000000000002</v>
+        <v>23</v>
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
@@ -6066,30 +6070,30 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.385608856088552</v>
+        <v>46.643784786641923</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3892988929889301</v>
+        <v>1.4025974025974026</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.84</v>
+        <v>10.78</v>
       </c>
       <c r="E55" s="9">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="F55" s="9">
-        <v>7.27</v>
+        <v>7.24</v>
       </c>
       <c r="G55" s="13">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="H55" s="13">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="I55" s="14">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
@@ -6100,14 +6104,14 @@
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1.0153846153846153</v>
+        <v>1</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
         <v>0.65</v>
       </c>
       <c r="N55" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O55" s="9">
         <v>0.47</v>
@@ -6126,35 +6130,35 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.72299999999999998</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.3680000000000001</v>
+        <v>1.403</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.677</v>
+        <v>16.585000000000001</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>5.4290000000000003</v>
+        <v>6.5</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.468</v>
+        <v>15.404</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22.132999999999999</v>
+        <v>22</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8.3330000000000002</v>
+        <v>8</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6163,51 +6167,51 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.471349353049902</v>
+        <v>45.710909090909084</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0018484288354899</v>
+        <v>0.98</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.82</v>
+        <v>11</v>
       </c>
       <c r="E56" s="13">
         <v>0.4</v>
       </c>
       <c r="F56" s="18">
-        <v>7.28</v>
+        <v>7.43</v>
       </c>
       <c r="G56" s="18">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="H56" s="13">
         <v>0.23</v>
       </c>
       <c r="I56" s="19">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>65.171874999999986</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1.015625</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="N56" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O56" s="18">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P56" s="18">
         <v>0.15</v>
@@ -6223,15 +6227,15 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.71299999999999997</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>0.98599999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.905999999999999</v>
+        <v>16.922999999999998</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
@@ -6239,11 +6243,11 @@
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.489000000000001</v>
+        <v>15.478999999999999</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.067</v>
+        <v>22.266999999999999</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
@@ -6251,7 +6255,7 @@
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.399999999999999</v>
+        <v>18.466999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6261,30 +6265,30 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>49.982107355864812</v>
+        <v>48.960077896786757</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0755467196819086</v>
+        <v>1.071080817916261</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.059999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="E57" s="9">
         <v>0.39</v>
       </c>
       <c r="F57" s="13">
-        <v>6.64</v>
+        <v>6.83</v>
       </c>
       <c r="G57" s="13">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="H57" s="13">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I57" s="14">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>65</v>
@@ -6295,7 +6299,7 @@
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>0.96969696969696972</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
@@ -6314,22 +6318,22 @@
         <v>0.02</v>
       </c>
       <c r="R57" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.79100000000000004</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.109</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.242000000000001</v>
+        <v>15.561</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
@@ -6337,19 +6341,19 @@
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>13.551</v>
+        <v>13.939</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.132999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>18.643000000000001</v>
+        <v>17.667000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6358,30 +6362,30 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>52.051759834368525</v>
+        <v>50.031840796019893</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0414078674948239</v>
+        <v>1.0218905472636814</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.66</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="E58" s="9">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F58" s="13">
-        <v>6.42</v>
+        <v>6.72</v>
       </c>
       <c r="G58" s="13">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="H58" s="9">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I58" s="14">
-        <v>2.44</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
@@ -6399,7 +6403,7 @@
         <v>0.64</v>
       </c>
       <c r="N58" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O58" s="13">
         <v>0.47</v>
@@ -6418,35 +6422,35 @@
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.79900000000000004</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.01</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.093999999999999</v>
+        <v>15.702999999999999</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>6.5</v>
+        <v>5.4290000000000003</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.66</v>
+        <v>14.298</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.067</v>
+        <v>20.533000000000001</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.428999999999998</v>
+        <v>17.786000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6455,51 +6459,51 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>56.055741360089172</v>
+        <v>55.01312910284463</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0769230769230769</v>
+        <v>1.0995623632385121</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>8.9700000000000006</v>
+        <v>9.14</v>
       </c>
       <c r="E59" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F59" s="13">
-        <v>6.11</v>
+        <v>6.21</v>
       </c>
       <c r="G59" s="13">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H59" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I59" s="14">
-        <v>2.0699999999999998</v>
+        <v>2.12</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>68.377049180327845</v>
+        <v>66.206349206349202</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0491803278688523</v>
+        <v>1.0158730158730158</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.6100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N59" s="9">
         <v>0.06</v>
       </c>
       <c r="O59" s="13">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6508,42 +6512,42 @@
         <v>0.02</v>
       </c>
       <c r="R59" s="14">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.82</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.026</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.705</v>
+        <v>14.507999999999999</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>6.5</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.577999999999999</v>
+        <v>13.212999999999999</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>18.856999999999999</v>
+        <v>19.286000000000001</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>15.923</v>
+        <v>15.143000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6556,7 +6560,7 @@
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1</v>
+        <v>1.0189520624303232</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
@@ -6566,16 +6570,16 @@
         <v>0.38</v>
       </c>
       <c r="F60" s="18">
-        <v>6.16</v>
+        <v>6.11</v>
       </c>
       <c r="G60" s="18">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
@@ -6586,14 +6590,14 @@
       </c>
       <c r="L60" s="5">
         <f t="shared" ref="L60" si="453">M59/M60</f>
-        <v>1</v>
+        <v>1.0327868852459015</v>
       </c>
       <c r="M60" s="4">
         <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
         <v>0.6100000000000001</v>
       </c>
       <c r="N60" s="18">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O60" s="18">
         <v>0.45</v>
@@ -6616,7 +6620,7 @@
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>1</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
@@ -6624,15 +6628,15 @@
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>6.3330000000000002</v>
+        <v>5.4290000000000003</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.689</v>
+        <v>13.577999999999999</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.428999999999998</v>
+        <v>18.786000000000001</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6640,7 +6644,7 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
-        <v>15.538</v>
+        <v>15.846</v>
       </c>
       <c r="AB60" s="20"/>
     </row>
@@ -6650,15 +6654,15 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>57.995386389850054</v>
+        <v>57.530892448512589</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0346020761245676</v>
+        <v>1.0263157894736845</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.67</v>
+        <v>8.7399999999999984</v>
       </c>
       <c r="E61" s="9">
         <v>0.39</v>
@@ -6667,13 +6671,13 @@
         <v>5.85</v>
       </c>
       <c r="G61" s="9">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H61" s="18">
-        <v>0.22</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I61" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J61" s="20" t="s">
         <v>69</v>
@@ -6710,15 +6714,15 @@
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.86199999999999999</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.052</v>
+        <v>1.0429999999999999</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>13.984</v>
+        <v>14.097</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
@@ -6730,15 +6734,15 @@
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z61" s="18">
         <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA61" s="10">
         <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
-        <v>15.615</v>
+        <v>15.769</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6747,27 +6751,27 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.740654205607463</v>
+        <v>57.138636363636351</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0128504672897196</v>
+        <v>0.99318181818181794</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.56</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="E62" s="9">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F62" s="13">
-        <v>5.73</v>
+        <v>5.94</v>
       </c>
       <c r="G62" s="9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H62" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I62" s="10">
         <v>2.0299999999999998</v>
@@ -6777,21 +6781,21 @@
       </c>
       <c r="K62" s="5">
         <f t="shared" ref="K62" si="480">M$2/M62</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" ref="L62" si="481">M61/M62</f>
-        <v>1.0163934426229508</v>
+        <v>1</v>
       </c>
       <c r="M62" s="4">
         <f t="shared" ref="M62" si="482">SUM(O62:Q62)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N62" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O62" s="13">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P62" s="9">
         <v>0.14000000000000001</v>
@@ -6807,31 +6811,31 @@
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.85899999999999999</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.997</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.032999999999999</v>
+        <v>14.194000000000001</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>5.125</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.733000000000001</v>
+        <v>12.913</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
@@ -6844,24 +6848,24 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>59.364817001180626</v>
+        <v>58.603729603729583</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.0106257378984651</v>
+        <v>1.0256410256410255</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.4700000000000006</v>
+        <v>8.5800000000000018</v>
       </c>
       <c r="E63" s="9">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="F63" s="9">
-        <v>5.64</v>
+        <v>5.73</v>
       </c>
       <c r="G63" s="9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H63" s="9">
         <v>0.23</v>
@@ -6878,7 +6882,7 @@
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>1</v>
+        <v>1.0163934426229508</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
@@ -6904,27 +6908,27 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.86799999999999999</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.0109999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.885</v>
+        <v>14.066000000000001</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>5.5709999999999997</v>
+        <v>5.8570000000000002</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.532999999999999</v>
+        <v>12.733000000000001</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
@@ -6941,30 +6945,30 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>65.132124352331587</v>
+        <v>64.963824289405679</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.0971502590673574</v>
+        <v>1.1085271317829459</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.7200000000000006</v>
+        <v>7.74</v>
       </c>
       <c r="E64" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F64" s="13">
-        <v>4.88</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="G64" s="9">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H64" s="9">
         <v>0.23</v>
       </c>
       <c r="I64" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
@@ -6982,7 +6986,7 @@
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -7001,27 +7005,27 @@
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.84299999999999997</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.97099999999999997</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.295999999999999</v>
+        <v>14.333</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.842000000000001</v>
+        <v>12.868</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
@@ -7029,7 +7033,104 @@
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>15.615</v>
+        <v>15.538</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="2">
+        <f t="shared" ref="B65" si="519">D$2/D65</f>
+        <v>67.583333333333314</v>
+      </c>
+      <c r="C65" s="2">
+        <f t="shared" ref="C65" si="520">D64/D65</f>
+        <v>1.0403225806451613</v>
+      </c>
+      <c r="D65" s="6">
+        <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
+        <v>7.44</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F65" s="13">
+        <v>4.59</v>
+      </c>
+      <c r="G65" s="9">
+        <v>2.62</v>
+      </c>
+      <c r="H65" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="I65" s="10">
+        <v>2.02</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K65" s="2">
+        <f t="shared" ref="K65" si="522">M$2/M65</f>
+        <v>83.419999999999987</v>
+      </c>
+      <c r="L65" s="2">
+        <f t="shared" ref="L65" si="523">M64/M65</f>
+        <v>1.08</v>
+      </c>
+      <c r="M65" s="6">
+        <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N65" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="O65" s="13">
+        <v>0.34</v>
+      </c>
+      <c r="P65" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R65" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="S65" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="T65" s="5">
+        <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
+        <v>0.81</v>
+      </c>
+      <c r="U65" s="5">
+        <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="V65" s="4">
+        <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
+        <v>14.88</v>
+      </c>
+      <c r="W65" s="9">
+        <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
+        <v>6.6669999999999998</v>
+      </c>
+      <c r="X65" s="13">
+        <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
+        <v>13.5</v>
+      </c>
+      <c r="Y65" s="9">
+        <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
+        <v>18.713999999999999</v>
+      </c>
+      <c r="Z65" s="9">
+        <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA65" s="10">
+        <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
+        <v>15.538</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F970EA5B-2345-458A-9596-3A288852717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A95AAD-7FDE-4528-9B40-1F227909ADA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="76">
   <si>
     <t>H23</t>
   </si>
@@ -305,6 +305,10 @@
   </si>
   <si>
     <t>H85</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H86</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -827,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB65"/>
+  <dimension ref="A1:AB66"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5973,27 +5977,27 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.255291005290999</v>
+        <v>33.746308724832211</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0006613756613758</v>
+        <v>1.0154362416107383</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.12</v>
+        <v>14.9</v>
       </c>
       <c r="E54" s="13">
         <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.63</v>
+        <v>7.51</v>
       </c>
       <c r="G54" s="9">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="H54" s="9">
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="I54" s="10">
         <v>4.74</v>
@@ -6003,65 +6007,65 @@
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>64.169230769230751</v>
+        <v>61.338235294117631</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>1</v>
+        <v>0.95588235294117641</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="N54" s="13">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O54" s="9">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="P54" s="9">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q54" s="9">
         <v>0.03</v>
       </c>
       <c r="R54" s="10">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="S54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.51800000000000002</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0009999999999999</v>
+        <v>1.0620000000000001</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.262</v>
+        <v>21.911999999999999</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.234000000000002</v>
+        <v>15.327</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.332999999999998</v>
+        <v>42.125</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>23</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.6</v>
+        <v>29.625</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6070,87 +6074,87 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.643784786641923</v>
+        <v>46.385608856088552</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.4025974025974026</v>
+        <v>1.374538745387454</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.78</v>
+        <v>10.84</v>
       </c>
       <c r="E55" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F55" s="9">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="G55" s="13">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="H55" s="13">
         <v>0.24</v>
       </c>
       <c r="I55" s="14">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
       </c>
       <c r="K55" s="2">
         <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
-        <v>64.169230769230751</v>
+        <v>62.253731343283569</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1</v>
+        <v>1.0149253731343284</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="N55" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O55" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P55" s="13">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q55" s="13">
         <v>0.03</v>
       </c>
       <c r="R55" s="14">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>63</v>
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.72699999999999998</v>
+        <v>0.745</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.403</v>
+        <v>1.3540000000000001</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.585000000000001</v>
+        <v>16.178999999999998</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>6.5</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.404</v>
+        <v>15.146000000000001</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22</v>
+        <v>20.812999999999999</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
@@ -6158,7 +6162,7 @@
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.2</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6167,27 +6171,27 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>45.710909090909084</v>
+        <v>46.428439519852255</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>0.98</v>
+        <v>1.0009233610341643</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="E56" s="13">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F56" s="18">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="G56" s="18">
         <v>3.34</v>
       </c>
       <c r="H56" s="13">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I56" s="19">
         <v>2.77</v>
@@ -6197,7 +6201,7 @@
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>64.169230769230751</v>
+        <v>62.253731343283569</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
@@ -6205,16 +6209,16 @@
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="N56" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O56" s="18">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="P56" s="18">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q56" s="13">
         <v>0.02</v>
@@ -6227,31 +6231,31 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.71199999999999997</v>
+        <v>0.746</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>0.98</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.922999999999998</v>
+        <v>16.164000000000001</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>5.7140000000000004</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.478999999999999</v>
+        <v>14.795999999999999</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.266999999999999</v>
+        <v>20.875</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
@@ -6265,51 +6269,51 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>48.960077896786757</v>
+        <v>50.081673306772899</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.071080817916261</v>
+        <v>1.0786852589641434</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.27</v>
+        <v>10.040000000000001</v>
       </c>
       <c r="E57" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F57" s="13">
-        <v>6.83</v>
+        <v>6.62</v>
       </c>
       <c r="G57" s="13">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="H57" s="13">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I57" s="14">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="K57" s="2">
         <f t="shared" ref="K57:K58" si="424">M$2/M57</f>
-        <v>63.196969696969681</v>
+        <v>65.171874999999986</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>0.98484848484848486</v>
+        <v>1.046875</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="N57" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O57" s="13">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="P57" s="13">
         <v>0.15</v>
@@ -6325,35 +6329,35 @@
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.77500000000000002</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0880000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.561</v>
+        <v>15.688000000000001</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>6.5</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>13.939</v>
+        <v>14.085000000000001</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>17.667000000000002</v>
+        <v>17.466999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6362,30 +6366,30 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>50.031840796019893</v>
+        <v>52.10569948186528</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0218905472636814</v>
+        <v>1.0404145077720208</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>10.050000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="E58" s="9">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F58" s="13">
-        <v>6.72</v>
+        <v>6.41</v>
       </c>
       <c r="G58" s="13">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="H58" s="9">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I58" s="14">
-        <v>2.4900000000000002</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
@@ -6396,7 +6400,7 @@
       </c>
       <c r="L58" s="2">
         <f t="shared" si="425"/>
-        <v>1.03125</v>
+        <v>1</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="426"/>
@@ -6415,42 +6419,42 @@
         <v>0.02</v>
       </c>
       <c r="R58" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>66</v>
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.76800000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>0.99099999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.702999999999999</v>
+        <v>15.077999999999999</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>5.4290000000000003</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>14.298</v>
+        <v>13.638</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.533000000000001</v>
+        <v>20.067</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.786000000000001</v>
+        <v>16.466999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6459,51 +6463,51 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>55.01312910284463</v>
+        <v>56.306830907054866</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0995623632385121</v>
+        <v>1.0806270996640539</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>9.14</v>
+        <v>8.93</v>
       </c>
       <c r="E59" s="9">
         <v>0.4</v>
       </c>
       <c r="F59" s="13">
-        <v>6.21</v>
+        <v>6.06</v>
       </c>
       <c r="G59" s="13">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="H59" s="9">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I59" s="14">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>66.206349206349202</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0158730158730158</v>
+        <v>1.0491803278688523</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.63</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N59" s="9">
         <v>0.06</v>
       </c>
       <c r="O59" s="13">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6519,15 +6523,15 @@
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.83099999999999996</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.0820000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.507999999999999</v>
+        <v>14.638999999999999</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
@@ -6535,19 +6539,19 @@
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.212999999999999</v>
+        <v>13.467000000000001</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>19.286000000000001</v>
+        <v>18.928999999999998</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>15.143000000000001</v>
+        <v>14.856999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6556,51 +6560,51 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>56.055741360089172</v>
+        <v>55.868888888888883</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0189520624303232</v>
+        <v>0.99222222222222223</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.9700000000000006</v>
+        <v>9</v>
       </c>
       <c r="E60" s="18">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F60" s="18">
-        <v>6.11</v>
+        <v>6.16</v>
       </c>
       <c r="G60" s="18">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.06</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
       </c>
       <c r="K60" s="5">
         <f t="shared" ref="K60" si="452">M$2/M60</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L60" s="5">
         <f t="shared" ref="L60" si="453">M59/M60</f>
-        <v>1.0327868852459015</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="M60" s="4">
         <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N60" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O60" s="18">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P60" s="18">
         <v>0.14000000000000001</v>
@@ -6609,34 +6613,34 @@
         <v>0.02</v>
       </c>
       <c r="R60" s="19">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S60" s="20" t="s">
         <v>68</v>
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>0.98699999999999999</v>
+        <v>1.008</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.705</v>
+        <v>14.516</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>5.4290000000000003</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.577999999999999</v>
+        <v>13.391</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.786000000000001</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6644,7 +6648,7 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
-        <v>15.846</v>
+        <v>14.5</v>
       </c>
       <c r="AB60" s="20"/>
     </row>
@@ -6654,30 +6658,30 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>57.530892448512589</v>
+        <v>58.264194669756648</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0263157894736845</v>
+        <v>1.0428736964078793</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.7399999999999984</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="E61" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F61" s="13">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="G61" s="9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H61" s="18">
-        <v>0.28000000000000003</v>
+        <v>0.22</v>
       </c>
       <c r="I61" s="10">
-        <v>2.0499999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J61" s="20" t="s">
         <v>69</v>
@@ -6688,14 +6692,14 @@
       </c>
       <c r="L61" s="5">
         <f t="shared" ref="L61" si="467">M60/M61</f>
-        <v>0.9838709677419355</v>
+        <v>1</v>
       </c>
       <c r="M61" s="4">
         <f t="shared" ref="M61" si="468">SUM(O61:Q61)</f>
         <v>0.62000000000000011</v>
       </c>
       <c r="N61" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O61" s="13">
         <v>0.46</v>
@@ -6707,14 +6711,14 @@
         <v>0.02</v>
       </c>
       <c r="R61" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S61" s="20" t="s">
         <v>69</v>
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.85499999999999998</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
@@ -6722,27 +6726,27 @@
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>14.097</v>
+        <v>13.919</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
-        <v>6.5</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>12.717000000000001</v>
+        <v>12.63</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z61" s="18">
         <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AA61" s="10">
         <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
-        <v>15.769</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6751,27 +6755,27 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>57.138636363636351</v>
+        <v>58.878220140515211</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>0.99318181818181794</v>
+        <v>1.0105386416861826</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.8000000000000007</v>
+        <v>8.5400000000000009</v>
       </c>
       <c r="E62" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F62" s="13">
-        <v>5.94</v>
+        <v>5.71</v>
       </c>
       <c r="G62" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H62" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I62" s="10">
         <v>2.0299999999999998</v>
@@ -6781,21 +6785,21 @@
       </c>
       <c r="K62" s="5">
         <f t="shared" ref="K62" si="480">M$2/M62</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" ref="L62" si="481">M61/M62</f>
-        <v>1</v>
+        <v>1.0163934426229508</v>
       </c>
       <c r="M62" s="4">
         <f t="shared" ref="M62" si="482">SUM(O62:Q62)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O62" s="13">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P62" s="9">
         <v>0.14000000000000001</v>
@@ -6804,42 +6808,42 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.84899999999999998</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.99299999999999999</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.194000000000001</v>
+        <v>14</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>6.6669999999999998</v>
+        <v>4.875</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.913</v>
+        <v>12.689</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>15.615</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6848,24 +6852,24 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>58.603729603729583</v>
+        <v>57.861910241657064</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.0256410256410255</v>
+        <v>0.98273878020713457</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.5800000000000018</v>
+        <v>8.6900000000000013</v>
       </c>
       <c r="E63" s="9">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="F63" s="9">
-        <v>5.73</v>
+        <v>5.86</v>
       </c>
       <c r="G63" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H63" s="9">
         <v>0.23</v>
@@ -6882,7 +6886,7 @@
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>1.0163934426229508</v>
+        <v>1</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
@@ -6908,27 +6912,27 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.85699999999999998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.0089999999999999</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>14.066000000000001</v>
+        <v>14.246</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>5.8570000000000002</v>
+        <v>6.7140000000000004</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.733000000000001</v>
+        <v>13.022</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
@@ -6945,30 +6949,30 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>64.963824289405679</v>
+        <v>65.90039318479684</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1085271317829459</v>
+        <v>1.1389252948885977</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.74</v>
+        <v>7.6300000000000008</v>
       </c>
       <c r="E64" s="9">
         <v>0.4</v>
       </c>
       <c r="F64" s="13">
-        <v>4.8899999999999997</v>
+        <v>4.79</v>
       </c>
       <c r="G64" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H64" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I64" s="10">
-        <v>2.02</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
@@ -6986,7 +6990,7 @@
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -6998,42 +7002,42 @@
         <v>0.02</v>
       </c>
       <c r="R64" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S64" s="20" t="s">
         <v>72</v>
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.84099999999999997</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.98099999999999998</v>
+        <v>1.008</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.333</v>
+        <v>14.13</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.868</v>
+        <v>12.605</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>15.538</v>
+        <v>14.356999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7042,51 +7046,51 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>67.583333333333314</v>
+        <v>68.132791327913267</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0403225806451613</v>
+        <v>1.0338753387533877</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.44</v>
+        <v>7.38</v>
       </c>
       <c r="E65" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F65" s="13">
-        <v>4.59</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="G65" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H65" s="9">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I65" s="10">
-        <v>2.02</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="K65" s="2">
         <f t="shared" ref="K65" si="522">M$2/M65</f>
-        <v>83.419999999999987</v>
+        <v>81.784313725490179</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" ref="L65" si="523">M64/M65</f>
-        <v>1.08</v>
+        <v>1.0588235294117647</v>
       </c>
       <c r="M65" s="6">
         <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="N65" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O65" s="13">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="P65" s="9">
         <v>0.14000000000000001</v>
@@ -7095,42 +7099,139 @@
         <v>0.02</v>
       </c>
       <c r="R65" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="T65" s="5">
+      <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.81</v>
-      </c>
-      <c r="U65" s="5">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.96299999999999997</v>
-      </c>
-      <c r="V65" s="4">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>14.88</v>
+        <v>14.471</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>13.5</v>
+        <v>13.029</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>15.538</v>
+        <v>14.356999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="2">
+        <f t="shared" ref="B66" si="533">D$2/D66</f>
+        <v>83.386401326699826</v>
+      </c>
+      <c r="C66" s="2">
+        <f t="shared" ref="C66" si="534">D65/D66</f>
+        <v>1.2238805970149254</v>
+      </c>
+      <c r="D66" s="6">
+        <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
+        <v>6.03</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="F66" s="13">
+        <v>3.22</v>
+      </c>
+      <c r="G66" s="9">
+        <v>2.59</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="I66" s="10">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K66" s="2">
+        <f t="shared" ref="K66" si="536">M$2/M66</f>
+        <v>88.744680851063805</v>
+      </c>
+      <c r="L66" s="2">
+        <f t="shared" ref="L66" si="537">M65/M66</f>
+        <v>1.0851063829787233</v>
+      </c>
+      <c r="M66" s="6">
+        <f t="shared" ref="M66" si="538">SUM(O66:Q66)</f>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="N66" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="O66" s="13">
+        <v>0.31</v>
+      </c>
+      <c r="P66" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R66" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S66" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="T66" s="2">
+        <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
+        <v>0.94</v>
+      </c>
+      <c r="U66" s="2">
+        <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
+        <v>1.1279999999999999</v>
+      </c>
+      <c r="V66" s="6">
+        <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
+        <v>12.83</v>
+      </c>
+      <c r="W66" s="9">
+        <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
+        <v>4.875</v>
+      </c>
+      <c r="X66" s="13">
+        <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
+        <v>10.387</v>
+      </c>
+      <c r="Y66" s="9">
+        <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
+        <v>18.5</v>
+      </c>
+      <c r="Z66" s="9">
+        <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
+        <v>11</v>
+      </c>
+      <c r="AA66" s="10">
+        <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
+        <v>14.356999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A95AAD-7FDE-4528-9B40-1F227909ADA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B19BFB4-87B8-41E6-BCBF-BC3F595E7454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="77">
   <si>
     <t>H23</t>
   </si>
@@ -309,6 +309,10 @@
   </si>
   <si>
     <t>H86</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H87</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -831,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB66"/>
+  <dimension ref="A1:AB67"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5977,87 +5981,87 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.746308724832211</v>
+        <v>33.387782204515268</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0154362416107383</v>
+        <v>1.0046480743691899</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>14.9</v>
+        <v>15.06</v>
       </c>
       <c r="E54" s="13">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="F54" s="9">
-        <v>7.51</v>
+        <v>7.59</v>
       </c>
       <c r="G54" s="9">
-        <v>6.74</v>
+        <v>6.82</v>
       </c>
       <c r="H54" s="9">
         <v>0.65</v>
       </c>
       <c r="I54" s="10">
-        <v>4.74</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>61.338235294117631</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>0.95588235294117641</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="N54" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O54" s="9">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="P54" s="9">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q54" s="9">
         <v>0.03</v>
       </c>
       <c r="R54" s="10">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="S54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.55000000000000004</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0620000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>21.911999999999999</v>
+        <v>22.818000000000001</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>15.327</v>
+        <v>15.813000000000001</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>42.125</v>
+        <v>45.466999999999999</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
@@ -6065,7 +6069,7 @@
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>29.625</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6074,27 +6078,27 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.385608856088552</v>
+        <v>46.342857142857142</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.374538745387454</v>
+        <v>1.3880184331797236</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="E55" s="9">
         <v>0.4</v>
       </c>
       <c r="F55" s="9">
-        <v>7.27</v>
+        <v>7.3</v>
       </c>
       <c r="G55" s="13">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="H55" s="13">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I55" s="14">
         <v>2.76</v>
@@ -6108,7 +6112,7 @@
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1.0149253731343284</v>
+        <v>0.9850746268656716</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
@@ -6127,22 +6131,22 @@
         <v>0.03</v>
       </c>
       <c r="R55" s="14">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>63</v>
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.745</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.3540000000000001</v>
+        <v>1.409</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.178999999999998</v>
+        <v>16.193999999999999</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
@@ -6150,19 +6154,19 @@
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.146000000000001</v>
+        <v>15.208</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>20.812999999999999</v>
+        <v>20.625</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8</v>
+        <v>8.3330000000000002</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>17.25</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6171,54 +6175,54 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.428439519852255</v>
+        <v>45.961608775137101</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>1.0009233610341643</v>
+        <v>0.99177330895795235</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.83</v>
+        <v>10.940000000000001</v>
       </c>
       <c r="E56" s="13">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="F56" s="18">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="G56" s="18">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="H56" s="13">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I56" s="19">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>64</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>62.253731343283569</v>
+        <v>65.171874999999986</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1</v>
+        <v>1.046875</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="N56" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O56" s="18">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="P56" s="18">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q56" s="13">
         <v>0.02</v>
@@ -6231,35 +6235,35 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.746</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>1.0009999999999999</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.164000000000001</v>
+        <v>17.094000000000001</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>14.795999999999999</v>
+        <v>15.744999999999999</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>20.875</v>
+        <v>22.067</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.466999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AB56" s="20"/>
     </row>
@@ -6269,27 +6273,27 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>50.081673306772899</v>
+        <v>49.58777120315581</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0786852589641434</v>
+        <v>1.0788954635108481</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.040000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="E57" s="9">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F57" s="13">
-        <v>6.62</v>
+        <v>6.69</v>
       </c>
       <c r="G57" s="13">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="H57" s="13">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I57" s="14">
         <v>2.62</v>
@@ -6299,21 +6303,21 @@
       </c>
       <c r="K57" s="2">
         <f t="shared" ref="K57:K58" si="424">M$2/M57</f>
-        <v>65.171874999999986</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>1.046875</v>
+        <v>0.98461538461538456</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="N57" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O57" s="13">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P57" s="13">
         <v>0.15</v>
@@ -6329,31 +6333,31 @@
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.76800000000000002</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.03</v>
+        <v>1.0960000000000001</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.688000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>14.085000000000001</v>
+        <v>13.938000000000001</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.2</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
@@ -6366,24 +6370,24 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>52.10569948186528</v>
+        <v>51.151576805696841</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0404145077720208</v>
+        <v>1.0315361139369279</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.65</v>
+        <v>9.83</v>
       </c>
       <c r="E58" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F58" s="13">
-        <v>6.41</v>
+        <v>6.56</v>
       </c>
       <c r="G58" s="13">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="H58" s="9">
         <v>0.23</v>
@@ -6400,7 +6404,7 @@
       </c>
       <c r="L58" s="2">
         <f t="shared" si="425"/>
-        <v>1</v>
+        <v>1.015625</v>
       </c>
       <c r="M58" s="6">
         <f t="shared" si="426"/>
@@ -6419,34 +6423,34 @@
         <v>0.02</v>
       </c>
       <c r="R58" s="14">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>66</v>
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.8</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.04</v>
+        <v>1.016</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.077999999999999</v>
+        <v>15.359</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>5.7140000000000004</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.638</v>
+        <v>13.957000000000001</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.067</v>
+        <v>20.266999999999999</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
@@ -6454,7 +6458,7 @@
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>16.466999999999999</v>
+        <v>17.643000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6463,51 +6467,51 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>56.306830907054866</v>
+        <v>55.133771929824547</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0806270996640539</v>
+        <v>1.0778508771929824</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>8.93</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="E59" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F59" s="13">
-        <v>6.06</v>
+        <v>6.22</v>
       </c>
       <c r="G59" s="13">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="H59" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I59" s="14">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0491803278688523</v>
+        <v>1.0322580645161288</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N59" s="9">
         <v>0.06</v>
       </c>
       <c r="O59" s="13">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6516,42 +6520,42 @@
         <v>0.02</v>
       </c>
       <c r="R59" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="T59" s="2">
         <f t="shared" ref="T59" si="441">ROUND(B59/K59,3)</f>
-        <v>0.82299999999999995</v>
+        <v>0.82</v>
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.03</v>
+        <v>1.044</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.638999999999999</v>
+        <v>14.71</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.467000000000001</v>
+        <v>13.522</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>18.928999999999998</v>
+        <v>19.071000000000002</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>14.856999999999999</v>
+        <v>16.077000000000002</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6560,30 +6564,30 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>55.868888888888883</v>
+        <v>56.243847874720345</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>0.99222222222222223</v>
+        <v>1.0201342281879193</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>9</v>
+        <v>8.9400000000000013</v>
       </c>
       <c r="E60" s="18">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="F60" s="18">
-        <v>6.16</v>
+        <v>6.09</v>
       </c>
       <c r="G60" s="18">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.0299999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
@@ -6594,14 +6598,14 @@
       </c>
       <c r="L60" s="5">
         <f t="shared" ref="L60" si="453">M59/M60</f>
-        <v>0.9838709677419355</v>
+        <v>1</v>
       </c>
       <c r="M60" s="4">
         <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
         <v>0.62000000000000011</v>
       </c>
       <c r="N60" s="18">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O60" s="18">
         <v>0.46</v>
@@ -6620,27 +6624,27 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.83</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>1.008</v>
+        <v>1.02</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.516</v>
+        <v>14.419</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.2859999999999996</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.391</v>
+        <v>13.239000000000001</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6648,7 +6652,7 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
-        <v>14.5</v>
+        <v>14.571</v>
       </c>
       <c r="AB60" s="20"/>
     </row>
@@ -6658,30 +6662,30 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>58.264194669756648</v>
+        <v>57.203640500568817</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0428736964078793</v>
+        <v>1.0170648464163823</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.6300000000000008</v>
+        <v>8.7900000000000009</v>
       </c>
       <c r="E61" s="9">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="F61" s="13">
-        <v>5.81</v>
+        <v>5.92</v>
       </c>
       <c r="G61" s="9">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H61" s="18">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I61" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.06</v>
       </c>
       <c r="J61" s="20" t="s">
         <v>69</v>
@@ -6711,42 +6715,42 @@
         <v>0.02</v>
       </c>
       <c r="R61" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S61" s="20" t="s">
         <v>69</v>
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.86599999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.0429999999999999</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>13.919</v>
+        <v>14.177</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6</v>
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>12.63</v>
+        <v>12.87</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.856999999999999</v>
       </c>
       <c r="Z61" s="18">
         <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA61" s="10">
         <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
-        <v>14.5</v>
+        <v>15.846</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6755,24 +6759,24 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.878220140515211</v>
+        <v>58.672112018669772</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0105386416861826</v>
+        <v>1.0256709451575263</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.5400000000000009</v>
+        <v>8.57</v>
       </c>
       <c r="E62" s="9">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F62" s="13">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="G62" s="9">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
@@ -6796,7 +6800,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6808,34 +6812,34 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.86099999999999999</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.99399999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14</v>
+        <v>14.048999999999999</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>4.875</v>
+        <v>6.3330000000000002</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.689</v>
+        <v>12.778</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.5</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6843,7 +6847,7 @@
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>14.5</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6852,30 +6856,30 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>57.861910241657064</v>
+        <v>59.016431924882625</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>0.98273878020713457</v>
+        <v>1.005868544600939</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.6900000000000013</v>
+        <v>8.52</v>
       </c>
       <c r="E63" s="9">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="F63" s="9">
-        <v>5.86</v>
+        <v>5.7</v>
       </c>
       <c r="G63" s="9">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="H63" s="9">
         <v>0.23</v>
       </c>
       <c r="I63" s="10">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J63" s="20" t="s">
         <v>71</v>
@@ -6912,27 +6916,27 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.84599999999999997</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>0.98299999999999998</v>
+        <v>1.006</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>14.246</v>
+        <v>13.967000000000001</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>6.7140000000000004</v>
+        <v>6</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>13.022</v>
+        <v>12.667</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.5</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
@@ -6940,7 +6944,7 @@
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
-        <v>15.538</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6949,30 +6953,30 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>65.90039318479684</v>
+        <v>65.216601815823594</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1389252948885977</v>
+        <v>1.1050583657587547</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.6300000000000008</v>
+        <v>7.7100000000000009</v>
       </c>
       <c r="E64" s="9">
         <v>0.4</v>
       </c>
       <c r="F64" s="13">
-        <v>4.79</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="G64" s="9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H64" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I64" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
@@ -6990,7 +6994,7 @@
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -7002,42 +7006,42 @@
         <v>0.02</v>
       </c>
       <c r="R64" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S64" s="20" t="s">
         <v>72</v>
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.85299999999999998</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>1.008</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.13</v>
+        <v>14.278</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>5</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.605</v>
+        <v>12.789</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>14.356999999999999</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7046,95 +7050,95 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>68.132791327913267</v>
+        <v>68.41088435374148</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0338753387533877</v>
+        <v>1.0489795918367348</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.38</v>
+        <v>7.3500000000000005</v>
       </c>
       <c r="E65" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F65" s="13">
-        <v>4.5599999999999996</v>
+        <v>4.53</v>
       </c>
       <c r="G65" s="9">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="H65" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I65" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="K65" s="2">
         <f t="shared" ref="K65" si="522">M$2/M65</f>
-        <v>81.784313725490179</v>
+        <v>83.419999999999987</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" ref="L65" si="523">M64/M65</f>
-        <v>1.0588235294117647</v>
+        <v>1.08</v>
       </c>
       <c r="M65" s="6">
         <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="N65" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O65" s="13">
         <v>0.35</v>
       </c>
       <c r="P65" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Q65" s="9">
         <v>0.02</v>
       </c>
       <c r="R65" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.83299999999999996</v>
+        <v>0.82</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.97599999999999998</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>14.471</v>
+        <v>14.7</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>5.5709999999999997</v>
+        <v>5</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>13.029</v>
+        <v>12.943</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>18.571000000000002</v>
+        <v>19.922999999999998</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>14.356999999999999</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7143,30 +7147,30 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>83.386401326699826</v>
+        <v>82.160130718954221</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2238805970149254</v>
+        <v>1.2009803921568627</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.03</v>
+        <v>6.120000000000001</v>
       </c>
       <c r="E66" s="9">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="F66" s="13">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="G66" s="9">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="H66" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I66" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>75</v>
@@ -7177,14 +7181,14 @@
       </c>
       <c r="L66" s="2">
         <f t="shared" ref="L66" si="537">M65/M66</f>
-        <v>1.0851063829787233</v>
+        <v>1.0638297872340425</v>
       </c>
       <c r="M66" s="6">
         <f t="shared" ref="M66" si="538">SUM(O66:Q66)</f>
         <v>0.47000000000000003</v>
       </c>
       <c r="N66" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O66" s="13">
         <v>0.31</v>
@@ -7196,42 +7200,139 @@
         <v>0.02</v>
       </c>
       <c r="R66" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>75</v>
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.94</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.1279999999999999</v>
+        <v>1.129</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>12.83</v>
+        <v>13.021000000000001</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>4.875</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.387</v>
+        <v>10.452</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.5</v>
+        <v>18.928999999999998</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
-        <v>14.356999999999999</v>
+        <v>15.615</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="2">
+        <f t="shared" ref="B67" si="547">D$2/D67</f>
+        <v>104.75416666666666</v>
+      </c>
+      <c r="C67" s="2">
+        <f t="shared" ref="C67" si="548">D66/D67</f>
+        <v>1.2750000000000004</v>
+      </c>
+      <c r="D67" s="6">
+        <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
+        <v>4.8</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="F67" s="9">
+        <v>3.24</v>
+      </c>
+      <c r="G67" s="13">
+        <v>1.34</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="I67" s="14">
+        <v>0.44</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K67" s="2">
+        <f t="shared" ref="K67" si="550">M$2/M67</f>
+        <v>90.673913043478237</v>
+      </c>
+      <c r="L67" s="2">
+        <f t="shared" ref="L67" si="551">M66/M67</f>
+        <v>1.0217391304347827</v>
+      </c>
+      <c r="M67" s="6">
+        <f t="shared" ref="M67" si="552">SUM(O67:Q67)</f>
+        <v>0.46</v>
+      </c>
+      <c r="N67" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O67" s="9">
+        <v>0.31</v>
+      </c>
+      <c r="P67" s="13">
+        <v>0.13</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R67" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S67" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="T67" s="2">
+        <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
+        <v>1.155</v>
+      </c>
+      <c r="U67" s="2">
+        <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
+        <v>1.248</v>
+      </c>
+      <c r="V67" s="6">
+        <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
+        <v>10.435</v>
+      </c>
+      <c r="W67" s="9">
+        <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
+        <v>6.2859999999999996</v>
+      </c>
+      <c r="X67" s="18">
+        <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
+        <v>10.452</v>
+      </c>
+      <c r="Y67" s="13">
+        <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
+        <v>10.308</v>
+      </c>
+      <c r="Z67" s="9">
+        <f t="shared" ref="Z67" si="559">ROUND(H67/Q67,3)</f>
+        <v>11</v>
+      </c>
+      <c r="AA67" s="14">
+        <f t="shared" ref="AA67" si="560">ROUND(I67/R67,3)</f>
+        <v>6.2859999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B19BFB4-87B8-41E6-BCBF-BC3F595E7454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1C487-C491-46B0-93D4-5434F7332852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="78">
   <si>
     <t>H23</t>
   </si>
@@ -313,6 +313,10 @@
   </si>
   <si>
     <t>H87</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H88</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -835,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB67"/>
+  <dimension ref="A1:AB68"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5981,51 +5985,51 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.387782204515268</v>
+        <v>33.655957161981256</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0046480743691899</v>
+        <v>1.0127175368139225</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.06</v>
+        <v>14.94</v>
       </c>
       <c r="E54" s="13">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.59</v>
+        <v>7.52</v>
       </c>
       <c r="G54" s="9">
-        <v>6.82</v>
+        <v>6.76</v>
       </c>
       <c r="H54" s="9">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I54" s="10">
-        <v>4.7699999999999996</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K54" s="5">
         <f t="shared" ref="K54" si="388">M$2/M54</f>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>0.98484848484848486</v>
+        <v>1</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N54" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O54" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P54" s="9">
         <v>0.15</v>
@@ -6041,35 +6045,35 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52800000000000002</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.02</v>
+        <v>1.0129999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>22.818000000000001</v>
+        <v>22.984999999999999</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>6</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X54" s="9">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>15.813000000000001</v>
+        <v>16</v>
       </c>
       <c r="Y54" s="9">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.466999999999999</v>
+        <v>45.067</v>
       </c>
       <c r="Z54" s="9">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.667000000000002</v>
+        <v>22</v>
       </c>
       <c r="AA54" s="10">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.8</v>
+        <v>31.266999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6078,54 +6082,54 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.342857142857142</v>
+        <v>46.385608856088552</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3880184331797236</v>
+        <v>1.3782287822878228</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
       <c r="E55" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F55" s="9">
         <v>7.3</v>
       </c>
       <c r="G55" s="13">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="H55" s="13">
         <v>0.25</v>
       </c>
       <c r="I55" s="14">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>63</v>
       </c>
       <c r="K55" s="2">
         <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
-        <v>62.253731343283569</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>0.9850746268656716</v>
+        <v>1</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="N55" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="O55" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P55" s="13">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q55" s="13">
         <v>0.03</v>
@@ -6138,27 +6142,27 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.74399999999999999</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.409</v>
+        <v>1.3779999999999999</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.193999999999999</v>
+        <v>16.677</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>5.7140000000000004</v>
+        <v>5.556</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.208</v>
+        <v>15.532</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>20.625</v>
+        <v>21.933</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
@@ -6166,7 +6170,7 @@
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.399999999999999</v>
+        <v>18.266999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6175,27 +6179,27 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>45.961608775137101</v>
+        <v>46.385608856088552</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>0.99177330895795235</v>
+        <v>1</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.940000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="E56" s="13">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="F56" s="18">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="G56" s="18">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="H56" s="13">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I56" s="19">
         <v>2.76</v>
@@ -6205,21 +6209,21 @@
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>65.171874999999986</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
-        <v>1.046875</v>
+        <v>1</v>
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="N56" s="13">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O56" s="18">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P56" s="18">
         <v>0.15</v>
@@ -6235,31 +6239,31 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.70499999999999996</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>0.94699999999999995</v>
+        <v>1</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>17.094000000000001</v>
+        <v>16.677</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
-        <v>6.8330000000000002</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.744999999999999</v>
+        <v>15.146000000000001</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.067</v>
+        <v>22.132999999999999</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
@@ -6273,27 +6277,27 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
-        <v>49.58777120315581</v>
+        <v>50.281999999999996</v>
       </c>
       <c r="C57" s="2">
         <f t="shared" ref="C57:C58" si="422">D56/D57</f>
-        <v>1.0788954635108481</v>
+        <v>1.0840000000000001</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="E57" s="9">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="F57" s="13">
-        <v>6.69</v>
+        <v>6.58</v>
       </c>
       <c r="G57" s="13">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="H57" s="13">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="I57" s="14">
         <v>2.62</v>
@@ -6307,7 +6311,7 @@
       </c>
       <c r="L57" s="2">
         <f t="shared" ref="L57:L58" si="425">M56/M57</f>
-        <v>0.98461538461538456</v>
+        <v>1</v>
       </c>
       <c r="M57" s="6">
         <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
@@ -6326,42 +6330,42 @@
         <v>0.02</v>
       </c>
       <c r="R57" s="14">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T57" s="2">
         <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
-        <v>0.77300000000000002</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="U57" s="2">
         <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
-        <v>1.0960000000000001</v>
+        <v>1.0840000000000001</v>
       </c>
       <c r="V57" s="6">
         <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
-        <v>15.6</v>
+        <v>15.385</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
-        <v>6.8330000000000002</v>
+        <v>7</v>
       </c>
       <c r="X57" s="13">
         <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
-        <v>13.938000000000001</v>
+        <v>13.708</v>
       </c>
       <c r="Y57" s="13">
         <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.2</v>
       </c>
       <c r="Z57" s="13">
         <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA57" s="14">
         <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
-        <v>17.466999999999999</v>
+        <v>18.713999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6370,30 +6374,30 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="421"/>
-        <v>51.151576805696841</v>
+        <v>52.051759834368525</v>
       </c>
       <c r="C58" s="2">
         <f t="shared" si="422"/>
-        <v>1.0315361139369279</v>
+        <v>1.0351966873706004</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="423"/>
-        <v>9.83</v>
+        <v>9.66</v>
       </c>
       <c r="E58" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F58" s="13">
-        <v>6.56</v>
+        <v>6.44</v>
       </c>
       <c r="G58" s="13">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="H58" s="9">
         <v>0.23</v>
       </c>
       <c r="I58" s="14">
-        <v>2.4700000000000002</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>66</v>
@@ -6411,7 +6415,7 @@
         <v>0.64</v>
       </c>
       <c r="N58" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O58" s="13">
         <v>0.47</v>
@@ -6423,34 +6427,34 @@
         <v>0.02</v>
       </c>
       <c r="R58" s="14">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>66</v>
       </c>
       <c r="T58" s="2">
         <f t="shared" si="427"/>
-        <v>0.78500000000000003</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="U58" s="2">
         <f t="shared" si="428"/>
-        <v>1.016</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="V58" s="6">
         <f t="shared" si="429"/>
-        <v>15.359</v>
+        <v>15.093999999999999</v>
       </c>
       <c r="W58" s="9">
         <f t="shared" si="430"/>
-        <v>5.5709999999999997</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X58" s="13">
         <f t="shared" si="431"/>
-        <v>13.957000000000001</v>
+        <v>13.702</v>
       </c>
       <c r="Y58" s="13">
         <f t="shared" si="432"/>
-        <v>20.266999999999999</v>
+        <v>19.933</v>
       </c>
       <c r="Z58" s="9">
         <f t="shared" si="433"/>
@@ -6458,7 +6462,7 @@
       </c>
       <c r="AA58" s="14">
         <f t="shared" si="434"/>
-        <v>17.643000000000001</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6467,51 +6471,51 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" ref="B59" si="435">D$2/D59</f>
-        <v>55.133771929824547</v>
+        <v>56.055741360089172</v>
       </c>
       <c r="C59" s="2">
         <f t="shared" ref="C59" si="436">D58/D59</f>
-        <v>1.0778508771929824</v>
+        <v>1.0769230769230769</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" ref="D59" si="437">SUM(F59:H59)</f>
-        <v>9.120000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="E59" s="9">
         <v>0.39</v>
       </c>
       <c r="F59" s="13">
-        <v>6.22</v>
+        <v>6.09</v>
       </c>
       <c r="G59" s="13">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="H59" s="9">
         <v>0.23</v>
       </c>
       <c r="I59" s="14">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>67</v>
       </c>
       <c r="K59" s="2">
         <f t="shared" ref="K59" si="438">M$2/M59</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" ref="L59" si="439">M58/M59</f>
-        <v>1.0322580645161288</v>
+        <v>1.0491803278688523</v>
       </c>
       <c r="M59" s="6">
         <f t="shared" ref="M59" si="440">SUM(O59:Q59)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N59" s="9">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O59" s="13">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P59" s="13">
         <v>0.14000000000000001</v>
@@ -6520,7 +6524,7 @@
         <v>0.02</v>
       </c>
       <c r="R59" s="14">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>67</v>
@@ -6531,23 +6535,23 @@
       </c>
       <c r="U59" s="2">
         <f t="shared" ref="U59" si="442">ROUND(C59/L59,3)</f>
-        <v>1.044</v>
+        <v>1.026</v>
       </c>
       <c r="V59" s="6">
         <f t="shared" ref="V59" si="443">ROUND(D59/M59,3)</f>
-        <v>14.71</v>
+        <v>14.705</v>
       </c>
       <c r="W59" s="9">
         <f t="shared" ref="W59" si="444">ROUND(E59/N59,3)</f>
-        <v>6.5</v>
+        <v>4.3330000000000002</v>
       </c>
       <c r="X59" s="13">
         <f t="shared" ref="X59" si="445">ROUND(F59/O59,3)</f>
-        <v>13.522</v>
+        <v>13.532999999999999</v>
       </c>
       <c r="Y59" s="13">
         <f t="shared" ref="Y59" si="446">ROUND(G59/P59,3)</f>
-        <v>19.071000000000002</v>
+        <v>18.928999999999998</v>
       </c>
       <c r="Z59" s="9">
         <f t="shared" ref="Z59" si="447">ROUND(H59/Q59,3)</f>
@@ -6555,7 +6559,7 @@
       </c>
       <c r="AA59" s="14">
         <f t="shared" ref="AA59" si="448">ROUND(I59/R59,3)</f>
-        <v>16.077000000000002</v>
+        <v>14.856999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6564,37 +6568,37 @@
       </c>
       <c r="B60" s="5">
         <f t="shared" ref="B60" si="449">D$2/D60</f>
-        <v>56.243847874720345</v>
+        <v>56.560179977502798</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" ref="C60" si="450">D59/D60</f>
-        <v>1.0201342281879193</v>
+        <v>1.0089988751406074</v>
       </c>
       <c r="D60" s="4">
         <f t="shared" ref="D60" si="451">SUM(F60:H60)</f>
-        <v>8.9400000000000013</v>
+        <v>8.89</v>
       </c>
       <c r="E60" s="18">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="F60" s="18">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
       <c r="G60" s="18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H60" s="18">
         <v>0.23</v>
       </c>
       <c r="I60" s="19">
-        <v>2.04</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>68</v>
       </c>
       <c r="K60" s="5">
         <f t="shared" ref="K60" si="452">M$2/M60</f>
-        <v>67.274193548387075</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L60" s="5">
         <f t="shared" ref="L60" si="453">M59/M60</f>
@@ -6602,13 +6606,13 @@
       </c>
       <c r="M60" s="4">
         <f t="shared" ref="M60" si="454">SUM(O60:Q60)</f>
-        <v>0.62000000000000011</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N60" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="O60" s="18">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="P60" s="18">
         <v>0.14000000000000001</v>
@@ -6624,27 +6628,27 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" ref="T60" si="455">ROUND(B60/K60,3)</f>
-        <v>0.83599999999999997</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" ref="U60" si="456">ROUND(C60/L60,3)</f>
-        <v>1.02</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="V60" s="4">
         <f t="shared" ref="V60" si="457">ROUND(D60/M60,3)</f>
-        <v>14.419</v>
+        <v>14.574</v>
       </c>
       <c r="W60" s="18">
         <f t="shared" ref="W60" si="458">ROUND(E60/N60,3)</f>
-        <v>6.2859999999999996</v>
+        <v>4.556</v>
       </c>
       <c r="X60" s="18">
         <f t="shared" ref="X60" si="459">ROUND(F60/O60,3)</f>
-        <v>13.239000000000001</v>
+        <v>13.467000000000001</v>
       </c>
       <c r="Y60" s="18">
         <f t="shared" ref="Y60" si="460">ROUND(G60/P60,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z60" s="18">
         <f t="shared" ref="Z60" si="461">ROUND(H60/Q60,3)</f>
@@ -6652,7 +6656,7 @@
       </c>
       <c r="AA60" s="19">
         <f t="shared" ref="AA60" si="462">ROUND(I60/R60,3)</f>
-        <v>14.571</v>
+        <v>14.5</v>
       </c>
       <c r="AB60" s="20"/>
     </row>
@@ -6662,51 +6666,51 @@
       </c>
       <c r="B61" s="5">
         <f t="shared" ref="B61" si="463">D$2/D61</f>
-        <v>57.203640500568817</v>
+        <v>57.928571428571423</v>
       </c>
       <c r="C61" s="5">
         <f t="shared" ref="C61" si="464">D60/D61</f>
-        <v>1.0170648464163823</v>
+        <v>1.024193548387097</v>
       </c>
       <c r="D61" s="4">
         <f t="shared" ref="D61" si="465">SUM(F61:H61)</f>
-        <v>8.7900000000000009</v>
+        <v>8.68</v>
       </c>
       <c r="E61" s="9">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="F61" s="13">
-        <v>5.92</v>
+        <v>5.84</v>
       </c>
       <c r="G61" s="9">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H61" s="18">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I61" s="10">
-        <v>2.06</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J61" s="20" t="s">
         <v>69</v>
       </c>
       <c r="K61" s="5">
         <f t="shared" ref="K61" si="466">M$2/M61</f>
-        <v>67.274193548387075</v>
+        <v>66.206349206349202</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" ref="L61" si="467">M60/M61</f>
-        <v>1</v>
+        <v>0.96825396825396837</v>
       </c>
       <c r="M61" s="4">
         <f t="shared" ref="M61" si="468">SUM(O61:Q61)</f>
-        <v>0.62000000000000011</v>
+        <v>0.63</v>
       </c>
       <c r="N61" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O61" s="13">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="P61" s="9">
         <v>0.14000000000000001</v>
@@ -6715,42 +6719,42 @@
         <v>0.02</v>
       </c>
       <c r="R61" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S61" s="20" t="s">
         <v>69</v>
       </c>
       <c r="T61" s="5">
         <f t="shared" ref="T61" si="469">ROUND(B61/K61,3)</f>
-        <v>0.85</v>
+        <v>0.875</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" ref="U61" si="470">ROUND(C61/L61,3)</f>
-        <v>1.0169999999999999</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="V61" s="4">
         <f t="shared" ref="V61" si="471">ROUND(D61/M61,3)</f>
-        <v>14.177</v>
+        <v>13.778</v>
       </c>
       <c r="W61" s="9">
         <f t="shared" ref="W61" si="472">ROUND(E61/N61,3)</f>
-        <v>6</v>
+        <v>6.2859999999999996</v>
       </c>
       <c r="X61" s="13">
         <f t="shared" ref="X61" si="473">ROUND(F61/O61,3)</f>
-        <v>12.87</v>
+        <v>12.426</v>
       </c>
       <c r="Y61" s="9">
         <f t="shared" ref="Y61" si="474">ROUND(G61/P61,3)</f>
-        <v>18.856999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z61" s="18">
         <f t="shared" ref="Z61" si="475">ROUND(H61/Q61,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA61" s="10">
         <f t="shared" ref="AA61" si="476">ROUND(I61/R61,3)</f>
-        <v>15.846</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6759,24 +6763,24 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.672112018669772</v>
+        <v>58.603729603729597</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0256709451575263</v>
+        <v>1.0116550116550116</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.57</v>
+        <v>8.58</v>
       </c>
       <c r="E62" s="9">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="F62" s="13">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="G62" s="9">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
@@ -6793,14 +6797,14 @@
       </c>
       <c r="L62" s="5">
         <f t="shared" ref="L62" si="481">M61/M62</f>
-        <v>1.0163934426229508</v>
+        <v>1.0327868852459015</v>
       </c>
       <c r="M62" s="4">
         <f t="shared" ref="M62" si="482">SUM(O62:Q62)</f>
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6812,34 +6816,34 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.85799999999999998</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>1.0089999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.048999999999999</v>
+        <v>14.066000000000001</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>6.3330000000000002</v>
+        <v>6.4290000000000003</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.778</v>
+        <v>12.756</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.5</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6847,7 +6851,7 @@
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>15.615</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6856,30 +6860,30 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>59.016431924882625</v>
+        <v>58.809356725146188</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.005868544600939</v>
+        <v>1.0035087719298246</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.52</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E63" s="9">
         <v>0.42</v>
       </c>
       <c r="F63" s="9">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="G63" s="9">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H63" s="9">
         <v>0.23</v>
       </c>
       <c r="I63" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J63" s="20" t="s">
         <v>71</v>
@@ -6916,15 +6920,15 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.86299999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.006</v>
+        <v>1.004</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.967000000000001</v>
+        <v>14.016</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
@@ -6932,11 +6936,11 @@
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.667</v>
+        <v>12.689</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.5</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
-        <v>15.615</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6953,24 +6957,24 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>65.216601815823594</v>
+        <v>65.301298701298677</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1050583657587547</v>
+        <v>1.1103896103896103</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.7100000000000009</v>
+        <v>7.7000000000000011</v>
       </c>
       <c r="E64" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F64" s="13">
-        <v>4.8600000000000003</v>
+        <v>4.87</v>
       </c>
       <c r="G64" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H64" s="9">
         <v>0.23</v>
@@ -6994,7 +6998,7 @@
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -7013,27 +7017,27 @@
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.84399999999999997</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.97799999999999998</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.278</v>
+        <v>14.259</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>6.6669999999999998</v>
+        <v>4.875</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.789</v>
+        <v>12.816000000000001</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
@@ -7044,33 +7048,33 @@
         <v>15.615</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>68.41088435374148</v>
+        <v>68.317934782608688</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0489795918367348</v>
+        <v>1.0461956521739133</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.3500000000000005</v>
+        <v>7.3599999999999994</v>
       </c>
       <c r="E65" s="9">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="F65" s="13">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="G65" s="9">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H65" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I65" s="10">
         <v>2.02</v>
@@ -7091,86 +7095,86 @@
         <v>0.5</v>
       </c>
       <c r="N65" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O65" s="13">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="P65" s="9">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q65" s="9">
         <v>0.02</v>
       </c>
       <c r="R65" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.82</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.97099999999999997</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>14.7</v>
+        <v>14.72</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>5</v>
+        <v>6.1429999999999998</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>12.943</v>
+        <v>13.265000000000001</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>19.922999999999998</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>15.538</v>
+        <v>14.429</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>82.160130718954221</v>
+        <v>83.110743801652873</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2009803921568627</v>
+        <v>1.2165289256198344</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.120000000000001</v>
+        <v>6.0500000000000007</v>
       </c>
       <c r="E66" s="9">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="F66" s="13">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="G66" s="9">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="H66" s="9">
         <v>0.23</v>
       </c>
       <c r="I66" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>75</v>
@@ -7188,7 +7192,7 @@
         <v>0.47000000000000003</v>
       </c>
       <c r="N66" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O66" s="13">
         <v>0.31</v>
@@ -7207,27 +7211,27 @@
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.92600000000000005</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.129</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>13.021000000000001</v>
+        <v>12.872</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>6.8330000000000002</v>
+        <v>6</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.452</v>
+        <v>10.419</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.928999999999998</v>
+        <v>18.5</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
@@ -7235,36 +7239,36 @@
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
-        <v>15.615</v>
+        <v>15.462</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
         <v>76</v>
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67" si="547">D$2/D67</f>
-        <v>104.75416666666666</v>
+        <v>104.10351966873705</v>
       </c>
       <c r="C67" s="2">
         <f t="shared" ref="C67" si="548">D66/D67</f>
-        <v>1.2750000000000004</v>
+        <v>1.2525879917184266</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="E67" s="9">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F67" s="9">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="G67" s="13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H67" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I67" s="14">
         <v>0.44</v>
@@ -7304,36 +7308,134 @@
       </c>
       <c r="T67" s="2">
         <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
-        <v>1.155</v>
+        <v>1.1479999999999999</v>
       </c>
       <c r="U67" s="2">
         <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
-        <v>1.248</v>
+        <v>1.226</v>
       </c>
       <c r="V67" s="6">
         <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
-        <v>10.435</v>
+        <v>10.5</v>
       </c>
       <c r="W67" s="9">
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
-        <v>6.2859999999999996</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X67" s="18">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
-        <v>10.452</v>
+        <v>10.484</v>
       </c>
       <c r="Y67" s="13">
         <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
-        <v>10.308</v>
+        <v>10.385</v>
       </c>
       <c r="Z67" s="9">
         <f t="shared" ref="Z67" si="559">ROUND(H67/Q67,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA67" s="14">
         <f t="shared" ref="AA67" si="560">ROUND(I67/R67,3)</f>
         <v>6.2859999999999996</v>
       </c>
+    </row>
+    <row r="68" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="5">
+        <f t="shared" ref="B68" si="561">D$2/D68</f>
+        <v>104.75416666666666</v>
+      </c>
+      <c r="C68" s="5">
+        <f t="shared" ref="C68" si="562">D67/D68</f>
+        <v>1.0062500000000001</v>
+      </c>
+      <c r="D68" s="4">
+        <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
+        <v>4.8</v>
+      </c>
+      <c r="E68" s="18">
+        <v>0.46</v>
+      </c>
+      <c r="F68" s="18">
+        <v>3.23</v>
+      </c>
+      <c r="G68" s="18">
+        <v>1.35</v>
+      </c>
+      <c r="H68" s="13">
+        <v>0.22</v>
+      </c>
+      <c r="I68" s="19">
+        <v>0.44</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K68" s="5">
+        <f t="shared" ref="K68" si="564">M$2/M68</f>
+        <v>90.673913043478237</v>
+      </c>
+      <c r="L68" s="5">
+        <f t="shared" ref="L68" si="565">M67/M68</f>
+        <v>1</v>
+      </c>
+      <c r="M68" s="4">
+        <f t="shared" ref="M68" si="566">SUM(O68:Q68)</f>
+        <v>0.46</v>
+      </c>
+      <c r="N68" s="18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O68" s="18">
+        <v>0.31</v>
+      </c>
+      <c r="P68" s="18">
+        <v>0.13</v>
+      </c>
+      <c r="Q68" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="R68" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S68" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="T68" s="5">
+        <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
+        <v>1.155</v>
+      </c>
+      <c r="U68" s="5">
+        <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
+        <v>1.006</v>
+      </c>
+      <c r="V68" s="4">
+        <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
+        <v>10.435</v>
+      </c>
+      <c r="W68" s="18">
+        <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
+        <v>6.5709999999999997</v>
+      </c>
+      <c r="X68" s="18">
+        <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
+        <v>10.419</v>
+      </c>
+      <c r="Y68" s="18">
+        <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
+        <v>10.385</v>
+      </c>
+      <c r="Z68" s="13">
+        <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
+        <v>11</v>
+      </c>
+      <c r="AA68" s="19">
+        <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
+        <v>6.2859999999999996</v>
+      </c>
+      <c r="AB68" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD1C487-C491-46B0-93D4-5434F7332852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9644F2-1940-4CF5-8882-13A5CA25AFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="79">
   <si>
     <t>H23</t>
   </si>
@@ -317,6 +317,10 @@
   </si>
   <si>
     <t>H88</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H89</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -839,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB68"/>
+  <dimension ref="A1:AB69"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -6763,24 +6767,24 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.603729603729597</v>
+        <v>58.062355658198605</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0116550116550116</v>
+        <v>1.0023094688221708</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.58</v>
+        <v>8.66</v>
       </c>
       <c r="E62" s="9">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="F62" s="13">
-        <v>5.74</v>
+        <v>5.83</v>
       </c>
       <c r="G62" s="9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
@@ -6804,7 +6808,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6816,34 +6820,34 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.85699999999999998</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.066000000000001</v>
+        <v>14.196999999999999</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>6.4290000000000003</v>
+        <v>7.1669999999999998</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.756</v>
+        <v>12.956</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6851,7 +6855,7 @@
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>14.5</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6860,24 +6864,24 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>58.809356725146188</v>
+        <v>57.861910241657064</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.0035087719298246</v>
+        <v>0.99654775604142676</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.5500000000000007</v>
+        <v>8.6900000000000013</v>
       </c>
       <c r="E63" s="9">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="F63" s="9">
-        <v>5.71</v>
+        <v>5.84</v>
       </c>
       <c r="G63" s="9">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H63" s="9">
         <v>0.23</v>
@@ -6890,21 +6894,21 @@
       </c>
       <c r="K63" s="5">
         <f t="shared" ref="K63" si="494">M$2/M63</f>
-        <v>68.377049180327845</v>
+        <v>66.206349206349202</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>1</v>
+        <v>0.96825396825396837</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
-        <v>0.6100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N63" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O63" s="9">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="P63" s="9">
         <v>0.14000000000000001</v>
@@ -6920,27 +6924,27 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.86</v>
+        <v>0.874</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.004</v>
+        <v>1.0289999999999999</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>14.016</v>
+        <v>13.794</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>6</v>
+        <v>5.4290000000000003</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.689</v>
+        <v>12.426</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
@@ -6961,20 +6965,20 @@
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1103896103896103</v>
+        <v>1.1285714285714286</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
         <v>7.7000000000000011</v>
       </c>
       <c r="E64" s="9">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="F64" s="13">
-        <v>4.87</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="G64" s="9">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H64" s="9">
         <v>0.23</v>
@@ -6991,14 +6995,14 @@
       </c>
       <c r="L64" s="2">
         <f t="shared" ref="L64" si="509">M63/M64</f>
-        <v>1.1296296296296298</v>
+        <v>1.1666666666666665</v>
       </c>
       <c r="M64" s="6">
         <f t="shared" ref="M64" si="510">SUM(O64:Q64)</f>
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -7021,7 +7025,7 @@
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.98299999999999998</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
@@ -7029,15 +7033,15 @@
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>4.875</v>
+        <v>8.6669999999999998</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.816000000000001</v>
+        <v>12.789</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
@@ -7054,45 +7058,45 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>68.317934782608688</v>
+        <v>67.311914323962498</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0461956521739133</v>
+        <v>1.030789825970549</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.3599999999999994</v>
+        <v>7.4700000000000006</v>
       </c>
       <c r="E65" s="9">
         <v>0.43</v>
       </c>
       <c r="F65" s="13">
-        <v>4.51</v>
+        <v>4.62</v>
       </c>
       <c r="G65" s="9">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H65" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I65" s="10">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="K65" s="2">
         <f t="shared" ref="K65" si="522">M$2/M65</f>
-        <v>83.419999999999987</v>
+        <v>85.122448979591809</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" ref="L65" si="523">M64/M65</f>
-        <v>1.08</v>
+        <v>1.1020408163265305</v>
       </c>
       <c r="M65" s="6">
         <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
-        <v>0.5</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="N65" s="9">
         <v>7.0000000000000007E-2</v>
@@ -7101,28 +7105,28 @@
         <v>0.34</v>
       </c>
       <c r="P65" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Q65" s="9">
         <v>0.02</v>
       </c>
       <c r="R65" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.81899999999999995</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.96899999999999997</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>14.72</v>
+        <v>15.244999999999999</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
@@ -7130,19 +7134,19 @@
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>13.265000000000001</v>
+        <v>13.587999999999999</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>18.643000000000001</v>
+        <v>20.154</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>14.429</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7151,30 +7155,30 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>83.110743801652873</v>
+        <v>83.248344370860906</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2165289256198344</v>
+        <v>1.2367549668874172</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.0500000000000007</v>
+        <v>6.0400000000000009</v>
       </c>
       <c r="E66" s="9">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="F66" s="13">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="G66" s="9">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="H66" s="9">
         <v>0.23</v>
       </c>
       <c r="I66" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>75</v>
@@ -7185,14 +7189,14 @@
       </c>
       <c r="L66" s="2">
         <f t="shared" ref="L66" si="537">M65/M66</f>
-        <v>1.0638297872340425</v>
+        <v>1.0425531914893618</v>
       </c>
       <c r="M66" s="6">
         <f t="shared" ref="M66" si="538">SUM(O66:Q66)</f>
         <v>0.47000000000000003</v>
       </c>
       <c r="N66" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O66" s="13">
         <v>0.31</v>
@@ -7204,34 +7208,34 @@
         <v>0.02</v>
       </c>
       <c r="R66" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>75</v>
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.93700000000000006</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.1439999999999999</v>
+        <v>1.1859999999999999</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>12.872</v>
+        <v>12.851000000000001</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>6</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.419</v>
+        <v>10.323</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.5</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
@@ -7239,7 +7243,7 @@
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
-        <v>15.462</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7248,21 +7252,21 @@
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67" si="547">D$2/D67</f>
-        <v>104.10351966873705</v>
+        <v>104.53638253638252</v>
       </c>
       <c r="C67" s="2">
         <f t="shared" ref="C67" si="548">D66/D67</f>
-        <v>1.2525879917184266</v>
+        <v>1.2557172557172558</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
-        <v>4.83</v>
+        <v>4.8100000000000005</v>
       </c>
       <c r="E67" s="9">
         <v>0.4</v>
       </c>
       <c r="F67" s="9">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="G67" s="13">
         <v>1.35</v>
@@ -7308,15 +7312,15 @@
       </c>
       <c r="T67" s="2">
         <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
-        <v>1.1479999999999999</v>
+        <v>1.153</v>
       </c>
       <c r="U67" s="2">
         <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
-        <v>1.226</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="V67" s="6">
         <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
-        <v>10.5</v>
+        <v>10.457000000000001</v>
       </c>
       <c r="W67" s="9">
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
@@ -7324,7 +7328,7 @@
       </c>
       <c r="X67" s="18">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
-        <v>10.484</v>
+        <v>10.419</v>
       </c>
       <c r="Y67" s="13">
         <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
@@ -7345,21 +7349,21 @@
       </c>
       <c r="B68" s="5">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>104.75416666666666</v>
+        <v>105.41299790356392</v>
       </c>
       <c r="C68" s="5">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>1.0062500000000001</v>
+        <v>1.0083857442348008</v>
       </c>
       <c r="D68" s="4">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.8</v>
+        <v>4.7700000000000005</v>
       </c>
       <c r="E68" s="18">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="F68" s="18">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="G68" s="18">
         <v>1.35</v>
@@ -7386,7 +7390,7 @@
         <v>0.46</v>
       </c>
       <c r="N68" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="O68" s="18">
         <v>0.31</v>
@@ -7405,23 +7409,23 @@
       </c>
       <c r="T68" s="5">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.155</v>
+        <v>1.163</v>
       </c>
       <c r="U68" s="5">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
-        <v>1.006</v>
+        <v>1.008</v>
       </c>
       <c r="V68" s="4">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.435</v>
+        <v>10.37</v>
       </c>
       <c r="W68" s="18">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
-        <v>6.5709999999999997</v>
+        <v>4.556</v>
       </c>
       <c r="X68" s="18">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.419</v>
+        <v>10.323</v>
       </c>
       <c r="Y68" s="18">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
@@ -7436,6 +7440,103 @@
         <v>6.2859999999999996</v>
       </c>
       <c r="AB68" s="20"/>
+    </row>
+    <row r="69" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="2">
+        <f t="shared" ref="B69" si="575">D$2/D69</f>
+        <v>105.85684210526314</v>
+      </c>
+      <c r="C69" s="2">
+        <f t="shared" ref="C69" si="576">D68/D69</f>
+        <v>1.0042105263157897</v>
+      </c>
+      <c r="D69" s="6">
+        <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
+        <v>4.75</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="F69" s="13">
+        <v>3.19</v>
+      </c>
+      <c r="G69" s="13">
+        <v>1.35</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="I69" s="14">
+        <v>0.44</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K69" s="2">
+        <f t="shared" ref="K69" si="578">M$2/M69</f>
+        <v>115.8611111111111</v>
+      </c>
+      <c r="L69" s="2">
+        <f t="shared" ref="L69" si="579">M68/M69</f>
+        <v>1.2777777777777779</v>
+      </c>
+      <c r="M69" s="6">
+        <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
+        <v>0.36</v>
+      </c>
+      <c r="N69" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="O69" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="P69" s="13">
+        <v>0.09</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R69" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="S69" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="T69" s="2">
+        <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="U69" s="2">
+        <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="V69" s="6">
+        <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
+        <v>13.194000000000001</v>
+      </c>
+      <c r="W69" s="9">
+        <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X69" s="13">
+        <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
+        <v>12.76</v>
+      </c>
+      <c r="Y69" s="13">
+        <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
+        <v>15</v>
+      </c>
+      <c r="Z69" s="9">
+        <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA69" s="14">
+        <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
+        <v>8.8000000000000007</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9644F2-1940-4CF5-8882-13A5CA25AFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AE04E1-37AF-4624-B263-76155BD6472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="81">
   <si>
     <t>H23</t>
   </si>
@@ -321,6 +321,14 @@
   </si>
   <si>
     <t>H89</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H90</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H91</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -843,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB69"/>
+  <dimension ref="A1:AB71"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -6767,27 +6775,27 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.062355658198605</v>
+        <v>58.878220140515211</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0023094688221708</v>
+        <v>1.0163934426229506</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.66</v>
+        <v>8.5400000000000009</v>
       </c>
       <c r="E62" s="9">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="F62" s="13">
-        <v>5.83</v>
+        <v>5.7</v>
       </c>
       <c r="G62" s="9">
         <v>2.6</v>
       </c>
       <c r="H62" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I62" s="10">
         <v>2.0299999999999998</v>
@@ -6808,7 +6816,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6820,30 +6828,30 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.84899999999999998</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.97</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.196999999999999</v>
+        <v>14</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>7.1669999999999998</v>
+        <v>5.8570000000000002</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.956</v>
+        <v>12.667</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
@@ -6851,11 +6859,11 @@
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>15.615</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6864,27 +6872,27 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>57.861910241657064</v>
+        <v>58.809356725146188</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>0.99654775604142676</v>
+        <v>0.99883040935672518</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.6900000000000013</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E63" s="9">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F63" s="9">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="G63" s="9">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H63" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I63" s="10">
         <v>2.02</v>
@@ -6894,21 +6902,21 @@
       </c>
       <c r="K63" s="5">
         <f t="shared" ref="K63" si="494">M$2/M63</f>
-        <v>66.206349206349202</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>0.96825396825396837</v>
+        <v>1</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
-        <v>0.63</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N63" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O63" s="9">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="P63" s="9">
         <v>0.14000000000000001</v>
@@ -6917,42 +6925,42 @@
         <v>0.02</v>
       </c>
       <c r="R63" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S63" s="20" t="s">
         <v>71</v>
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.874</v>
+        <v>0.86</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.0289999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.794</v>
+        <v>14.016</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>5.4290000000000003</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.426</v>
+        <v>12.667</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
-        <v>15.538</v>
+        <v>14.429</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6961,21 +6969,21 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>65.301298701298677</v>
+        <v>65.216601815823594</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1285714285714286</v>
+        <v>1.1089494163424125</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.7000000000000011</v>
+        <v>7.7100000000000009</v>
       </c>
       <c r="E64" s="9">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="F64" s="13">
-        <v>4.8600000000000003</v>
+        <v>4.87</v>
       </c>
       <c r="G64" s="9">
         <v>2.61</v>
@@ -6984,7 +6992,7 @@
         <v>0.23</v>
       </c>
       <c r="I64" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
@@ -6995,14 +7003,14 @@
       </c>
       <c r="L64" s="2">
         <f t="shared" ref="L64" si="509">M63/M64</f>
-        <v>1.1666666666666665</v>
+        <v>1.1296296296296298</v>
       </c>
       <c r="M64" s="6">
         <f t="shared" ref="M64" si="510">SUM(O64:Q64)</f>
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -7014,30 +7022,30 @@
         <v>0.02</v>
       </c>
       <c r="R64" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S64" s="20" t="s">
         <v>72</v>
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.84499999999999997</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.96699999999999997</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.259</v>
+        <v>14.278</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>8.6669999999999998</v>
+        <v>5</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.789</v>
+        <v>12.816000000000001</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
@@ -7049,7 +7057,7 @@
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>15.615</v>
+        <v>14.429</v>
       </c>
     </row>
     <row r="65" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7058,95 +7066,95 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>67.311914323962498</v>
+        <v>68.317934782608688</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.030789825970549</v>
+        <v>1.0475543478260869</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.4700000000000006</v>
+        <v>7.36</v>
       </c>
       <c r="E65" s="9">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="F65" s="13">
-        <v>4.62</v>
+        <v>4.54</v>
       </c>
       <c r="G65" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H65" s="9">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I65" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="K65" s="2">
         <f t="shared" ref="K65" si="522">M$2/M65</f>
-        <v>85.122448979591809</v>
+        <v>81.784313725490179</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" ref="L65" si="523">M64/M65</f>
-        <v>1.1020408163265305</v>
+        <v>1.0588235294117647</v>
       </c>
       <c r="M65" s="6">
         <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
-        <v>0.49000000000000005</v>
+        <v>0.51</v>
       </c>
       <c r="N65" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O65" s="13">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="P65" s="9">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q65" s="9">
         <v>0.02</v>
       </c>
       <c r="R65" s="10">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.79100000000000004</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.93500000000000005</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>15.244999999999999</v>
+        <v>14.430999999999999</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>6.1429999999999998</v>
+        <v>4.2</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>13.587999999999999</v>
+        <v>12.971</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>20.154</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>15.615</v>
+        <v>14.356999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7155,24 +7163,24 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>83.248344370860906</v>
+        <v>82.700657894736835</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2367549668874172</v>
+        <v>1.2105263157894737</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.0400000000000009</v>
+        <v>6.08</v>
       </c>
       <c r="E66" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F66" s="13">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="G66" s="9">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H66" s="9">
         <v>0.23</v>
@@ -7189,7 +7197,7 @@
       </c>
       <c r="L66" s="2">
         <f t="shared" ref="L66" si="537">M65/M66</f>
-        <v>1.0425531914893618</v>
+        <v>1.0851063829787233</v>
       </c>
       <c r="M66" s="6">
         <f t="shared" ref="M66" si="538">SUM(O66:Q66)</f>
@@ -7208,34 +7216,34 @@
         <v>0.02</v>
       </c>
       <c r="R66" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>75</v>
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.93799999999999994</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.1859999999999999</v>
+        <v>1.1160000000000001</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>12.851000000000001</v>
+        <v>12.936</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.323</v>
+        <v>10.419</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
@@ -7243,7 +7251,7 @@
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
-        <v>14.5</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7252,21 +7260,21 @@
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67" si="547">D$2/D67</f>
-        <v>104.53638253638252</v>
+        <v>104.97286012526092</v>
       </c>
       <c r="C67" s="2">
         <f t="shared" ref="C67" si="548">D66/D67</f>
-        <v>1.2557172557172558</v>
+        <v>1.2693110647181627</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
-        <v>4.8100000000000005</v>
+        <v>4.7900000000000009</v>
       </c>
       <c r="E67" s="9">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="F67" s="9">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="G67" s="13">
         <v>1.35</v>
@@ -7312,23 +7320,23 @@
       </c>
       <c r="T67" s="2">
         <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
-        <v>1.153</v>
+        <v>1.1579999999999999</v>
       </c>
       <c r="U67" s="2">
         <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
-        <v>1.2290000000000001</v>
+        <v>1.242</v>
       </c>
       <c r="V67" s="6">
         <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
-        <v>10.457000000000001</v>
+        <v>10.413</v>
       </c>
       <c r="W67" s="9">
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.1429999999999998</v>
       </c>
       <c r="X67" s="18">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
-        <v>10.419</v>
+        <v>10.355</v>
       </c>
       <c r="Y67" s="13">
         <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
@@ -7349,51 +7357,51 @@
       </c>
       <c r="B68" s="5">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>105.41299790356392</v>
+        <v>106.08016877637131</v>
       </c>
       <c r="C68" s="5">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>1.0083857442348008</v>
+        <v>1.0105485232067515</v>
       </c>
       <c r="D68" s="4">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.7700000000000005</v>
+        <v>4.7399999999999993</v>
       </c>
       <c r="E68" s="18">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F68" s="18">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="G68" s="18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H68" s="13">
         <v>0.22</v>
       </c>
       <c r="I68" s="19">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J68" s="20" t="s">
         <v>77</v>
       </c>
       <c r="K68" s="5">
         <f t="shared" ref="K68" si="564">M$2/M68</f>
-        <v>90.673913043478237</v>
+        <v>92.688888888888869</v>
       </c>
       <c r="L68" s="5">
         <f t="shared" ref="L68" si="565">M67/M68</f>
-        <v>1</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="M68" s="4">
         <f t="shared" ref="M68" si="566">SUM(O68:Q68)</f>
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="N68" s="18">
         <v>0.09</v>
       </c>
       <c r="O68" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="P68" s="18">
         <v>0.13</v>
@@ -7409,27 +7417,27 @@
       </c>
       <c r="T68" s="5">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.163</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="U68" s="5">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
-        <v>1.008</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="V68" s="4">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.37</v>
+        <v>10.532999999999999</v>
       </c>
       <c r="W68" s="18">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
-        <v>4.556</v>
+        <v>4.444</v>
       </c>
       <c r="X68" s="18">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.323</v>
+        <v>10.632999999999999</v>
       </c>
       <c r="Y68" s="18">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
-        <v>10.385</v>
+        <v>10.231</v>
       </c>
       <c r="Z68" s="13">
         <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
@@ -7437,7 +7445,7 @@
       </c>
       <c r="AA68" s="19">
         <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
-        <v>6.2859999999999996</v>
+        <v>6.1429999999999998</v>
       </c>
       <c r="AB68" s="20"/>
     </row>
@@ -7447,27 +7455,27 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" ref="B69" si="575">D$2/D69</f>
-        <v>105.85684210526314</v>
+        <v>105.19246861924684</v>
       </c>
       <c r="C69" s="2">
         <f t="shared" ref="C69" si="576">D68/D69</f>
-        <v>1.0042105263157897</v>
+        <v>0.99163179916317967</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="E69" s="9">
         <v>0.44</v>
       </c>
       <c r="F69" s="13">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="G69" s="13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H69" s="9">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="I69" s="14">
         <v>0.44</v>
@@ -7481,14 +7489,14 @@
       </c>
       <c r="L69" s="2">
         <f t="shared" ref="L69" si="579">M68/M69</f>
-        <v>1.2777777777777779</v>
+        <v>1.25</v>
       </c>
       <c r="M69" s="6">
         <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
         <v>0.36</v>
       </c>
       <c r="N69" s="9">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="O69" s="13">
         <v>0.25</v>
@@ -7507,34 +7515,229 @@
       </c>
       <c r="T69" s="2">
         <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
-        <v>0.91400000000000003</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="U69" s="2">
         <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
-        <v>0.78600000000000003</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="V69" s="6">
         <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
-        <v>13.194000000000001</v>
+        <v>13.278</v>
       </c>
       <c r="W69" s="9">
         <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
-        <v>4.4000000000000004</v>
+        <v>7.3330000000000002</v>
       </c>
       <c r="X69" s="13">
         <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
-        <v>12.76</v>
+        <v>12.88</v>
       </c>
       <c r="Y69" s="13">
         <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
-        <v>15</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="Z69" s="9">
         <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA69" s="14">
         <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="5">
+        <f t="shared" ref="B70" si="589">D$2/D70</f>
+        <v>105.19246861924684</v>
+      </c>
+      <c r="C70" s="5">
+        <f t="shared" ref="C70" si="590">D69/D70</f>
+        <v>1</v>
+      </c>
+      <c r="D70" s="4">
+        <f t="shared" ref="D70" si="591">SUM(F70:H70)</f>
+        <v>4.78</v>
+      </c>
+      <c r="E70" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="F70" s="18">
+        <v>3.23</v>
+      </c>
+      <c r="G70" s="18">
+        <v>1.34</v>
+      </c>
+      <c r="H70" s="18">
+        <v>0.21</v>
+      </c>
+      <c r="I70" s="19">
+        <v>0.44</v>
+      </c>
+      <c r="J70" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="K70" s="5">
+        <f t="shared" ref="K70" si="592">M$2/M70</f>
+        <v>119.17142857142856</v>
+      </c>
+      <c r="L70" s="5">
+        <f t="shared" ref="L70" si="593">M69/M70</f>
+        <v>1.0285714285714287</v>
+      </c>
+      <c r="M70" s="4">
+        <f t="shared" ref="M70" si="594">SUM(O70:Q70)</f>
+        <v>0.35</v>
+      </c>
+      <c r="N70" s="18">
+        <v>0.06</v>
+      </c>
+      <c r="O70" s="18">
+        <v>0.24</v>
+      </c>
+      <c r="P70" s="18">
+        <v>0.09</v>
+      </c>
+      <c r="Q70" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R70" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="S70" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="T70" s="5">
+        <f t="shared" ref="T70" si="595">ROUND(B70/K70,3)</f>
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="U70" s="5">
+        <f t="shared" ref="U70" si="596">ROUND(C70/L70,3)</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="V70" s="4">
+        <f t="shared" ref="V70" si="597">ROUND(D70/M70,3)</f>
+        <v>13.657</v>
+      </c>
+      <c r="W70" s="18">
+        <f t="shared" ref="W70" si="598">ROUND(E70/N70,3)</f>
+        <v>6.6669999999999998</v>
+      </c>
+      <c r="X70" s="18">
+        <f t="shared" ref="X70" si="599">ROUND(F70/O70,3)</f>
+        <v>13.458</v>
+      </c>
+      <c r="Y70" s="18">
+        <f t="shared" ref="Y70" si="600">ROUND(G70/P70,3)</f>
+        <v>14.888999999999999</v>
+      </c>
+      <c r="Z70" s="18">
+        <f t="shared" ref="Z70" si="601">ROUND(H70/Q70,3)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA70" s="19">
+        <f t="shared" ref="AA70" si="602">ROUND(I70/R70,3)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AB70" s="20"/>
+    </row>
+    <row r="71" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="2">
+        <f t="shared" ref="B71" si="603">D$2/D71</f>
+        <v>116.39351851851849</v>
+      </c>
+      <c r="C71" s="2">
+        <f t="shared" ref="C71" si="604">D70/D71</f>
+        <v>1.1064814814814814</v>
+      </c>
+      <c r="D71" s="6">
+        <f t="shared" ref="D71" si="605">SUM(F71:H71)</f>
+        <v>4.32</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F71" s="13">
+        <v>2.77</v>
+      </c>
+      <c r="G71" s="9">
+        <v>1.34</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="I71" s="10">
+        <v>0.44</v>
+      </c>
+      <c r="J71" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="K71" s="2">
+        <f t="shared" ref="K71" si="606">M$2/M71</f>
+        <v>126.39393939393936</v>
+      </c>
+      <c r="L71" s="2">
+        <f t="shared" ref="L71" si="607">M70/M71</f>
+        <v>1.0606060606060606</v>
+      </c>
+      <c r="M71" s="6">
+        <f t="shared" ref="M71" si="608">SUM(O71:Q71)</f>
+        <v>0.33</v>
+      </c>
+      <c r="N71" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="O71" s="13">
+        <v>0.22</v>
+      </c>
+      <c r="P71" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R71" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="S71" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="T71" s="2">
+        <f t="shared" ref="T71" si="609">ROUND(B71/K71,3)</f>
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="U71" s="2">
+        <f t="shared" ref="U71" si="610">ROUND(C71/L71,3)</f>
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="V71" s="6">
+        <f t="shared" ref="V71" si="611">ROUND(D71/M71,3)</f>
+        <v>13.090999999999999</v>
+      </c>
+      <c r="W71" s="9">
+        <f t="shared" ref="W71" si="612">ROUND(E71/N71,3)</f>
+        <v>5</v>
+      </c>
+      <c r="X71" s="13">
+        <f t="shared" ref="X71" si="613">ROUND(F71/O71,3)</f>
+        <v>12.590999999999999</v>
+      </c>
+      <c r="Y71" s="9">
+        <f t="shared" ref="Y71" si="614">ROUND(G71/P71,3)</f>
+        <v>14.888999999999999</v>
+      </c>
+      <c r="Z71" s="9">
+        <f t="shared" ref="Z71" si="615">ROUND(H71/Q71,3)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA71" s="10">
+        <f t="shared" ref="AA71" si="616">ROUND(I71/R71,3)</f>
         <v>8.8000000000000007</v>
       </c>
     </row>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AE04E1-37AF-4624-B263-76155BD6472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F65BEB-0FE7-4C1E-958A-A12C3C9D51BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="83">
   <si>
     <t>H23</t>
   </si>
@@ -329,6 +329,14 @@
   </si>
   <si>
     <t>H91</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H92</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H93</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -851,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB71"/>
+  <dimension ref="A1:AB73"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -6775,27 +6783,27 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.878220140515211</v>
+        <v>58.603729603729597</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0163934426229506</v>
+        <v>1.0116550116550116</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.5400000000000009</v>
+        <v>8.58</v>
       </c>
       <c r="E62" s="9">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F62" s="13">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="G62" s="9">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H62" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I62" s="10">
         <v>2.0299999999999998</v>
@@ -6816,7 +6824,7 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="N62" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O62" s="13">
         <v>0.45</v>
@@ -6828,42 +6836,42 @@
         <v>0.02</v>
       </c>
       <c r="R62" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S62" s="20" t="s">
         <v>70</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.86099999999999999</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.98399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14</v>
+        <v>14.066000000000001</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>5.8570000000000002</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.667</v>
+        <v>12.756</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA62" s="10">
         <f t="shared" ref="AA62" si="490">ROUND(I62/R62,3)</f>
-        <v>14.5</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6872,18 +6880,18 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>58.809356725146188</v>
+        <v>58.878220140515211</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>0.99883040935672518</v>
+        <v>1.0046838407494145</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.5500000000000007</v>
+        <v>8.5400000000000009</v>
       </c>
       <c r="E63" s="9">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F63" s="9">
         <v>5.7</v>
@@ -6892,7 +6900,7 @@
         <v>2.61</v>
       </c>
       <c r="H63" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I63" s="10">
         <v>2.02</v>
@@ -6902,21 +6910,21 @@
       </c>
       <c r="K63" s="5">
         <f t="shared" ref="K63" si="494">M$2/M63</f>
-        <v>68.377049180327845</v>
+        <v>66.206349206349202</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>1</v>
+        <v>0.96825396825396837</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
-        <v>0.6100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N63" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O63" s="9">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="P63" s="9">
         <v>0.14000000000000001</v>
@@ -6925,30 +6933,30 @@
         <v>0.02</v>
       </c>
       <c r="R63" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S63" s="20" t="s">
         <v>71</v>
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.86</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>0.999</v>
+        <v>1.038</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>14.016</v>
+        <v>13.555999999999999</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>5.7140000000000004</v>
+        <v>7.5</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.667</v>
+        <v>12.128</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
@@ -6956,11 +6964,11 @@
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
-        <v>14.429</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6969,21 +6977,21 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>65.216601815823594</v>
+        <v>64.963824289405679</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1089494163424125</v>
+        <v>1.103359173126615</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.7100000000000009</v>
+        <v>7.74</v>
       </c>
       <c r="E64" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F64" s="13">
-        <v>4.87</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G64" s="9">
         <v>2.61</v>
@@ -6992,64 +7000,64 @@
         <v>0.23</v>
       </c>
       <c r="I64" s="10">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
       </c>
       <c r="K64" s="2">
         <f t="shared" ref="K64" si="508">M$2/M64</f>
-        <v>77.240740740740719</v>
+        <v>78.698113207547152</v>
       </c>
       <c r="L64" s="2">
         <f t="shared" ref="L64" si="509">M63/M64</f>
-        <v>1.1296296296296298</v>
+        <v>1.1886792452830188</v>
       </c>
       <c r="M64" s="6">
         <f t="shared" ref="M64" si="510">SUM(O64:Q64)</f>
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="N64" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
       </c>
       <c r="P64" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Q64" s="9">
         <v>0.02</v>
       </c>
       <c r="R64" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S64" s="20" t="s">
         <v>72</v>
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.84399999999999997</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.98199999999999998</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.278</v>
+        <v>14.603999999999999</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>5</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.816000000000001</v>
+        <v>12.895</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.643000000000001</v>
+        <v>20.077000000000002</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
@@ -7057,7 +7065,7 @@
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>14.429</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="65" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7066,30 +7074,30 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>68.317934782608688</v>
+        <v>67.7654986522911</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0475543478260869</v>
+        <v>1.0431266846361187</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="E65" s="9">
         <v>0.42</v>
       </c>
       <c r="F65" s="13">
-        <v>4.54</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="G65" s="9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H65" s="9">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="I65" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
@@ -7100,14 +7108,14 @@
       </c>
       <c r="L65" s="2">
         <f t="shared" ref="L65" si="523">M64/M65</f>
-        <v>1.0588235294117647</v>
+        <v>1.0392156862745099</v>
       </c>
       <c r="M65" s="6">
         <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
         <v>0.51</v>
       </c>
       <c r="N65" s="9">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="O65" s="13">
         <v>0.35</v>
@@ -7119,42 +7127,42 @@
         <v>0.02</v>
       </c>
       <c r="R65" s="10">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.83499999999999996</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.98899999999999999</v>
+        <v>1.004</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>14.430999999999999</v>
+        <v>14.548999999999999</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>12.971</v>
+        <v>13.029</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>14.356999999999999</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7163,30 +7171,30 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>82.700657894736835</v>
+        <v>82.564860426929386</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2105263157894737</v>
+        <v>1.2183908045977012</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.08</v>
+        <v>6.09</v>
       </c>
       <c r="E66" s="9">
         <v>0.39</v>
       </c>
       <c r="F66" s="13">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="G66" s="9">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H66" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I66" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>75</v>
@@ -7204,7 +7212,7 @@
         <v>0.47000000000000003</v>
       </c>
       <c r="N66" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O66" s="13">
         <v>0.31</v>
@@ -7223,35 +7231,35 @@
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.93200000000000005</v>
+        <v>0.93</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.1160000000000001</v>
+        <v>1.123</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>12.936</v>
+        <v>12.957000000000001</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>6.5</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.419</v>
+        <v>10.452</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.713999999999999</v>
+        <v>18.643000000000001</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
-        <v>15.615</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7260,30 +7268,30 @@
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67" si="547">D$2/D67</f>
-        <v>104.97286012526092</v>
+        <v>105.63445378151258</v>
       </c>
       <c r="C67" s="2">
         <f t="shared" ref="C67" si="548">D66/D67</f>
-        <v>1.2693110647181627</v>
+        <v>1.2794117647058822</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
-        <v>4.7900000000000009</v>
+        <v>4.7600000000000007</v>
       </c>
       <c r="E67" s="9">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="F67" s="9">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="G67" s="13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H67" s="9">
         <v>0.23</v>
       </c>
       <c r="I67" s="14">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>76</v>
@@ -7320,27 +7328,27 @@
       </c>
       <c r="T67" s="2">
         <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
-        <v>1.1579999999999999</v>
+        <v>1.165</v>
       </c>
       <c r="U67" s="2">
         <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
-        <v>1.242</v>
+        <v>1.252</v>
       </c>
       <c r="V67" s="6">
         <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
-        <v>10.413</v>
+        <v>10.348000000000001</v>
       </c>
       <c r="W67" s="9">
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
-        <v>6.1429999999999998</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X67" s="18">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
-        <v>10.355</v>
+        <v>10.323</v>
       </c>
       <c r="Y67" s="13">
         <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
-        <v>10.385</v>
+        <v>10.231</v>
       </c>
       <c r="Z67" s="9">
         <f t="shared" ref="Z67" si="559">ROUND(H67/Q67,3)</f>
@@ -7348,7 +7356,7 @@
       </c>
       <c r="AA67" s="14">
         <f t="shared" ref="AA67" si="560">ROUND(I67/R67,3)</f>
-        <v>6.2859999999999996</v>
+        <v>6.1429999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7357,51 +7365,51 @@
       </c>
       <c r="B68" s="5">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>106.08016877637131</v>
+        <v>105.41299790356393</v>
       </c>
       <c r="C68" s="5">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>1.0105485232067515</v>
+        <v>0.99790356394129998</v>
       </c>
       <c r="D68" s="4">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.7399999999999993</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="E68" s="18">
         <v>0.4</v>
       </c>
       <c r="F68" s="18">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="G68" s="18">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H68" s="13">
         <v>0.22</v>
       </c>
       <c r="I68" s="19">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J68" s="20" t="s">
         <v>77</v>
       </c>
       <c r="K68" s="5">
         <f t="shared" ref="K68" si="564">M$2/M68</f>
-        <v>92.688888888888869</v>
+        <v>90.673913043478237</v>
       </c>
       <c r="L68" s="5">
         <f t="shared" ref="L68" si="565">M67/M68</f>
-        <v>1.0222222222222221</v>
+        <v>1</v>
       </c>
       <c r="M68" s="4">
         <f t="shared" ref="M68" si="566">SUM(O68:Q68)</f>
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="N68" s="18">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O68" s="18">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="P68" s="18">
         <v>0.13</v>
@@ -7417,27 +7425,27 @@
       </c>
       <c r="T68" s="5">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.1439999999999999</v>
+        <v>1.163</v>
       </c>
       <c r="U68" s="5">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
-        <v>0.98899999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="V68" s="4">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.532999999999999</v>
+        <v>10.37</v>
       </c>
       <c r="W68" s="18">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
-        <v>4.444</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X68" s="18">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.632999999999999</v>
+        <v>10.355</v>
       </c>
       <c r="Y68" s="18">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
-        <v>10.231</v>
+        <v>10.308</v>
       </c>
       <c r="Z68" s="13">
         <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
@@ -7445,7 +7453,7 @@
       </c>
       <c r="AA68" s="19">
         <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
-        <v>6.1429999999999998</v>
+        <v>6.2859999999999996</v>
       </c>
       <c r="AB68" s="20"/>
     </row>
@@ -7455,30 +7463,30 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" ref="B69" si="575">D$2/D69</f>
-        <v>105.19246861924684</v>
+        <v>106.30443974630019</v>
       </c>
       <c r="C69" s="2">
         <f t="shared" ref="C69" si="576">D68/D69</f>
-        <v>0.99163179916317967</v>
+        <v>1.0084566596194502</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
-        <v>4.78</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="E69" s="9">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F69" s="13">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="G69" s="13">
         <v>1.34</v>
       </c>
       <c r="H69" s="9">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="I69" s="14">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>78</v>
@@ -7489,14 +7497,14 @@
       </c>
       <c r="L69" s="2">
         <f t="shared" ref="L69" si="579">M68/M69</f>
-        <v>1.25</v>
+        <v>1.2777777777777779</v>
       </c>
       <c r="M69" s="6">
         <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
         <v>0.36</v>
       </c>
       <c r="N69" s="9">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O69" s="13">
         <v>0.25</v>
@@ -7515,23 +7523,23 @@
       </c>
       <c r="T69" s="2">
         <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
-        <v>0.90800000000000003</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="U69" s="2">
         <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
-        <v>0.79300000000000004</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="V69" s="6">
         <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
-        <v>13.278</v>
+        <v>13.138999999999999</v>
       </c>
       <c r="W69" s="9">
         <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
-        <v>7.3330000000000002</v>
+        <v>5</v>
       </c>
       <c r="X69" s="13">
         <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
-        <v>12.88</v>
+        <v>12.76</v>
       </c>
       <c r="Y69" s="13">
         <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
@@ -7539,11 +7547,11 @@
       </c>
       <c r="Z69" s="9">
         <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA69" s="14">
         <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
-        <v>8.8000000000000007</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="70" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7552,24 +7560,24 @@
       </c>
       <c r="B70" s="5">
         <f t="shared" ref="B70" si="589">D$2/D70</f>
-        <v>105.19246861924684</v>
+        <v>104.75416666666666</v>
       </c>
       <c r="C70" s="5">
         <f t="shared" ref="C70" si="590">D69/D70</f>
-        <v>1</v>
+        <v>0.98541666666666683</v>
       </c>
       <c r="D70" s="4">
         <f t="shared" ref="D70" si="591">SUM(F70:H70)</f>
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="E70" s="18">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F70" s="18">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="G70" s="18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H70" s="18">
         <v>0.21</v>
@@ -7582,21 +7590,21 @@
       </c>
       <c r="K70" s="5">
         <f t="shared" ref="K70" si="592">M$2/M70</f>
-        <v>119.17142857142856</v>
+        <v>115.8611111111111</v>
       </c>
       <c r="L70" s="5">
         <f t="shared" ref="L70" si="593">M69/M70</f>
-        <v>1.0285714285714287</v>
+        <v>1</v>
       </c>
       <c r="M70" s="4">
         <f t="shared" ref="M70" si="594">SUM(O70:Q70)</f>
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="N70" s="18">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O70" s="18">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="P70" s="18">
         <v>0.09</v>
@@ -7612,27 +7620,27 @@
       </c>
       <c r="T70" s="5">
         <f t="shared" ref="T70" si="595">ROUND(B70/K70,3)</f>
-        <v>0.88300000000000001</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" ref="U70" si="596">ROUND(C70/L70,3)</f>
-        <v>0.97199999999999998</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="V70" s="4">
         <f t="shared" ref="V70" si="597">ROUND(D70/M70,3)</f>
-        <v>13.657</v>
+        <v>13.333</v>
       </c>
       <c r="W70" s="18">
         <f t="shared" ref="W70" si="598">ROUND(E70/N70,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.8570000000000002</v>
       </c>
       <c r="X70" s="18">
         <f t="shared" ref="X70" si="599">ROUND(F70/O70,3)</f>
-        <v>13.458</v>
+        <v>12.96</v>
       </c>
       <c r="Y70" s="18">
         <f t="shared" ref="Y70" si="600">ROUND(G70/P70,3)</f>
-        <v>14.888999999999999</v>
+        <v>15</v>
       </c>
       <c r="Z70" s="18">
         <f t="shared" ref="Z70" si="601">ROUND(H70/Q70,3)</f>
@@ -7650,30 +7658,30 @@
       </c>
       <c r="B71" s="2">
         <f t="shared" ref="B71" si="603">D$2/D71</f>
-        <v>116.39351851851849</v>
+        <v>116.66357308584686</v>
       </c>
       <c r="C71" s="2">
         <f t="shared" ref="C71" si="604">D70/D71</f>
-        <v>1.1064814814814814</v>
+        <v>1.1136890951276102</v>
       </c>
       <c r="D71" s="6">
         <f t="shared" ref="D71" si="605">SUM(F71:H71)</f>
-        <v>4.32</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="E71" s="9">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="F71" s="13">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="G71" s="9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H71" s="9">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="I71" s="10">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J71" s="20" t="s">
         <v>80</v>
@@ -7684,14 +7692,14 @@
       </c>
       <c r="L71" s="2">
         <f t="shared" ref="L71" si="607">M70/M71</f>
-        <v>1.0606060606060606</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="M71" s="6">
         <f t="shared" ref="M71" si="608">SUM(O71:Q71)</f>
         <v>0.33</v>
       </c>
       <c r="N71" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="13">
         <v>0.22</v>
@@ -7710,36 +7718,231 @@
       </c>
       <c r="T71" s="2">
         <f t="shared" ref="T71" si="609">ROUND(B71/K71,3)</f>
-        <v>0.92100000000000004</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="U71" s="2">
         <f t="shared" ref="U71" si="610">ROUND(C71/L71,3)</f>
-        <v>1.0429999999999999</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="V71" s="6">
         <f t="shared" ref="V71" si="611">ROUND(D71/M71,3)</f>
-        <v>13.090999999999999</v>
+        <v>13.061</v>
       </c>
       <c r="W71" s="9">
         <f t="shared" ref="W71" si="612">ROUND(E71/N71,3)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X71" s="13">
         <f t="shared" ref="X71" si="613">ROUND(F71/O71,3)</f>
-        <v>12.590999999999999</v>
+        <v>12.545</v>
       </c>
       <c r="Y71" s="9">
         <f t="shared" ref="Y71" si="614">ROUND(G71/P71,3)</f>
-        <v>14.888999999999999</v>
+        <v>14.778</v>
       </c>
       <c r="Z71" s="9">
         <f t="shared" ref="Z71" si="615">ROUND(H71/Q71,3)</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA71" s="10">
         <f t="shared" ref="AA71" si="616">ROUND(I71/R71,3)</f>
-        <v>8.8000000000000007</v>
-      </c>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="2">
+        <f t="shared" ref="B72" si="617">D$2/D72</f>
+        <v>121.45410628019323</v>
+      </c>
+      <c r="C72" s="2">
+        <f t="shared" ref="C72" si="618">D71/D72</f>
+        <v>1.0410628019323671</v>
+      </c>
+      <c r="D72" s="6">
+        <f t="shared" ref="D72" si="619">SUM(F72:H72)</f>
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F72" s="9">
+        <v>2.82</v>
+      </c>
+      <c r="G72" s="13">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="I72" s="14">
+        <v>0.36</v>
+      </c>
+      <c r="J72" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="K72" s="2">
+        <f t="shared" ref="K72" si="620">M$2/M72</f>
+        <v>130.34374999999997</v>
+      </c>
+      <c r="L72" s="2">
+        <f t="shared" ref="L72" si="621">M71/M72</f>
+        <v>1.03125</v>
+      </c>
+      <c r="M72" s="6">
+        <f t="shared" ref="M72" si="622">SUM(O72:Q72)</f>
+        <v>0.32</v>
+      </c>
+      <c r="N72" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="O72" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="P72" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R72" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="S72" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="T72" s="2">
+        <f t="shared" ref="T72" si="623">ROUND(B72/K72,3)</f>
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="U72" s="2">
+        <f t="shared" ref="U72" si="624">ROUND(C72/L72,3)</f>
+        <v>1.01</v>
+      </c>
+      <c r="V72" s="6">
+        <f t="shared" ref="V72" si="625">ROUND(D72/M72,3)</f>
+        <v>12.938000000000001</v>
+      </c>
+      <c r="W72" s="9">
+        <f t="shared" ref="W72" si="626">ROUND(E72/N72,3)</f>
+        <v>6.6669999999999998</v>
+      </c>
+      <c r="X72" s="9">
+        <f t="shared" ref="X72" si="627">ROUND(F72/O72,3)</f>
+        <v>12.818</v>
+      </c>
+      <c r="Y72" s="13">
+        <f t="shared" ref="Y72" si="628">ROUND(G72/P72,3)</f>
+        <v>14</v>
+      </c>
+      <c r="Z72" s="9">
+        <f t="shared" ref="Z72" si="629">ROUND(H72/Q72,3)</f>
+        <v>10</v>
+      </c>
+      <c r="AA72" s="14">
+        <f t="shared" ref="AA72" si="630">ROUND(I72/R72,3)</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="5">
+        <f t="shared" ref="B73" si="631">D$2/D73</f>
+        <v>122.34063260340633</v>
+      </c>
+      <c r="C73" s="5">
+        <f t="shared" ref="C73" si="632">D72/D73</f>
+        <v>1.0072992700729928</v>
+      </c>
+      <c r="D73" s="4">
+        <f t="shared" ref="D73" si="633">SUM(F73:H73)</f>
+        <v>4.1099999999999994</v>
+      </c>
+      <c r="E73" s="18">
+        <v>0.42</v>
+      </c>
+      <c r="F73" s="18">
+        <v>2.76</v>
+      </c>
+      <c r="G73" s="18">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H73" s="18">
+        <v>0.22</v>
+      </c>
+      <c r="I73" s="19">
+        <v>0.36</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="K73" s="5">
+        <f t="shared" ref="K73" si="634">M$2/M73</f>
+        <v>130.34374999999997</v>
+      </c>
+      <c r="L73" s="5">
+        <f t="shared" ref="L73" si="635">M72/M73</f>
+        <v>1</v>
+      </c>
+      <c r="M73" s="4">
+        <f t="shared" ref="M73" si="636">SUM(O73:Q73)</f>
+        <v>0.32</v>
+      </c>
+      <c r="N73" s="18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O73" s="18">
+        <v>0.22</v>
+      </c>
+      <c r="P73" s="18">
+        <v>0.08</v>
+      </c>
+      <c r="Q73" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R73" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="S73" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="T73" s="5">
+        <f t="shared" ref="T73" si="637">ROUND(B73/K73,3)</f>
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="U73" s="5">
+        <f t="shared" ref="U73" si="638">ROUND(C73/L73,3)</f>
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="V73" s="4">
+        <f t="shared" ref="V73" si="639">ROUND(D73/M73,3)</f>
+        <v>12.843999999999999</v>
+      </c>
+      <c r="W73" s="18">
+        <f t="shared" ref="W73" si="640">ROUND(E73/N73,3)</f>
+        <v>6</v>
+      </c>
+      <c r="X73" s="18">
+        <f t="shared" ref="X73" si="641">ROUND(F73/O73,3)</f>
+        <v>12.545</v>
+      </c>
+      <c r="Y73" s="18">
+        <f t="shared" ref="Y73" si="642">ROUND(G73/P73,3)</f>
+        <v>14.125</v>
+      </c>
+      <c r="Z73" s="18">
+        <f t="shared" ref="Z73" si="643">ROUND(H73/Q73,3)</f>
+        <v>11</v>
+      </c>
+      <c r="AA73" s="19">
+        <f t="shared" ref="AA73" si="644">ROUND(I73/R73,3)</f>
+        <v>7.2</v>
+      </c>
+      <c r="AB73" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F65BEB-0FE7-4C1E-958A-A12C3C9D51BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D278FDE-C018-4B90-81E0-65AB6C924377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="84">
   <si>
     <t>H23</t>
   </si>
@@ -337,6 +337,10 @@
   </si>
   <si>
     <t>H93</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H94</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -859,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB73"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -6783,24 +6787,24 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.603729603729597</v>
+        <v>58.399535423925656</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0116550116550116</v>
+        <v>1.0081300813008129</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.58</v>
+        <v>8.6100000000000012</v>
       </c>
       <c r="E62" s="9">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F62" s="13">
-        <v>5.74</v>
+        <v>5.78</v>
       </c>
       <c r="G62" s="9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H62" s="9">
         <v>0.23</v>
@@ -6843,27 +6847,27 @@
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.85699999999999998</v>
+        <v>0.85399999999999998</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.98</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.066000000000001</v>
+        <v>14.115</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.756</v>
+        <v>12.843999999999999</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z62" s="18">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
@@ -6880,51 +6884,51 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>58.878220140515211</v>
+        <v>59.224970553592456</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.0046838407494145</v>
+        <v>1.0141342756183747</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.5400000000000009</v>
+        <v>8.49</v>
       </c>
       <c r="E63" s="9">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="F63" s="9">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="G63" s="9">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="H63" s="9">
         <v>0.23</v>
       </c>
       <c r="I63" s="10">
-        <v>2.02</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J63" s="20" t="s">
         <v>71</v>
       </c>
       <c r="K63" s="5">
         <f t="shared" ref="K63" si="494">M$2/M63</f>
-        <v>66.206349206349202</v>
+        <v>68.377049180327845</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
-        <v>0.96825396825396837</v>
+        <v>1</v>
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
-        <v>0.63</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="N63" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O63" s="9">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="P63" s="9">
         <v>0.14000000000000001</v>
@@ -6940,27 +6944,27 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.88900000000000001</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.038</v>
+        <v>1.014</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.555999999999999</v>
+        <v>13.917999999999999</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>7.5</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.128</v>
+        <v>12.6</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
-        <v>15.538</v>
+        <v>15.462</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6977,54 +6981,54 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>64.963824289405679</v>
+        <v>66.073587385019707</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.103359173126615</v>
+        <v>1.1156373193166886</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.74</v>
+        <v>7.6099999999999994</v>
       </c>
       <c r="E64" s="9">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="F64" s="13">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="G64" s="9">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="H64" s="9">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I64" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
       </c>
       <c r="K64" s="2">
         <f t="shared" ref="K64" si="508">M$2/M64</f>
-        <v>78.698113207547152</v>
+        <v>77.240740740740719</v>
       </c>
       <c r="L64" s="2">
         <f t="shared" ref="L64" si="509">M63/M64</f>
-        <v>1.1886792452830188</v>
+        <v>1.1296296296296298</v>
       </c>
       <c r="M64" s="6">
         <f t="shared" ref="M64" si="510">SUM(O64:Q64)</f>
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
       </c>
       <c r="P64" s="9">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q64" s="9">
         <v>0.02</v>
@@ -7037,35 +7041,35 @@
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.82499999999999996</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.92800000000000005</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.603999999999999</v>
+        <v>14.093</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>5.5709999999999997</v>
+        <v>7.5</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.895</v>
+        <v>12.632</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>20.077000000000002</v>
+        <v>18.5</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>15.615</v>
+        <v>15.462</v>
       </c>
     </row>
     <row r="65" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7074,54 +7078,54 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>67.7654986522911</v>
+        <v>67.674293405114398</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0431266846361187</v>
+        <v>1.0242261103633916</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.42</v>
+        <v>7.43</v>
       </c>
       <c r="E65" s="9">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="F65" s="13">
-        <v>4.5599999999999996</v>
+        <v>4.59</v>
       </c>
       <c r="G65" s="9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H65" s="9">
         <v>0.24</v>
       </c>
       <c r="I65" s="10">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
       </c>
       <c r="K65" s="2">
         <f t="shared" ref="K65" si="522">M$2/M65</f>
-        <v>81.784313725490179</v>
+        <v>85.122448979591809</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" ref="L65" si="523">M64/M65</f>
-        <v>1.0392156862745099</v>
+        <v>1.1020408163265305</v>
       </c>
       <c r="M65" s="6">
         <f t="shared" ref="M65" si="524">SUM(O65:Q65)</f>
-        <v>0.51</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="N65" s="9">
         <v>0.06</v>
       </c>
       <c r="O65" s="13">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="P65" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Q65" s="9">
         <v>0.02</v>
@@ -7134,27 +7138,27 @@
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.82899999999999996</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>1.004</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>14.548999999999999</v>
+        <v>15.163</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>7</v>
+        <v>7.1669999999999998</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>13.029</v>
+        <v>13.5</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>18.713999999999999</v>
+        <v>20</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
@@ -7162,7 +7166,7 @@
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>15.538</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7171,27 +7175,27 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>82.564860426929386</v>
+        <v>82.700657894736835</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2183908045977012</v>
+        <v>1.2220394736842104</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="E66" s="9">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="F66" s="13">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="G66" s="9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H66" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I66" s="10">
         <v>2.02</v>
@@ -7205,7 +7209,7 @@
       </c>
       <c r="L66" s="2">
         <f t="shared" ref="L66" si="537">M65/M66</f>
-        <v>1.0851063829787233</v>
+        <v>1.0425531914893618</v>
       </c>
       <c r="M66" s="6">
         <f t="shared" ref="M66" si="538">SUM(O66:Q66)</f>
@@ -7231,31 +7235,31 @@
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.93</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.123</v>
+        <v>1.1719999999999999</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>12.957000000000001</v>
+        <v>12.936</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.452</v>
+        <v>10.484</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.643000000000001</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
@@ -7268,30 +7272,30 @@
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67" si="547">D$2/D67</f>
-        <v>105.63445378151258</v>
+        <v>103.24845995893222</v>
       </c>
       <c r="C67" s="2">
         <f t="shared" ref="C67" si="548">D66/D67</f>
-        <v>1.2794117647058822</v>
+        <v>1.2484599589322383</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
-        <v>4.7600000000000007</v>
+        <v>4.87</v>
       </c>
       <c r="E67" s="9">
         <v>0.39</v>
       </c>
       <c r="F67" s="9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G67" s="13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H67" s="9">
         <v>0.23</v>
       </c>
       <c r="I67" s="14">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>76</v>
@@ -7328,15 +7332,15 @@
       </c>
       <c r="T67" s="2">
         <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
-        <v>1.165</v>
+        <v>1.139</v>
       </c>
       <c r="U67" s="2">
         <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
-        <v>1.252</v>
+        <v>1.222</v>
       </c>
       <c r="V67" s="6">
         <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
-        <v>10.348000000000001</v>
+        <v>10.587</v>
       </c>
       <c r="W67" s="9">
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
@@ -7344,11 +7348,11 @@
       </c>
       <c r="X67" s="18">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
-        <v>10.323</v>
+        <v>10.645</v>
       </c>
       <c r="Y67" s="13">
         <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
-        <v>10.231</v>
+        <v>10.308</v>
       </c>
       <c r="Z67" s="9">
         <f t="shared" ref="Z67" si="559">ROUND(H67/Q67,3)</f>
@@ -7356,7 +7360,7 @@
       </c>
       <c r="AA67" s="14">
         <f t="shared" ref="AA67" si="560">ROUND(I67/R67,3)</f>
-        <v>6.1429999999999998</v>
+        <v>6.2859999999999996</v>
       </c>
     </row>
     <row r="68" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7365,27 +7369,27 @@
       </c>
       <c r="B68" s="5">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>105.41299790356393</v>
+        <v>103.67422680412371</v>
       </c>
       <c r="C68" s="5">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>0.99790356394129998</v>
+        <v>1.0041237113402062</v>
       </c>
       <c r="D68" s="4">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.7699999999999996</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="E68" s="18">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="F68" s="18">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="G68" s="18">
         <v>1.34</v>
       </c>
       <c r="H68" s="13">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I68" s="19">
         <v>0.44</v>
@@ -7406,7 +7410,7 @@
         <v>0.46</v>
       </c>
       <c r="N68" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O68" s="18">
         <v>0.31</v>
@@ -7425,23 +7429,23 @@
       </c>
       <c r="T68" s="5">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.163</v>
+        <v>1.143</v>
       </c>
       <c r="U68" s="5">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
-        <v>0.998</v>
+        <v>1.004</v>
       </c>
       <c r="V68" s="4">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.37</v>
+        <v>10.542999999999999</v>
       </c>
       <c r="W68" s="18">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
-        <v>5.7140000000000004</v>
+        <v>7.6669999999999998</v>
       </c>
       <c r="X68" s="18">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.355</v>
+        <v>10.645</v>
       </c>
       <c r="Y68" s="18">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
@@ -7449,7 +7453,7 @@
       </c>
       <c r="Z68" s="13">
         <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA68" s="19">
         <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
@@ -7463,51 +7467,51 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" ref="B69" si="575">D$2/D69</f>
-        <v>106.30443974630019</v>
+        <v>104.10351966873705</v>
       </c>
       <c r="C69" s="2">
         <f t="shared" ref="C69" si="576">D68/D69</f>
-        <v>1.0084566596194502</v>
+        <v>1.0041407867494823</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
-        <v>4.7300000000000004</v>
+        <v>4.83</v>
       </c>
       <c r="E69" s="9">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="F69" s="13">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="G69" s="13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H69" s="9">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I69" s="14">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>78</v>
       </c>
       <c r="K69" s="2">
         <f t="shared" ref="K69" si="578">M$2/M69</f>
-        <v>115.8611111111111</v>
+        <v>119.17142857142856</v>
       </c>
       <c r="L69" s="2">
         <f t="shared" ref="L69" si="579">M68/M69</f>
-        <v>1.2777777777777779</v>
+        <v>1.3142857142857145</v>
       </c>
       <c r="M69" s="6">
         <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="N69" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O69" s="13">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="P69" s="13">
         <v>0.09</v>
@@ -7523,35 +7527,35 @@
       </c>
       <c r="T69" s="2">
         <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
-        <v>0.91800000000000004</v>
+        <v>0.874</v>
       </c>
       <c r="U69" s="2">
         <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
-        <v>0.78900000000000003</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="V69" s="6">
         <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
-        <v>13.138999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="W69" s="9">
         <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
-        <v>5</v>
+        <v>6.1669999999999998</v>
       </c>
       <c r="X69" s="13">
         <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
-        <v>12.76</v>
+        <v>13.583</v>
       </c>
       <c r="Y69" s="13">
         <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
-        <v>14.888999999999999</v>
+        <v>15.111000000000001</v>
       </c>
       <c r="Z69" s="9">
         <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA69" s="14">
         <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="70" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7560,30 +7564,30 @@
       </c>
       <c r="B70" s="5">
         <f t="shared" ref="B70" si="589">D$2/D70</f>
-        <v>104.75416666666666</v>
+        <v>104.97286012526095</v>
       </c>
       <c r="C70" s="5">
         <f t="shared" ref="C70" si="590">D69/D70</f>
-        <v>0.98541666666666683</v>
+        <v>1.0083507306889352</v>
       </c>
       <c r="D70" s="4">
         <f t="shared" ref="D70" si="591">SUM(F70:H70)</f>
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="E70" s="18">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F70" s="18">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="G70" s="18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H70" s="18">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="I70" s="19">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J70" s="20" t="s">
         <v>79</v>
@@ -7594,7 +7598,7 @@
       </c>
       <c r="L70" s="5">
         <f t="shared" ref="L70" si="593">M69/M70</f>
-        <v>1</v>
+        <v>0.97222222222222221</v>
       </c>
       <c r="M70" s="4">
         <f t="shared" ref="M70" si="594">SUM(O70:Q70)</f>
@@ -7620,35 +7624,35 @@
       </c>
       <c r="T70" s="5">
         <f t="shared" ref="T70" si="595">ROUND(B70/K70,3)</f>
-        <v>0.90400000000000003</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" ref="U70" si="596">ROUND(C70/L70,3)</f>
-        <v>0.98499999999999999</v>
+        <v>1.0369999999999999</v>
       </c>
       <c r="V70" s="4">
         <f t="shared" ref="V70" si="597">ROUND(D70/M70,3)</f>
-        <v>13.333</v>
+        <v>13.305999999999999</v>
       </c>
       <c r="W70" s="18">
         <f t="shared" ref="W70" si="598">ROUND(E70/N70,3)</f>
-        <v>5.8570000000000002</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X70" s="18">
         <f t="shared" ref="X70" si="599">ROUND(F70/O70,3)</f>
-        <v>12.96</v>
+        <v>12.92</v>
       </c>
       <c r="Y70" s="18">
         <f t="shared" ref="Y70" si="600">ROUND(G70/P70,3)</f>
-        <v>15</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="Z70" s="18">
         <f t="shared" ref="Z70" si="601">ROUND(H70/Q70,3)</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA70" s="19">
         <f t="shared" ref="AA70" si="602">ROUND(I70/R70,3)</f>
-        <v>8.8000000000000007</v>
+        <v>8.6</v>
       </c>
       <c r="AB70" s="20"/>
     </row>
@@ -7658,24 +7662,24 @@
       </c>
       <c r="B71" s="2">
         <f t="shared" ref="B71" si="603">D$2/D71</f>
-        <v>116.66357308584686</v>
+        <v>116.39351851851852</v>
       </c>
       <c r="C71" s="2">
         <f t="shared" ref="C71" si="604">D70/D71</f>
-        <v>1.1136890951276102</v>
+        <v>1.1087962962962965</v>
       </c>
       <c r="D71" s="6">
         <f t="shared" ref="D71" si="605">SUM(F71:H71)</f>
-        <v>4.3099999999999996</v>
+        <v>4.3199999999999994</v>
       </c>
       <c r="E71" s="9">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="F71" s="13">
         <v>2.76</v>
       </c>
       <c r="G71" s="9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H71" s="9">
         <v>0.22</v>
@@ -7718,19 +7722,19 @@
       </c>
       <c r="T71" s="2">
         <f t="shared" ref="T71" si="609">ROUND(B71/K71,3)</f>
-        <v>0.92300000000000004</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="U71" s="2">
         <f t="shared" ref="U71" si="610">ROUND(C71/L71,3)</f>
-        <v>1.0209999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="V71" s="6">
         <f t="shared" ref="V71" si="611">ROUND(D71/M71,3)</f>
-        <v>13.061</v>
+        <v>13.090999999999999</v>
       </c>
       <c r="W71" s="9">
         <f t="shared" ref="W71" si="612">ROUND(E71/N71,3)</f>
-        <v>6</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X71" s="13">
         <f t="shared" ref="X71" si="613">ROUND(F71/O71,3)</f>
@@ -7738,7 +7742,7 @@
       </c>
       <c r="Y71" s="9">
         <f t="shared" ref="Y71" si="614">ROUND(G71/P71,3)</f>
-        <v>14.778</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="Z71" s="9">
         <f t="shared" ref="Z71" si="615">ROUND(H71/Q71,3)</f>
@@ -7755,27 +7759,27 @@
       </c>
       <c r="B72" s="2">
         <f t="shared" ref="B72" si="617">D$2/D72</f>
-        <v>121.45410628019323</v>
+        <v>121.74818401937044</v>
       </c>
       <c r="C72" s="2">
         <f t="shared" ref="C72" si="618">D71/D72</f>
-        <v>1.0410628019323671</v>
+        <v>1.0460048426150119</v>
       </c>
       <c r="D72" s="6">
         <f t="shared" ref="D72" si="619">SUM(F72:H72)</f>
-        <v>4.1399999999999997</v>
+        <v>4.13</v>
       </c>
       <c r="E72" s="9">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="F72" s="9">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="G72" s="13">
-        <v>1.1200000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H72" s="9">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I72" s="14">
         <v>0.36</v>
@@ -7796,7 +7800,7 @@
         <v>0.32</v>
       </c>
       <c r="N72" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O72" s="9">
         <v>0.22</v>
@@ -7815,31 +7819,31 @@
       </c>
       <c r="T72" s="2">
         <f t="shared" ref="T72" si="623">ROUND(B72/K72,3)</f>
-        <v>0.93200000000000005</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="U72" s="2">
         <f t="shared" ref="U72" si="624">ROUND(C72/L72,3)</f>
-        <v>1.01</v>
+        <v>1.014</v>
       </c>
       <c r="V72" s="6">
         <f t="shared" ref="V72" si="625">ROUND(D72/M72,3)</f>
-        <v>12.938000000000001</v>
+        <v>12.906000000000001</v>
       </c>
       <c r="W72" s="9">
         <f t="shared" ref="W72" si="626">ROUND(E72/N72,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.7140000000000004</v>
       </c>
       <c r="X72" s="9">
         <f t="shared" ref="X72" si="627">ROUND(F72/O72,3)</f>
-        <v>12.818</v>
+        <v>12.682</v>
       </c>
       <c r="Y72" s="13">
         <f t="shared" ref="Y72" si="628">ROUND(G72/P72,3)</f>
-        <v>14</v>
+        <v>14.125</v>
       </c>
       <c r="Z72" s="9">
         <f t="shared" ref="Z72" si="629">ROUND(H72/Q72,3)</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA72" s="14">
         <f t="shared" ref="AA72" si="630">ROUND(I72/R72,3)</f>
@@ -7852,27 +7856,27 @@
       </c>
       <c r="B73" s="5">
         <f t="shared" ref="B73" si="631">D$2/D73</f>
-        <v>122.34063260340633</v>
+        <v>122.34063260340631</v>
       </c>
       <c r="C73" s="5">
         <f t="shared" ref="C73" si="632">D72/D73</f>
-        <v>1.0072992700729928</v>
+        <v>1.0048661800486618</v>
       </c>
       <c r="D73" s="4">
         <f t="shared" ref="D73" si="633">SUM(F73:H73)</f>
-        <v>4.1099999999999994</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="E73" s="18">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="F73" s="18">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="G73" s="18">
         <v>1.1299999999999999</v>
       </c>
       <c r="H73" s="18">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I73" s="19">
         <v>0.36</v>
@@ -7893,7 +7897,7 @@
         <v>0.32</v>
       </c>
       <c r="N73" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O73" s="18">
         <v>0.22</v>
@@ -7916,7 +7920,7 @@
       </c>
       <c r="U73" s="5">
         <f t="shared" ref="U73" si="638">ROUND(C73/L73,3)</f>
-        <v>1.0069999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="V73" s="4">
         <f t="shared" ref="V73" si="639">ROUND(D73/M73,3)</f>
@@ -7924,11 +7928,11 @@
       </c>
       <c r="W73" s="18">
         <f t="shared" ref="W73" si="640">ROUND(E73/N73,3)</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="X73" s="18">
         <f t="shared" ref="X73" si="641">ROUND(F73/O73,3)</f>
-        <v>12.545</v>
+        <v>12.590999999999999</v>
       </c>
       <c r="Y73" s="18">
         <f t="shared" ref="Y73" si="642">ROUND(G73/P73,3)</f>
@@ -7936,13 +7940,110 @@
       </c>
       <c r="Z73" s="18">
         <f t="shared" ref="Z73" si="643">ROUND(H73/Q73,3)</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA73" s="19">
         <f t="shared" ref="AA73" si="644">ROUND(I73/R73,3)</f>
         <v>7.2</v>
       </c>
       <c r="AB73" s="20"/>
+    </row>
+    <row r="74" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="5">
+        <f t="shared" ref="B74" si="645">D$2/D74</f>
+        <v>122.04368932038832</v>
+      </c>
+      <c r="C74" s="5">
+        <f t="shared" ref="C74" si="646">D73/D74</f>
+        <v>0.99757281553398058</v>
+      </c>
+      <c r="D74" s="4">
+        <f t="shared" ref="D74" si="647">SUM(F74:H74)</f>
+        <v>4.12</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="9">
+        <v>2.77</v>
+      </c>
+      <c r="G74" s="9">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H74" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="I74" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="K74" s="5">
+        <f t="shared" ref="K74" si="648">M$2/M74</f>
+        <v>130.34374999999997</v>
+      </c>
+      <c r="L74" s="5">
+        <f t="shared" ref="L74" si="649">M73/M74</f>
+        <v>1</v>
+      </c>
+      <c r="M74" s="4">
+        <f t="shared" ref="M74" si="650">SUM(O74:Q74)</f>
+        <v>0.32</v>
+      </c>
+      <c r="N74" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O74" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="P74" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="Q74" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R74" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="S74" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="T74" s="5">
+        <f t="shared" ref="T74" si="651">ROUND(B74/K74,3)</f>
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="U74" s="5">
+        <f t="shared" ref="U74" si="652">ROUND(C74/L74,3)</f>
+        <v>0.998</v>
+      </c>
+      <c r="V74" s="4">
+        <f t="shared" ref="V74" si="653">ROUND(D74/M74,3)</f>
+        <v>12.875</v>
+      </c>
+      <c r="W74" s="18">
+        <f t="shared" ref="W74" si="654">ROUND(E74/N74,3)</f>
+        <v>5.7140000000000004</v>
+      </c>
+      <c r="X74" s="18">
+        <f t="shared" ref="X74" si="655">ROUND(F74/O74,3)</f>
+        <v>12.590999999999999</v>
+      </c>
+      <c r="Y74" s="18">
+        <f t="shared" ref="Y74" si="656">ROUND(G74/P74,3)</f>
+        <v>14.125</v>
+      </c>
+      <c r="Z74" s="18">
+        <f t="shared" ref="Z74" si="657">ROUND(H74/Q74,3)</f>
+        <v>11</v>
+      </c>
+      <c r="AA74" s="19">
+        <f t="shared" ref="AA74" si="658">ROUND(I74/R74,3)</f>
+        <v>7.2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D278FDE-C018-4B90-81E0-65AB6C924377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BB5EA8-E05D-4D38-BE51-F08EF1C99F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="85">
   <si>
     <t>H23</t>
   </si>
@@ -341,6 +341,10 @@
   </si>
   <si>
     <t>H94</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H95</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -417,12 +421,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -485,7 +495,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -548,6 +558,57 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -863,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB74"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -965,93 +1026,93 @@
       </c>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="27">
         <v>1</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="27">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="28">
         <f>SUM(F2:H2)</f>
         <v>502.81999999999994</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="27">
         <v>369.63</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="35">
         <v>174.9</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="35">
         <v>144.88999999999999</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="35">
         <v>183.03</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="36">
         <v>293.08999999999997</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="27">
         <v>1</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="27">
         <v>1</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="28">
         <v>41.709999999999994</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="27">
         <v>93.96</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="35">
         <v>6.59</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="35">
         <v>15.56</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="35">
         <v>19.559999999999999</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="36">
         <v>33.96</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="27">
         <f t="shared" ref="T2:T20" si="0">ROUND(B2/K2,3)</f>
         <v>1</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2" s="27">
         <f t="shared" ref="U2:U20" si="1">ROUND(C2/L2,3)</f>
         <v>1</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="28">
         <f t="shared" ref="V2:V20" si="2">ROUND(D2/M2,3)</f>
         <v>12.055</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="27">
         <f t="shared" ref="W2:W20" si="3">ROUND(E2/N2,3)</f>
         <v>3.9340000000000002</v>
       </c>
-      <c r="X2" s="8">
+      <c r="X2" s="35">
         <f t="shared" ref="X2:X20" si="4">ROUND(F2/O2,3)</f>
         <v>26.54</v>
       </c>
-      <c r="Y2" s="8">
+      <c r="Y2" s="35">
         <f t="shared" ref="Y2:Y20" si="5">ROUND(G2/P2,3)</f>
         <v>9.3119999999999994</v>
       </c>
-      <c r="Z2" s="8">
+      <c r="Z2" s="35">
         <f t="shared" ref="Z2:Z20" si="6">ROUND(H2/Q2,3)</f>
         <v>9.3569999999999993</v>
       </c>
-      <c r="AA2" s="7">
+      <c r="AA2" s="36">
         <f t="shared" ref="AA2:AA20" si="7">ROUND(I2/R2,3)</f>
         <v>8.6300000000000008</v>
       </c>
@@ -1541,98 +1602,98 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="27">
         <f t="shared" si="9"/>
         <v>2.1582110052365007</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="27">
         <f t="shared" si="10"/>
         <v>0.99334706841789</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="28">
         <f t="shared" si="8"/>
         <v>232.98</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="27">
         <v>667.66</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="35">
         <v>98.75</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="35">
         <v>132.88</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="35">
         <v>1.35</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="36">
         <v>114.88</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="27">
         <f t="shared" si="11"/>
         <v>3.5895008605851975</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="27">
         <f t="shared" si="12"/>
         <v>1.0060240963855422</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="28">
         <f t="shared" si="13"/>
         <v>11.62</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="27">
         <v>121.4</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="35">
         <v>4.75</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="35">
         <v>6.6</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="35">
         <v>0.27</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="36">
         <v>6.02</v>
       </c>
-      <c r="S8" s="15" t="s">
+      <c r="S8" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="27">
         <f t="shared" si="0"/>
         <v>0.60099999999999998</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8" s="27">
         <f t="shared" si="1"/>
         <v>0.98699999999999999</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="28">
         <f t="shared" si="2"/>
         <v>20.05</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="27">
         <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
-      <c r="X8" s="8">
+      <c r="X8" s="35">
         <f t="shared" si="4"/>
         <v>20.789000000000001</v>
       </c>
-      <c r="Y8" s="8">
+      <c r="Y8" s="35">
         <f t="shared" si="5"/>
         <v>20.132999999999999</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="Z8" s="35">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="36">
         <f t="shared" si="7"/>
         <v>19.082999999999998</v>
       </c>
@@ -2123,98 +2184,98 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="27">
         <f t="shared" si="9"/>
         <v>3.3443298969072162</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="27">
         <f t="shared" si="10"/>
         <v>1.0026604589291652</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="28">
         <f t="shared" si="8"/>
         <v>150.35</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="27">
         <v>293.14</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="34">
         <v>30.84</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="35">
         <v>118.09</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="35">
         <v>1.42</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="36">
         <v>93.68</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="27">
         <f t="shared" si="11"/>
         <v>5.3405889884763109</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="27">
         <f t="shared" si="12"/>
         <v>1.0179257362355951</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14" s="28">
         <f t="shared" si="13"/>
         <v>7.8100000000000005</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="27">
         <v>100.03</v>
       </c>
-      <c r="O14" s="1">
+      <c r="O14" s="34">
         <v>1.1299999999999999</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="35">
         <v>6.41</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="35">
         <v>0.27</v>
       </c>
-      <c r="R14" s="7">
+      <c r="R14" s="36">
         <v>5.35</v>
       </c>
-      <c r="S14" s="17" t="s">
+      <c r="S14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="27">
         <f t="shared" si="0"/>
         <v>0.626</v>
       </c>
-      <c r="U14" s="5">
+      <c r="U14" s="27">
         <f t="shared" si="1"/>
         <v>0.98499999999999999</v>
       </c>
-      <c r="V14" s="4">
+      <c r="V14" s="28">
         <f t="shared" si="2"/>
         <v>19.251000000000001</v>
       </c>
-      <c r="W14" s="5">
+      <c r="W14" s="27">
         <f t="shared" si="3"/>
         <v>2.931</v>
       </c>
-      <c r="X14" s="1">
+      <c r="X14" s="34">
         <f t="shared" si="4"/>
         <v>27.292000000000002</v>
       </c>
-      <c r="Y14" s="8">
+      <c r="Y14" s="35">
         <f t="shared" si="5"/>
         <v>18.422999999999998</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="Z14" s="35">
         <f t="shared" si="6"/>
         <v>5.2590000000000003</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AA14" s="36">
         <f t="shared" si="7"/>
         <v>17.510000000000002</v>
       </c>
@@ -2608,98 +2669,98 @@
       </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="27">
         <f t="shared" si="9"/>
         <v>4.4446212322107304</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="27">
         <f t="shared" si="10"/>
         <v>1.0311146468664367</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="28">
         <f t="shared" si="14"/>
         <v>113.13000000000001</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="24">
         <v>294.64</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="24">
         <v>30.59</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="25">
         <v>81.010000000000005</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="24">
         <v>1.53</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="29">
         <v>63.79</v>
       </c>
-      <c r="J19" s="17" t="s">
+      <c r="J19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="27">
         <f t="shared" si="11"/>
         <v>7.6252285191956117</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="27">
         <f t="shared" si="12"/>
         <v>1.129798903107861</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M19" s="28">
         <f t="shared" si="13"/>
         <v>5.47</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="24">
         <v>14.02</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="24">
         <v>1.18</v>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="25">
         <v>4</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="Q19" s="24">
         <v>0.28999999999999998</v>
       </c>
-      <c r="R19" s="10">
+      <c r="R19" s="29">
         <v>3.58</v>
       </c>
-      <c r="S19" s="17" t="s">
+      <c r="S19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="T19" s="5">
+      <c r="T19" s="27">
         <f t="shared" si="0"/>
         <v>0.58299999999999996</v>
       </c>
-      <c r="U19" s="5">
+      <c r="U19" s="27">
         <f t="shared" si="1"/>
         <v>0.91300000000000003</v>
       </c>
-      <c r="V19" s="4">
+      <c r="V19" s="28">
         <f t="shared" si="2"/>
         <v>20.681999999999999</v>
       </c>
-      <c r="W19" s="9">
+      <c r="W19" s="24">
         <f t="shared" si="3"/>
         <v>21.015999999999998</v>
       </c>
-      <c r="X19" s="9">
+      <c r="X19" s="24">
         <f t="shared" si="4"/>
         <v>25.923999999999999</v>
       </c>
-      <c r="Y19" s="13">
+      <c r="Y19" s="25">
         <f t="shared" si="5"/>
         <v>20.253</v>
       </c>
-      <c r="Z19" s="9">
+      <c r="Z19" s="24">
         <f t="shared" si="6"/>
         <v>5.2759999999999998</v>
       </c>
-      <c r="AA19" s="10">
+      <c r="AA19" s="29">
         <f t="shared" si="7"/>
         <v>17.818000000000001</v>
       </c>
@@ -3578,98 +3639,98 @@
       </c>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="22">
         <f t="shared" ref="B29" si="110">D$2/D29</f>
         <v>13.033177812337998</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="22">
         <f t="shared" ref="C29" si="111">D28/D29</f>
         <v>1.1905132192846035</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="23">
         <f t="shared" ref="D29" si="112">SUM(F29:H29)</f>
         <v>38.58</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="24">
         <v>243.45</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="24">
         <v>24.9</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="25">
         <v>12.11</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="24">
         <v>1.57</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="32">
         <v>15.35</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="J29" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="22">
         <f t="shared" ref="K29:K30" si="113">M$2/M29</f>
         <v>22.792349726775953</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29" s="22">
         <f t="shared" ref="L29:L30" si="114">M28/M29</f>
         <v>1.1693989071038251</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="23">
         <f t="shared" ref="M29:M30" si="115">SUM(O29:Q29)</f>
         <v>1.83</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="24">
         <v>11.6</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="24">
         <v>0.92</v>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="25">
         <v>0.64</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="Q29" s="24">
         <v>0.27</v>
       </c>
-      <c r="R29" s="19">
+      <c r="R29" s="32">
         <v>0.76</v>
       </c>
-      <c r="S29" s="17" t="s">
+      <c r="S29" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T29" s="22">
         <f t="shared" ref="T29" si="116">ROUND(B29/K29,3)</f>
         <v>0.57199999999999995</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="22">
         <f t="shared" ref="U29" si="117">ROUND(C29/L29,3)</f>
         <v>1.018</v>
       </c>
-      <c r="V29" s="6">
+      <c r="V29" s="23">
         <f t="shared" ref="V29" si="118">ROUND(D29/M29,3)</f>
         <v>21.082000000000001</v>
       </c>
-      <c r="W29" s="9">
+      <c r="W29" s="24">
         <f t="shared" ref="W29" si="119">ROUND(E29/N29,3)</f>
         <v>20.986999999999998</v>
       </c>
-      <c r="X29" s="9">
+      <c r="X29" s="24">
         <f t="shared" ref="X29" si="120">ROUND(F29/O29,3)</f>
         <v>27.065000000000001</v>
       </c>
-      <c r="Y29" s="13">
+      <c r="Y29" s="25">
         <f t="shared" ref="Y29" si="121">ROUND(G29/P29,3)</f>
         <v>18.922000000000001</v>
       </c>
-      <c r="Z29" s="9">
+      <c r="Z29" s="24">
         <f t="shared" ref="Z29" si="122">ROUND(H29/Q29,3)</f>
         <v>5.8150000000000004</v>
       </c>
-      <c r="AA29" s="19">
+      <c r="AA29" s="32">
         <f t="shared" ref="AA29" si="123">ROUND(I29/R29,3)</f>
         <v>20.196999999999999</v>
       </c>
@@ -4451,98 +4512,98 @@
       </c>
     </row>
     <row r="38" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="27">
         <f t="shared" si="193"/>
         <v>20.217933252915159</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="27">
         <f t="shared" si="194"/>
         <v>0.98150381986328916</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="28">
         <f t="shared" si="195"/>
         <v>24.869999999999997</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="25">
         <v>144.19999999999999</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="31">
         <v>12.67</v>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="31">
         <v>11.12</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="31">
         <v>1.08</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="32">
         <v>13</v>
       </c>
-      <c r="J38" s="20" t="s">
+      <c r="J38" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K38" s="27">
         <f t="shared" si="138"/>
         <v>40.105769230769226</v>
       </c>
-      <c r="L38" s="5">
+      <c r="L38" s="27">
         <f t="shared" si="139"/>
         <v>1.0673076923076923</v>
       </c>
-      <c r="M38" s="4">
+      <c r="M38" s="28">
         <f t="shared" si="140"/>
         <v>1.04</v>
       </c>
-      <c r="N38" s="13">
+      <c r="N38" s="25">
         <v>7.02</v>
       </c>
-      <c r="O38" s="18">
+      <c r="O38" s="31">
         <v>0.6</v>
       </c>
-      <c r="P38" s="18">
+      <c r="P38" s="31">
         <v>0.42</v>
       </c>
-      <c r="Q38" s="18">
+      <c r="Q38" s="31">
         <v>0.02</v>
       </c>
-      <c r="R38" s="19">
+      <c r="R38" s="32">
         <v>0.61</v>
       </c>
-      <c r="S38" s="20" t="s">
+      <c r="S38" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="T38" s="5">
+      <c r="T38" s="27">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
         <v>0.504</v>
       </c>
-      <c r="U38" s="5">
+      <c r="U38" s="27">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
         <v>0.92</v>
       </c>
-      <c r="V38" s="4">
+      <c r="V38" s="28">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
         <v>23.913</v>
       </c>
-      <c r="W38" s="13">
+      <c r="W38" s="25">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
         <v>20.541</v>
       </c>
-      <c r="X38" s="18">
+      <c r="X38" s="31">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
         <v>21.117000000000001</v>
       </c>
-      <c r="Y38" s="18">
+      <c r="Y38" s="31">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
         <v>26.475999999999999</v>
       </c>
-      <c r="Z38" s="18">
+      <c r="Z38" s="31">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
         <v>54</v>
       </c>
-      <c r="AA38" s="19">
+      <c r="AA38" s="32">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
         <v>21.311</v>
       </c>
@@ -4937,98 +4998,98 @@
       </c>
     </row>
     <row r="43" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="27">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
         <v>21.880765883376846</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="27">
         <f t="shared" ref="C43" si="255">D42/D43</f>
         <v>1.0813751087902523</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="28">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
         <v>22.98</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="24">
         <v>1</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="25">
         <v>10.82</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="24">
         <v>11.09</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="24">
         <v>1.07</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="29">
         <v>12.7</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="J43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K43" s="27">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
         <v>42.999999999999993</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43" s="27">
         <f t="shared" ref="L43" si="258">M42/M43</f>
         <v>1.0206185567010309</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M43" s="28">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
         <v>0.97</v>
       </c>
-      <c r="N43" s="9">
+      <c r="N43" s="24">
         <v>0.09</v>
       </c>
-      <c r="O43" s="13">
+      <c r="O43" s="25">
         <v>0.59</v>
       </c>
-      <c r="P43" s="9">
+      <c r="P43" s="24">
         <v>0.36</v>
       </c>
-      <c r="Q43" s="9">
+      <c r="Q43" s="24">
         <v>0.02</v>
       </c>
-      <c r="R43" s="10">
+      <c r="R43" s="29">
         <v>0.59</v>
       </c>
-      <c r="S43" s="12" t="s">
+      <c r="S43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="T43" s="5">
+      <c r="T43" s="27">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
         <v>0.50900000000000001</v>
       </c>
-      <c r="U43" s="5">
+      <c r="U43" s="27">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
         <v>1.06</v>
       </c>
-      <c r="V43" s="4">
+      <c r="V43" s="28">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
         <v>23.690999999999999</v>
       </c>
-      <c r="W43" s="9">
+      <c r="W43" s="24">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
         <v>11.111000000000001</v>
       </c>
-      <c r="X43" s="13">
+      <c r="X43" s="25">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
         <v>18.338999999999999</v>
       </c>
-      <c r="Y43" s="9">
+      <c r="Y43" s="24">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
         <v>30.806000000000001</v>
       </c>
-      <c r="Z43" s="9">
+      <c r="Z43" s="24">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
         <v>53.5</v>
       </c>
-      <c r="AA43" s="10">
+      <c r="AA43" s="29">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
         <v>21.524999999999999</v>
       </c>
@@ -5713,98 +5774,98 @@
       </c>
     </row>
     <row r="51" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="22">
         <f t="shared" ref="B51" si="360">D$2/D51</f>
         <v>32.608300907911797</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="22">
         <f t="shared" ref="C51" si="361">D50/D51</f>
         <v>1.1335927367055771</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="23">
         <f t="shared" ref="D51" si="362">SUM(F51:H51)</f>
         <v>15.42</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="24">
         <v>0.66</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="24">
         <v>7.76</v>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="25">
         <v>7.01</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="24">
         <v>0.65</v>
       </c>
-      <c r="I51" s="14">
+      <c r="I51" s="26">
         <v>4.96</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="22">
         <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
         <v>62.253731343283569</v>
       </c>
-      <c r="L51" s="2">
+      <c r="L51" s="22">
         <f t="shared" ref="L51:L53" si="364">M50/M51</f>
         <v>1.1044776119402984</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="23">
         <f t="shared" ref="M51:M53" si="365">SUM(O51:Q51)</f>
         <v>0.67</v>
       </c>
-      <c r="N51" s="9">
+      <c r="N51" s="24">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O51" s="9">
+      <c r="O51" s="24">
         <v>0.47</v>
       </c>
-      <c r="P51" s="13">
+      <c r="P51" s="25">
         <v>0.17</v>
       </c>
-      <c r="Q51" s="9">
+      <c r="Q51" s="24">
         <v>0.03</v>
       </c>
-      <c r="R51" s="14">
+      <c r="R51" s="26">
         <v>0.18</v>
       </c>
-      <c r="S51" s="12" t="s">
+      <c r="S51" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="T51" s="2">
+      <c r="T51" s="22">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="U51" s="2">
+      <c r="U51" s="22">
         <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
         <v>1.026</v>
       </c>
-      <c r="V51" s="6">
+      <c r="V51" s="23">
         <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
         <v>23.015000000000001</v>
       </c>
-      <c r="W51" s="9">
+      <c r="W51" s="24">
         <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
         <v>9.4290000000000003</v>
       </c>
-      <c r="X51" s="9">
+      <c r="X51" s="24">
         <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
         <v>16.510999999999999</v>
       </c>
-      <c r="Y51" s="13">
+      <c r="Y51" s="25">
         <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
         <v>41.234999999999999</v>
       </c>
-      <c r="Z51" s="9">
+      <c r="Z51" s="24">
         <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
         <v>21.667000000000002</v>
       </c>
-      <c r="AA51" s="14">
+      <c r="AA51" s="26">
         <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
         <v>27.556000000000001</v>
       </c>
@@ -6393,98 +6454,98 @@
       </c>
     </row>
     <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="22">
         <f t="shared" si="421"/>
         <v>52.051759834368525</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="22">
         <f t="shared" si="422"/>
         <v>1.0351966873706004</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="23">
         <f t="shared" si="423"/>
         <v>9.66</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="24">
         <v>0.4</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="25">
         <v>6.44</v>
       </c>
-      <c r="G58" s="13">
+      <c r="G58" s="25">
         <v>2.99</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="24">
         <v>0.23</v>
       </c>
-      <c r="I58" s="14">
+      <c r="I58" s="26">
         <v>2.4300000000000002</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K58" s="22">
         <f t="shared" si="424"/>
         <v>65.171874999999986</v>
       </c>
-      <c r="L58" s="2">
+      <c r="L58" s="22">
         <f t="shared" si="425"/>
         <v>1.015625</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="23">
         <f t="shared" si="426"/>
         <v>0.64</v>
       </c>
-      <c r="N58" s="9">
+      <c r="N58" s="24">
         <v>0.06</v>
       </c>
-      <c r="O58" s="13">
+      <c r="O58" s="25">
         <v>0.47</v>
       </c>
-      <c r="P58" s="13">
+      <c r="P58" s="25">
         <v>0.15</v>
       </c>
-      <c r="Q58" s="9">
+      <c r="Q58" s="24">
         <v>0.02</v>
       </c>
-      <c r="R58" s="14">
+      <c r="R58" s="26">
         <v>0.15</v>
       </c>
-      <c r="S58" s="12" t="s">
+      <c r="S58" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="T58" s="2">
+      <c r="T58" s="22">
         <f t="shared" si="427"/>
         <v>0.79900000000000004</v>
       </c>
-      <c r="U58" s="2">
+      <c r="U58" s="22">
         <f t="shared" si="428"/>
         <v>1.0189999999999999</v>
       </c>
-      <c r="V58" s="6">
+      <c r="V58" s="23">
         <f t="shared" si="429"/>
         <v>15.093999999999999</v>
       </c>
-      <c r="W58" s="9">
+      <c r="W58" s="24">
         <f t="shared" si="430"/>
         <v>6.6669999999999998</v>
       </c>
-      <c r="X58" s="13">
+      <c r="X58" s="25">
         <f t="shared" si="431"/>
         <v>13.702</v>
       </c>
-      <c r="Y58" s="13">
+      <c r="Y58" s="25">
         <f t="shared" si="432"/>
         <v>19.933</v>
       </c>
-      <c r="Z58" s="9">
+      <c r="Z58" s="24">
         <f t="shared" si="433"/>
         <v>11.5</v>
       </c>
-      <c r="AA58" s="14">
+      <c r="AA58" s="26">
         <f t="shared" si="434"/>
         <v>16.2</v>
       </c>
@@ -6787,21 +6848,21 @@
       </c>
       <c r="B62" s="5">
         <f t="shared" ref="B62" si="477">D$2/D62</f>
-        <v>58.399535423925656</v>
+        <v>58.672112018669772</v>
       </c>
       <c r="C62" s="5">
         <f t="shared" ref="C62" si="478">D61/D62</f>
-        <v>1.0081300813008129</v>
+        <v>1.0128354725787632</v>
       </c>
       <c r="D62" s="4">
         <f t="shared" ref="D62" si="479">SUM(F62:H62)</f>
-        <v>8.6100000000000012</v>
+        <v>8.57</v>
       </c>
       <c r="E62" s="9">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="F62" s="13">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="G62" s="9">
         <v>2.6</v>
@@ -6817,21 +6878,21 @@
       </c>
       <c r="K62" s="5">
         <f t="shared" ref="K62" si="480">M$2/M62</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" ref="L62" si="481">M61/M62</f>
-        <v>1.0327868852459015</v>
+        <v>1.0161290322580643</v>
       </c>
       <c r="M62" s="4">
         <f t="shared" ref="M62" si="482">SUM(O62:Q62)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N62" s="9">
         <v>0.06</v>
       </c>
       <c r="O62" s="13">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P62" s="9">
         <v>0.14000000000000001</v>
@@ -6847,23 +6908,23 @@
       </c>
       <c r="T62" s="5">
         <f t="shared" ref="T62" si="483">ROUND(B62/K62,3)</f>
-        <v>0.85399999999999998</v>
+        <v>0.872</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" ref="U62" si="484">ROUND(C62/L62,3)</f>
-        <v>0.97599999999999998</v>
+        <v>0.997</v>
       </c>
       <c r="V62" s="4">
         <f t="shared" ref="V62" si="485">ROUND(D62/M62,3)</f>
-        <v>14.115</v>
+        <v>13.823</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" ref="W62" si="486">ROUND(E62/N62,3)</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="X62" s="13">
         <f t="shared" ref="X62" si="487">ROUND(F62/O62,3)</f>
-        <v>12.843999999999999</v>
+        <v>12.478</v>
       </c>
       <c r="Y62" s="9">
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
@@ -6884,37 +6945,37 @@
       </c>
       <c r="B63" s="5">
         <f t="shared" ref="B63" si="491">D$2/D63</f>
-        <v>59.224970553592456</v>
+        <v>58.062355658198605</v>
       </c>
       <c r="C63" s="5">
         <f t="shared" ref="C63" si="492">D62/D63</f>
-        <v>1.0141342756183747</v>
+        <v>0.98960739030023093</v>
       </c>
       <c r="D63" s="4">
         <f t="shared" ref="D63" si="493">SUM(F63:H63)</f>
-        <v>8.49</v>
+        <v>8.66</v>
       </c>
       <c r="E63" s="9">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="F63" s="9">
-        <v>5.67</v>
+        <v>5.79</v>
       </c>
       <c r="G63" s="9">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="H63" s="9">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I63" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J63" s="20" t="s">
         <v>71</v>
       </c>
       <c r="K63" s="5">
         <f t="shared" ref="K63" si="494">M$2/M63</f>
-        <v>68.377049180327845</v>
+        <v>67.274193548387075</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" ref="L63" si="495">M62/M63</f>
@@ -6922,13 +6983,13 @@
       </c>
       <c r="M63" s="4">
         <f t="shared" ref="M63" si="496">SUM(O63:Q63)</f>
-        <v>0.6100000000000001</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="N63" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O63" s="9">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="P63" s="9">
         <v>0.14000000000000001</v>
@@ -6944,35 +7005,35 @@
       </c>
       <c r="T63" s="5">
         <f t="shared" ref="T63" si="497">ROUND(B63/K63,3)</f>
-        <v>0.86599999999999999</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" ref="U63" si="498">ROUND(C63/L63,3)</f>
-        <v>1.014</v>
+        <v>0.99</v>
       </c>
       <c r="V63" s="4">
         <f t="shared" ref="V63" si="499">ROUND(D63/M63,3)</f>
-        <v>13.917999999999999</v>
+        <v>13.968</v>
       </c>
       <c r="W63" s="9">
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
-        <v>5.5709999999999997</v>
+        <v>6.2859999999999996</v>
       </c>
       <c r="X63" s="18">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
-        <v>12.6</v>
+        <v>12.587</v>
       </c>
       <c r="Y63" s="9">
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
-        <v>18.5</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z63" s="18">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA63" s="10">
         <f t="shared" ref="AA63" si="504">ROUND(I63/R63,3)</f>
-        <v>15.462</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6981,30 +7042,30 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" ref="B64" si="505">D$2/D64</f>
-        <v>66.073587385019707</v>
+        <v>64.217113665389519</v>
       </c>
       <c r="C64" s="2">
         <f t="shared" ref="C64" si="506">D63/D64</f>
-        <v>1.1156373193166886</v>
+        <v>1.1060025542784164</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" ref="D64" si="507">SUM(F64:H64)</f>
-        <v>7.6099999999999994</v>
+        <v>7.83</v>
       </c>
       <c r="E64" s="9">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="F64" s="13">
-        <v>4.8</v>
+        <v>4.97</v>
       </c>
       <c r="G64" s="9">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="H64" s="9">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I64" s="10">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J64" s="20" t="s">
         <v>72</v>
@@ -7015,14 +7076,14 @@
       </c>
       <c r="L64" s="2">
         <f t="shared" ref="L64" si="509">M63/M64</f>
-        <v>1.1296296296296298</v>
+        <v>1.1481481481481484</v>
       </c>
       <c r="M64" s="6">
         <f t="shared" ref="M64" si="510">SUM(O64:Q64)</f>
         <v>0.54</v>
       </c>
       <c r="N64" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O64" s="13">
         <v>0.38</v>
@@ -7041,35 +7102,35 @@
       </c>
       <c r="T64" s="2">
         <f t="shared" ref="T64" si="511">ROUND(B64/K64,3)</f>
-        <v>0.85499999999999998</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="U64" s="2">
         <f t="shared" ref="U64" si="512">ROUND(C64/L64,3)</f>
-        <v>0.98799999999999999</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="V64" s="6">
         <f t="shared" ref="V64" si="513">ROUND(D64/M64,3)</f>
-        <v>14.093</v>
+        <v>14.5</v>
       </c>
       <c r="W64" s="9">
         <f t="shared" ref="W64" si="514">ROUND(E64/N64,3)</f>
-        <v>7.5</v>
+        <v>7.4290000000000003</v>
       </c>
       <c r="X64" s="13">
         <f t="shared" ref="X64" si="515">ROUND(F64/O64,3)</f>
-        <v>12.632</v>
+        <v>13.079000000000001</v>
       </c>
       <c r="Y64" s="9">
         <f t="shared" ref="Y64" si="516">ROUND(G64/P64,3)</f>
-        <v>18.5</v>
+        <v>18.786000000000001</v>
       </c>
       <c r="Z64" s="9">
         <f t="shared" ref="Z64" si="517">ROUND(H64/Q64,3)</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA64" s="10">
         <f t="shared" ref="AA64" si="518">ROUND(I64/R64,3)</f>
-        <v>15.462</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="65" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7078,30 +7139,30 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" ref="B65" si="519">D$2/D65</f>
-        <v>67.674293405114398</v>
+        <v>67.583333333333329</v>
       </c>
       <c r="C65" s="2">
         <f t="shared" ref="C65" si="520">D64/D65</f>
-        <v>1.0242261103633916</v>
+        <v>1.0524193548387097</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" ref="D65" si="521">SUM(F65:H65)</f>
-        <v>7.43</v>
+        <v>7.4399999999999995</v>
       </c>
       <c r="E65" s="9">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="F65" s="13">
-        <v>4.59</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G65" s="9">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H65" s="9">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I65" s="10">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>74</v>
@@ -7138,35 +7199,35 @@
       </c>
       <c r="T65" s="2">
         <f t="shared" ref="T65" si="525">ROUND(B65/K65,3)</f>
-        <v>0.79500000000000004</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="U65" s="2">
         <f t="shared" ref="U65" si="526">ROUND(C65/L65,3)</f>
-        <v>0.92900000000000005</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="V65" s="6">
         <f t="shared" ref="V65" si="527">ROUND(D65/M65,3)</f>
-        <v>15.163</v>
+        <v>15.183999999999999</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" ref="W65" si="528">ROUND(E65/N65,3)</f>
-        <v>7.1669999999999998</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X65" s="13">
         <f t="shared" ref="X65" si="529">ROUND(F65/O65,3)</f>
-        <v>13.5</v>
+        <v>13.529</v>
       </c>
       <c r="Y65" s="9">
         <f t="shared" ref="Y65" si="530">ROUND(G65/P65,3)</f>
-        <v>20</v>
+        <v>20.077000000000002</v>
       </c>
       <c r="Z65" s="9">
         <f t="shared" ref="Z65" si="531">ROUND(H65/Q65,3)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA65" s="10">
         <f t="shared" ref="AA65" si="532">ROUND(I65/R65,3)</f>
-        <v>15.615</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7175,30 +7236,30 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" ref="B66" si="533">D$2/D66</f>
-        <v>82.700657894736835</v>
+        <v>82.836902800658962</v>
       </c>
       <c r="C66" s="2">
         <f t="shared" ref="C66" si="534">D65/D66</f>
-        <v>1.2220394736842104</v>
+        <v>1.2257001647446457</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" ref="D66" si="535">SUM(F66:H66)</f>
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="E66" s="9">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="F66" s="13">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="G66" s="9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H66" s="9">
         <v>0.23</v>
       </c>
       <c r="I66" s="10">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>75</v>
@@ -7216,7 +7277,7 @@
         <v>0.47000000000000003</v>
       </c>
       <c r="N66" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O66" s="13">
         <v>0.31</v>
@@ -7235,27 +7296,27 @@
       </c>
       <c r="T66" s="2">
         <f t="shared" ref="T66" si="539">ROUND(B66/K66,3)</f>
-        <v>0.93200000000000005</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="U66" s="2">
         <f t="shared" ref="U66" si="540">ROUND(C66/L66,3)</f>
-        <v>1.1719999999999999</v>
+        <v>1.1759999999999999</v>
       </c>
       <c r="V66" s="6">
         <f t="shared" ref="V66" si="541">ROUND(D66/M66,3)</f>
-        <v>12.936</v>
+        <v>12.914999999999999</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" ref="W66" si="542">ROUND(E66/N66,3)</f>
-        <v>6</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X66" s="13">
         <f t="shared" ref="X66" si="543">ROUND(F66/O66,3)</f>
-        <v>10.484</v>
+        <v>10.387</v>
       </c>
       <c r="Y66" s="9">
         <f t="shared" ref="Y66" si="544">ROUND(G66/P66,3)</f>
-        <v>18.571000000000002</v>
+        <v>18.713999999999999</v>
       </c>
       <c r="Z66" s="9">
         <f t="shared" ref="Z66" si="545">ROUND(H66/Q66,3)</f>
@@ -7263,7 +7324,7 @@
       </c>
       <c r="AA66" s="10">
         <f t="shared" ref="AA66" si="546">ROUND(I66/R66,3)</f>
-        <v>15.538</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7272,27 +7333,27 @@
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67" si="547">D$2/D67</f>
-        <v>103.24845995893222</v>
+        <v>104.75416666666663</v>
       </c>
       <c r="C67" s="2">
         <f t="shared" ref="C67" si="548">D66/D67</f>
-        <v>1.2484599589322383</v>
+        <v>1.2645833333333332</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" ref="D67" si="549">SUM(F67:H67)</f>
-        <v>4.87</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="E67" s="9">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="F67" s="9">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="G67" s="13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H67" s="9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="I67" s="14">
         <v>0.44</v>
@@ -7313,7 +7374,7 @@
         <v>0.46</v>
       </c>
       <c r="N67" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O67" s="9">
         <v>0.31</v>
@@ -7332,31 +7393,31 @@
       </c>
       <c r="T67" s="2">
         <f t="shared" ref="T67" si="553">ROUND(B67/K67,3)</f>
-        <v>1.139</v>
+        <v>1.155</v>
       </c>
       <c r="U67" s="2">
         <f t="shared" ref="U67" si="554">ROUND(C67/L67,3)</f>
-        <v>1.222</v>
+        <v>1.238</v>
       </c>
       <c r="V67" s="6">
         <f t="shared" ref="V67" si="555">ROUND(D67/M67,3)</f>
-        <v>10.587</v>
+        <v>10.435</v>
       </c>
       <c r="W67" s="9">
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
-        <v>5.5709999999999997</v>
+        <v>7.1669999999999998</v>
       </c>
       <c r="X67" s="18">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
-        <v>10.645</v>
+        <v>10.355</v>
       </c>
       <c r="Y67" s="13">
         <f t="shared" ref="Y67" si="558">ROUND(G67/P67,3)</f>
-        <v>10.308</v>
+        <v>10.385</v>
       </c>
       <c r="Z67" s="9">
         <f t="shared" ref="Z67" si="559">ROUND(H67/Q67,3)</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA67" s="14">
         <f t="shared" ref="AA67" si="560">ROUND(I67/R67,3)</f>
@@ -7364,98 +7425,98 @@
       </c>
     </row>
     <row r="68" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="27">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>103.67422680412371</v>
-      </c>
-      <c r="C68" s="5">
+        <v>105.19246861924684</v>
+      </c>
+      <c r="C68" s="27">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>1.0041237113402062</v>
-      </c>
-      <c r="D68" s="4">
+        <v>1.0041841004184102</v>
+      </c>
+      <c r="D68" s="28">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="E68" s="18">
-        <v>0.46</v>
-      </c>
-      <c r="F68" s="18">
-        <v>3.3</v>
-      </c>
-      <c r="G68" s="18">
+        <v>4.78</v>
+      </c>
+      <c r="E68" s="31">
+        <v>0.4</v>
+      </c>
+      <c r="F68" s="31">
+        <v>3.22</v>
+      </c>
+      <c r="G68" s="31">
         <v>1.34</v>
       </c>
-      <c r="H68" s="13">
-        <v>0.21</v>
-      </c>
-      <c r="I68" s="19">
+      <c r="H68" s="25">
+        <v>0.22</v>
+      </c>
+      <c r="I68" s="32">
         <v>0.44</v>
       </c>
-      <c r="J68" s="20" t="s">
+      <c r="J68" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="K68" s="5">
+      <c r="K68" s="27">
         <f t="shared" ref="K68" si="564">M$2/M68</f>
         <v>90.673913043478237</v>
       </c>
-      <c r="L68" s="5">
+      <c r="L68" s="27">
         <f t="shared" ref="L68" si="565">M67/M68</f>
         <v>1</v>
       </c>
-      <c r="M68" s="4">
+      <c r="M68" s="28">
         <f t="shared" ref="M68" si="566">SUM(O68:Q68)</f>
         <v>0.46</v>
       </c>
-      <c r="N68" s="18">
-        <v>0.06</v>
-      </c>
-      <c r="O68" s="18">
+      <c r="N68" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="O68" s="31">
         <v>0.31</v>
       </c>
-      <c r="P68" s="18">
+      <c r="P68" s="31">
         <v>0.13</v>
       </c>
-      <c r="Q68" s="13">
+      <c r="Q68" s="25">
         <v>0.02</v>
       </c>
-      <c r="R68" s="19">
+      <c r="R68" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S68" s="20" t="s">
+      <c r="S68" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="T68" s="5">
+      <c r="T68" s="27">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.143</v>
-      </c>
-      <c r="U68" s="5">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="U68" s="27">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
         <v>1.004</v>
       </c>
-      <c r="V68" s="4">
+      <c r="V68" s="28">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.542999999999999</v>
-      </c>
-      <c r="W68" s="18">
+        <v>10.391</v>
+      </c>
+      <c r="W68" s="31">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
-        <v>7.6669999999999998</v>
-      </c>
-      <c r="X68" s="18">
+        <v>4</v>
+      </c>
+      <c r="X68" s="31">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.645</v>
-      </c>
-      <c r="Y68" s="18">
+        <v>10.387</v>
+      </c>
+      <c r="Y68" s="31">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
         <v>10.308</v>
       </c>
-      <c r="Z68" s="13">
+      <c r="Z68" s="25">
         <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AA68" s="19">
+        <v>11</v>
+      </c>
+      <c r="AA68" s="32">
         <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
         <v>6.2859999999999996</v>
       </c>
@@ -7467,27 +7528,27 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" ref="B69" si="575">D$2/D69</f>
-        <v>104.10351966873705</v>
+        <v>105.19246861924684</v>
       </c>
       <c r="C69" s="2">
         <f t="shared" ref="C69" si="576">D68/D69</f>
-        <v>1.0041407867494823</v>
+        <v>1</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="E69" s="9">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="F69" s="13">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="G69" s="13">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H69" s="9">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="I69" s="14">
         <v>0.44</v>
@@ -7497,21 +7558,21 @@
       </c>
       <c r="K69" s="2">
         <f t="shared" ref="K69" si="578">M$2/M69</f>
-        <v>119.17142857142856</v>
+        <v>115.8611111111111</v>
       </c>
       <c r="L69" s="2">
         <f t="shared" ref="L69" si="579">M68/M69</f>
-        <v>1.3142857142857145</v>
+        <v>1.2777777777777779</v>
       </c>
       <c r="M69" s="6">
         <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="N69" s="9">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O69" s="13">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="P69" s="13">
         <v>0.09</v>
@@ -7527,31 +7588,31 @@
       </c>
       <c r="T69" s="2">
         <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
-        <v>0.874</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="U69" s="2">
         <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
-        <v>0.76400000000000001</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="V69" s="6">
         <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
-        <v>13.8</v>
+        <v>13.278</v>
       </c>
       <c r="W69" s="9">
         <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
-        <v>6.1669999999999998</v>
+        <v>6.4290000000000003</v>
       </c>
       <c r="X69" s="13">
         <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
-        <v>13.583</v>
+        <v>12.96</v>
       </c>
       <c r="Y69" s="13">
         <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
-        <v>15.111000000000001</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="Z69" s="9">
         <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA69" s="14">
         <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
@@ -7564,21 +7625,21 @@
       </c>
       <c r="B70" s="5">
         <f t="shared" ref="B70" si="589">D$2/D70</f>
-        <v>104.97286012526095</v>
+        <v>105.19246861924684</v>
       </c>
       <c r="C70" s="5">
         <f t="shared" ref="C70" si="590">D69/D70</f>
-        <v>1.0083507306889352</v>
+        <v>1</v>
       </c>
       <c r="D70" s="4">
         <f t="shared" ref="D70" si="591">SUM(F70:H70)</f>
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="E70" s="18">
         <v>0.4</v>
       </c>
       <c r="F70" s="18">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="G70" s="18">
         <v>1.34</v>
@@ -7598,14 +7659,14 @@
       </c>
       <c r="L70" s="5">
         <f t="shared" ref="L70" si="593">M69/M70</f>
-        <v>0.97222222222222221</v>
+        <v>1</v>
       </c>
       <c r="M70" s="4">
         <f t="shared" ref="M70" si="594">SUM(O70:Q70)</f>
         <v>0.36</v>
       </c>
       <c r="N70" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O70" s="18">
         <v>0.25</v>
@@ -7624,23 +7685,23 @@
       </c>
       <c r="T70" s="5">
         <f t="shared" ref="T70" si="595">ROUND(B70/K70,3)</f>
-        <v>0.90600000000000003</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" ref="U70" si="596">ROUND(C70/L70,3)</f>
-        <v>1.0369999999999999</v>
+        <v>1</v>
       </c>
       <c r="V70" s="4">
         <f t="shared" ref="V70" si="597">ROUND(D70/M70,3)</f>
-        <v>13.305999999999999</v>
+        <v>13.278</v>
       </c>
       <c r="W70" s="18">
         <f t="shared" ref="W70" si="598">ROUND(E70/N70,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X70" s="18">
         <f t="shared" ref="X70" si="599">ROUND(F70/O70,3)</f>
-        <v>12.92</v>
+        <v>12.88</v>
       </c>
       <c r="Y70" s="18">
         <f t="shared" ref="Y70" si="600">ROUND(G70/P70,3)</f>
@@ -7662,21 +7723,21 @@
       </c>
       <c r="B71" s="2">
         <f t="shared" ref="B71" si="603">D$2/D71</f>
-        <v>116.39351851851852</v>
+        <v>116.12471131639721</v>
       </c>
       <c r="C71" s="2">
         <f t="shared" ref="C71" si="604">D70/D71</f>
-        <v>1.1087962962962965</v>
+        <v>1.1039260969976905</v>
       </c>
       <c r="D71" s="6">
         <f t="shared" ref="D71" si="605">SUM(F71:H71)</f>
-        <v>4.3199999999999994</v>
+        <v>4.33</v>
       </c>
       <c r="E71" s="9">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="F71" s="13">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="G71" s="9">
         <v>1.34</v>
@@ -7703,7 +7764,7 @@
         <v>0.33</v>
       </c>
       <c r="N71" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O71" s="13">
         <v>0.22</v>
@@ -7722,23 +7783,23 @@
       </c>
       <c r="T71" s="2">
         <f t="shared" ref="T71" si="609">ROUND(B71/K71,3)</f>
-        <v>0.92100000000000004</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="U71" s="2">
         <f t="shared" ref="U71" si="610">ROUND(C71/L71,3)</f>
-        <v>1.016</v>
+        <v>1.012</v>
       </c>
       <c r="V71" s="6">
         <f t="shared" ref="V71" si="611">ROUND(D71/M71,3)</f>
-        <v>13.090999999999999</v>
+        <v>13.121</v>
       </c>
       <c r="W71" s="9">
         <f t="shared" ref="W71" si="612">ROUND(E71/N71,3)</f>
-        <v>5.7140000000000004</v>
+        <v>7.3330000000000002</v>
       </c>
       <c r="X71" s="13">
         <f t="shared" ref="X71" si="613">ROUND(F71/O71,3)</f>
-        <v>12.545</v>
+        <v>12.590999999999999</v>
       </c>
       <c r="Y71" s="9">
         <f t="shared" ref="Y71" si="614">ROUND(G71/P71,3)</f>
@@ -7759,27 +7820,27 @@
       </c>
       <c r="B72" s="2">
         <f t="shared" ref="B72" si="617">D$2/D72</f>
-        <v>121.74818401937044</v>
+        <v>122.04368932038832</v>
       </c>
       <c r="C72" s="2">
         <f t="shared" ref="C72" si="618">D71/D72</f>
-        <v>1.0460048426150119</v>
+        <v>1.0509708737864079</v>
       </c>
       <c r="D72" s="6">
         <f t="shared" ref="D72" si="619">SUM(F72:H72)</f>
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="E72" s="9">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="F72" s="9">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="G72" s="13">
-        <v>1.1299999999999999</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H72" s="9">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="I72" s="14">
         <v>0.36</v>
@@ -7819,31 +7880,31 @@
       </c>
       <c r="T72" s="2">
         <f t="shared" ref="T72" si="623">ROUND(B72/K72,3)</f>
-        <v>0.93400000000000005</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="U72" s="2">
         <f t="shared" ref="U72" si="624">ROUND(C72/L72,3)</f>
-        <v>1.014</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="V72" s="6">
         <f t="shared" ref="V72" si="625">ROUND(D72/M72,3)</f>
-        <v>12.906000000000001</v>
+        <v>12.875</v>
       </c>
       <c r="W72" s="9">
         <f t="shared" ref="W72" si="626">ROUND(E72/N72,3)</f>
-        <v>6.7140000000000004</v>
+        <v>5.8570000000000002</v>
       </c>
       <c r="X72" s="9">
         <f t="shared" ref="X72" si="627">ROUND(F72/O72,3)</f>
-        <v>12.682</v>
+        <v>12.727</v>
       </c>
       <c r="Y72" s="13">
         <f t="shared" ref="Y72" si="628">ROUND(G72/P72,3)</f>
-        <v>14.125</v>
+        <v>14</v>
       </c>
       <c r="Z72" s="9">
         <f t="shared" ref="Z72" si="629">ROUND(H72/Q72,3)</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA72" s="14">
         <f t="shared" ref="AA72" si="630">ROUND(I72/R72,3)</f>
@@ -7856,21 +7917,21 @@
       </c>
       <c r="B73" s="5">
         <f t="shared" ref="B73" si="631">D$2/D73</f>
-        <v>122.34063260340631</v>
+        <v>122.6390243902439</v>
       </c>
       <c r="C73" s="5">
         <f t="shared" ref="C73" si="632">D72/D73</f>
-        <v>1.0048661800486618</v>
+        <v>1.0048780487804878</v>
       </c>
       <c r="D73" s="4">
         <f t="shared" ref="D73" si="633">SUM(F73:H73)</f>
-        <v>4.1100000000000003</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E73" s="18">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F73" s="18">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="G73" s="18">
         <v>1.1299999999999999</v>
@@ -7897,7 +7958,7 @@
         <v>0.32</v>
       </c>
       <c r="N73" s="18">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O73" s="18">
         <v>0.22</v>
@@ -7916,7 +7977,7 @@
       </c>
       <c r="T73" s="5">
         <f t="shared" ref="T73" si="637">ROUND(B73/K73,3)</f>
-        <v>0.93899999999999995</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="U73" s="5">
         <f t="shared" ref="U73" si="638">ROUND(C73/L73,3)</f>
@@ -7924,15 +7985,15 @@
       </c>
       <c r="V73" s="4">
         <f t="shared" ref="V73" si="639">ROUND(D73/M73,3)</f>
-        <v>12.843999999999999</v>
+        <v>12.813000000000001</v>
       </c>
       <c r="W73" s="18">
         <f t="shared" ref="W73" si="640">ROUND(E73/N73,3)</f>
-        <v>6.5</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X73" s="18">
         <f t="shared" ref="X73" si="641">ROUND(F73/O73,3)</f>
-        <v>12.590999999999999</v>
+        <v>12.545</v>
       </c>
       <c r="Y73" s="18">
         <f t="shared" ref="Y73" si="642">ROUND(G73/P73,3)</f>
@@ -7954,21 +8015,21 @@
       </c>
       <c r="B74" s="5">
         <f t="shared" ref="B74" si="645">D$2/D74</f>
-        <v>122.04368932038832</v>
+        <v>120.87019230769229</v>
       </c>
       <c r="C74" s="5">
         <f t="shared" ref="C74" si="646">D73/D74</f>
-        <v>0.99757281553398058</v>
+        <v>0.98557692307692291</v>
       </c>
       <c r="D74" s="4">
         <f t="shared" ref="D74" si="647">SUM(F74:H74)</f>
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="E74" s="9">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F74" s="9">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="G74" s="9">
         <v>1.1299999999999999</v>
@@ -7977,28 +8038,28 @@
         <v>0.22</v>
       </c>
       <c r="I74" s="10">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J74" s="20" t="s">
         <v>83</v>
       </c>
       <c r="K74" s="5">
-        <f t="shared" ref="K74" si="648">M$2/M74</f>
-        <v>130.34374999999997</v>
+        <f t="shared" ref="K74:K75" si="648">M$2/M74</f>
+        <v>134.54838709677418</v>
       </c>
       <c r="L74" s="5">
-        <f t="shared" ref="L74" si="649">M73/M74</f>
-        <v>1</v>
+        <f t="shared" ref="L74:L75" si="649">M73/M74</f>
+        <v>1.032258064516129</v>
       </c>
       <c r="M74" s="4">
-        <f t="shared" ref="M74" si="650">SUM(O74:Q74)</f>
-        <v>0.32</v>
+        <f t="shared" ref="M74:M75" si="650">SUM(O74:Q74)</f>
+        <v>0.31</v>
       </c>
       <c r="N74" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O74" s="9">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="P74" s="9">
         <v>0.08</v>
@@ -8014,23 +8075,23 @@
       </c>
       <c r="T74" s="5">
         <f t="shared" ref="T74" si="651">ROUND(B74/K74,3)</f>
-        <v>0.93600000000000005</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="U74" s="5">
         <f t="shared" ref="U74" si="652">ROUND(C74/L74,3)</f>
-        <v>0.998</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="V74" s="4">
         <f t="shared" ref="V74" si="653">ROUND(D74/M74,3)</f>
-        <v>12.875</v>
+        <v>13.419</v>
       </c>
       <c r="W74" s="18">
         <f t="shared" ref="W74" si="654">ROUND(E74/N74,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X74" s="18">
         <f t="shared" ref="X74" si="655">ROUND(F74/O74,3)</f>
-        <v>12.590999999999999</v>
+        <v>13.381</v>
       </c>
       <c r="Y74" s="18">
         <f t="shared" ref="Y74" si="656">ROUND(G74/P74,3)</f>
@@ -8042,7 +8103,104 @@
       </c>
       <c r="AA74" s="19">
         <f t="shared" ref="AA74" si="658">ROUND(I74/R74,3)</f>
-        <v>7.2</v>
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="22">
+        <f t="shared" ref="B75" si="659">D$2/D75</f>
+        <v>137.00817438692096</v>
+      </c>
+      <c r="C75" s="22">
+        <f t="shared" ref="C75" si="660">D74/D75</f>
+        <v>1.1335149863760217</v>
+      </c>
+      <c r="D75" s="23">
+        <f t="shared" ref="D75" si="661">SUM(F75:H75)</f>
+        <v>3.6700000000000004</v>
+      </c>
+      <c r="E75" s="25">
+        <v>0.38</v>
+      </c>
+      <c r="F75" s="25">
+        <v>2.66</v>
+      </c>
+      <c r="G75" s="25">
+        <v>0.91</v>
+      </c>
+      <c r="H75" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="I75" s="26">
+        <v>0.21</v>
+      </c>
+      <c r="J75" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="K75" s="22">
+        <f t="shared" si="648"/>
+        <v>139.0333333333333</v>
+      </c>
+      <c r="L75" s="22">
+        <f t="shared" si="649"/>
+        <v>1.0333333333333332</v>
+      </c>
+      <c r="M75" s="23">
+        <f t="shared" si="650"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N75" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="O75" s="25">
+        <v>0.22</v>
+      </c>
+      <c r="P75" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="Q75" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="R75" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="S75" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="T75" s="22">
+        <f t="shared" ref="T75" si="662">ROUND(B75/K75,3)</f>
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="U75" s="22">
+        <f t="shared" ref="U75" si="663">ROUND(C75/L75,3)</f>
+        <v>1.097</v>
+      </c>
+      <c r="V75" s="23">
+        <f t="shared" ref="V75" si="664">ROUND(D75/M75,3)</f>
+        <v>12.233000000000001</v>
+      </c>
+      <c r="W75" s="25">
+        <f t="shared" ref="W75" si="665">ROUND(E75/N75,3)</f>
+        <v>6.3330000000000002</v>
+      </c>
+      <c r="X75" s="25">
+        <f t="shared" ref="X75" si="666">ROUND(F75/O75,3)</f>
+        <v>12.090999999999999</v>
+      </c>
+      <c r="Y75" s="25">
+        <f t="shared" ref="Y75" si="667">ROUND(G75/P75,3)</f>
+        <v>15.167</v>
+      </c>
+      <c r="Z75" s="25">
+        <f t="shared" ref="Z75" si="668">ROUND(H75/Q75,3)</f>
+        <v>5</v>
+      </c>
+      <c r="AA75" s="26">
+        <f t="shared" ref="AA75" si="669">ROUND(I75/R75,3)</f>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BB5EA8-E05D-4D38-BE51-F08EF1C99F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7A296E-1F31-49DF-9713-7EBC6044198E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="86">
   <si>
     <t>H23</t>
   </si>
@@ -345,6 +345,10 @@
   </si>
   <si>
     <t>H95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H96</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -421,7 +425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +435,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,7 +505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -609,6 +619,45 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -924,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB76"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -7430,51 +7479,51 @@
       </c>
       <c r="B68" s="27">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>105.19246861924684</v>
+        <v>106.98297872340424</v>
       </c>
       <c r="C68" s="27">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>1.0041841004184102</v>
+        <v>1.021276595744681</v>
       </c>
       <c r="D68" s="28">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="E68" s="31">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F68" s="31">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="G68" s="31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H68" s="25">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I68" s="32">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J68" s="30" t="s">
         <v>77</v>
       </c>
       <c r="K68" s="27">
         <f t="shared" ref="K68" si="564">M$2/M68</f>
-        <v>90.673913043478237</v>
+        <v>92.688888888888869</v>
       </c>
       <c r="L68" s="27">
         <f t="shared" ref="L68" si="565">M67/M68</f>
-        <v>1</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="M68" s="28">
         <f t="shared" ref="M68" si="566">SUM(O68:Q68)</f>
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="N68" s="31">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O68" s="31">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="P68" s="31">
         <v>0.13</v>
@@ -7490,35 +7539,35 @@
       </c>
       <c r="T68" s="27">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.1599999999999999</v>
+        <v>1.1539999999999999</v>
       </c>
       <c r="U68" s="27">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
-        <v>1.004</v>
+        <v>0.999</v>
       </c>
       <c r="V68" s="28">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.391</v>
+        <v>10.444000000000001</v>
       </c>
       <c r="W68" s="31">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
-        <v>4</v>
+        <v>5.5709999999999997</v>
       </c>
       <c r="X68" s="31">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.387</v>
+        <v>10.532999999999999</v>
       </c>
       <c r="Y68" s="31">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
-        <v>10.308</v>
+        <v>10.231</v>
       </c>
       <c r="Z68" s="25">
         <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA68" s="32">
         <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
-        <v>6.2859999999999996</v>
+        <v>6.1429999999999998</v>
       </c>
       <c r="AB68" s="20"/>
     </row>
@@ -7528,30 +7577,30 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" ref="B69" si="575">D$2/D69</f>
-        <v>105.19246861924684</v>
+        <v>106.52966101694915</v>
       </c>
       <c r="C69" s="2">
         <f t="shared" ref="C69" si="576">D68/D69</f>
-        <v>1</v>
+        <v>0.9957627118644069</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="E69" s="9">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="F69" s="13">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="G69" s="13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H69" s="9">
         <v>0.2</v>
       </c>
       <c r="I69" s="14">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>78</v>
@@ -7562,14 +7611,14 @@
       </c>
       <c r="L69" s="2">
         <f t="shared" ref="L69" si="579">M68/M69</f>
-        <v>1.2777777777777779</v>
+        <v>1.25</v>
       </c>
       <c r="M69" s="6">
         <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
         <v>0.36</v>
       </c>
       <c r="N69" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O69" s="13">
         <v>0.25</v>
@@ -7588,27 +7637,27 @@
       </c>
       <c r="T69" s="2">
         <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
-        <v>0.90800000000000003</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="U69" s="2">
         <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
-        <v>0.78300000000000003</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="V69" s="6">
         <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
-        <v>13.278</v>
+        <v>13.111000000000001</v>
       </c>
       <c r="W69" s="9">
         <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
-        <v>6.4290000000000003</v>
+        <v>7.1669999999999998</v>
       </c>
       <c r="X69" s="13">
         <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
-        <v>12.96</v>
+        <v>12.76</v>
       </c>
       <c r="Y69" s="13">
         <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
-        <v>14.888999999999999</v>
+        <v>14.778</v>
       </c>
       <c r="Z69" s="9">
         <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
@@ -7616,7 +7665,7 @@
       </c>
       <c r="AA69" s="14">
         <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
-        <v>8.8000000000000007</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="70" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7625,51 +7674,51 @@
       </c>
       <c r="B70" s="5">
         <f t="shared" ref="B70" si="589">D$2/D70</f>
-        <v>105.19246861924684</v>
+        <v>106.30443974630019</v>
       </c>
       <c r="C70" s="5">
         <f t="shared" ref="C70" si="590">D69/D70</f>
-        <v>1</v>
+        <v>0.99788583509513729</v>
       </c>
       <c r="D70" s="4">
         <f t="shared" ref="D70" si="591">SUM(F70:H70)</f>
-        <v>4.78</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="E70" s="18">
         <v>0.4</v>
       </c>
       <c r="F70" s="18">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="G70" s="18">
         <v>1.34</v>
       </c>
       <c r="H70" s="18">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="I70" s="19">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J70" s="20" t="s">
         <v>79</v>
       </c>
       <c r="K70" s="5">
         <f t="shared" ref="K70" si="592">M$2/M70</f>
-        <v>115.8611111111111</v>
+        <v>119.17142857142856</v>
       </c>
       <c r="L70" s="5">
         <f t="shared" ref="L70" si="593">M69/M70</f>
-        <v>1</v>
+        <v>1.0285714285714287</v>
       </c>
       <c r="M70" s="4">
         <f t="shared" ref="M70" si="594">SUM(O70:Q70)</f>
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="N70" s="18">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O70" s="18">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="P70" s="18">
         <v>0.09</v>
@@ -7685,23 +7734,23 @@
       </c>
       <c r="T70" s="5">
         <f t="shared" ref="T70" si="595">ROUND(B70/K70,3)</f>
-        <v>0.90800000000000003</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" ref="U70" si="596">ROUND(C70/L70,3)</f>
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V70" s="4">
         <f t="shared" ref="V70" si="597">ROUND(D70/M70,3)</f>
-        <v>13.278</v>
+        <v>13.513999999999999</v>
       </c>
       <c r="W70" s="18">
         <f t="shared" ref="W70" si="598">ROUND(E70/N70,3)</f>
-        <v>6.6669999999999998</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X70" s="18">
         <f t="shared" ref="X70" si="599">ROUND(F70/O70,3)</f>
-        <v>12.88</v>
+        <v>13.292</v>
       </c>
       <c r="Y70" s="18">
         <f t="shared" ref="Y70" si="600">ROUND(G70/P70,3)</f>
@@ -7709,499 +7758,598 @@
       </c>
       <c r="Z70" s="18">
         <f t="shared" ref="Z70" si="601">ROUND(H70/Q70,3)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA70" s="19">
         <f t="shared" ref="AA70" si="602">ROUND(I70/R70,3)</f>
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AB70" s="20"/>
     </row>
     <row r="71" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="41">
         <f t="shared" ref="B71" si="603">D$2/D71</f>
-        <v>116.12471131639721</v>
-      </c>
-      <c r="C71" s="2">
+        <v>115.85714285714285</v>
+      </c>
+      <c r="C71" s="41">
         <f t="shared" ref="C71" si="604">D70/D71</f>
-        <v>1.1039260969976905</v>
-      </c>
-      <c r="D71" s="6">
+        <v>1.0898617511520738</v>
+      </c>
+      <c r="D71" s="42">
         <f t="shared" ref="D71" si="605">SUM(F71:H71)</f>
-        <v>4.33</v>
-      </c>
-      <c r="E71" s="9">
+        <v>4.34</v>
+      </c>
+      <c r="E71" s="43">
+        <v>0.39</v>
+      </c>
+      <c r="F71" s="44">
+        <v>2.78</v>
+      </c>
+      <c r="G71" s="43">
+        <v>1.34</v>
+      </c>
+      <c r="H71" s="43">
+        <v>0.22</v>
+      </c>
+      <c r="I71" s="45">
         <v>0.44</v>
       </c>
-      <c r="F71" s="13">
-        <v>2.77</v>
-      </c>
-      <c r="G71" s="9">
-        <v>1.34</v>
-      </c>
-      <c r="H71" s="9">
-        <v>0.22</v>
-      </c>
-      <c r="I71" s="10">
-        <v>0.43</v>
-      </c>
-      <c r="J71" s="20" t="s">
+      <c r="J71" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="K71" s="2">
+      <c r="K71" s="41">
         <f t="shared" ref="K71" si="606">M$2/M71</f>
         <v>126.39393939393936</v>
       </c>
-      <c r="L71" s="2">
+      <c r="L71" s="41">
         <f t="shared" ref="L71" si="607">M70/M71</f>
-        <v>1.0909090909090908</v>
-      </c>
-      <c r="M71" s="6">
+        <v>1.0606060606060606</v>
+      </c>
+      <c r="M71" s="42">
         <f t="shared" ref="M71" si="608">SUM(O71:Q71)</f>
         <v>0.33</v>
       </c>
-      <c r="N71" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="O71" s="13">
+      <c r="N71" s="43">
+        <v>0.09</v>
+      </c>
+      <c r="O71" s="44">
         <v>0.22</v>
       </c>
-      <c r="P71" s="9">
+      <c r="P71" s="43">
         <v>0.09</v>
       </c>
-      <c r="Q71" s="9">
+      <c r="Q71" s="43">
         <v>0.02</v>
       </c>
-      <c r="R71" s="10">
+      <c r="R71" s="45">
         <v>0.05</v>
       </c>
-      <c r="S71" s="20" t="s">
+      <c r="S71" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="T71" s="2">
+      <c r="T71" s="41">
         <f t="shared" ref="T71" si="609">ROUND(B71/K71,3)</f>
-        <v>0.91900000000000004</v>
-      </c>
-      <c r="U71" s="2">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="U71" s="41">
         <f t="shared" ref="U71" si="610">ROUND(C71/L71,3)</f>
-        <v>1.012</v>
-      </c>
-      <c r="V71" s="6">
+        <v>1.028</v>
+      </c>
+      <c r="V71" s="42">
         <f t="shared" ref="V71" si="611">ROUND(D71/M71,3)</f>
-        <v>13.121</v>
-      </c>
-      <c r="W71" s="9">
+        <v>13.151999999999999</v>
+      </c>
+      <c r="W71" s="43">
         <f t="shared" ref="W71" si="612">ROUND(E71/N71,3)</f>
-        <v>7.3330000000000002</v>
-      </c>
-      <c r="X71" s="13">
+        <v>4.3330000000000002</v>
+      </c>
+      <c r="X71" s="44">
         <f t="shared" ref="X71" si="613">ROUND(F71/O71,3)</f>
-        <v>12.590999999999999</v>
-      </c>
-      <c r="Y71" s="9">
+        <v>12.635999999999999</v>
+      </c>
+      <c r="Y71" s="43">
         <f t="shared" ref="Y71" si="614">ROUND(G71/P71,3)</f>
         <v>14.888999999999999</v>
       </c>
-      <c r="Z71" s="9">
+      <c r="Z71" s="43">
         <f t="shared" ref="Z71" si="615">ROUND(H71/Q71,3)</f>
         <v>11</v>
       </c>
-      <c r="AA71" s="10">
+      <c r="AA71" s="45">
         <f t="shared" ref="AA71" si="616">ROUND(I71/R71,3)</f>
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="72" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="41">
         <f t="shared" ref="B72" si="617">D$2/D72</f>
-        <v>122.04368932038832</v>
-      </c>
-      <c r="C72" s="2">
+        <v>123.54299754299753</v>
+      </c>
+      <c r="C72" s="41">
         <f t="shared" ref="C72" si="618">D71/D72</f>
-        <v>1.0509708737864079</v>
-      </c>
-      <c r="D72" s="6">
+        <v>1.0663390663390662</v>
+      </c>
+      <c r="D72" s="42">
         <f t="shared" ref="D72" si="619">SUM(F72:H72)</f>
-        <v>4.12</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0.41</v>
-      </c>
-      <c r="F72" s="9">
-        <v>2.8</v>
-      </c>
-      <c r="G72" s="13">
+        <v>4.07</v>
+      </c>
+      <c r="E72" s="43">
+        <v>0.39</v>
+      </c>
+      <c r="F72" s="43">
+        <v>2.74</v>
+      </c>
+      <c r="G72" s="44">
         <v>1.1200000000000001</v>
       </c>
-      <c r="H72" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="I72" s="14">
+      <c r="H72" s="43">
+        <v>0.21</v>
+      </c>
+      <c r="I72" s="46">
         <v>0.36</v>
       </c>
-      <c r="J72" s="20" t="s">
+      <c r="J72" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="K72" s="2">
+      <c r="K72" s="41">
         <f t="shared" ref="K72" si="620">M$2/M72</f>
         <v>130.34374999999997</v>
       </c>
-      <c r="L72" s="2">
+      <c r="L72" s="41">
         <f t="shared" ref="L72" si="621">M71/M72</f>
         <v>1.03125</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="42">
         <f t="shared" ref="M72" si="622">SUM(O72:Q72)</f>
         <v>0.32</v>
       </c>
-      <c r="N72" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O72" s="9">
+      <c r="N72" s="43">
+        <v>0.06</v>
+      </c>
+      <c r="O72" s="43">
         <v>0.22</v>
       </c>
-      <c r="P72" s="13">
+      <c r="P72" s="44">
         <v>0.08</v>
       </c>
-      <c r="Q72" s="9">
+      <c r="Q72" s="43">
         <v>0.02</v>
       </c>
-      <c r="R72" s="14">
+      <c r="R72" s="46">
         <v>0.05</v>
       </c>
-      <c r="S72" s="20" t="s">
+      <c r="S72" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="T72" s="2">
+      <c r="T72" s="41">
         <f t="shared" ref="T72" si="623">ROUND(B72/K72,3)</f>
-        <v>0.93600000000000005</v>
-      </c>
-      <c r="U72" s="2">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="U72" s="41">
         <f t="shared" ref="U72" si="624">ROUND(C72/L72,3)</f>
-        <v>1.0189999999999999</v>
-      </c>
-      <c r="V72" s="6">
+        <v>1.034</v>
+      </c>
+      <c r="V72" s="42">
         <f t="shared" ref="V72" si="625">ROUND(D72/M72,3)</f>
-        <v>12.875</v>
-      </c>
-      <c r="W72" s="9">
+        <v>12.718999999999999</v>
+      </c>
+      <c r="W72" s="43">
         <f t="shared" ref="W72" si="626">ROUND(E72/N72,3)</f>
-        <v>5.8570000000000002</v>
-      </c>
-      <c r="X72" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="X72" s="43">
         <f t="shared" ref="X72" si="627">ROUND(F72/O72,3)</f>
-        <v>12.727</v>
-      </c>
-      <c r="Y72" s="13">
+        <v>12.455</v>
+      </c>
+      <c r="Y72" s="44">
         <f t="shared" ref="Y72" si="628">ROUND(G72/P72,3)</f>
         <v>14</v>
       </c>
-      <c r="Z72" s="9">
+      <c r="Z72" s="43">
         <f t="shared" ref="Z72" si="629">ROUND(H72/Q72,3)</f>
-        <v>10</v>
-      </c>
-      <c r="AA72" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="AA72" s="46">
         <f t="shared" ref="AA72" si="630">ROUND(I72/R72,3)</f>
         <v>7.2</v>
       </c>
     </row>
     <row r="73" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="47">
         <f t="shared" ref="B73" si="631">D$2/D73</f>
-        <v>122.6390243902439</v>
-      </c>
-      <c r="C73" s="5">
+        <v>123.24019607843135</v>
+      </c>
+      <c r="C73" s="47">
         <f t="shared" ref="C73" si="632">D72/D73</f>
-        <v>1.0048780487804878</v>
-      </c>
-      <c r="D73" s="4">
+        <v>0.99754901960784315</v>
+      </c>
+      <c r="D73" s="48">
         <f t="shared" ref="D73" si="633">SUM(F73:H73)</f>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="E73" s="18">
+        <v>4.08</v>
+      </c>
+      <c r="E73" s="49">
         <v>0.4</v>
       </c>
-      <c r="F73" s="18">
-        <v>2.76</v>
-      </c>
-      <c r="G73" s="18">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="H73" s="18">
+      <c r="F73" s="49">
+        <v>2.75</v>
+      </c>
+      <c r="G73" s="49">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H73" s="49">
         <v>0.21</v>
       </c>
-      <c r="I73" s="19">
+      <c r="I73" s="50">
         <v>0.36</v>
       </c>
-      <c r="J73" s="20" t="s">
+      <c r="J73" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="K73" s="5">
+      <c r="K73" s="47">
         <f t="shared" ref="K73" si="634">M$2/M73</f>
         <v>130.34374999999997</v>
       </c>
-      <c r="L73" s="5">
+      <c r="L73" s="47">
         <f t="shared" ref="L73" si="635">M72/M73</f>
         <v>1</v>
       </c>
-      <c r="M73" s="4">
+      <c r="M73" s="48">
         <f t="shared" ref="M73" si="636">SUM(O73:Q73)</f>
         <v>0.32</v>
       </c>
-      <c r="N73" s="18">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O73" s="18">
+      <c r="N73" s="49">
+        <v>0.06</v>
+      </c>
+      <c r="O73" s="49">
         <v>0.22</v>
       </c>
-      <c r="P73" s="18">
+      <c r="P73" s="49">
         <v>0.08</v>
       </c>
-      <c r="Q73" s="18">
+      <c r="Q73" s="49">
         <v>0.02</v>
       </c>
-      <c r="R73" s="19">
+      <c r="R73" s="50">
         <v>0.05</v>
       </c>
-      <c r="S73" s="20" t="s">
+      <c r="S73" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="T73" s="5">
+      <c r="T73" s="47">
         <f t="shared" ref="T73" si="637">ROUND(B73/K73,3)</f>
-        <v>0.94099999999999995</v>
-      </c>
-      <c r="U73" s="5">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="U73" s="47">
         <f t="shared" ref="U73" si="638">ROUND(C73/L73,3)</f>
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="V73" s="4">
+        <v>0.998</v>
+      </c>
+      <c r="V73" s="48">
         <f t="shared" ref="V73" si="639">ROUND(D73/M73,3)</f>
-        <v>12.813000000000001</v>
-      </c>
-      <c r="W73" s="18">
+        <v>12.75</v>
+      </c>
+      <c r="W73" s="49">
         <f t="shared" ref="W73" si="640">ROUND(E73/N73,3)</f>
-        <v>5.7140000000000004</v>
-      </c>
-      <c r="X73" s="18">
+        <v>6.6669999999999998</v>
+      </c>
+      <c r="X73" s="49">
         <f t="shared" ref="X73" si="641">ROUND(F73/O73,3)</f>
-        <v>12.545</v>
-      </c>
-      <c r="Y73" s="18">
+        <v>12.5</v>
+      </c>
+      <c r="Y73" s="49">
         <f t="shared" ref="Y73" si="642">ROUND(G73/P73,3)</f>
-        <v>14.125</v>
-      </c>
-      <c r="Z73" s="18">
+        <v>14</v>
+      </c>
+      <c r="Z73" s="49">
         <f t="shared" ref="Z73" si="643">ROUND(H73/Q73,3)</f>
         <v>10.5</v>
       </c>
-      <c r="AA73" s="19">
+      <c r="AA73" s="50">
         <f t="shared" ref="AA73" si="644">ROUND(I73/R73,3)</f>
         <v>7.2</v>
       </c>
       <c r="AB73" s="20"/>
     </row>
     <row r="74" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="47">
         <f t="shared" ref="B74" si="645">D$2/D74</f>
-        <v>120.87019230769229</v>
-      </c>
-      <c r="C74" s="5">
+        <v>122.93887530562345</v>
+      </c>
+      <c r="C74" s="47">
         <f t="shared" ref="C74" si="646">D73/D74</f>
-        <v>0.98557692307692291</v>
-      </c>
-      <c r="D74" s="4">
+        <v>0.99755501222493892</v>
+      </c>
+      <c r="D74" s="48">
         <f t="shared" ref="D74" si="647">SUM(F74:H74)</f>
-        <v>4.16</v>
-      </c>
-      <c r="E74" s="9">
-        <v>0.41</v>
-      </c>
-      <c r="F74" s="9">
-        <v>2.81</v>
-      </c>
-      <c r="G74" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="H74" s="9">
+        <v>4.09</v>
+      </c>
+      <c r="E74" s="43">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="43">
+        <v>2.76</v>
+      </c>
+      <c r="G74" s="43">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H74" s="43">
+        <v>0.21</v>
+      </c>
+      <c r="I74" s="45">
+        <v>0.36</v>
+      </c>
+      <c r="J74" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="K74" s="47">
+        <f t="shared" ref="K74:K76" si="648">M$2/M74</f>
+        <v>130.34374999999997</v>
+      </c>
+      <c r="L74" s="47">
+        <f t="shared" ref="L74:L76" si="649">M73/M74</f>
+        <v>1</v>
+      </c>
+      <c r="M74" s="48">
+        <f t="shared" ref="M74:M76" si="650">SUM(O74:Q74)</f>
+        <v>0.32</v>
+      </c>
+      <c r="N74" s="43">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O74" s="43">
         <v>0.22</v>
       </c>
-      <c r="I74" s="10">
-        <v>0.37</v>
-      </c>
-      <c r="J74" s="20" t="s">
+      <c r="P74" s="43">
+        <v>0.08</v>
+      </c>
+      <c r="Q74" s="43">
+        <v>0.02</v>
+      </c>
+      <c r="R74" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="S74" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K74" s="5">
-        <f t="shared" ref="K74:K75" si="648">M$2/M74</f>
-        <v>134.54838709677418</v>
-      </c>
-      <c r="L74" s="5">
-        <f t="shared" ref="L74:L75" si="649">M73/M74</f>
-        <v>1.032258064516129</v>
-      </c>
-      <c r="M74" s="4">
-        <f t="shared" ref="M74:M75" si="650">SUM(O74:Q74)</f>
-        <v>0.31</v>
-      </c>
-      <c r="N74" s="9">
+      <c r="T74" s="47">
+        <f t="shared" ref="T74" si="651">ROUND(B74/K74,3)</f>
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="U74" s="47">
+        <f t="shared" ref="U74" si="652">ROUND(C74/L74,3)</f>
+        <v>0.998</v>
+      </c>
+      <c r="V74" s="48">
+        <f t="shared" ref="V74" si="653">ROUND(D74/M74,3)</f>
+        <v>12.781000000000001</v>
+      </c>
+      <c r="W74" s="49">
+        <f t="shared" ref="W74" si="654">ROUND(E74/N74,3)</f>
+        <v>5.7140000000000004</v>
+      </c>
+      <c r="X74" s="49">
+        <f t="shared" ref="X74" si="655">ROUND(F74/O74,3)</f>
+        <v>12.545</v>
+      </c>
+      <c r="Y74" s="49">
+        <f t="shared" ref="Y74" si="656">ROUND(G74/P74,3)</f>
+        <v>14</v>
+      </c>
+      <c r="Z74" s="49">
+        <f t="shared" ref="Z74" si="657">ROUND(H74/Q74,3)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA74" s="50">
+        <f t="shared" ref="AA74" si="658">ROUND(I74/R74,3)</f>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="41">
+        <f t="shared" ref="B75" si="659">D$2/D75</f>
+        <v>135.89729729729729</v>
+      </c>
+      <c r="C75" s="41">
+        <f t="shared" ref="C75" si="660">D74/D75</f>
+        <v>1.1054054054054052</v>
+      </c>
+      <c r="D75" s="42">
+        <f t="shared" ref="D75" si="661">SUM(F75:H75)</f>
+        <v>3.7</v>
+      </c>
+      <c r="E75" s="44">
+        <v>0.39</v>
+      </c>
+      <c r="F75" s="44">
+        <v>2.69</v>
+      </c>
+      <c r="G75" s="44">
+        <v>0.91</v>
+      </c>
+      <c r="H75" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="I75" s="46">
+        <v>0.21</v>
+      </c>
+      <c r="J75" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="K75" s="41">
+        <f t="shared" si="648"/>
+        <v>134.54838709677415</v>
+      </c>
+      <c r="L75" s="41">
+        <f t="shared" si="649"/>
+        <v>1.0322580645161288</v>
+      </c>
+      <c r="M75" s="42">
+        <f t="shared" si="650"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="N75" s="44">
         <v>0.06</v>
       </c>
-      <c r="O74" s="9">
-        <v>0.21</v>
-      </c>
-      <c r="P74" s="9">
-        <v>0.08</v>
-      </c>
-      <c r="Q74" s="9">
+      <c r="O75" s="44">
+        <v>0.23</v>
+      </c>
+      <c r="P75" s="44">
+        <v>0.06</v>
+      </c>
+      <c r="Q75" s="44">
         <v>0.02</v>
       </c>
-      <c r="R74" s="10">
+      <c r="R75" s="46">
         <v>0.05</v>
       </c>
-      <c r="S74" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="T74" s="5">
-        <f t="shared" ref="T74" si="651">ROUND(B74/K74,3)</f>
-        <v>0.89800000000000002</v>
-      </c>
-      <c r="U74" s="5">
-        <f t="shared" ref="U74" si="652">ROUND(C74/L74,3)</f>
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="V74" s="4">
-        <f t="shared" ref="V74" si="653">ROUND(D74/M74,3)</f>
-        <v>13.419</v>
-      </c>
-      <c r="W74" s="18">
-        <f t="shared" ref="W74" si="654">ROUND(E74/N74,3)</f>
-        <v>6.8330000000000002</v>
-      </c>
-      <c r="X74" s="18">
-        <f t="shared" ref="X74" si="655">ROUND(F74/O74,3)</f>
-        <v>13.381</v>
-      </c>
-      <c r="Y74" s="18">
-        <f t="shared" ref="Y74" si="656">ROUND(G74/P74,3)</f>
-        <v>14.125</v>
-      </c>
-      <c r="Z74" s="18">
-        <f t="shared" ref="Z74" si="657">ROUND(H74/Q74,3)</f>
-        <v>11</v>
-      </c>
-      <c r="AA74" s="19">
-        <f t="shared" ref="AA74" si="658">ROUND(I74/R74,3)</f>
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="30" t="s">
+      <c r="S75" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B75" s="22">
-        <f t="shared" ref="B75" si="659">D$2/D75</f>
-        <v>137.00817438692096</v>
-      </c>
-      <c r="C75" s="22">
-        <f t="shared" ref="C75" si="660">D74/D75</f>
-        <v>1.1335149863760217</v>
-      </c>
-      <c r="D75" s="23">
-        <f t="shared" ref="D75" si="661">SUM(F75:H75)</f>
-        <v>3.6700000000000004</v>
-      </c>
-      <c r="E75" s="25">
-        <v>0.38</v>
-      </c>
-      <c r="F75" s="25">
-        <v>2.66</v>
-      </c>
-      <c r="G75" s="25">
-        <v>0.91</v>
-      </c>
-      <c r="H75" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="I75" s="26">
-        <v>0.21</v>
-      </c>
-      <c r="J75" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="K75" s="22">
-        <f t="shared" si="648"/>
-        <v>139.0333333333333</v>
-      </c>
-      <c r="L75" s="22">
-        <f t="shared" si="649"/>
-        <v>1.0333333333333332</v>
-      </c>
-      <c r="M75" s="23">
-        <f t="shared" si="650"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="N75" s="25">
-        <v>0.06</v>
-      </c>
-      <c r="O75" s="25">
-        <v>0.22</v>
-      </c>
-      <c r="P75" s="25">
-        <v>0.06</v>
-      </c>
-      <c r="Q75" s="25">
-        <v>0.02</v>
-      </c>
-      <c r="R75" s="26">
-        <v>0.05</v>
-      </c>
-      <c r="S75" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="T75" s="22">
+      <c r="T75" s="41">
         <f t="shared" ref="T75" si="662">ROUND(B75/K75,3)</f>
-        <v>0.98499999999999999</v>
-      </c>
-      <c r="U75" s="22">
+        <v>1.01</v>
+      </c>
+      <c r="U75" s="41">
         <f t="shared" ref="U75" si="663">ROUND(C75/L75,3)</f>
-        <v>1.097</v>
-      </c>
-      <c r="V75" s="23">
+        <v>1.071</v>
+      </c>
+      <c r="V75" s="42">
         <f t="shared" ref="V75" si="664">ROUND(D75/M75,3)</f>
-        <v>12.233000000000001</v>
-      </c>
-      <c r="W75" s="25">
+        <v>11.935</v>
+      </c>
+      <c r="W75" s="44">
         <f t="shared" ref="W75" si="665">ROUND(E75/N75,3)</f>
-        <v>6.3330000000000002</v>
-      </c>
-      <c r="X75" s="25">
+        <v>6.5</v>
+      </c>
+      <c r="X75" s="44">
         <f t="shared" ref="X75" si="666">ROUND(F75/O75,3)</f>
-        <v>12.090999999999999</v>
-      </c>
-      <c r="Y75" s="25">
+        <v>11.696</v>
+      </c>
+      <c r="Y75" s="44">
         <f t="shared" ref="Y75" si="667">ROUND(G75/P75,3)</f>
         <v>15.167</v>
       </c>
-      <c r="Z75" s="25">
+      <c r="Z75" s="44">
         <f t="shared" ref="Z75" si="668">ROUND(H75/Q75,3)</f>
         <v>5</v>
       </c>
-      <c r="AA75" s="26">
+      <c r="AA75" s="46">
         <f t="shared" ref="AA75" si="669">ROUND(I75/R75,3)</f>
         <v>4.2</v>
       </c>
+      <c r="AB75" s="38"/>
+    </row>
+    <row r="76" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76" s="27">
+        <f t="shared" ref="B76" si="670">D$2/D76</f>
+        <v>134.44385026737964</v>
+      </c>
+      <c r="C76" s="27">
+        <f t="shared" ref="C76" si="671">D75/D76</f>
+        <v>0.98930481283422456</v>
+      </c>
+      <c r="D76" s="28">
+        <f t="shared" ref="D76" si="672">SUM(F76:H76)</f>
+        <v>3.74</v>
+      </c>
+      <c r="E76" s="31">
+        <v>0.44</v>
+      </c>
+      <c r="F76" s="31">
+        <v>2.74</v>
+      </c>
+      <c r="G76" s="31">
+        <v>0.9</v>
+      </c>
+      <c r="H76" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="I76" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="J76" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K76" s="27">
+        <f t="shared" si="648"/>
+        <v>134.54838709677415</v>
+      </c>
+      <c r="L76" s="27">
+        <f t="shared" si="649"/>
+        <v>1</v>
+      </c>
+      <c r="M76" s="28">
+        <f t="shared" si="650"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="N76" s="31">
+        <v>0.06</v>
+      </c>
+      <c r="O76" s="31">
+        <v>0.23</v>
+      </c>
+      <c r="P76" s="31">
+        <v>0.06</v>
+      </c>
+      <c r="Q76" s="31">
+        <v>0.02</v>
+      </c>
+      <c r="R76" s="32">
+        <v>0.04</v>
+      </c>
+      <c r="S76" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="T76" s="27">
+        <f t="shared" ref="T76" si="673">ROUND(B76/K76,3)</f>
+        <v>0.999</v>
+      </c>
+      <c r="U76" s="27">
+        <f t="shared" ref="U76" si="674">ROUND(C76/L76,3)</f>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="V76" s="28">
+        <f t="shared" ref="V76" si="675">ROUND(D76/M76,3)</f>
+        <v>12.065</v>
+      </c>
+      <c r="W76" s="31">
+        <f t="shared" ref="W76" si="676">ROUND(E76/N76,3)</f>
+        <v>7.3330000000000002</v>
+      </c>
+      <c r="X76" s="31">
+        <f t="shared" ref="X76" si="677">ROUND(F76/O76,3)</f>
+        <v>11.913</v>
+      </c>
+      <c r="Y76" s="31">
+        <f t="shared" ref="Y76" si="678">ROUND(G76/P76,3)</f>
+        <v>15</v>
+      </c>
+      <c r="Z76" s="31">
+        <f t="shared" ref="Z76" si="679">ROUND(H76/Q76,3)</f>
+        <v>5</v>
+      </c>
+      <c r="AA76" s="32">
+        <f t="shared" ref="AA76" si="680">ROUND(I76/R76,3)</f>
+        <v>5</v>
+      </c>
+      <c r="AB76" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7A296E-1F31-49DF-9713-7EBC6044198E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C79440-FAF8-4A1C-A3F6-503390ADCCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="88">
   <si>
     <t>H23</t>
   </si>
@@ -349,6 +349,14 @@
   </si>
   <si>
     <t>H96</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H97</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H98</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +513,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -629,35 +637,20 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -973,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB76"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -6849,7 +6842,7 @@
       <c r="P61" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Q61" s="13">
+      <c r="Q61" s="18">
         <v>0.02</v>
       </c>
       <c r="R61" s="10">
@@ -6979,7 +6972,7 @@
         <f t="shared" ref="Y62" si="488">ROUND(G62/P62,3)</f>
         <v>18.571000000000002</v>
       </c>
-      <c r="Z62" s="18">
+      <c r="Z62" s="9">
         <f t="shared" ref="Z62" si="489">ROUND(H62/Q62,3)</f>
         <v>11.5</v>
       </c>
@@ -7068,7 +7061,7 @@
         <f t="shared" ref="W63" si="500">ROUND(E63/N63,3)</f>
         <v>6.2859999999999996</v>
       </c>
-      <c r="X63" s="18">
+      <c r="X63" s="9">
         <f t="shared" ref="X63" si="501">ROUND(F63/O63,3)</f>
         <v>12.587</v>
       </c>
@@ -7076,7 +7069,7 @@
         <f t="shared" ref="Y63" si="502">ROUND(G63/P63,3)</f>
         <v>18.713999999999999</v>
       </c>
-      <c r="Z63" s="18">
+      <c r="Z63" s="9">
         <f t="shared" ref="Z63" si="503">ROUND(H63/Q63,3)</f>
         <v>12.5</v>
       </c>
@@ -7116,7 +7109,7 @@
       <c r="I64" s="10">
         <v>2.0299999999999998</v>
       </c>
-      <c r="J64" s="20" t="s">
+      <c r="J64" s="12" t="s">
         <v>72</v>
       </c>
       <c r="K64" s="2">
@@ -7146,7 +7139,7 @@
       <c r="R64" s="10">
         <v>0.13</v>
       </c>
-      <c r="S64" s="20" t="s">
+      <c r="S64" s="12" t="s">
         <v>72</v>
       </c>
       <c r="T64" s="2">
@@ -7456,7 +7449,7 @@
         <f t="shared" ref="W67" si="556">ROUND(E67/N67,3)</f>
         <v>7.1669999999999998</v>
       </c>
-      <c r="X67" s="18">
+      <c r="X67" s="9">
         <f t="shared" ref="X67" si="557">ROUND(F67/O67,3)</f>
         <v>10.355</v>
       </c>
@@ -7479,51 +7472,51 @@
       </c>
       <c r="B68" s="27">
         <f t="shared" ref="B68" si="561">D$2/D68</f>
-        <v>106.98297872340424</v>
+        <v>104.10351966873706</v>
       </c>
       <c r="C68" s="27">
         <f t="shared" ref="C68" si="562">D67/D68</f>
-        <v>1.021276595744681</v>
+        <v>0.99378881987577672</v>
       </c>
       <c r="D68" s="28">
         <f t="shared" ref="D68" si="563">SUM(F68:H68)</f>
-        <v>4.7</v>
+        <v>4.8299999999999992</v>
       </c>
       <c r="E68" s="31">
         <v>0.39</v>
       </c>
       <c r="F68" s="31">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="G68" s="31">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H68" s="25">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="I68" s="32">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J68" s="30" t="s">
         <v>77</v>
       </c>
       <c r="K68" s="27">
         <f t="shared" ref="K68" si="564">M$2/M68</f>
-        <v>92.688888888888869</v>
+        <v>90.673913043478237</v>
       </c>
       <c r="L68" s="27">
         <f t="shared" ref="L68" si="565">M67/M68</f>
-        <v>1.0222222222222221</v>
+        <v>1</v>
       </c>
       <c r="M68" s="28">
         <f t="shared" ref="M68" si="566">SUM(O68:Q68)</f>
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="N68" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O68" s="31">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="P68" s="31">
         <v>0.13</v>
@@ -7539,15 +7532,15 @@
       </c>
       <c r="T68" s="27">
         <f t="shared" ref="T68" si="567">ROUND(B68/K68,3)</f>
-        <v>1.1539999999999999</v>
+        <v>1.1479999999999999</v>
       </c>
       <c r="U68" s="27">
         <f t="shared" ref="U68" si="568">ROUND(C68/L68,3)</f>
-        <v>0.999</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="V68" s="28">
         <f t="shared" ref="V68" si="569">ROUND(D68/M68,3)</f>
-        <v>10.444000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="W68" s="31">
         <f t="shared" ref="W68" si="570">ROUND(E68/N68,3)</f>
@@ -7555,19 +7548,19 @@
       </c>
       <c r="X68" s="31">
         <f t="shared" ref="X68" si="571">ROUND(F68/O68,3)</f>
-        <v>10.532999999999999</v>
+        <v>10.516</v>
       </c>
       <c r="Y68" s="31">
         <f t="shared" ref="Y68" si="572">ROUND(G68/P68,3)</f>
-        <v>10.231</v>
+        <v>10.385</v>
       </c>
       <c r="Z68" s="25">
         <f t="shared" ref="Z68" si="573">ROUND(H68/Q68,3)</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA68" s="32">
         <f t="shared" ref="AA68" si="574">ROUND(I68/R68,3)</f>
-        <v>6.1429999999999998</v>
+        <v>6.2859999999999996</v>
       </c>
       <c r="AB68" s="20"/>
     </row>
@@ -7577,30 +7570,30 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" ref="B69" si="575">D$2/D69</f>
-        <v>106.52966101694915</v>
+        <v>104.97286012526095</v>
       </c>
       <c r="C69" s="2">
         <f t="shared" ref="C69" si="576">D68/D69</f>
-        <v>0.9957627118644069</v>
+        <v>1.008350730688935</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" ref="D69" si="577">SUM(F69:H69)</f>
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="E69" s="9">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="F69" s="13">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="G69" s="13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H69" s="9">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="I69" s="14">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>78</v>
@@ -7611,7 +7604,7 @@
       </c>
       <c r="L69" s="2">
         <f t="shared" ref="L69" si="579">M68/M69</f>
-        <v>1.25</v>
+        <v>1.2777777777777779</v>
       </c>
       <c r="M69" s="6">
         <f t="shared" ref="M69" si="580">SUM(O69:Q69)</f>
@@ -7637,35 +7630,35 @@
       </c>
       <c r="T69" s="2">
         <f t="shared" ref="T69" si="581">ROUND(B69/K69,3)</f>
-        <v>0.91900000000000004</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="U69" s="2">
         <f t="shared" ref="U69" si="582">ROUND(C69/L69,3)</f>
-        <v>0.79700000000000004</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="V69" s="6">
         <f t="shared" ref="V69" si="583">ROUND(D69/M69,3)</f>
-        <v>13.111000000000001</v>
+        <v>13.305999999999999</v>
       </c>
       <c r="W69" s="9">
         <f t="shared" ref="W69" si="584">ROUND(E69/N69,3)</f>
-        <v>7.1669999999999998</v>
+        <v>6.8330000000000002</v>
       </c>
       <c r="X69" s="13">
         <f t="shared" ref="X69" si="585">ROUND(F69/O69,3)</f>
-        <v>12.76</v>
+        <v>12.92</v>
       </c>
       <c r="Y69" s="13">
         <f t="shared" ref="Y69" si="586">ROUND(G69/P69,3)</f>
-        <v>14.778</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="Z69" s="9">
         <f t="shared" ref="Z69" si="587">ROUND(H69/Q69,3)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA69" s="14">
         <f t="shared" ref="AA69" si="588">ROUND(I69/R69,3)</f>
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="70" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7674,27 +7667,27 @@
       </c>
       <c r="B70" s="5">
         <f t="shared" ref="B70" si="589">D$2/D70</f>
-        <v>106.30443974630019</v>
+        <v>104.53638253638253</v>
       </c>
       <c r="C70" s="5">
         <f t="shared" ref="C70" si="590">D69/D70</f>
-        <v>0.99788583509513729</v>
+        <v>0.99584199584199595</v>
       </c>
       <c r="D70" s="4">
         <f t="shared" ref="D70" si="591">SUM(F70:H70)</f>
-        <v>4.7300000000000004</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="E70" s="18">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F70" s="18">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="G70" s="18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H70" s="18">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="I70" s="19">
         <v>0.44</v>
@@ -7715,7 +7708,7 @@
         <v>0.35</v>
       </c>
       <c r="N70" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O70" s="18">
         <v>0.24</v>
@@ -7734,31 +7727,31 @@
       </c>
       <c r="T70" s="5">
         <f t="shared" ref="T70" si="595">ROUND(B70/K70,3)</f>
-        <v>0.89200000000000002</v>
+        <v>0.877</v>
       </c>
       <c r="U70" s="5">
         <f t="shared" ref="U70" si="596">ROUND(C70/L70,3)</f>
-        <v>0.97</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="V70" s="4">
         <f t="shared" ref="V70" si="597">ROUND(D70/M70,3)</f>
-        <v>13.513999999999999</v>
+        <v>13.743</v>
       </c>
       <c r="W70" s="18">
         <f t="shared" ref="W70" si="598">ROUND(E70/N70,3)</f>
-        <v>5.7140000000000004</v>
+        <v>6.5</v>
       </c>
       <c r="X70" s="18">
         <f t="shared" ref="X70" si="599">ROUND(F70/O70,3)</f>
-        <v>13.292</v>
+        <v>13.5</v>
       </c>
       <c r="Y70" s="18">
         <f t="shared" ref="Y70" si="600">ROUND(G70/P70,3)</f>
-        <v>14.888999999999999</v>
+        <v>15</v>
       </c>
       <c r="Z70" s="18">
         <f t="shared" ref="Z70" si="601">ROUND(H70/Q70,3)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA70" s="19">
         <f t="shared" ref="AA70" si="602">ROUND(I70/R70,3)</f>
@@ -7767,487 +7760,487 @@
       <c r="AB70" s="20"/>
     </row>
     <row r="71" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="40" t="s">
+      <c r="A71" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="41">
+      <c r="B71" s="2">
         <f t="shared" ref="B71" si="603">D$2/D71</f>
-        <v>115.85714285714285</v>
-      </c>
-      <c r="C71" s="41">
+        <v>116.66357308584686</v>
+      </c>
+      <c r="C71" s="2">
         <f t="shared" ref="C71" si="604">D70/D71</f>
-        <v>1.0898617511520738</v>
-      </c>
-      <c r="D71" s="42">
+        <v>1.1160092807424593</v>
+      </c>
+      <c r="D71" s="6">
         <f t="shared" ref="D71" si="605">SUM(F71:H71)</f>
-        <v>4.34</v>
-      </c>
-      <c r="E71" s="43">
-        <v>0.39</v>
-      </c>
-      <c r="F71" s="44">
-        <v>2.78</v>
-      </c>
-      <c r="G71" s="43">
-        <v>1.34</v>
-      </c>
-      <c r="H71" s="43">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="F71" s="13">
+        <v>2.76</v>
+      </c>
+      <c r="G71" s="9">
+        <v>1.33</v>
+      </c>
+      <c r="H71" s="9">
         <v>0.22</v>
       </c>
-      <c r="I71" s="45">
-        <v>0.44</v>
-      </c>
-      <c r="J71" s="40" t="s">
+      <c r="I71" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="J71" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="K71" s="41">
+      <c r="K71" s="2">
         <f t="shared" ref="K71" si="606">M$2/M71</f>
-        <v>126.39393939393936</v>
-      </c>
-      <c r="L71" s="41">
+        <v>122.67647058823526</v>
+      </c>
+      <c r="L71" s="2">
         <f t="shared" ref="L71" si="607">M70/M71</f>
-        <v>1.0606060606060606</v>
-      </c>
-      <c r="M71" s="42">
+        <v>1.0294117647058822</v>
+      </c>
+      <c r="M71" s="6">
         <f t="shared" ref="M71" si="608">SUM(O71:Q71)</f>
-        <v>0.33</v>
-      </c>
-      <c r="N71" s="43">
+        <v>0.34</v>
+      </c>
+      <c r="N71" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="O71" s="13">
+        <v>0.23</v>
+      </c>
+      <c r="P71" s="9">
         <v>0.09</v>
       </c>
-      <c r="O71" s="44">
-        <v>0.22</v>
-      </c>
-      <c r="P71" s="43">
-        <v>0.09</v>
-      </c>
-      <c r="Q71" s="43">
+      <c r="Q71" s="9">
         <v>0.02</v>
       </c>
-      <c r="R71" s="45">
+      <c r="R71" s="10">
         <v>0.05</v>
       </c>
-      <c r="S71" s="40" t="s">
+      <c r="S71" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="T71" s="41">
+      <c r="T71" s="2">
         <f t="shared" ref="T71" si="609">ROUND(B71/K71,3)</f>
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="U71" s="41">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="U71" s="2">
         <f t="shared" ref="U71" si="610">ROUND(C71/L71,3)</f>
-        <v>1.028</v>
-      </c>
-      <c r="V71" s="42">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="V71" s="6">
         <f t="shared" ref="V71" si="611">ROUND(D71/M71,3)</f>
-        <v>13.151999999999999</v>
-      </c>
-      <c r="W71" s="43">
+        <v>12.676</v>
+      </c>
+      <c r="W71" s="9">
         <f t="shared" ref="W71" si="612">ROUND(E71/N71,3)</f>
-        <v>4.3330000000000002</v>
-      </c>
-      <c r="X71" s="44">
+        <v>6.6669999999999998</v>
+      </c>
+      <c r="X71" s="13">
         <f t="shared" ref="X71" si="613">ROUND(F71/O71,3)</f>
-        <v>12.635999999999999</v>
-      </c>
-      <c r="Y71" s="43">
+        <v>12</v>
+      </c>
+      <c r="Y71" s="9">
         <f t="shared" ref="Y71" si="614">ROUND(G71/P71,3)</f>
-        <v>14.888999999999999</v>
-      </c>
-      <c r="Z71" s="43">
+        <v>14.778</v>
+      </c>
+      <c r="Z71" s="9">
         <f t="shared" ref="Z71" si="615">ROUND(H71/Q71,3)</f>
         <v>11</v>
       </c>
-      <c r="AA71" s="45">
+      <c r="AA71" s="10">
         <f t="shared" ref="AA71" si="616">ROUND(I71/R71,3)</f>
-        <v>8.8000000000000007</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="72" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="40" t="s">
+      <c r="A72" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B72" s="41">
+      <c r="B72" s="2">
         <f t="shared" ref="B72" si="617">D$2/D72</f>
-        <v>123.54299754299753</v>
-      </c>
-      <c r="C72" s="41">
+        <v>121.74818401937044</v>
+      </c>
+      <c r="C72" s="2">
         <f t="shared" ref="C72" si="618">D71/D72</f>
-        <v>1.0663390663390662</v>
-      </c>
-      <c r="D72" s="42">
+        <v>1.0435835351089588</v>
+      </c>
+      <c r="D72" s="6">
         <f t="shared" ref="D72" si="619">SUM(F72:H72)</f>
-        <v>4.07</v>
-      </c>
-      <c r="E72" s="43">
+        <v>4.13</v>
+      </c>
+      <c r="E72" s="9">
         <v>0.39</v>
       </c>
-      <c r="F72" s="43">
-        <v>2.74</v>
-      </c>
-      <c r="G72" s="44">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H72" s="43">
-        <v>0.21</v>
-      </c>
-      <c r="I72" s="46">
+      <c r="F72" s="9">
+        <v>2.78</v>
+      </c>
+      <c r="G72" s="13">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="I72" s="14">
         <v>0.36</v>
       </c>
-      <c r="J72" s="40" t="s">
+      <c r="J72" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="K72" s="41">
+      <c r="K72" s="2">
         <f t="shared" ref="K72" si="620">M$2/M72</f>
         <v>130.34374999999997</v>
       </c>
-      <c r="L72" s="41">
+      <c r="L72" s="2">
         <f t="shared" ref="L72" si="621">M71/M72</f>
-        <v>1.03125</v>
-      </c>
-      <c r="M72" s="42">
+        <v>1.0625</v>
+      </c>
+      <c r="M72" s="6">
         <f t="shared" ref="M72" si="622">SUM(O72:Q72)</f>
         <v>0.32</v>
       </c>
-      <c r="N72" s="43">
+      <c r="N72" s="9">
         <v>0.06</v>
       </c>
-      <c r="O72" s="43">
+      <c r="O72" s="9">
         <v>0.22</v>
       </c>
-      <c r="P72" s="44">
+      <c r="P72" s="13">
         <v>0.08</v>
       </c>
-      <c r="Q72" s="43">
+      <c r="Q72" s="9">
         <v>0.02</v>
       </c>
-      <c r="R72" s="46">
+      <c r="R72" s="14">
         <v>0.05</v>
       </c>
-      <c r="S72" s="40" t="s">
+      <c r="S72" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="T72" s="41">
+      <c r="T72" s="2">
         <f t="shared" ref="T72" si="623">ROUND(B72/K72,3)</f>
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="U72" s="41">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="U72" s="2">
         <f t="shared" ref="U72" si="624">ROUND(C72/L72,3)</f>
-        <v>1.034</v>
-      </c>
-      <c r="V72" s="42">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="V72" s="6">
         <f t="shared" ref="V72" si="625">ROUND(D72/M72,3)</f>
-        <v>12.718999999999999</v>
-      </c>
-      <c r="W72" s="43">
+        <v>12.906000000000001</v>
+      </c>
+      <c r="W72" s="9">
         <f t="shared" ref="W72" si="626">ROUND(E72/N72,3)</f>
         <v>6.5</v>
       </c>
-      <c r="X72" s="43">
+      <c r="X72" s="9">
         <f t="shared" ref="X72" si="627">ROUND(F72/O72,3)</f>
-        <v>12.455</v>
-      </c>
-      <c r="Y72" s="44">
+        <v>12.635999999999999</v>
+      </c>
+      <c r="Y72" s="13">
         <f t="shared" ref="Y72" si="628">ROUND(G72/P72,3)</f>
-        <v>14</v>
-      </c>
-      <c r="Z72" s="43">
+        <v>14.125</v>
+      </c>
+      <c r="Z72" s="9">
         <f t="shared" ref="Z72" si="629">ROUND(H72/Q72,3)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AA72" s="46">
+        <v>11</v>
+      </c>
+      <c r="AA72" s="14">
         <f t="shared" ref="AA72" si="630">ROUND(I72/R72,3)</f>
         <v>7.2</v>
       </c>
     </row>
     <row r="73" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B73" s="47">
+      <c r="B73" s="5">
         <f t="shared" ref="B73" si="631">D$2/D73</f>
-        <v>123.24019607843135</v>
-      </c>
-      <c r="C73" s="47">
+        <v>122.6390243902439</v>
+      </c>
+      <c r="C73" s="5">
         <f t="shared" ref="C73" si="632">D72/D73</f>
-        <v>0.99754901960784315</v>
-      </c>
-      <c r="D73" s="48">
+        <v>1.0073170731707317</v>
+      </c>
+      <c r="D73" s="4">
         <f t="shared" ref="D73" si="633">SUM(F73:H73)</f>
-        <v>4.08</v>
-      </c>
-      <c r="E73" s="49">
-        <v>0.4</v>
-      </c>
-      <c r="F73" s="49">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E73" s="18">
+        <v>0.42</v>
+      </c>
+      <c r="F73" s="18">
         <v>2.75</v>
       </c>
-      <c r="G73" s="49">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H73" s="49">
-        <v>0.21</v>
-      </c>
-      <c r="I73" s="50">
+      <c r="G73" s="18">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H73" s="18">
+        <v>0.22</v>
+      </c>
+      <c r="I73" s="19">
         <v>0.36</v>
       </c>
-      <c r="J73" s="40" t="s">
+      <c r="J73" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="K73" s="47">
+      <c r="K73" s="5">
         <f t="shared" ref="K73" si="634">M$2/M73</f>
         <v>130.34374999999997</v>
       </c>
-      <c r="L73" s="47">
+      <c r="L73" s="5">
         <f t="shared" ref="L73" si="635">M72/M73</f>
         <v>1</v>
       </c>
-      <c r="M73" s="48">
+      <c r="M73" s="4">
         <f t="shared" ref="M73" si="636">SUM(O73:Q73)</f>
         <v>0.32</v>
       </c>
-      <c r="N73" s="49">
-        <v>0.06</v>
-      </c>
-      <c r="O73" s="49">
+      <c r="N73" s="18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O73" s="18">
         <v>0.22</v>
       </c>
-      <c r="P73" s="49">
+      <c r="P73" s="18">
         <v>0.08</v>
       </c>
-      <c r="Q73" s="49">
+      <c r="Q73" s="18">
         <v>0.02</v>
       </c>
-      <c r="R73" s="50">
+      <c r="R73" s="19">
         <v>0.05</v>
       </c>
-      <c r="S73" s="40" t="s">
+      <c r="S73" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="T73" s="47">
+      <c r="T73" s="5">
         <f t="shared" ref="T73" si="637">ROUND(B73/K73,3)</f>
-        <v>0.94599999999999995</v>
-      </c>
-      <c r="U73" s="47">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="U73" s="5">
         <f t="shared" ref="U73" si="638">ROUND(C73/L73,3)</f>
-        <v>0.998</v>
-      </c>
-      <c r="V73" s="48">
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="V73" s="4">
         <f t="shared" ref="V73" si="639">ROUND(D73/M73,3)</f>
-        <v>12.75</v>
-      </c>
-      <c r="W73" s="49">
+        <v>12.813000000000001</v>
+      </c>
+      <c r="W73" s="18">
         <f t="shared" ref="W73" si="640">ROUND(E73/N73,3)</f>
-        <v>6.6669999999999998</v>
-      </c>
-      <c r="X73" s="49">
+        <v>6</v>
+      </c>
+      <c r="X73" s="18">
         <f t="shared" ref="X73" si="641">ROUND(F73/O73,3)</f>
         <v>12.5</v>
       </c>
-      <c r="Y73" s="49">
+      <c r="Y73" s="18">
         <f t="shared" ref="Y73" si="642">ROUND(G73/P73,3)</f>
-        <v>14</v>
-      </c>
-      <c r="Z73" s="49">
+        <v>14.125</v>
+      </c>
+      <c r="Z73" s="18">
         <f t="shared" ref="Z73" si="643">ROUND(H73/Q73,3)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AA73" s="50">
+        <v>11</v>
+      </c>
+      <c r="AA73" s="19">
         <f t="shared" ref="AA73" si="644">ROUND(I73/R73,3)</f>
         <v>7.2</v>
       </c>
       <c r="AB73" s="20"/>
     </row>
     <row r="74" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="40" t="s">
+      <c r="A74" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="47">
+      <c r="B74" s="5">
         <f t="shared" ref="B74" si="645">D$2/D74</f>
         <v>122.93887530562345</v>
       </c>
-      <c r="C74" s="47">
+      <c r="C74" s="5">
         <f t="shared" ref="C74" si="646">D73/D74</f>
-        <v>0.99755501222493892</v>
-      </c>
-      <c r="D74" s="48">
+        <v>1.002444987775061</v>
+      </c>
+      <c r="D74" s="4">
         <f t="shared" ref="D74" si="647">SUM(F74:H74)</f>
         <v>4.09</v>
       </c>
-      <c r="E74" s="43">
-        <v>0.4</v>
-      </c>
-      <c r="F74" s="43">
-        <v>2.76</v>
-      </c>
-      <c r="G74" s="43">
+      <c r="E74" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="F74" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="G74" s="9">
         <v>1.1200000000000001</v>
       </c>
-      <c r="H74" s="43">
-        <v>0.21</v>
-      </c>
-      <c r="I74" s="45">
+      <c r="H74" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="I74" s="10">
         <v>0.36</v>
       </c>
-      <c r="J74" s="40" t="s">
+      <c r="J74" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K74" s="47">
+      <c r="K74" s="5">
         <f t="shared" ref="K74:K76" si="648">M$2/M74</f>
         <v>130.34374999999997</v>
       </c>
-      <c r="L74" s="47">
+      <c r="L74" s="5">
         <f t="shared" ref="L74:L76" si="649">M73/M74</f>
         <v>1</v>
       </c>
-      <c r="M74" s="48">
+      <c r="M74" s="4">
         <f t="shared" ref="M74:M76" si="650">SUM(O74:Q74)</f>
         <v>0.32</v>
       </c>
-      <c r="N74" s="43">
+      <c r="N74" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O74" s="43">
+      <c r="O74" s="9">
         <v>0.22</v>
       </c>
-      <c r="P74" s="43">
+      <c r="P74" s="9">
         <v>0.08</v>
       </c>
-      <c r="Q74" s="43">
+      <c r="Q74" s="9">
         <v>0.02</v>
       </c>
-      <c r="R74" s="45">
+      <c r="R74" s="10">
         <v>0.05</v>
       </c>
-      <c r="S74" s="40" t="s">
+      <c r="S74" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="T74" s="47">
+      <c r="T74" s="5">
         <f t="shared" ref="T74" si="651">ROUND(B74/K74,3)</f>
         <v>0.94299999999999995</v>
       </c>
-      <c r="U74" s="47">
+      <c r="U74" s="5">
         <f t="shared" ref="U74" si="652">ROUND(C74/L74,3)</f>
-        <v>0.998</v>
-      </c>
-      <c r="V74" s="48">
+        <v>1.002</v>
+      </c>
+      <c r="V74" s="4">
         <f t="shared" ref="V74" si="653">ROUND(D74/M74,3)</f>
         <v>12.781000000000001</v>
       </c>
-      <c r="W74" s="49">
+      <c r="W74" s="9">
         <f t="shared" ref="W74" si="654">ROUND(E74/N74,3)</f>
-        <v>5.7140000000000004</v>
-      </c>
-      <c r="X74" s="49">
+        <v>5.5709999999999997</v>
+      </c>
+      <c r="X74" s="9">
         <f t="shared" ref="X74" si="655">ROUND(F74/O74,3)</f>
-        <v>12.545</v>
-      </c>
-      <c r="Y74" s="49">
+        <v>12.5</v>
+      </c>
+      <c r="Y74" s="9">
         <f t="shared" ref="Y74" si="656">ROUND(G74/P74,3)</f>
         <v>14</v>
       </c>
-      <c r="Z74" s="49">
+      <c r="Z74" s="9">
         <f t="shared" ref="Z74" si="657">ROUND(H74/Q74,3)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AA74" s="50">
+        <v>11</v>
+      </c>
+      <c r="AA74" s="10">
         <f t="shared" ref="AA74" si="658">ROUND(I74/R74,3)</f>
         <v>7.2</v>
       </c>
     </row>
     <row r="75" spans="1:28" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="40" t="s">
+      <c r="A75" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B75" s="41">
+      <c r="B75" s="2">
         <f t="shared" ref="B75" si="659">D$2/D75</f>
-        <v>135.89729729729729</v>
-      </c>
-      <c r="C75" s="41">
+        <v>137.38251366120215</v>
+      </c>
+      <c r="C75" s="2">
         <f t="shared" ref="C75" si="660">D74/D75</f>
-        <v>1.1054054054054052</v>
-      </c>
-      <c r="D75" s="42">
+        <v>1.1174863387978142</v>
+      </c>
+      <c r="D75" s="6">
         <f t="shared" ref="D75" si="661">SUM(F75:H75)</f>
-        <v>3.7</v>
-      </c>
-      <c r="E75" s="44">
-        <v>0.39</v>
-      </c>
-      <c r="F75" s="44">
-        <v>2.69</v>
-      </c>
-      <c r="G75" s="44">
+        <v>3.66</v>
+      </c>
+      <c r="E75" s="13">
+        <v>0.38</v>
+      </c>
+      <c r="F75" s="13">
+        <v>2.66</v>
+      </c>
+      <c r="G75" s="13">
         <v>0.91</v>
       </c>
-      <c r="H75" s="44">
-        <v>0.1</v>
-      </c>
-      <c r="I75" s="46">
+      <c r="H75" s="13">
+        <v>0.09</v>
+      </c>
+      <c r="I75" s="14">
         <v>0.21</v>
       </c>
-      <c r="J75" s="40" t="s">
+      <c r="J75" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="K75" s="41">
+      <c r="K75" s="2">
         <f t="shared" si="648"/>
-        <v>134.54838709677415</v>
-      </c>
-      <c r="L75" s="41">
+        <v>139.0333333333333</v>
+      </c>
+      <c r="L75" s="2">
         <f t="shared" si="649"/>
-        <v>1.0322580645161288</v>
-      </c>
-      <c r="M75" s="42">
+        <v>1.0666666666666664</v>
+      </c>
+      <c r="M75" s="6">
         <f t="shared" si="650"/>
-        <v>0.31000000000000005</v>
-      </c>
-      <c r="N75" s="44">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N75" s="13">
         <v>0.06</v>
       </c>
-      <c r="O75" s="44">
-        <v>0.23</v>
-      </c>
-      <c r="P75" s="44">
+      <c r="O75" s="13">
+        <v>0.22</v>
+      </c>
+      <c r="P75" s="13">
         <v>0.06</v>
       </c>
-      <c r="Q75" s="44">
+      <c r="Q75" s="13">
         <v>0.02</v>
       </c>
-      <c r="R75" s="46">
+      <c r="R75" s="14">
         <v>0.05</v>
       </c>
-      <c r="S75" s="40" t="s">
+      <c r="S75" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="T75" s="41">
+      <c r="T75" s="2">
         <f t="shared" ref="T75" si="662">ROUND(B75/K75,3)</f>
-        <v>1.01</v>
-      </c>
-      <c r="U75" s="41">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="U75" s="2">
         <f t="shared" ref="U75" si="663">ROUND(C75/L75,3)</f>
-        <v>1.071</v>
-      </c>
-      <c r="V75" s="42">
+        <v>1.048</v>
+      </c>
+      <c r="V75" s="6">
         <f t="shared" ref="V75" si="664">ROUND(D75/M75,3)</f>
-        <v>11.935</v>
-      </c>
-      <c r="W75" s="44">
+        <v>12.2</v>
+      </c>
+      <c r="W75" s="13">
         <f t="shared" ref="W75" si="665">ROUND(E75/N75,3)</f>
-        <v>6.5</v>
-      </c>
-      <c r="X75" s="44">
+        <v>6.3330000000000002</v>
+      </c>
+      <c r="X75" s="13">
         <f t="shared" ref="X75" si="666">ROUND(F75/O75,3)</f>
-        <v>11.696</v>
-      </c>
-      <c r="Y75" s="44">
+        <v>12.090999999999999</v>
+      </c>
+      <c r="Y75" s="13">
         <f t="shared" ref="Y75" si="667">ROUND(G75/P75,3)</f>
         <v>15.167</v>
       </c>
-      <c r="Z75" s="44">
+      <c r="Z75" s="13">
         <f t="shared" ref="Z75" si="668">ROUND(H75/Q75,3)</f>
-        <v>5</v>
-      </c>
-      <c r="AA75" s="46">
+        <v>4.5</v>
+      </c>
+      <c r="AA75" s="14">
         <f t="shared" ref="AA75" si="669">ROUND(I75/R75,3)</f>
         <v>4.2</v>
       </c>
@@ -8259,21 +8252,21 @@
       </c>
       <c r="B76" s="27">
         <f t="shared" ref="B76" si="670">D$2/D76</f>
-        <v>134.44385026737964</v>
+        <v>140.84593837535013</v>
       </c>
       <c r="C76" s="27">
         <f t="shared" ref="C76" si="671">D75/D76</f>
-        <v>0.98930481283422456</v>
+        <v>1.0252100840336136</v>
       </c>
       <c r="D76" s="28">
         <f t="shared" ref="D76" si="672">SUM(F76:H76)</f>
-        <v>3.74</v>
+        <v>3.57</v>
       </c>
       <c r="E76" s="31">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="F76" s="31">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="G76" s="31">
         <v>0.9</v>
@@ -8289,7 +8282,7 @@
       </c>
       <c r="K76" s="27">
         <f t="shared" si="648"/>
-        <v>134.54838709677415</v>
+        <v>139.0333333333333</v>
       </c>
       <c r="L76" s="27">
         <f t="shared" si="649"/>
@@ -8297,13 +8290,13 @@
       </c>
       <c r="M76" s="28">
         <f t="shared" si="650"/>
-        <v>0.31000000000000005</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="N76" s="31">
         <v>0.06</v>
       </c>
       <c r="O76" s="31">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="P76" s="31">
         <v>0.06</v>
@@ -8312,44 +8305,238 @@
         <v>0.02</v>
       </c>
       <c r="R76" s="32">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="S76" s="30" t="s">
         <v>85</v>
       </c>
       <c r="T76" s="27">
-        <f t="shared" ref="T76" si="673">ROUND(B76/K76,3)</f>
-        <v>0.999</v>
+        <f t="shared" ref="T76:T78" si="673">ROUND(B76/K76,3)</f>
+        <v>1.0129999999999999</v>
       </c>
       <c r="U76" s="27">
-        <f t="shared" ref="U76" si="674">ROUND(C76/L76,3)</f>
-        <v>0.98899999999999999</v>
+        <f t="shared" ref="U76:U78" si="674">ROUND(C76/L76,3)</f>
+        <v>1.0249999999999999</v>
       </c>
       <c r="V76" s="28">
-        <f t="shared" ref="V76" si="675">ROUND(D76/M76,3)</f>
-        <v>12.065</v>
+        <f t="shared" ref="V76:V78" si="675">ROUND(D76/M76,3)</f>
+        <v>11.9</v>
       </c>
       <c r="W76" s="31">
-        <f t="shared" ref="W76" si="676">ROUND(E76/N76,3)</f>
-        <v>7.3330000000000002</v>
+        <f t="shared" ref="W76:W78" si="676">ROUND(E76/N76,3)</f>
+        <v>6.1669999999999998</v>
       </c>
       <c r="X76" s="31">
-        <f t="shared" ref="X76" si="677">ROUND(F76/O76,3)</f>
-        <v>11.913</v>
+        <f t="shared" ref="X76:X78" si="677">ROUND(F76/O76,3)</f>
+        <v>11.682</v>
       </c>
       <c r="Y76" s="31">
-        <f t="shared" ref="Y76" si="678">ROUND(G76/P76,3)</f>
+        <f t="shared" ref="Y76:Y78" si="678">ROUND(G76/P76,3)</f>
         <v>15</v>
       </c>
       <c r="Z76" s="31">
-        <f t="shared" ref="Z76" si="679">ROUND(H76/Q76,3)</f>
+        <f t="shared" ref="Z76:Z78" si="679">ROUND(H76/Q76,3)</f>
         <v>5</v>
       </c>
       <c r="AA76" s="32">
-        <f t="shared" ref="AA76" si="680">ROUND(I76/R76,3)</f>
+        <f t="shared" ref="AA76:AA78" si="680">ROUND(I76/R76,3)</f>
+        <v>4</v>
+      </c>
+      <c r="AB76" s="20"/>
+    </row>
+    <row r="77" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" s="44">
+        <f t="shared" ref="B77:B78" si="681">D$2/D77</f>
+        <v>152.83282674772033</v>
+      </c>
+      <c r="C77" s="44">
+        <f t="shared" ref="C77:C78" si="682">D76/D77</f>
+        <v>1.0851063829787233</v>
+      </c>
+      <c r="D77" s="45">
+        <f t="shared" ref="D77:D78" si="683">SUM(F77:H77)</f>
+        <v>3.29</v>
+      </c>
+      <c r="E77" s="43">
+        <v>0.39</v>
+      </c>
+      <c r="F77" s="9">
+        <v>2.59</v>
+      </c>
+      <c r="G77" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I77" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="J77" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="K77" s="44">
+        <f t="shared" ref="K77:K78" si="684">M$2/M77</f>
+        <v>139.0333333333333</v>
+      </c>
+      <c r="L77" s="44">
+        <f t="shared" ref="L77:L78" si="685">M76/M77</f>
+        <v>1</v>
+      </c>
+      <c r="M77" s="45">
+        <f t="shared" ref="M77:M78" si="686">SUM(O77:Q77)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N77" s="43">
+        <v>0.06</v>
+      </c>
+      <c r="O77" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="P77" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R77" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="S77" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="T77" s="44">
+        <f t="shared" si="673"/>
+        <v>1.099</v>
+      </c>
+      <c r="U77" s="44">
+        <f t="shared" si="674"/>
+        <v>1.085</v>
+      </c>
+      <c r="V77" s="45">
+        <f t="shared" si="675"/>
+        <v>10.967000000000001</v>
+      </c>
+      <c r="W77" s="43">
+        <f t="shared" si="676"/>
+        <v>6.5</v>
+      </c>
+      <c r="X77" s="9">
+        <f t="shared" si="677"/>
+        <v>11.773</v>
+      </c>
+      <c r="Y77" s="13">
+        <f t="shared" si="678"/>
+        <v>10</v>
+      </c>
+      <c r="Z77" s="9">
+        <f t="shared" si="679"/>
         <v>5</v>
       </c>
-      <c r="AB76" s="20"/>
+      <c r="AA77" s="10">
+        <f t="shared" si="680"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78" s="41">
+        <f t="shared" si="681"/>
+        <v>149.64880952380952</v>
+      </c>
+      <c r="C78" s="41">
+        <f t="shared" si="682"/>
+        <v>0.97916666666666674</v>
+      </c>
+      <c r="D78" s="42">
+        <f t="shared" si="683"/>
+        <v>3.36</v>
+      </c>
+      <c r="E78" s="43">
+        <v>0.38</v>
+      </c>
+      <c r="F78" s="9">
+        <v>2.67</v>
+      </c>
+      <c r="G78" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="H78" s="13">
+        <v>0.09</v>
+      </c>
+      <c r="I78" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="J78" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="K78" s="41">
+        <f t="shared" si="684"/>
+        <v>139.0333333333333</v>
+      </c>
+      <c r="L78" s="41">
+        <f t="shared" si="685"/>
+        <v>1</v>
+      </c>
+      <c r="M78" s="42">
+        <f t="shared" si="686"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N78" s="43">
+        <v>0.06</v>
+      </c>
+      <c r="O78" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="P78" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="Q78" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="R78" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="S78" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="T78" s="41">
+        <f t="shared" si="673"/>
+        <v>1.0760000000000001</v>
+      </c>
+      <c r="U78" s="41">
+        <f t="shared" si="674"/>
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="V78" s="42">
+        <f t="shared" si="675"/>
+        <v>11.2</v>
+      </c>
+      <c r="W78" s="43">
+        <f t="shared" si="676"/>
+        <v>6.3330000000000002</v>
+      </c>
+      <c r="X78" s="9">
+        <f t="shared" si="677"/>
+        <v>11.609</v>
+      </c>
+      <c r="Y78" s="9">
+        <f t="shared" si="678"/>
+        <v>10</v>
+      </c>
+      <c r="Z78" s="13">
+        <f t="shared" si="679"/>
+        <v>9</v>
+      </c>
+      <c r="AA78" s="10">
+        <f t="shared" si="680"/>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60930FA8-F0CC-4767-AE0C-D4DEED37322B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEC56CA-DF4A-48FA-A15A-8E1A8FFD769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="90">
   <si>
     <t>H23</t>
   </si>
@@ -361,6 +361,10 @@
   </si>
   <si>
     <t>H99</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H100</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -369,7 +373,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000_);[Red]\(0.000\)"/>
+    <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -521,121 +525,121 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -952,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB79"/>
+  <dimension ref="A1:AB80"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="5"/>
@@ -8245,51 +8249,51 @@
       </c>
       <c r="B76" s="8">
         <f t="shared" ref="B76" si="670">D$2/D76</f>
-        <v>140.45418994413407</v>
+        <v>139.59633536923931</v>
       </c>
       <c r="C76" s="8">
         <f t="shared" ref="C76" si="671">D75/D76</f>
-        <v>1.0279329608938546</v>
+        <v>1.0216546363131593</v>
       </c>
       <c r="D76" s="9">
         <f t="shared" ref="D76" si="672">SUM(F76:H76)</f>
-        <v>3.58</v>
+        <v>3.6019999999999999</v>
       </c>
       <c r="E76" s="34">
-        <v>0.4</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F76" s="34">
-        <v>2.5739999999999998</v>
+        <v>2.6070000000000002</v>
       </c>
       <c r="G76" s="34">
-        <v>0.90300000000000002</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="H76" s="34">
-        <v>0.10299999999999999</v>
+        <v>9.4E-2</v>
       </c>
       <c r="I76" s="31">
-        <v>0.20300000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J76" s="33" t="s">
         <v>85</v>
       </c>
       <c r="K76" s="8">
         <f t="shared" si="648"/>
-        <v>137.20394736842101</v>
+        <v>142.35494880546071</v>
       </c>
       <c r="L76" s="8">
         <f t="shared" si="649"/>
-        <v>0.98355263157894735</v>
+        <v>1.0204778156996588</v>
       </c>
       <c r="M76" s="9">
         <f t="shared" si="650"/>
-        <v>0.30400000000000005</v>
+        <v>0.29300000000000004</v>
       </c>
       <c r="N76" s="34">
         <v>0.06</v>
       </c>
       <c r="O76" s="34">
-        <v>0.22500000000000001</v>
+        <v>0.214</v>
       </c>
       <c r="P76" s="34">
         <v>6.3E-2</v>
@@ -8305,35 +8309,35 @@
       </c>
       <c r="T76" s="8">
         <f t="shared" ref="T76:T78" si="673">ROUND(B76/K76,3)</f>
-        <v>1.024</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="U76" s="8">
         <f t="shared" ref="U76:U78" si="674">ROUND(C76/L76,3)</f>
-        <v>1.0449999999999999</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="V76" s="9">
         <f t="shared" ref="V76:V78" si="675">ROUND(D76/M76,3)</f>
-        <v>11.776</v>
+        <v>12.294</v>
       </c>
       <c r="W76" s="34">
         <f t="shared" ref="W76:W78" si="676">ROUND(E76/N76,3)</f>
-        <v>6.6669999999999998</v>
+        <v>6.383</v>
       </c>
       <c r="X76" s="34">
         <f t="shared" ref="X76:X78" si="677">ROUND(F76/O76,3)</f>
-        <v>11.44</v>
+        <v>12.182</v>
       </c>
       <c r="Y76" s="34">
         <f t="shared" ref="Y76:Y78" si="678">ROUND(G76/P76,3)</f>
-        <v>14.333</v>
+        <v>14.302</v>
       </c>
       <c r="Z76" s="34">
         <f t="shared" ref="Z76:Z78" si="679">ROUND(H76/Q76,3)</f>
-        <v>6.4379999999999997</v>
+        <v>5.875</v>
       </c>
       <c r="AA76" s="31">
         <f t="shared" ref="AA76:AA78" si="680">ROUND(I76/R76,3)</f>
-        <v>4.6139999999999999</v>
+        <v>4.5449999999999999</v>
       </c>
       <c r="AB76" s="32"/>
     </row>
@@ -8343,95 +8347,95 @@
       </c>
       <c r="B77" s="2">
         <f t="shared" ref="B77:B78" si="681">D$2/D77</f>
-        <v>154.00490045941808</v>
+        <v>154.71569230769234</v>
       </c>
       <c r="C77" s="2">
         <f t="shared" ref="C77:C78" si="682">D76/D77</f>
-        <v>1.0964777947932618</v>
+        <v>1.1083076923076924</v>
       </c>
       <c r="D77" s="13">
         <f t="shared" ref="D77:D78" si="683">SUM(F77:H77)</f>
-        <v>3.2650000000000001</v>
+        <v>3.2499999999999996</v>
       </c>
       <c r="E77" s="6">
-        <v>0.38</v>
+        <v>0.376</v>
       </c>
       <c r="F77" s="6">
-        <v>2.573</v>
+        <v>2.5539999999999998</v>
       </c>
       <c r="G77" s="23">
-        <v>0.60099999999999998</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="H77" s="6">
-        <v>9.0999999999999998E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I77" s="28">
-        <v>0.20100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J77" s="32" t="s">
         <v>86</v>
       </c>
       <c r="K77" s="2">
-        <f t="shared" ref="K77:K79" si="684">M$2/M77</f>
-        <v>138.11258278145692</v>
+        <f t="shared" ref="K77:K78" si="684">M$2/M77</f>
+        <v>143.82758620689651</v>
       </c>
       <c r="L77" s="2">
-        <f t="shared" ref="L77:L79" si="685">M76/M77</f>
-        <v>1.0066225165562914</v>
+        <f t="shared" ref="L77:L78" si="685">M76/M77</f>
+        <v>1.0103448275862068</v>
       </c>
       <c r="M77" s="13">
-        <f t="shared" ref="M77:M79" si="686">SUM(O77:Q77)</f>
-        <v>0.30200000000000005</v>
+        <f t="shared" ref="M77:M80" si="686">SUM(O77:Q77)</f>
+        <v>0.29000000000000004</v>
       </c>
       <c r="N77" s="6">
-        <v>6.2E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="O77" s="6">
-        <v>0.22700000000000001</v>
+        <v>0.214</v>
       </c>
       <c r="P77" s="23">
-        <v>5.8999999999999997E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="Q77" s="6">
-        <v>1.6E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="R77" s="28">
-        <v>0.04</v>
+        <v>3.9E-2</v>
       </c>
       <c r="S77" s="32" t="s">
         <v>86</v>
       </c>
       <c r="T77" s="2">
         <f t="shared" si="673"/>
-        <v>1.115</v>
+        <v>1.0760000000000001</v>
       </c>
       <c r="U77" s="2">
         <f t="shared" si="674"/>
-        <v>1.089</v>
+        <v>1.097</v>
       </c>
       <c r="V77" s="13">
         <f t="shared" si="675"/>
-        <v>10.811</v>
+        <v>11.207000000000001</v>
       </c>
       <c r="W77" s="6">
         <f t="shared" si="676"/>
-        <v>6.1289999999999996</v>
+        <v>6.4829999999999997</v>
       </c>
       <c r="X77" s="6">
         <f t="shared" si="677"/>
-        <v>11.335000000000001</v>
+        <v>11.935</v>
       </c>
       <c r="Y77" s="23">
         <f t="shared" si="678"/>
-        <v>10.186</v>
+        <v>10.491</v>
       </c>
       <c r="Z77" s="6">
         <f t="shared" si="679"/>
-        <v>5.6879999999999997</v>
+        <v>5.1580000000000004</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="680"/>
-        <v>5.0250000000000004</v>
+        <v>5.1280000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8440,51 +8444,51 @@
       </c>
       <c r="B78" s="2">
         <f t="shared" si="681"/>
-        <v>154.57300952966492</v>
+        <v>154.62054120541205</v>
       </c>
       <c r="C78" s="2">
         <f t="shared" si="682"/>
-        <v>1.003688902551491</v>
+        <v>0.99938499384993829</v>
       </c>
       <c r="D78" s="13">
         <f t="shared" si="683"/>
-        <v>3.2530000000000001</v>
+        <v>3.2520000000000002</v>
       </c>
       <c r="E78" s="6">
-        <v>0.38400000000000001</v>
+        <v>0.376</v>
       </c>
       <c r="F78" s="6">
         <v>2.556</v>
       </c>
       <c r="G78" s="6">
-        <v>0.59899999999999998</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="H78" s="23">
-        <v>9.8000000000000004E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I78" s="24">
-        <v>0.20200000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J78" s="32" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="2">
         <f t="shared" si="684"/>
-        <v>147.90780141843967</v>
+        <v>143.82758620689651</v>
       </c>
       <c r="L78" s="2">
         <f t="shared" si="685"/>
-        <v>1.0709219858156029</v>
+        <v>1</v>
       </c>
       <c r="M78" s="13">
         <f t="shared" si="686"/>
-        <v>0.28200000000000003</v>
+        <v>0.29000000000000004</v>
       </c>
       <c r="N78" s="6">
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="O78" s="6">
-        <v>0.214</v>
+        <v>0.222</v>
       </c>
       <c r="P78" s="6">
         <v>5.6000000000000001E-2</v>
@@ -8500,35 +8504,35 @@
       </c>
       <c r="T78" s="2">
         <f t="shared" si="673"/>
-        <v>1.0449999999999999</v>
+        <v>1.075</v>
       </c>
       <c r="U78" s="2">
         <f t="shared" si="674"/>
-        <v>0.93700000000000006</v>
+        <v>0.999</v>
       </c>
       <c r="V78" s="13">
         <f t="shared" si="675"/>
-        <v>11.535</v>
+        <v>11.214</v>
       </c>
       <c r="W78" s="6">
         <f t="shared" si="676"/>
-        <v>6.508</v>
+        <v>6.3730000000000002</v>
       </c>
       <c r="X78" s="6">
         <f t="shared" si="677"/>
-        <v>11.944000000000001</v>
+        <v>11.513999999999999</v>
       </c>
       <c r="Y78" s="6">
         <f t="shared" si="678"/>
-        <v>10.696</v>
+        <v>10.661</v>
       </c>
       <c r="Z78" s="23">
         <f t="shared" si="679"/>
-        <v>8.1669999999999998</v>
+        <v>8.25</v>
       </c>
       <c r="AA78" s="24">
         <f t="shared" si="680"/>
-        <v>5.4589999999999996</v>
+        <v>5.4050000000000002</v>
       </c>
     </row>
     <row r="79" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8537,96 +8541,194 @@
       </c>
       <c r="B79" s="2">
         <f t="shared" ref="B79" si="687">D$2/D79</f>
-        <v>154.76331178824253</v>
+        <v>153.58155161881493</v>
       </c>
       <c r="C79" s="2">
         <f t="shared" ref="C79" si="688">D78/D79</f>
-        <v>1.0012311480455525</v>
+        <v>0.99328039095907172</v>
       </c>
       <c r="D79" s="13">
         <f t="shared" ref="D79" si="689">SUM(F79:H79)</f>
-        <v>3.2490000000000001</v>
+        <v>3.2739999999999996</v>
       </c>
       <c r="E79" s="6">
-        <v>0.45700000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="F79" s="23">
-        <v>2.5510000000000002</v>
+        <v>2.5779999999999998</v>
       </c>
       <c r="G79" s="23">
-        <v>0.6</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="H79" s="6">
-        <v>9.8000000000000004E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I79" s="28">
-        <v>0.19900000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="J79" s="32" t="s">
         <v>88</v>
       </c>
       <c r="K79" s="2">
-        <f t="shared" ref="K79" si="690">M$2/M79</f>
-        <v>157.99242424242422</v>
+        <f t="shared" ref="K79:K80" si="690">M$2/M79</f>
+        <v>160.42307692307691</v>
       </c>
       <c r="L79" s="2">
-        <f t="shared" ref="L79" si="691">M78/M79</f>
-        <v>1.0681818181818183</v>
+        <f t="shared" ref="L79:L80" si="691">M78/M79</f>
+        <v>1.1153846153846154</v>
       </c>
       <c r="M79" s="13">
         <f t="shared" si="686"/>
-        <v>0.26400000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="N79" s="6">
-        <v>6.3E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="O79" s="23">
-        <v>0.2</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="P79" s="23">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="Q79" s="6">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="R79" s="28">
-        <v>3.5999999999999997E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="S79" s="32" t="s">
         <v>88</v>
       </c>
       <c r="T79" s="2">
         <f t="shared" ref="T79" si="692">ROUND(B79/K79,3)</f>
-        <v>0.98</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="U79" s="2">
         <f t="shared" ref="U79" si="693">ROUND(C79/L79,3)</f>
-        <v>0.93700000000000006</v>
+        <v>0.89100000000000001</v>
       </c>
       <c r="V79" s="13">
         <f t="shared" ref="V79" si="694">ROUND(D79/M79,3)</f>
-        <v>12.307</v>
+        <v>12.592000000000001</v>
       </c>
       <c r="W79" s="6">
         <f t="shared" ref="W79" si="695">ROUND(E79/N79,3)</f>
-        <v>7.2539999999999996</v>
+        <v>6.3789999999999996</v>
       </c>
       <c r="X79" s="23">
         <f t="shared" ref="X79" si="696">ROUND(F79/O79,3)</f>
-        <v>12.755000000000001</v>
+        <v>13.086</v>
       </c>
       <c r="Y79" s="23">
         <f t="shared" ref="Y79" si="697">ROUND(G79/P79,3)</f>
-        <v>11.765000000000001</v>
+        <v>11.744999999999999</v>
       </c>
       <c r="Z79" s="6">
         <f t="shared" ref="Z79" si="698">ROUND(H79/Q79,3)</f>
-        <v>7.5380000000000003</v>
+        <v>8.0830000000000002</v>
       </c>
       <c r="AA79" s="28">
         <f t="shared" ref="AA79" si="699">ROUND(I79/R79,3)</f>
-        <v>5.5279999999999996</v>
-      </c>
+        <v>5.7430000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" s="14">
+        <f t="shared" ref="B80" si="700">D$2/D80</f>
+        <v>154.1938055811101</v>
+      </c>
+      <c r="C80" s="14">
+        <f t="shared" ref="C80" si="701">D79/D80</f>
+        <v>1.0039865072063783</v>
+      </c>
+      <c r="D80" s="17">
+        <f t="shared" ref="D80" si="702">SUM(F80:H80)</f>
+        <v>3.2609999999999997</v>
+      </c>
+      <c r="E80" s="22">
+        <v>0.43</v>
+      </c>
+      <c r="F80" s="22">
+        <v>2.57</v>
+      </c>
+      <c r="G80" s="22">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="H80" s="22">
+        <v>9.4E-2</v>
+      </c>
+      <c r="I80" s="35">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="J80" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="K80" s="14">
+        <f t="shared" si="690"/>
+        <v>160.42307692307691</v>
+      </c>
+      <c r="L80" s="14">
+        <f t="shared" si="691"/>
+        <v>1</v>
+      </c>
+      <c r="M80" s="17">
+        <f t="shared" si="686"/>
+        <v>0.26</v>
+      </c>
+      <c r="N80" s="22">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="O80" s="22">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="P80" s="22">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q80" s="22">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R80" s="35">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S80" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="T80" s="14">
+        <f t="shared" ref="T80" si="703">ROUND(B80/K80,3)</f>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="U80" s="14">
+        <f t="shared" ref="U80" si="704">ROUND(C80/L80,3)</f>
+        <v>1.004</v>
+      </c>
+      <c r="V80" s="17">
+        <f t="shared" ref="V80" si="705">ROUND(D80/M80,3)</f>
+        <v>12.542</v>
+      </c>
+      <c r="W80" s="22">
+        <f t="shared" ref="W80" si="706">ROUND(E80/N80,3)</f>
+        <v>6.2320000000000002</v>
+      </c>
+      <c r="X80" s="22">
+        <f t="shared" ref="X80" si="707">ROUND(F80/O80,3)</f>
+        <v>13.045999999999999</v>
+      </c>
+      <c r="Y80" s="22">
+        <f t="shared" ref="Y80" si="708">ROUND(G80/P80,3)</f>
+        <v>11.706</v>
+      </c>
+      <c r="Z80" s="22">
+        <f t="shared" ref="Z80" si="709">ROUND(H80/Q80,3)</f>
+        <v>7.8330000000000002</v>
+      </c>
+      <c r="AA80" s="35">
+        <f t="shared" ref="AA80" si="710">ROUND(I80/R80,3)</f>
+        <v>5.6390000000000002</v>
+      </c>
+      <c r="AB80" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEC56CA-DF4A-48FA-A15A-8E1A8FFD769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45488E82-8A05-4BD0-82D6-60350FA49B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="93">
   <si>
     <t>H23</t>
   </si>
@@ -365,6 +365,18 @@
   </si>
   <si>
     <t>H100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H101</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H103</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -956,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB80"/>
+  <dimension ref="A1:AB83"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="5"/>
@@ -8249,30 +8261,30 @@
       </c>
       <c r="B76" s="8">
         <f t="shared" ref="B76" si="670">D$2/D76</f>
-        <v>139.59633536923931</v>
+        <v>138.4814100798678</v>
       </c>
       <c r="C76" s="8">
         <f t="shared" ref="C76" si="671">D75/D76</f>
-        <v>1.0216546363131593</v>
+        <v>1.0134949049848525</v>
       </c>
       <c r="D76" s="9">
         <f t="shared" ref="D76" si="672">SUM(F76:H76)</f>
-        <v>3.6019999999999999</v>
+        <v>3.6310000000000002</v>
       </c>
       <c r="E76" s="34">
-        <v>0.38300000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="F76" s="34">
-        <v>2.6070000000000002</v>
+        <v>2.6269999999999998</v>
       </c>
       <c r="G76" s="34">
-        <v>0.90100000000000002</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="H76" s="34">
-        <v>9.4E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I76" s="31">
-        <v>0.2</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="J76" s="33" t="s">
         <v>85</v>
@@ -8309,35 +8321,35 @@
       </c>
       <c r="T76" s="8">
         <f t="shared" ref="T76:T78" si="673">ROUND(B76/K76,3)</f>
-        <v>0.98099999999999998</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="U76" s="8">
         <f t="shared" ref="U76:U78" si="674">ROUND(C76/L76,3)</f>
-        <v>1.0009999999999999</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="V76" s="9">
         <f t="shared" ref="V76:V78" si="675">ROUND(D76/M76,3)</f>
-        <v>12.294</v>
+        <v>12.391999999999999</v>
       </c>
       <c r="W76" s="34">
         <f t="shared" ref="W76:W78" si="676">ROUND(E76/N76,3)</f>
-        <v>6.383</v>
+        <v>6.2169999999999996</v>
       </c>
       <c r="X76" s="34">
         <f t="shared" ref="X76:X78" si="677">ROUND(F76/O76,3)</f>
-        <v>12.182</v>
+        <v>12.276</v>
       </c>
       <c r="Y76" s="34">
         <f t="shared" ref="Y76:Y78" si="678">ROUND(G76/P76,3)</f>
-        <v>14.302</v>
+        <v>14.365</v>
       </c>
       <c r="Z76" s="34">
         <f t="shared" ref="Z76:Z78" si="679">ROUND(H76/Q76,3)</f>
-        <v>5.875</v>
+        <v>6.1879999999999997</v>
       </c>
       <c r="AA76" s="31">
         <f t="shared" ref="AA76:AA78" si="680">ROUND(I76/R76,3)</f>
-        <v>4.5449999999999999</v>
+        <v>4.5679999999999996</v>
       </c>
       <c r="AB76" s="32"/>
     </row>
@@ -8347,57 +8359,57 @@
       </c>
       <c r="B77" s="2">
         <f t="shared" ref="B77:B78" si="681">D$2/D77</f>
-        <v>154.71569230769234</v>
+        <v>151.04415740462602</v>
       </c>
       <c r="C77" s="2">
         <f t="shared" ref="C77:C78" si="682">D76/D77</f>
-        <v>1.1083076923076924</v>
+        <v>1.0907179333133075</v>
       </c>
       <c r="D77" s="13">
         <f t="shared" ref="D77:D78" si="683">SUM(F77:H77)</f>
-        <v>3.2499999999999996</v>
+        <v>3.3289999999999997</v>
       </c>
       <c r="E77" s="6">
-        <v>0.376</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="F77" s="6">
-        <v>2.5539999999999998</v>
+        <v>2.6259999999999999</v>
       </c>
       <c r="G77" s="23">
-        <v>0.59799999999999998</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="H77" s="6">
-        <v>9.8000000000000004E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I77" s="28">
-        <v>0.2</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="J77" s="32" t="s">
         <v>86</v>
       </c>
       <c r="K77" s="2">
         <f t="shared" ref="K77:K78" si="684">M$2/M77</f>
-        <v>143.82758620689651</v>
+        <v>142.84246575342462</v>
       </c>
       <c r="L77" s="2">
         <f t="shared" ref="L77:L78" si="685">M76/M77</f>
-        <v>1.0103448275862068</v>
+        <v>1.0034246575342465</v>
       </c>
       <c r="M77" s="13">
         <f t="shared" ref="M77:M80" si="686">SUM(O77:Q77)</f>
-        <v>0.29000000000000004</v>
+        <v>0.29200000000000004</v>
       </c>
       <c r="N77" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="O77" s="6">
+        <v>0.218</v>
+      </c>
+      <c r="P77" s="23">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="O77" s="6">
-        <v>0.214</v>
-      </c>
-      <c r="P77" s="23">
-        <v>5.7000000000000002E-2</v>
-      </c>
       <c r="Q77" s="6">
-        <v>1.9E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="R77" s="28">
         <v>3.9E-2</v>
@@ -8407,35 +8419,35 @@
       </c>
       <c r="T77" s="2">
         <f t="shared" si="673"/>
-        <v>1.0760000000000001</v>
+        <v>1.0569999999999999</v>
       </c>
       <c r="U77" s="2">
         <f t="shared" si="674"/>
-        <v>1.097</v>
+        <v>1.087</v>
       </c>
       <c r="V77" s="13">
         <f t="shared" si="675"/>
-        <v>11.207000000000001</v>
+        <v>11.401</v>
       </c>
       <c r="W77" s="6">
         <f t="shared" si="676"/>
-        <v>6.4829999999999997</v>
+        <v>6.7</v>
       </c>
       <c r="X77" s="6">
         <f t="shared" si="677"/>
-        <v>11.935</v>
+        <v>12.045999999999999</v>
       </c>
       <c r="Y77" s="23">
         <f t="shared" si="678"/>
-        <v>10.491</v>
+        <v>10.362</v>
       </c>
       <c r="Z77" s="6">
         <f t="shared" si="679"/>
-        <v>5.1580000000000004</v>
+        <v>6.375</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="680"/>
-        <v>5.1280000000000001</v>
+        <v>5.1539999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8444,51 +8456,51 @@
       </c>
       <c r="B78" s="2">
         <f t="shared" si="681"/>
-        <v>154.62054120541205</v>
+        <v>149.91830649970188</v>
       </c>
       <c r="C78" s="2">
         <f t="shared" si="682"/>
-        <v>0.99938499384993829</v>
+        <v>0.99254621347644612</v>
       </c>
       <c r="D78" s="13">
         <f t="shared" si="683"/>
-        <v>3.2520000000000002</v>
+        <v>3.3539999999999996</v>
       </c>
       <c r="E78" s="6">
-        <v>0.376</v>
+        <v>0.371</v>
       </c>
       <c r="F78" s="6">
-        <v>2.556</v>
+        <v>2.6629999999999998</v>
       </c>
       <c r="G78" s="6">
-        <v>0.59699999999999998</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="H78" s="23">
-        <v>9.9000000000000005E-2</v>
+        <v>0.09</v>
       </c>
       <c r="I78" s="24">
-        <v>0.2</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="J78" s="32" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="2">
         <f t="shared" si="684"/>
-        <v>143.82758620689651</v>
+        <v>146.86619718309856</v>
       </c>
       <c r="L78" s="2">
         <f t="shared" si="685"/>
-        <v>1</v>
+        <v>1.028169014084507</v>
       </c>
       <c r="M78" s="13">
         <f t="shared" si="686"/>
-        <v>0.29000000000000004</v>
+        <v>0.28400000000000003</v>
       </c>
       <c r="N78" s="6">
-        <v>5.8999999999999997E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O78" s="6">
-        <v>0.222</v>
+        <v>0.216</v>
       </c>
       <c r="P78" s="6">
         <v>5.6000000000000001E-2</v>
@@ -8504,35 +8516,35 @@
       </c>
       <c r="T78" s="2">
         <f t="shared" si="673"/>
-        <v>1.075</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="U78" s="2">
         <f t="shared" si="674"/>
-        <v>0.999</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="V78" s="13">
         <f t="shared" si="675"/>
-        <v>11.214</v>
+        <v>11.81</v>
       </c>
       <c r="W78" s="6">
         <f t="shared" si="676"/>
-        <v>6.3730000000000002</v>
+        <v>6.1829999999999998</v>
       </c>
       <c r="X78" s="6">
         <f t="shared" si="677"/>
-        <v>11.513999999999999</v>
+        <v>12.329000000000001</v>
       </c>
       <c r="Y78" s="6">
         <f t="shared" si="678"/>
-        <v>10.661</v>
+        <v>10.731999999999999</v>
       </c>
       <c r="Z78" s="23">
         <f t="shared" si="679"/>
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA78" s="24">
         <f t="shared" si="680"/>
-        <v>5.4050000000000002</v>
+        <v>5.4320000000000004</v>
       </c>
     </row>
     <row r="79" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8541,27 +8553,27 @@
       </c>
       <c r="B79" s="2">
         <f t="shared" ref="B79" si="687">D$2/D79</f>
-        <v>153.58155161881493</v>
+        <v>151.13495641719268</v>
       </c>
       <c r="C79" s="2">
         <f t="shared" ref="C79" si="688">D78/D79</f>
-        <v>0.99328039095907172</v>
+        <v>1.0081154192966635</v>
       </c>
       <c r="D79" s="13">
         <f t="shared" ref="D79" si="689">SUM(F79:H79)</f>
-        <v>3.2739999999999996</v>
+        <v>3.327</v>
       </c>
       <c r="E79" s="6">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="F79" s="23">
-        <v>2.5779999999999998</v>
+        <v>2.625</v>
       </c>
       <c r="G79" s="23">
-        <v>0.59899999999999998</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H79" s="6">
-        <v>9.7000000000000003E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I79" s="28">
         <v>0.20100000000000001</v>
@@ -8571,65 +8583,65 @@
       </c>
       <c r="K79" s="2">
         <f t="shared" ref="K79:K80" si="690">M$2/M79</f>
-        <v>160.42307692307691</v>
+        <v>155.05576208178437</v>
       </c>
       <c r="L79" s="2">
         <f t="shared" ref="L79:L80" si="691">M78/M79</f>
-        <v>1.1153846153846154</v>
+        <v>1.0557620817843867</v>
       </c>
       <c r="M79" s="13">
         <f t="shared" si="686"/>
-        <v>0.26</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="N79" s="6">
-        <v>5.8000000000000003E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O79" s="23">
-        <v>0.19700000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="P79" s="23">
-        <v>5.0999999999999997E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q79" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R79" s="28">
-        <v>3.5000000000000003E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S79" s="32" t="s">
         <v>88</v>
       </c>
       <c r="T79" s="2">
         <f t="shared" ref="T79" si="692">ROUND(B79/K79,3)</f>
-        <v>0.95699999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="U79" s="2">
         <f t="shared" ref="U79" si="693">ROUND(C79/L79,3)</f>
-        <v>0.89100000000000001</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="V79" s="13">
         <f t="shared" ref="V79" si="694">ROUND(D79/M79,3)</f>
-        <v>12.592000000000001</v>
+        <v>12.368</v>
       </c>
       <c r="W79" s="6">
         <f t="shared" ref="W79" si="695">ROUND(E79/N79,3)</f>
-        <v>6.3789999999999996</v>
+        <v>6.6139999999999999</v>
       </c>
       <c r="X79" s="23">
         <f t="shared" ref="X79" si="696">ROUND(F79/O79,3)</f>
-        <v>13.086</v>
+        <v>12.805</v>
       </c>
       <c r="Y79" s="23">
         <f t="shared" ref="Y79" si="697">ROUND(G79/P79,3)</f>
-        <v>11.744999999999999</v>
+        <v>11.615</v>
       </c>
       <c r="Z79" s="6">
         <f t="shared" ref="Z79" si="698">ROUND(H79/Q79,3)</f>
-        <v>8.0830000000000002</v>
+        <v>8.1669999999999998</v>
       </c>
       <c r="AA79" s="28">
         <f t="shared" ref="AA79" si="699">ROUND(I79/R79,3)</f>
-        <v>5.7430000000000003</v>
+        <v>5.5830000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:28" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8638,54 +8650,54 @@
       </c>
       <c r="B80" s="14">
         <f t="shared" ref="B80" si="700">D$2/D80</f>
-        <v>154.1938055811101</v>
+        <v>152.92761557177616</v>
       </c>
       <c r="C80" s="14">
         <f t="shared" ref="C80" si="701">D79/D80</f>
-        <v>1.0039865072063783</v>
+        <v>1.011861313868613</v>
       </c>
       <c r="D80" s="17">
         <f t="shared" ref="D80" si="702">SUM(F80:H80)</f>
-        <v>3.2609999999999997</v>
+        <v>3.2880000000000003</v>
       </c>
       <c r="E80" s="22">
-        <v>0.43</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="F80" s="22">
-        <v>2.57</v>
+        <v>2.5950000000000002</v>
       </c>
       <c r="G80" s="22">
-        <v>0.59699999999999998</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="H80" s="22">
-        <v>9.4E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I80" s="35">
-        <v>0.20300000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J80" s="32" t="s">
         <v>89</v>
       </c>
       <c r="K80" s="14">
         <f t="shared" si="690"/>
-        <v>160.42307692307691</v>
+        <v>156.21722846441943</v>
       </c>
       <c r="L80" s="14">
         <f t="shared" si="691"/>
-        <v>1</v>
+        <v>1.0074906367041199</v>
       </c>
       <c r="M80" s="17">
         <f t="shared" si="686"/>
-        <v>0.26</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="N80" s="22">
-        <v>6.9000000000000006E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="O80" s="22">
-        <v>0.19700000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="P80" s="22">
-        <v>5.0999999999999997E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q80" s="22">
         <v>1.2E-2</v>
@@ -8697,38 +8709,329 @@
         <v>89</v>
       </c>
       <c r="T80" s="14">
-        <f t="shared" ref="T80" si="703">ROUND(B80/K80,3)</f>
-        <v>0.96099999999999997</v>
+        <f t="shared" ref="T80:T83" si="703">ROUND(B80/K80,3)</f>
+        <v>0.97899999999999998</v>
       </c>
       <c r="U80" s="14">
-        <f t="shared" ref="U80" si="704">ROUND(C80/L80,3)</f>
+        <f t="shared" ref="U80:U83" si="704">ROUND(C80/L80,3)</f>
         <v>1.004</v>
       </c>
       <c r="V80" s="17">
-        <f t="shared" ref="V80" si="705">ROUND(D80/M80,3)</f>
-        <v>12.542</v>
+        <f t="shared" ref="V80:V83" si="705">ROUND(D80/M80,3)</f>
+        <v>12.315</v>
       </c>
       <c r="W80" s="22">
-        <f t="shared" ref="W80" si="706">ROUND(E80/N80,3)</f>
-        <v>6.2320000000000002</v>
+        <f t="shared" ref="W80:W83" si="706">ROUND(E80/N80,3)</f>
+        <v>6.569</v>
       </c>
       <c r="X80" s="22">
-        <f t="shared" ref="X80" si="707">ROUND(F80/O80,3)</f>
-        <v>13.045999999999999</v>
+        <f t="shared" ref="X80:X83" si="707">ROUND(F80/O80,3)</f>
+        <v>12.782999999999999</v>
       </c>
       <c r="Y80" s="22">
-        <f t="shared" ref="Y80" si="708">ROUND(G80/P80,3)</f>
-        <v>11.706</v>
+        <f t="shared" ref="Y80:Y83" si="708">ROUND(G80/P80,3)</f>
+        <v>11.5</v>
       </c>
       <c r="Z80" s="22">
-        <f t="shared" ref="Z80" si="709">ROUND(H80/Q80,3)</f>
-        <v>7.8330000000000002</v>
+        <f t="shared" ref="Z80:Z83" si="709">ROUND(H80/Q80,3)</f>
+        <v>7.9169999999999998</v>
       </c>
       <c r="AA80" s="35">
-        <f t="shared" ref="AA80" si="710">ROUND(I80/R80,3)</f>
-        <v>5.6390000000000002</v>
+        <f t="shared" ref="AA80:AA83" si="710">ROUND(I80/R80,3)</f>
+        <v>5.556</v>
       </c>
       <c r="AB80" s="32"/>
+    </row>
+    <row r="81" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="14">
+        <f t="shared" ref="B81:B83" si="711">D$2/D81</f>
+        <v>152.09497882637629</v>
+      </c>
+      <c r="C81" s="14">
+        <f t="shared" ref="C81:C83" si="712">D80/D81</f>
+        <v>0.99455535390199645</v>
+      </c>
+      <c r="D81" s="17">
+        <f t="shared" ref="D81:D83" si="713">SUM(F81:H81)</f>
+        <v>3.306</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="F81" s="6">
+        <v>2.61</v>
+      </c>
+      <c r="G81" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="6">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="I81" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J81" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="K81" s="14">
+        <f t="shared" ref="K81:K83" si="714">M$2/M81</f>
+        <v>158.59315589353608</v>
+      </c>
+      <c r="L81" s="14">
+        <f t="shared" ref="L81:L83" si="715">M80/M81</f>
+        <v>1.0152091254752851</v>
+      </c>
+      <c r="M81" s="17">
+        <f t="shared" ref="M81:M83" si="716">SUM(O81:Q81)</f>
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="N81" s="6">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="O81" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="P81" s="6">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R81" s="28">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S81" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="T81" s="14">
+        <f t="shared" si="703"/>
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="U81" s="14">
+        <f t="shared" si="704"/>
+        <v>0.98</v>
+      </c>
+      <c r="V81" s="17">
+        <f t="shared" si="705"/>
+        <v>12.57</v>
+      </c>
+      <c r="W81" s="22">
+        <f t="shared" si="706"/>
+        <v>6.5890000000000004</v>
+      </c>
+      <c r="X81" s="22">
+        <f t="shared" si="707"/>
+        <v>13.05</v>
+      </c>
+      <c r="Y81" s="22">
+        <f t="shared" si="708"/>
+        <v>11.765000000000001</v>
+      </c>
+      <c r="Z81" s="22">
+        <f t="shared" si="709"/>
+        <v>8</v>
+      </c>
+      <c r="AA81" s="35">
+        <f t="shared" si="710"/>
+        <v>5.556</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="14">
+        <f t="shared" si="711"/>
+        <v>152.14099848714071</v>
+      </c>
+      <c r="C82" s="14">
+        <f t="shared" si="712"/>
+        <v>1.0003025718608169</v>
+      </c>
+      <c r="D82" s="17">
+        <f t="shared" si="713"/>
+        <v>3.3049999999999997</v>
+      </c>
+      <c r="E82" s="6">
+        <v>0.378</v>
+      </c>
+      <c r="F82" s="6">
+        <v>2.6040000000000001</v>
+      </c>
+      <c r="G82" s="6">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="H82" s="6">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="I82" s="28">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="J82" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="K82" s="14">
+        <f t="shared" si="714"/>
+        <v>157.99242424242422</v>
+      </c>
+      <c r="L82" s="14">
+        <f t="shared" si="715"/>
+        <v>0.99621212121212122</v>
+      </c>
+      <c r="M82" s="17">
+        <f t="shared" si="716"/>
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="N82" s="6">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="O82" s="6">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="P82" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R82" s="28">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S82" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="T82" s="14">
+        <f t="shared" si="703"/>
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="U82" s="14">
+        <f t="shared" si="704"/>
+        <v>1.004</v>
+      </c>
+      <c r="V82" s="17">
+        <f t="shared" si="705"/>
+        <v>12.519</v>
+      </c>
+      <c r="W82" s="22">
+        <f t="shared" si="706"/>
+        <v>6.5170000000000003</v>
+      </c>
+      <c r="X82" s="22">
+        <f t="shared" si="707"/>
+        <v>12.891</v>
+      </c>
+      <c r="Y82" s="22">
+        <f t="shared" si="708"/>
+        <v>12.06</v>
+      </c>
+      <c r="Z82" s="22">
+        <f t="shared" si="709"/>
+        <v>8.1669999999999998</v>
+      </c>
+      <c r="AA82" s="35">
+        <f t="shared" si="710"/>
+        <v>5.5830000000000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" s="14">
+        <f t="shared" si="711"/>
+        <v>150.90816326530614</v>
+      </c>
+      <c r="C83" s="14">
+        <f t="shared" si="712"/>
+        <v>0.99189675870348137</v>
+      </c>
+      <c r="D83" s="17">
+        <f t="shared" si="713"/>
+        <v>3.3319999999999999</v>
+      </c>
+      <c r="E83" s="6">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="F83" s="6">
+        <v>2.637</v>
+      </c>
+      <c r="G83" s="6">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="H83" s="6">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="I83" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J83" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="K83" s="14">
+        <f t="shared" si="714"/>
+        <v>155.63432835820893</v>
+      </c>
+      <c r="L83" s="14">
+        <f t="shared" si="715"/>
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="M83" s="17">
+        <f t="shared" si="716"/>
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="N83" s="6">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="O83" s="6">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="P83" s="6">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R83" s="28">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S83" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="T83" s="14">
+        <f t="shared" si="703"/>
+        <v>0.97</v>
+      </c>
+      <c r="U83" s="14">
+        <f t="shared" si="704"/>
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="V83" s="17">
+        <f t="shared" si="705"/>
+        <v>12.433</v>
+      </c>
+      <c r="W83" s="22">
+        <f t="shared" si="706"/>
+        <v>6.415</v>
+      </c>
+      <c r="X83" s="22">
+        <f t="shared" si="707"/>
+        <v>12.926</v>
+      </c>
+      <c r="Y83" s="22">
+        <f t="shared" si="708"/>
+        <v>11.577</v>
+      </c>
+      <c r="Z83" s="22">
+        <f t="shared" si="709"/>
+        <v>7.75</v>
+      </c>
+      <c r="AA83" s="35">
+        <f t="shared" si="710"/>
+        <v>5.4050000000000002</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45488E82-8A05-4BD0-82D6-60350FA49B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8CE3C5-CEB7-4F0B-86D8-FC7A452891C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="4545" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="96">
   <si>
     <t>H23</t>
   </si>
@@ -377,6 +377,18 @@
   </si>
   <si>
     <t>H103</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H105</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H106</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -968,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB83"/>
+  <dimension ref="A1:AB86"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="5"/>
@@ -8256,100 +8268,100 @@
       <c r="AB75" s="38"/>
     </row>
     <row r="76" spans="1:28" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="33" t="s">
+      <c r="A76" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="14">
         <f t="shared" ref="B76" si="670">D$2/D76</f>
-        <v>138.4814100798678</v>
-      </c>
-      <c r="C76" s="8">
+        <v>138.71062068965517</v>
+      </c>
+      <c r="C76" s="14">
         <f t="shared" ref="C76" si="671">D75/D76</f>
-        <v>1.0134949049848525</v>
-      </c>
-      <c r="D76" s="9">
+        <v>1.0151724137931033</v>
+      </c>
+      <c r="D76" s="17">
         <f t="shared" ref="D76" si="672">SUM(F76:H76)</f>
-        <v>3.6310000000000002</v>
-      </c>
-      <c r="E76" s="34">
-        <v>0.373</v>
-      </c>
-      <c r="F76" s="34">
-        <v>2.6269999999999998</v>
-      </c>
-      <c r="G76" s="34">
-        <v>0.90500000000000003</v>
-      </c>
-      <c r="H76" s="34">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="I76" s="31">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="J76" s="33" t="s">
+        <v>3.6250000000000004</v>
+      </c>
+      <c r="E76" s="22">
+        <v>0.37</v>
+      </c>
+      <c r="F76" s="22">
+        <v>2.6240000000000001</v>
+      </c>
+      <c r="G76" s="22">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="H76" s="22">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="I76" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="J76" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="K76" s="8">
+      <c r="K76" s="14">
         <f t="shared" si="648"/>
-        <v>142.35494880546071</v>
-      </c>
-      <c r="L76" s="8">
+        <v>140.43771043771039</v>
+      </c>
+      <c r="L76" s="14">
         <f t="shared" si="649"/>
-        <v>1.0204778156996588</v>
-      </c>
-      <c r="M76" s="9">
+        <v>1.0067340067340067</v>
+      </c>
+      <c r="M76" s="17">
         <f t="shared" si="650"/>
-        <v>0.29300000000000004</v>
-      </c>
-      <c r="N76" s="34">
-        <v>0.06</v>
-      </c>
-      <c r="O76" s="34">
-        <v>0.214</v>
-      </c>
-      <c r="P76" s="34">
+        <v>0.29700000000000004</v>
+      </c>
+      <c r="N76" s="22">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="O76" s="22">
+        <v>0.218</v>
+      </c>
+      <c r="P76" s="22">
         <v>6.3E-2</v>
       </c>
-      <c r="Q76" s="34">
+      <c r="Q76" s="22">
         <v>1.6E-2</v>
       </c>
-      <c r="R76" s="31">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="S76" s="33" t="s">
+      <c r="R76" s="35">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="S76" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="T76" s="8">
+      <c r="T76" s="14">
         <f t="shared" ref="T76:T78" si="673">ROUND(B76/K76,3)</f>
-        <v>0.97299999999999998</v>
-      </c>
-      <c r="U76" s="8">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="U76" s="14">
         <f t="shared" ref="U76:U78" si="674">ROUND(C76/L76,3)</f>
-        <v>0.99299999999999999</v>
-      </c>
-      <c r="V76" s="9">
+        <v>1.008</v>
+      </c>
+      <c r="V76" s="17">
         <f t="shared" ref="V76:V78" si="675">ROUND(D76/M76,3)</f>
-        <v>12.391999999999999</v>
-      </c>
-      <c r="W76" s="34">
+        <v>12.205</v>
+      </c>
+      <c r="W76" s="22">
         <f t="shared" ref="W76:W78" si="676">ROUND(E76/N76,3)</f>
-        <v>6.2169999999999996</v>
-      </c>
-      <c r="X76" s="34">
+        <v>6.2709999999999999</v>
+      </c>
+      <c r="X76" s="22">
         <f t="shared" ref="X76:X78" si="677">ROUND(F76/O76,3)</f>
-        <v>12.276</v>
-      </c>
-      <c r="Y76" s="34">
+        <v>12.037000000000001</v>
+      </c>
+      <c r="Y76" s="22">
         <f t="shared" ref="Y76:Y78" si="678">ROUND(G76/P76,3)</f>
-        <v>14.365</v>
-      </c>
-      <c r="Z76" s="34">
+        <v>14.381</v>
+      </c>
+      <c r="Z76" s="22">
         <f t="shared" ref="Z76:Z78" si="679">ROUND(H76/Q76,3)</f>
-        <v>6.1879999999999997</v>
-      </c>
-      <c r="AA76" s="31">
+        <v>5.9379999999999997</v>
+      </c>
+      <c r="AA76" s="35">
         <f t="shared" ref="AA76:AA78" si="680">ROUND(I76/R76,3)</f>
-        <v>4.5679999999999996</v>
+        <v>4.444</v>
       </c>
       <c r="AB76" s="32"/>
     </row>
@@ -8359,27 +8371,27 @@
       </c>
       <c r="B77" s="2">
         <f t="shared" ref="B77:B78" si="681">D$2/D77</f>
-        <v>151.04415740462602</v>
+        <v>149.16226638979532</v>
       </c>
       <c r="C77" s="2">
         <f t="shared" ref="C77:C78" si="682">D76/D77</f>
-        <v>1.0907179333133075</v>
+        <v>1.0753485612577871</v>
       </c>
       <c r="D77" s="13">
         <f t="shared" ref="D77:D78" si="683">SUM(F77:H77)</f>
-        <v>3.3289999999999997</v>
+        <v>3.371</v>
       </c>
       <c r="E77" s="6">
-        <v>0.40200000000000002</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="F77" s="6">
-        <v>2.6259999999999999</v>
+        <v>2.653</v>
       </c>
       <c r="G77" s="23">
-        <v>0.60099999999999998</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H77" s="6">
-        <v>0.10199999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="I77" s="28">
         <v>0.20100000000000001</v>
@@ -8389,27 +8401,27 @@
       </c>
       <c r="K77" s="2">
         <f t="shared" ref="K77:K78" si="684">M$2/M77</f>
-        <v>142.84246575342462</v>
+        <v>141.38983050847455</v>
       </c>
       <c r="L77" s="2">
         <f t="shared" ref="L77:L78" si="685">M76/M77</f>
-        <v>1.0034246575342465</v>
+        <v>1.0067796610169493</v>
       </c>
       <c r="M77" s="13">
         <f t="shared" ref="M77:M80" si="686">SUM(O77:Q77)</f>
-        <v>0.29200000000000004</v>
+        <v>0.29500000000000004</v>
       </c>
       <c r="N77" s="6">
-        <v>0.06</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="O77" s="6">
-        <v>0.218</v>
+        <v>0.219</v>
       </c>
       <c r="P77" s="23">
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="Q77" s="6">
-        <v>1.6E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="R77" s="28">
         <v>3.9E-2</v>
@@ -8419,31 +8431,31 @@
       </c>
       <c r="T77" s="2">
         <f t="shared" si="673"/>
-        <v>1.0569999999999999</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="U77" s="2">
         <f t="shared" si="674"/>
-        <v>1.087</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="V77" s="13">
         <f t="shared" si="675"/>
-        <v>11.401</v>
+        <v>11.427</v>
       </c>
       <c r="W77" s="6">
         <f t="shared" si="676"/>
-        <v>6.7</v>
+        <v>7.6879999999999997</v>
       </c>
       <c r="X77" s="6">
         <f t="shared" si="677"/>
-        <v>12.045999999999999</v>
+        <v>12.114000000000001</v>
       </c>
       <c r="Y77" s="23">
         <f t="shared" si="678"/>
-        <v>10.362</v>
+        <v>10.414</v>
       </c>
       <c r="Z77" s="6">
         <f t="shared" si="679"/>
-        <v>6.375</v>
+        <v>6.3330000000000002</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="680"/>
@@ -8456,51 +8468,51 @@
       </c>
       <c r="B78" s="2">
         <f t="shared" si="681"/>
-        <v>149.91830649970188</v>
+        <v>151.49924676107261</v>
       </c>
       <c r="C78" s="2">
         <f t="shared" si="682"/>
-        <v>0.99254621347644612</v>
+        <v>1.0156673696896656</v>
       </c>
       <c r="D78" s="13">
         <f t="shared" si="683"/>
-        <v>3.3539999999999996</v>
+        <v>3.319</v>
       </c>
       <c r="E78" s="6">
-        <v>0.371</v>
+        <v>0.38</v>
       </c>
       <c r="F78" s="6">
-        <v>2.6629999999999998</v>
+        <v>2.6190000000000002</v>
       </c>
       <c r="G78" s="6">
-        <v>0.60099999999999998</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="H78" s="23">
-        <v>0.09</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I78" s="24">
-        <v>0.20100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J78" s="32" t="s">
         <v>87</v>
       </c>
       <c r="K78" s="2">
         <f t="shared" si="684"/>
-        <v>146.86619718309856</v>
+        <v>145.8391608391608</v>
       </c>
       <c r="L78" s="2">
         <f t="shared" si="685"/>
-        <v>1.028169014084507</v>
+        <v>1.0314685314685315</v>
       </c>
       <c r="M78" s="13">
         <f t="shared" si="686"/>
-        <v>0.28400000000000003</v>
+        <v>0.28600000000000003</v>
       </c>
       <c r="N78" s="6">
-        <v>0.06</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="O78" s="6">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
       <c r="P78" s="6">
         <v>5.6000000000000001E-2</v>
@@ -8509,139 +8521,139 @@
         <v>1.2E-2</v>
       </c>
       <c r="R78" s="24">
-        <v>3.6999999999999998E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="S78" s="32" t="s">
         <v>87</v>
       </c>
       <c r="T78" s="2">
         <f t="shared" si="673"/>
-        <v>1.0209999999999999</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="U78" s="2">
         <f t="shared" si="674"/>
-        <v>0.96499999999999997</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="V78" s="13">
         <f t="shared" si="675"/>
-        <v>11.81</v>
+        <v>11.605</v>
       </c>
       <c r="W78" s="6">
         <f t="shared" si="676"/>
-        <v>6.1829999999999998</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="X78" s="6">
         <f t="shared" si="677"/>
-        <v>12.329000000000001</v>
+        <v>12.013999999999999</v>
       </c>
       <c r="Y78" s="6">
         <f t="shared" si="678"/>
-        <v>10.731999999999999</v>
+        <v>10.75</v>
       </c>
       <c r="Z78" s="23">
         <f t="shared" si="679"/>
-        <v>7.5</v>
+        <v>8.1669999999999998</v>
       </c>
       <c r="AA78" s="24">
         <f t="shared" si="680"/>
-        <v>5.4320000000000004</v>
+        <v>5.2629999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="32" t="s">
+      <c r="A79" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="29">
         <f t="shared" ref="B79" si="687">D$2/D79</f>
-        <v>151.13495641719268</v>
-      </c>
-      <c r="C79" s="2">
+        <v>146.55377440979308</v>
+      </c>
+      <c r="C79" s="29">
         <f t="shared" ref="C79" si="688">D78/D79</f>
-        <v>1.0081154192966635</v>
-      </c>
-      <c r="D79" s="13">
+        <v>0.96735645584377727</v>
+      </c>
+      <c r="D79" s="30">
         <f t="shared" ref="D79" si="689">SUM(F79:H79)</f>
-        <v>3.327</v>
-      </c>
-      <c r="E79" s="6">
+        <v>3.431</v>
+      </c>
+      <c r="E79" s="25">
         <v>0.377</v>
       </c>
-      <c r="F79" s="23">
-        <v>2.625</v>
-      </c>
-      <c r="G79" s="23">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="H79" s="6">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="I79" s="28">
+      <c r="F79" s="26">
+        <v>2.7149999999999999</v>
+      </c>
+      <c r="G79" s="26">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H79" s="25">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="I79" s="27">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="J79" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="K79" s="29">
+        <f t="shared" ref="K79:K80" si="690">M$2/M79</f>
+        <v>157.3962264150943</v>
+      </c>
+      <c r="L79" s="29">
+        <f t="shared" ref="L79:L80" si="691">M78/M79</f>
+        <v>1.0792452830188679</v>
+      </c>
+      <c r="M79" s="30">
+        <f t="shared" si="686"/>
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="N79" s="25">
+        <v>5.5E-2</v>
+      </c>
+      <c r="O79" s="26">
         <v>0.20100000000000001</v>
       </c>
-      <c r="J79" s="32" t="s">
+      <c r="P79" s="26">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Q79" s="25">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R79" s="27">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S79" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="K79" s="2">
-        <f t="shared" ref="K79:K80" si="690">M$2/M79</f>
-        <v>155.05576208178437</v>
-      </c>
-      <c r="L79" s="2">
-        <f t="shared" ref="L79:L80" si="691">M78/M79</f>
-        <v>1.0557620817843867</v>
-      </c>
-      <c r="M79" s="13">
-        <f t="shared" si="686"/>
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="N79" s="6">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="O79" s="23">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="P79" s="23">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="Q79" s="6">
-        <v>1.2E-2</v>
-      </c>
-      <c r="R79" s="28">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="S79" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="T79" s="2">
+      <c r="T79" s="29">
         <f t="shared" ref="T79" si="692">ROUND(B79/K79,3)</f>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="U79" s="2">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="U79" s="29">
         <f t="shared" ref="U79" si="693">ROUND(C79/L79,3)</f>
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="V79" s="13">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="V79" s="30">
         <f t="shared" ref="V79" si="694">ROUND(D79/M79,3)</f>
-        <v>12.368</v>
-      </c>
-      <c r="W79" s="6">
+        <v>12.946999999999999</v>
+      </c>
+      <c r="W79" s="25">
         <f t="shared" ref="W79" si="695">ROUND(E79/N79,3)</f>
-        <v>6.6139999999999999</v>
-      </c>
-      <c r="X79" s="23">
+        <v>6.8550000000000004</v>
+      </c>
+      <c r="X79" s="26">
         <f t="shared" ref="X79" si="696">ROUND(F79/O79,3)</f>
-        <v>12.805</v>
-      </c>
-      <c r="Y79" s="23">
+        <v>13.507</v>
+      </c>
+      <c r="Y79" s="26">
         <f t="shared" ref="Y79" si="697">ROUND(G79/P79,3)</f>
-        <v>11.615</v>
-      </c>
-      <c r="Z79" s="6">
+        <v>11.788</v>
+      </c>
+      <c r="Z79" s="25">
         <f t="shared" ref="Z79" si="698">ROUND(H79/Q79,3)</f>
-        <v>8.1669999999999998</v>
-      </c>
-      <c r="AA79" s="28">
+        <v>8.5830000000000002</v>
+      </c>
+      <c r="AA79" s="27">
         <f t="shared" ref="AA79" si="699">ROUND(I79/R79,3)</f>
-        <v>5.5830000000000002</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="80" spans="1:28" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8650,95 +8662,95 @@
       </c>
       <c r="B80" s="14">
         <f t="shared" ref="B80" si="700">D$2/D80</f>
-        <v>152.92761557177616</v>
+        <v>152.18704600484264</v>
       </c>
       <c r="C80" s="14">
         <f t="shared" ref="C80" si="701">D79/D80</f>
-        <v>1.011861313868613</v>
+        <v>1.0384382566585957</v>
       </c>
       <c r="D80" s="17">
         <f t="shared" ref="D80" si="702">SUM(F80:H80)</f>
-        <v>3.2880000000000003</v>
+        <v>3.3039999999999998</v>
       </c>
       <c r="E80" s="22">
-        <v>0.38100000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="F80" s="22">
-        <v>2.5950000000000002</v>
+        <v>2.6040000000000001</v>
       </c>
       <c r="G80" s="22">
         <v>0.59799999999999998</v>
       </c>
       <c r="H80" s="22">
-        <v>9.5000000000000001E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I80" s="35">
-        <v>0.2</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="J80" s="32" t="s">
         <v>89</v>
       </c>
       <c r="K80" s="14">
         <f t="shared" si="690"/>
-        <v>156.21722846441943</v>
+        <v>152.78388278388275</v>
       </c>
       <c r="L80" s="14">
         <f t="shared" si="691"/>
-        <v>1.0074906367041199</v>
+        <v>0.97069597069597069</v>
       </c>
       <c r="M80" s="17">
         <f t="shared" si="686"/>
-        <v>0.26700000000000002</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="N80" s="22">
-        <v>5.8000000000000003E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="O80" s="22">
-        <v>0.20300000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="P80" s="22">
-        <v>5.1999999999999998E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="Q80" s="22">
-        <v>1.2E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R80" s="35">
-        <v>3.5999999999999997E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="S80" s="32" t="s">
         <v>89</v>
       </c>
       <c r="T80" s="14">
         <f t="shared" ref="T80:T83" si="703">ROUND(B80/K80,3)</f>
-        <v>0.97899999999999998</v>
+        <v>0.996</v>
       </c>
       <c r="U80" s="14">
         <f t="shared" ref="U80:U83" si="704">ROUND(C80/L80,3)</f>
-        <v>1.004</v>
+        <v>1.07</v>
       </c>
       <c r="V80" s="17">
         <f t="shared" ref="V80:V83" si="705">ROUND(D80/M80,3)</f>
-        <v>12.315</v>
+        <v>12.103</v>
       </c>
       <c r="W80" s="22">
         <f t="shared" ref="W80:W83" si="706">ROUND(E80/N80,3)</f>
-        <v>6.569</v>
+        <v>6.0659999999999998</v>
       </c>
       <c r="X80" s="22">
         <f t="shared" ref="X80:X83" si="707">ROUND(F80/O80,3)</f>
-        <v>12.782999999999999</v>
+        <v>12.702</v>
       </c>
       <c r="Y80" s="22">
         <f t="shared" ref="Y80:Y83" si="708">ROUND(G80/P80,3)</f>
-        <v>11.5</v>
+        <v>11.282999999999999</v>
       </c>
       <c r="Z80" s="22">
         <f t="shared" ref="Z80:Z83" si="709">ROUND(H80/Q80,3)</f>
-        <v>7.9169999999999998</v>
+        <v>6.8</v>
       </c>
       <c r="AA80" s="35">
         <f t="shared" ref="AA80:AA83" si="710">ROUND(I80/R80,3)</f>
-        <v>5.556</v>
+        <v>5.3680000000000003</v>
       </c>
       <c r="AB80" s="32"/>
     </row>
@@ -8748,27 +8760,27 @@
       </c>
       <c r="B81" s="14">
         <f t="shared" ref="B81:B83" si="711">D$2/D81</f>
-        <v>152.09497882637629</v>
+        <v>153.76941896024465</v>
       </c>
       <c r="C81" s="14">
         <f t="shared" ref="C81:C83" si="712">D80/D81</f>
-        <v>0.99455535390199645</v>
+        <v>1.0103975535168195</v>
       </c>
       <c r="D81" s="17">
         <f t="shared" ref="D81:D83" si="713">SUM(F81:H81)</f>
-        <v>3.306</v>
+        <v>3.27</v>
       </c>
       <c r="E81" s="6">
-        <v>0.36899999999999999</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F81" s="6">
-        <v>2.61</v>
+        <v>2.5760000000000001</v>
       </c>
       <c r="G81" s="6">
-        <v>0.6</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="H81" s="6">
-        <v>9.6000000000000002E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="I81" s="28">
         <v>0.2</v>
@@ -8777,66 +8789,66 @@
         <v>90</v>
       </c>
       <c r="K81" s="14">
-        <f t="shared" ref="K81:K83" si="714">M$2/M81</f>
-        <v>158.59315589353608</v>
+        <f t="shared" ref="K81:K86" si="714">M$2/M81</f>
+        <v>150.57761732851981</v>
       </c>
       <c r="L81" s="14">
-        <f t="shared" ref="L81:L83" si="715">M80/M81</f>
-        <v>1.0152091254752851</v>
+        <f t="shared" ref="L81:L86" si="715">M80/M81</f>
+        <v>0.98555956678700363</v>
       </c>
       <c r="M81" s="17">
-        <f t="shared" ref="M81:M83" si="716">SUM(O81:Q81)</f>
-        <v>0.26300000000000001</v>
+        <f t="shared" ref="M81:M86" si="716">SUM(O81:Q81)</f>
+        <v>0.27700000000000002</v>
       </c>
       <c r="N81" s="6">
-        <v>5.6000000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="O81" s="6">
-        <v>0.2</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="P81" s="6">
-        <v>5.0999999999999997E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="Q81" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R81" s="28">
-        <v>3.5999999999999997E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="S81" s="32" t="s">
         <v>90</v>
       </c>
       <c r="T81" s="14">
         <f t="shared" si="703"/>
-        <v>0.95899999999999996</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="U81" s="14">
         <f t="shared" si="704"/>
-        <v>0.98</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="V81" s="17">
         <f t="shared" si="705"/>
-        <v>12.57</v>
+        <v>11.805</v>
       </c>
       <c r="W81" s="22">
         <f t="shared" si="706"/>
-        <v>6.5890000000000004</v>
+        <v>6.4</v>
       </c>
       <c r="X81" s="22">
         <f t="shared" si="707"/>
-        <v>13.05</v>
+        <v>12.151</v>
       </c>
       <c r="Y81" s="22">
         <f t="shared" si="708"/>
-        <v>11.765000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="Z81" s="22">
         <f t="shared" si="709"/>
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AA81" s="35">
         <f t="shared" si="710"/>
-        <v>5.556</v>
+        <v>5.2629999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8845,27 +8857,27 @@
       </c>
       <c r="B82" s="14">
         <f t="shared" si="711"/>
-        <v>152.14099848714071</v>
+        <v>151.2713598074609</v>
       </c>
       <c r="C82" s="14">
         <f t="shared" si="712"/>
-        <v>1.0003025718608169</v>
+        <v>0.98375451263537894</v>
       </c>
       <c r="D82" s="17">
         <f t="shared" si="713"/>
-        <v>3.3049999999999997</v>
+        <v>3.3240000000000003</v>
       </c>
       <c r="E82" s="6">
-        <v>0.378</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F82" s="6">
-        <v>2.6040000000000001</v>
+        <v>2.6240000000000001</v>
       </c>
       <c r="G82" s="6">
-        <v>0.60299999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="H82" s="6">
-        <v>9.8000000000000004E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I82" s="28">
         <v>0.20100000000000001</v>
@@ -8875,65 +8887,65 @@
       </c>
       <c r="K82" s="14">
         <f t="shared" si="714"/>
-        <v>157.99242424242422</v>
+        <v>150.03597122302153</v>
       </c>
       <c r="L82" s="14">
         <f t="shared" si="715"/>
-        <v>0.99621212121212122</v>
+        <v>0.99640287769784175</v>
       </c>
       <c r="M82" s="17">
         <f t="shared" si="716"/>
-        <v>0.26400000000000001</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="N82" s="6">
-        <v>5.8000000000000003E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="O82" s="6">
-        <v>0.20200000000000001</v>
+        <v>0.215</v>
       </c>
       <c r="P82" s="6">
-        <v>0.05</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="Q82" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R82" s="28">
-        <v>3.5999999999999997E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="S82" s="32" t="s">
         <v>91</v>
       </c>
       <c r="T82" s="14">
         <f t="shared" si="703"/>
-        <v>0.96299999999999997</v>
+        <v>1.008</v>
       </c>
       <c r="U82" s="14">
         <f t="shared" si="704"/>
-        <v>1.004</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="V82" s="17">
         <f t="shared" si="705"/>
-        <v>12.519</v>
+        <v>11.957000000000001</v>
       </c>
       <c r="W82" s="22">
         <f t="shared" si="706"/>
-        <v>6.5170000000000003</v>
+        <v>6.9640000000000004</v>
       </c>
       <c r="X82" s="22">
         <f t="shared" si="707"/>
-        <v>12.891</v>
+        <v>12.205</v>
       </c>
       <c r="Y82" s="22">
         <f t="shared" si="708"/>
-        <v>12.06</v>
+        <v>11.765000000000001</v>
       </c>
       <c r="Z82" s="22">
         <f t="shared" si="709"/>
-        <v>8.1669999999999998</v>
+        <v>8.3330000000000002</v>
       </c>
       <c r="AA82" s="35">
         <f t="shared" si="710"/>
-        <v>5.5830000000000002</v>
+        <v>5.4320000000000004</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8942,57 +8954,57 @@
       </c>
       <c r="B83" s="14">
         <f t="shared" si="711"/>
-        <v>150.90816326530614</v>
+        <v>153.06727549467274</v>
       </c>
       <c r="C83" s="14">
         <f t="shared" si="712"/>
-        <v>0.99189675870348137</v>
+        <v>1.0118721461187214</v>
       </c>
       <c r="D83" s="17">
         <f t="shared" si="713"/>
-        <v>3.3319999999999999</v>
+        <v>3.2850000000000001</v>
       </c>
       <c r="E83" s="6">
-        <v>0.41699999999999998</v>
+        <v>0.376</v>
       </c>
       <c r="F83" s="6">
-        <v>2.637</v>
+        <v>2.585</v>
       </c>
       <c r="G83" s="6">
-        <v>0.60199999999999998</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="H83" s="6">
-        <v>9.2999999999999999E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I83" s="28">
-        <v>0.2</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="J83" s="32" t="s">
         <v>92</v>
       </c>
       <c r="K83" s="14">
         <f t="shared" si="714"/>
-        <v>155.63432835820893</v>
+        <v>152.22627737226273</v>
       </c>
       <c r="L83" s="14">
         <f t="shared" si="715"/>
-        <v>0.9850746268656716</v>
+        <v>1.0145985401459854</v>
       </c>
       <c r="M83" s="17">
         <f t="shared" si="716"/>
-        <v>0.26800000000000002</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="N83" s="6">
-        <v>6.5000000000000002E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="O83" s="6">
-        <v>0.20399999999999999</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="P83" s="6">
-        <v>5.1999999999999998E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="Q83" s="6">
-        <v>1.2E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R83" s="28">
         <v>3.6999999999999998E-2</v>
@@ -9002,34 +9014,325 @@
       </c>
       <c r="T83" s="14">
         <f t="shared" si="703"/>
-        <v>0.97</v>
+        <v>1.006</v>
       </c>
       <c r="U83" s="14">
         <f t="shared" si="704"/>
-        <v>1.0069999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="V83" s="17">
         <f t="shared" si="705"/>
-        <v>12.433</v>
+        <v>11.989000000000001</v>
       </c>
       <c r="W83" s="22">
         <f t="shared" si="706"/>
-        <v>6.415</v>
+        <v>6.1639999999999997</v>
       </c>
       <c r="X83" s="22">
         <f t="shared" si="707"/>
-        <v>12.926</v>
+        <v>12.428000000000001</v>
       </c>
       <c r="Y83" s="22">
         <f t="shared" si="708"/>
-        <v>11.577</v>
+        <v>11.302</v>
       </c>
       <c r="Z83" s="22">
         <f t="shared" si="709"/>
-        <v>7.75</v>
+        <v>7.7690000000000001</v>
       </c>
       <c r="AA83" s="35">
         <f t="shared" si="710"/>
+        <v>5.3780000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" s="14">
+        <f t="shared" ref="B84:B85" si="717">D$2/D84</f>
+        <v>150.90816326530611</v>
+      </c>
+      <c r="C84" s="14">
+        <f t="shared" ref="C84:C85" si="718">D83/D84</f>
+        <v>0.98589435774309719</v>
+      </c>
+      <c r="D84" s="17">
+        <f t="shared" ref="D84:D85" si="719">SUM(F84:H84)</f>
+        <v>3.3320000000000003</v>
+      </c>
+      <c r="E84" s="6">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="F84" s="6">
+        <v>2.6280000000000001</v>
+      </c>
+      <c r="G84" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H84" s="6">
+        <v>0.104</v>
+      </c>
+      <c r="I84" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J84" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="K84" s="14">
+        <f t="shared" si="714"/>
+        <v>153.34558823529409</v>
+      </c>
+      <c r="L84" s="14">
+        <f t="shared" si="715"/>
+        <v>1.0073529411764706</v>
+      </c>
+      <c r="M84" s="17">
+        <f t="shared" si="716"/>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="N84" s="6">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="O84" s="6">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="P84" s="6">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R84" s="28">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="S84" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="T84" s="14">
+        <f t="shared" ref="T84:T85" si="720">ROUND(B84/K84,3)</f>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="U84" s="14">
+        <f t="shared" ref="U84:U85" si="721">ROUND(C84/L84,3)</f>
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="V84" s="17">
+        <f t="shared" ref="V84:V85" si="722">ROUND(D84/M84,3)</f>
+        <v>12.25</v>
+      </c>
+      <c r="W84" s="22">
+        <f t="shared" ref="W84:W85" si="723">ROUND(E84/N84,3)</f>
+        <v>7.1609999999999996</v>
+      </c>
+      <c r="X84" s="22">
+        <f t="shared" ref="X84:X85" si="724">ROUND(F84/O84,3)</f>
+        <v>12.696</v>
+      </c>
+      <c r="Y84" s="22">
+        <f t="shared" ref="Y84:Y85" si="725">ROUND(G84/P84,3)</f>
+        <v>11.321</v>
+      </c>
+      <c r="Z84" s="22">
+        <f t="shared" ref="Z84:Z85" si="726">ROUND(H84/Q84,3)</f>
+        <v>8.6669999999999998</v>
+      </c>
+      <c r="AA84" s="35">
+        <f t="shared" ref="AA84:AA85" si="727">ROUND(I84/R84,3)</f>
+        <v>5.2629999999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" s="14">
+        <f t="shared" si="717"/>
+        <v>153.53465648854962</v>
+      </c>
+      <c r="C85" s="14">
+        <f t="shared" si="718"/>
+        <v>1.0174045801526719</v>
+      </c>
+      <c r="D85" s="17">
+        <f t="shared" si="719"/>
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0.373</v>
+      </c>
+      <c r="F85" s="6">
+        <v>2.5760000000000001</v>
+      </c>
+      <c r="G85" s="6">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="H85" s="6">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="I85" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J85" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="K85" s="14">
+        <f t="shared" si="714"/>
+        <v>152.78388278388275</v>
+      </c>
+      <c r="L85" s="14">
+        <f t="shared" si="715"/>
+        <v>0.99633699633699635</v>
+      </c>
+      <c r="M85" s="17">
+        <f t="shared" si="716"/>
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="N85" s="6">
+        <v>5.5E-2</v>
+      </c>
+      <c r="O85" s="6">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="P85" s="6">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R85" s="28">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S85" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="T85" s="14">
+        <f t="shared" si="720"/>
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="U85" s="14">
+        <f t="shared" si="721"/>
+        <v>1.0209999999999999</v>
+      </c>
+      <c r="V85" s="17">
+        <f t="shared" si="722"/>
+        <v>11.996</v>
+      </c>
+      <c r="W85" s="22">
+        <f t="shared" si="723"/>
+        <v>6.782</v>
+      </c>
+      <c r="X85" s="22">
+        <f t="shared" si="724"/>
+        <v>12.385</v>
+      </c>
+      <c r="Y85" s="22">
+        <f t="shared" si="725"/>
+        <v>11.577</v>
+      </c>
+      <c r="Z85" s="22">
+        <f t="shared" si="726"/>
+        <v>7.4619999999999997</v>
+      </c>
+      <c r="AA85" s="35">
+        <f t="shared" si="727"/>
+        <v>5.4050000000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86" s="14">
+        <f t="shared" ref="B86" si="728">D$2/D86</f>
+        <v>154.05208333333334</v>
+      </c>
+      <c r="C86" s="14">
+        <f t="shared" ref="C86" si="729">D85/D86</f>
+        <v>1.0033700980392155</v>
+      </c>
+      <c r="D86" s="17">
+        <f t="shared" ref="D86" si="730">SUM(F86:H86)</f>
+        <v>3.2640000000000002</v>
+      </c>
+      <c r="E86" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="F86" s="6">
+        <v>2.5720000000000001</v>
+      </c>
+      <c r="G86" s="6">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="H86" s="6">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="I86" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J86" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="K86" s="14">
+        <f t="shared" si="714"/>
+        <v>148.96428571428567</v>
+      </c>
+      <c r="L86" s="14">
+        <f t="shared" si="715"/>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="M86" s="17">
+        <f t="shared" si="716"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N86" s="6">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="O86" s="6">
+        <v>0.214</v>
+      </c>
+      <c r="P86" s="6">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R86" s="28">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S86" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="T86" s="14">
+        <f t="shared" ref="T86" si="731">ROUND(B86/K86,3)</f>
+        <v>1.034</v>
+      </c>
+      <c r="U86" s="14">
+        <f t="shared" ref="U86" si="732">ROUND(C86/L86,3)</f>
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="V86" s="17">
+        <f t="shared" ref="V86" si="733">ROUND(D86/M86,3)</f>
+        <v>11.657</v>
+      </c>
+      <c r="W86" s="22">
+        <f t="shared" ref="W86" si="734">ROUND(E86/N86,3)</f>
+        <v>7.0750000000000002</v>
+      </c>
+      <c r="X86" s="22">
+        <f t="shared" ref="X86" si="735">ROUND(F86/O86,3)</f>
+        <v>12.019</v>
+      </c>
+      <c r="Y86" s="22">
+        <f t="shared" ref="Y86" si="736">ROUND(G86/P86,3)</f>
+        <v>11.302</v>
+      </c>
+      <c r="Z86" s="22">
+        <f t="shared" ref="Z86" si="737">ROUND(H86/Q86,3)</f>
+        <v>7.1539999999999999</v>
+      </c>
+      <c r="AA86" s="35">
+        <f t="shared" ref="AA86" si="738">ROUND(I86/R86,3)</f>
         <v>5.4050000000000002</v>
       </c>
     </row>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8CE3C5-CEB7-4F0B-86D8-FC7A452891C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EB0A6C-952F-41A7-B8A1-9F4587B9AACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="99">
   <si>
     <t>H23</t>
   </si>
@@ -389,6 +389,18 @@
   </si>
   <si>
     <t>H106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H108</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H109</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -980,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB86"/>
+  <dimension ref="A1:AB89"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="5"/>
@@ -8565,95 +8577,95 @@
       </c>
       <c r="B79" s="29">
         <f t="shared" ref="B79" si="687">D$2/D79</f>
-        <v>146.55377440979308</v>
+        <v>152.00302297460703</v>
       </c>
       <c r="C79" s="29">
         <f t="shared" ref="C79" si="688">D78/D79</f>
-        <v>0.96735645584377727</v>
+        <v>1.0033252720677146</v>
       </c>
       <c r="D79" s="30">
         <f t="shared" ref="D79" si="689">SUM(F79:H79)</f>
-        <v>3.431</v>
+        <v>3.3079999999999998</v>
       </c>
       <c r="E79" s="25">
-        <v>0.377</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="F79" s="26">
-        <v>2.7149999999999999</v>
+        <v>2.6059999999999999</v>
       </c>
       <c r="G79" s="26">
-        <v>0.61299999999999999</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="H79" s="25">
-        <v>0.10299999999999999</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I79" s="27">
-        <v>0.20699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J79" s="33" t="s">
         <v>88</v>
       </c>
       <c r="K79" s="29">
         <f t="shared" ref="K79:K80" si="690">M$2/M79</f>
-        <v>157.3962264150943</v>
+        <v>155.05576208178437</v>
       </c>
       <c r="L79" s="29">
         <f t="shared" ref="L79:L80" si="691">M78/M79</f>
-        <v>1.0792452830188679</v>
+        <v>1.0631970260223049</v>
       </c>
       <c r="M79" s="30">
         <f t="shared" si="686"/>
-        <v>0.26500000000000001</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="N79" s="25">
-        <v>5.5E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="O79" s="26">
-        <v>0.20100000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="P79" s="26">
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q79" s="25">
-        <v>1.2E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="R79" s="27">
-        <v>3.5999999999999997E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="S79" s="33" t="s">
         <v>88</v>
       </c>
       <c r="T79" s="29">
         <f t="shared" ref="T79" si="692">ROUND(B79/K79,3)</f>
-        <v>0.93100000000000005</v>
+        <v>0.98</v>
       </c>
       <c r="U79" s="29">
         <f t="shared" ref="U79" si="693">ROUND(C79/L79,3)</f>
-        <v>0.89600000000000002</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="V79" s="30">
         <f t="shared" ref="V79" si="694">ROUND(D79/M79,3)</f>
-        <v>12.946999999999999</v>
+        <v>12.297000000000001</v>
       </c>
       <c r="W79" s="25">
         <f t="shared" ref="W79" si="695">ROUND(E79/N79,3)</f>
-        <v>6.8550000000000004</v>
+        <v>6.1589999999999998</v>
       </c>
       <c r="X79" s="26">
         <f t="shared" ref="X79" si="696">ROUND(F79/O79,3)</f>
-        <v>13.507</v>
+        <v>12.837</v>
       </c>
       <c r="Y79" s="26">
         <f t="shared" ref="Y79" si="697">ROUND(G79/P79,3)</f>
-        <v>11.788</v>
+        <v>11.596</v>
       </c>
       <c r="Z79" s="25">
         <f t="shared" ref="Z79" si="698">ROUND(H79/Q79,3)</f>
-        <v>8.5830000000000002</v>
+        <v>7.0709999999999997</v>
       </c>
       <c r="AA79" s="27">
         <f t="shared" ref="AA79" si="699">ROUND(I79/R79,3)</f>
-        <v>5.75</v>
+        <v>5.4050000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:28" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8662,95 +8674,95 @@
       </c>
       <c r="B80" s="14">
         <f t="shared" ref="B80" si="700">D$2/D80</f>
-        <v>152.18704600484264</v>
+        <v>152.04898699727852</v>
       </c>
       <c r="C80" s="14">
         <f t="shared" ref="C80" si="701">D79/D80</f>
-        <v>1.0384382566585957</v>
+        <v>1.0003023888720894</v>
       </c>
       <c r="D80" s="17">
         <f t="shared" ref="D80" si="702">SUM(F80:H80)</f>
-        <v>3.3039999999999998</v>
+        <v>3.3069999999999999</v>
       </c>
       <c r="E80" s="22">
-        <v>0.37</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F80" s="22">
-        <v>2.6040000000000001</v>
+        <v>2.6080000000000001</v>
       </c>
       <c r="G80" s="22">
-        <v>0.59799999999999998</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="H80" s="22">
         <v>0.10199999999999999</v>
       </c>
       <c r="I80" s="35">
-        <v>0.20399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J80" s="32" t="s">
         <v>89</v>
       </c>
       <c r="K80" s="14">
         <f t="shared" si="690"/>
-        <v>152.78388278388275</v>
+        <v>151.67272727272723</v>
       </c>
       <c r="L80" s="14">
         <f t="shared" si="691"/>
-        <v>0.97069597069597069</v>
+        <v>0.97818181818181815</v>
       </c>
       <c r="M80" s="17">
         <f t="shared" si="686"/>
-        <v>0.27300000000000002</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="N80" s="22">
-        <v>6.0999999999999999E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="O80" s="22">
-        <v>0.20499999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="P80" s="22">
-        <v>5.2999999999999999E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q80" s="22">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="R80" s="35">
-        <v>3.7999999999999999E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S80" s="32" t="s">
         <v>89</v>
       </c>
       <c r="T80" s="14">
         <f t="shared" ref="T80:T83" si="703">ROUND(B80/K80,3)</f>
-        <v>0.996</v>
+        <v>1.002</v>
       </c>
       <c r="U80" s="14">
         <f t="shared" ref="U80:U83" si="704">ROUND(C80/L80,3)</f>
-        <v>1.07</v>
+        <v>1.0229999999999999</v>
       </c>
       <c r="V80" s="17">
         <f t="shared" ref="V80:V83" si="705">ROUND(D80/M80,3)</f>
-        <v>12.103</v>
+        <v>12.025</v>
       </c>
       <c r="W80" s="22">
         <f t="shared" ref="W80:W83" si="706">ROUND(E80/N80,3)</f>
-        <v>6.0659999999999998</v>
+        <v>6.8570000000000002</v>
       </c>
       <c r="X80" s="22">
         <f t="shared" ref="X80:X83" si="707">ROUND(F80/O80,3)</f>
-        <v>12.702</v>
+        <v>12.36</v>
       </c>
       <c r="Y80" s="22">
         <f t="shared" ref="Y80:Y83" si="708">ROUND(G80/P80,3)</f>
-        <v>11.282999999999999</v>
+        <v>11.481</v>
       </c>
       <c r="Z80" s="22">
         <f t="shared" ref="Z80:Z83" si="709">ROUND(H80/Q80,3)</f>
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA80" s="35">
         <f t="shared" ref="AA80:AA83" si="710">ROUND(I80/R80,3)</f>
-        <v>5.3680000000000003</v>
+        <v>5.556</v>
       </c>
       <c r="AB80" s="32"/>
     </row>
@@ -8760,27 +8772,27 @@
       </c>
       <c r="B81" s="14">
         <f t="shared" ref="B81:B83" si="711">D$2/D81</f>
-        <v>153.76941896024465</v>
+        <v>151.86529749320445</v>
       </c>
       <c r="C81" s="14">
         <f t="shared" ref="C81:C83" si="712">D80/D81</f>
-        <v>1.0103975535168195</v>
+        <v>0.99879190576864985</v>
       </c>
       <c r="D81" s="17">
         <f t="shared" ref="D81:D83" si="713">SUM(F81:H81)</f>
-        <v>3.27</v>
+        <v>3.3110000000000004</v>
       </c>
       <c r="E81" s="6">
-        <v>0.38400000000000001</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="F81" s="6">
-        <v>2.5760000000000001</v>
+        <v>2.6150000000000002</v>
       </c>
       <c r="G81" s="6">
-        <v>0.60099999999999998</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="H81" s="6">
-        <v>9.2999999999999999E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I81" s="28">
         <v>0.2</v>
@@ -8790,21 +8802,21 @@
       </c>
       <c r="K81" s="14">
         <f t="shared" ref="K81:K86" si="714">M$2/M81</f>
-        <v>150.57761732851981</v>
+        <v>153.9114391143911</v>
       </c>
       <c r="L81" s="14">
         <f t="shared" ref="L81:L86" si="715">M80/M81</f>
-        <v>0.98555956678700363</v>
+        <v>1.014760147601476</v>
       </c>
       <c r="M81" s="17">
         <f t="shared" ref="M81:M86" si="716">SUM(O81:Q81)</f>
-        <v>0.27700000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="N81" s="6">
-        <v>0.06</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="O81" s="6">
-        <v>0.21199999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="P81" s="6">
         <v>5.2999999999999999E-2</v>
@@ -8813,42 +8825,42 @@
         <v>1.2E-2</v>
       </c>
       <c r="R81" s="28">
-        <v>3.7999999999999999E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="S81" s="32" t="s">
         <v>90</v>
       </c>
       <c r="T81" s="14">
         <f t="shared" si="703"/>
-        <v>1.0209999999999999</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="U81" s="14">
         <f t="shared" si="704"/>
-        <v>1.0249999999999999</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="V81" s="17">
         <f t="shared" si="705"/>
-        <v>11.805</v>
+        <v>12.218</v>
       </c>
       <c r="W81" s="22">
         <f t="shared" si="706"/>
-        <v>6.4</v>
+        <v>6.8040000000000003</v>
       </c>
       <c r="X81" s="22">
         <f t="shared" si="707"/>
-        <v>12.151</v>
+        <v>12.694000000000001</v>
       </c>
       <c r="Y81" s="22">
         <f t="shared" si="708"/>
-        <v>11.34</v>
+        <v>11.302</v>
       </c>
       <c r="Z81" s="22">
         <f t="shared" si="709"/>
-        <v>7.75</v>
+        <v>8.0830000000000002</v>
       </c>
       <c r="AA81" s="35">
         <f t="shared" si="710"/>
-        <v>5.2629999999999999</v>
+        <v>5.4050000000000002</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8857,95 +8869,95 @@
       </c>
       <c r="B82" s="14">
         <f t="shared" si="711"/>
-        <v>151.2713598074609</v>
+        <v>153.16052391105694</v>
       </c>
       <c r="C82" s="14">
         <f t="shared" si="712"/>
-        <v>0.98375451263537894</v>
+        <v>1.0085287846481876</v>
       </c>
       <c r="D82" s="17">
         <f t="shared" si="713"/>
-        <v>3.3240000000000003</v>
+        <v>3.2830000000000004</v>
       </c>
       <c r="E82" s="6">
-        <v>0.38300000000000001</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="F82" s="6">
-        <v>2.6240000000000001</v>
+        <v>2.5960000000000001</v>
       </c>
       <c r="G82" s="6">
         <v>0.6</v>
       </c>
       <c r="H82" s="6">
-        <v>0.1</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="I82" s="28">
-        <v>0.20100000000000001</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="J82" s="32" t="s">
         <v>91</v>
       </c>
       <c r="K82" s="14">
         <f t="shared" si="714"/>
-        <v>150.03597122302153</v>
+        <v>157.99242424242422</v>
       </c>
       <c r="L82" s="14">
         <f t="shared" si="715"/>
-        <v>0.99640287769784175</v>
+        <v>1.0265151515151516</v>
       </c>
       <c r="M82" s="17">
         <f t="shared" si="716"/>
-        <v>0.27800000000000002</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="N82" s="6">
-        <v>5.5E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="O82" s="6">
-        <v>0.215</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="P82" s="6">
-        <v>5.0999999999999997E-2</v>
+        <v>0.05</v>
       </c>
       <c r="Q82" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R82" s="28">
-        <v>3.6999999999999998E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="S82" s="32" t="s">
         <v>91</v>
       </c>
       <c r="T82" s="14">
         <f t="shared" si="703"/>
-        <v>1.008</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="U82" s="14">
         <f t="shared" si="704"/>
-        <v>0.98699999999999999</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="V82" s="17">
         <f t="shared" si="705"/>
-        <v>11.957000000000001</v>
+        <v>12.436</v>
       </c>
       <c r="W82" s="22">
         <f t="shared" si="706"/>
-        <v>6.9640000000000004</v>
+        <v>6.6269999999999998</v>
       </c>
       <c r="X82" s="22">
         <f t="shared" si="707"/>
-        <v>12.205</v>
+        <v>12.851000000000001</v>
       </c>
       <c r="Y82" s="22">
         <f t="shared" si="708"/>
-        <v>11.765000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z82" s="22">
         <f t="shared" si="709"/>
-        <v>8.3330000000000002</v>
+        <v>7.25</v>
       </c>
       <c r="AA82" s="35">
         <f t="shared" si="710"/>
-        <v>5.4320000000000004</v>
+        <v>5.6859999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8954,67 +8966,67 @@
       </c>
       <c r="B83" s="14">
         <f t="shared" si="711"/>
-        <v>153.06727549467274</v>
+        <v>152.04898699727852</v>
       </c>
       <c r="C83" s="14">
         <f t="shared" si="712"/>
-        <v>1.0118721461187214</v>
+        <v>0.99274266706985193</v>
       </c>
       <c r="D83" s="17">
         <f t="shared" si="713"/>
-        <v>3.2850000000000001</v>
+        <v>3.3069999999999999</v>
       </c>
       <c r="E83" s="6">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="F83" s="6">
-        <v>2.585</v>
+        <v>2.6110000000000002</v>
       </c>
       <c r="G83" s="6">
-        <v>0.59899999999999998</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="H83" s="6">
-        <v>0.10100000000000001</v>
+        <v>9.4E-2</v>
       </c>
       <c r="I83" s="28">
-        <v>0.19900000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J83" s="32" t="s">
         <v>92</v>
       </c>
       <c r="K83" s="14">
         <f t="shared" si="714"/>
-        <v>152.22627737226273</v>
+        <v>157.3962264150943</v>
       </c>
       <c r="L83" s="14">
         <f t="shared" si="715"/>
-        <v>1.0145985401459854</v>
+        <v>0.99622641509433962</v>
       </c>
       <c r="M83" s="17">
         <f t="shared" si="716"/>
-        <v>0.27400000000000002</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="N83" s="6">
-        <v>6.0999999999999999E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="O83" s="6">
-        <v>0.20799999999999999</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="P83" s="6">
-        <v>5.2999999999999999E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="Q83" s="6">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="R83" s="28">
-        <v>3.6999999999999998E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S83" s="32" t="s">
         <v>92</v>
       </c>
       <c r="T83" s="14">
         <f t="shared" si="703"/>
-        <v>1.006</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="U83" s="14">
         <f t="shared" si="704"/>
@@ -9022,27 +9034,27 @@
       </c>
       <c r="V83" s="17">
         <f t="shared" si="705"/>
-        <v>11.989000000000001</v>
+        <v>12.478999999999999</v>
       </c>
       <c r="W83" s="22">
         <f t="shared" si="706"/>
-        <v>6.1639999999999997</v>
+        <v>6.3390000000000004</v>
       </c>
       <c r="X83" s="22">
         <f t="shared" si="707"/>
-        <v>12.428000000000001</v>
+        <v>12.926</v>
       </c>
       <c r="Y83" s="22">
         <f t="shared" si="708"/>
-        <v>11.302</v>
+        <v>11.804</v>
       </c>
       <c r="Z83" s="22">
         <f t="shared" si="709"/>
-        <v>7.7690000000000001</v>
+        <v>7.8330000000000002</v>
       </c>
       <c r="AA83" s="35">
         <f t="shared" si="710"/>
-        <v>5.3780000000000001</v>
+        <v>5.556</v>
       </c>
     </row>
     <row r="84" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9051,30 +9063,30 @@
       </c>
       <c r="B84" s="14">
         <f t="shared" ref="B84:B85" si="717">D$2/D84</f>
-        <v>150.90816326530611</v>
+        <v>152.9741405536964</v>
       </c>
       <c r="C84" s="14">
         <f t="shared" ref="C84:C85" si="718">D83/D84</f>
-        <v>0.98589435774309719</v>
+        <v>1.0060845756008518</v>
       </c>
       <c r="D84" s="17">
         <f t="shared" ref="D84:D85" si="719">SUM(F84:H84)</f>
-        <v>3.3320000000000003</v>
+        <v>3.2869999999999999</v>
       </c>
       <c r="E84" s="6">
-        <v>0.40100000000000002</v>
+        <v>0.373</v>
       </c>
       <c r="F84" s="6">
-        <v>2.6280000000000001</v>
+        <v>2.5939999999999999</v>
       </c>
       <c r="G84" s="6">
-        <v>0.6</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="H84" s="6">
-        <v>0.104</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="I84" s="28">
-        <v>0.2</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="J84" s="32" t="s">
         <v>93</v>
@@ -9085,61 +9097,61 @@
       </c>
       <c r="L84" s="14">
         <f t="shared" si="715"/>
-        <v>1.0073529411764706</v>
+        <v>0.97426470588235292</v>
       </c>
       <c r="M84" s="17">
         <f t="shared" si="716"/>
         <v>0.27200000000000002</v>
       </c>
       <c r="N84" s="6">
-        <v>5.6000000000000001E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="O84" s="6">
-        <v>0.20699999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="P84" s="6">
-        <v>5.2999999999999999E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="Q84" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R84" s="28">
-        <v>3.7999999999999999E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S84" s="32" t="s">
         <v>93</v>
       </c>
       <c r="T84" s="14">
         <f t="shared" ref="T84:T85" si="720">ROUND(B84/K84,3)</f>
-        <v>0.98399999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="U84" s="14">
         <f t="shared" ref="U84:U85" si="721">ROUND(C84/L84,3)</f>
-        <v>0.97899999999999998</v>
+        <v>1.0329999999999999</v>
       </c>
       <c r="V84" s="17">
         <f t="shared" ref="V84:V85" si="722">ROUND(D84/M84,3)</f>
-        <v>12.25</v>
+        <v>12.085000000000001</v>
       </c>
       <c r="W84" s="22">
         <f t="shared" ref="W84:W85" si="723">ROUND(E84/N84,3)</f>
-        <v>7.1609999999999996</v>
+        <v>6.431</v>
       </c>
       <c r="X84" s="22">
         <f t="shared" ref="X84:X85" si="724">ROUND(F84/O84,3)</f>
-        <v>12.696</v>
+        <v>12.411</v>
       </c>
       <c r="Y84" s="22">
         <f t="shared" ref="Y84:Y85" si="725">ROUND(G84/P84,3)</f>
-        <v>11.321</v>
+        <v>11.706</v>
       </c>
       <c r="Z84" s="22">
         <f t="shared" ref="Z84:Z85" si="726">ROUND(H84/Q84,3)</f>
-        <v>8.6669999999999998</v>
+        <v>8</v>
       </c>
       <c r="AA84" s="35">
         <f t="shared" ref="AA84:AA85" si="727">ROUND(I84/R84,3)</f>
-        <v>5.2629999999999999</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9148,27 +9160,27 @@
       </c>
       <c r="B85" s="14">
         <f t="shared" si="717"/>
-        <v>153.53465648854962</v>
+        <v>153.62847540482738</v>
       </c>
       <c r="C85" s="14">
         <f t="shared" si="718"/>
-        <v>1.0174045801526719</v>
+        <v>1.0042774213260006</v>
       </c>
       <c r="D85" s="17">
         <f t="shared" si="719"/>
-        <v>3.2749999999999999</v>
+        <v>3.2730000000000001</v>
       </c>
       <c r="E85" s="6">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="F85" s="6">
-        <v>2.5760000000000001</v>
+        <v>2.5840000000000001</v>
       </c>
       <c r="G85" s="6">
-        <v>0.60199999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="H85" s="6">
-        <v>9.7000000000000003E-2</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="I85" s="28">
         <v>0.2</v>
@@ -9178,65 +9190,65 @@
       </c>
       <c r="K85" s="14">
         <f t="shared" si="714"/>
-        <v>152.78388278388275</v>
+        <v>154.48148148148144</v>
       </c>
       <c r="L85" s="14">
         <f t="shared" si="715"/>
-        <v>0.99633699633699635</v>
+        <v>1.0074074074074073</v>
       </c>
       <c r="M85" s="17">
         <f t="shared" si="716"/>
-        <v>0.27300000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="N85" s="6">
-        <v>5.5E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="O85" s="6">
         <v>0.20799999999999999</v>
       </c>
       <c r="P85" s="6">
-        <v>5.1999999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="Q85" s="6">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="R85" s="28">
-        <v>3.6999999999999998E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="S85" s="32" t="s">
         <v>94</v>
       </c>
       <c r="T85" s="14">
         <f t="shared" si="720"/>
-        <v>1.0049999999999999</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="U85" s="14">
         <f t="shared" si="721"/>
-        <v>1.0209999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="V85" s="17">
         <f t="shared" si="722"/>
-        <v>11.996</v>
+        <v>12.122</v>
       </c>
       <c r="W85" s="22">
         <f t="shared" si="723"/>
-        <v>6.782</v>
+        <v>6.5339999999999998</v>
       </c>
       <c r="X85" s="22">
         <f t="shared" si="724"/>
-        <v>12.385</v>
+        <v>12.423</v>
       </c>
       <c r="Y85" s="22">
         <f t="shared" si="725"/>
-        <v>11.577</v>
+        <v>12</v>
       </c>
       <c r="Z85" s="22">
         <f t="shared" si="726"/>
-        <v>7.4619999999999997</v>
+        <v>7.4169999999999998</v>
       </c>
       <c r="AA85" s="35">
         <f t="shared" si="727"/>
-        <v>5.4050000000000002</v>
+        <v>5.7140000000000004</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9245,24 +9257,24 @@
       </c>
       <c r="B86" s="14">
         <f t="shared" ref="B86" si="728">D$2/D86</f>
-        <v>154.05208333333334</v>
+        <v>152.41770233404063</v>
       </c>
       <c r="C86" s="14">
         <f t="shared" ref="C86" si="729">D85/D86</f>
-        <v>1.0033700980392155</v>
+        <v>0.99211882388602612</v>
       </c>
       <c r="D86" s="17">
         <f t="shared" ref="D86" si="730">SUM(F86:H86)</f>
-        <v>3.2640000000000002</v>
+        <v>3.2989999999999999</v>
       </c>
       <c r="E86" s="6">
-        <v>0.375</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="F86" s="6">
-        <v>2.5720000000000001</v>
+        <v>2.605</v>
       </c>
       <c r="G86" s="6">
-        <v>0.59899999999999998</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="H86" s="6">
         <v>9.2999999999999999E-2</v>
@@ -9275,65 +9287,356 @@
       </c>
       <c r="K86" s="14">
         <f t="shared" si="714"/>
-        <v>148.96428571428567</v>
+        <v>157.99242424242422</v>
       </c>
       <c r="L86" s="14">
         <f t="shared" si="715"/>
-        <v>0.97499999999999998</v>
+        <v>1.0227272727272727</v>
       </c>
       <c r="M86" s="17">
         <f t="shared" si="716"/>
-        <v>0.28000000000000003</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="N86" s="6">
-        <v>5.2999999999999999E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O86" s="6">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="P86" s="6">
-        <v>5.2999999999999999E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q86" s="6">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="R86" s="28">
-        <v>3.6999999999999998E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S86" s="32" t="s">
         <v>95</v>
       </c>
       <c r="T86" s="14">
         <f t="shared" ref="T86" si="731">ROUND(B86/K86,3)</f>
-        <v>1.034</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="U86" s="14">
         <f t="shared" ref="U86" si="732">ROUND(C86/L86,3)</f>
-        <v>1.0289999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="V86" s="17">
         <f t="shared" ref="V86" si="733">ROUND(D86/M86,3)</f>
-        <v>11.657</v>
+        <v>12.496</v>
       </c>
       <c r="W86" s="22">
         <f t="shared" ref="W86" si="734">ROUND(E86/N86,3)</f>
-        <v>7.0750000000000002</v>
+        <v>5.6139999999999999</v>
       </c>
       <c r="X86" s="22">
         <f t="shared" ref="X86" si="735">ROUND(F86/O86,3)</f>
-        <v>12.019</v>
+        <v>13.025</v>
       </c>
       <c r="Y86" s="22">
         <f t="shared" ref="Y86" si="736">ROUND(G86/P86,3)</f>
-        <v>11.302</v>
+        <v>11.558</v>
       </c>
       <c r="Z86" s="22">
         <f t="shared" ref="Z86" si="737">ROUND(H86/Q86,3)</f>
-        <v>7.1539999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="AA86" s="35">
         <f t="shared" ref="AA86" si="738">ROUND(I86/R86,3)</f>
-        <v>5.4050000000000002</v>
+        <v>5.556</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" s="14">
+        <f t="shared" ref="B87:B89" si="739">D$2/D87</f>
+        <v>151.81944444444446</v>
+      </c>
+      <c r="C87" s="14">
+        <f t="shared" ref="C87:C89" si="740">D86/D87</f>
+        <v>0.99607487922705318</v>
+      </c>
+      <c r="D87" s="17">
+        <f t="shared" ref="D87:D89" si="741">SUM(F87:H87)</f>
+        <v>3.3119999999999998</v>
+      </c>
+      <c r="E87" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="F87" s="6">
+        <v>2.609</v>
+      </c>
+      <c r="G87" s="6">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="H87" s="6">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I87" s="28">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="J87" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="K87" s="14">
+        <f t="shared" ref="K87:K89" si="742">M$2/M87</f>
+        <v>157.99242424242422</v>
+      </c>
+      <c r="L87" s="14">
+        <f t="shared" ref="L87:L89" si="743">M86/M87</f>
+        <v>1</v>
+      </c>
+      <c r="M87" s="17">
+        <f t="shared" ref="M87:M89" si="744">SUM(O87:Q87)</f>
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="N87" s="6">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="O87" s="6">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="P87" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R87" s="28">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S87" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="T87" s="14">
+        <f t="shared" ref="T87:T89" si="745">ROUND(B87/K87,3)</f>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="U87" s="14">
+        <f t="shared" ref="U87:U89" si="746">ROUND(C87/L87,3)</f>
+        <v>0.996</v>
+      </c>
+      <c r="V87" s="17">
+        <f t="shared" ref="V87:V89" si="747">ROUND(D87/M87,3)</f>
+        <v>12.545</v>
+      </c>
+      <c r="W87" s="22">
+        <f t="shared" ref="W87:W89" si="748">ROUND(E87/N87,3)</f>
+        <v>6.5519999999999996</v>
+      </c>
+      <c r="X87" s="22">
+        <f t="shared" ref="X87:X89" si="749">ROUND(F87/O87,3)</f>
+        <v>12.916</v>
+      </c>
+      <c r="Y87" s="22">
+        <f t="shared" ref="Y87:Y89" si="750">ROUND(G87/P87,3)</f>
+        <v>12.02</v>
+      </c>
+      <c r="Z87" s="22">
+        <f t="shared" ref="Z87:Z89" si="751">ROUND(H87/Q87,3)</f>
+        <v>8.5</v>
+      </c>
+      <c r="AA87" s="35">
+        <f t="shared" ref="AA87:AA89" si="752">ROUND(I87/R87,3)</f>
+        <v>5.5830000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88" s="14">
+        <f t="shared" si="739"/>
+        <v>152.3253559527416</v>
+      </c>
+      <c r="C88" s="14">
+        <f t="shared" si="740"/>
+        <v>1.0033323235383216</v>
+      </c>
+      <c r="D88" s="17">
+        <f t="shared" si="741"/>
+        <v>3.3010000000000002</v>
+      </c>
+      <c r="E88" s="6">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="F88" s="6">
+        <v>2.6110000000000002</v>
+      </c>
+      <c r="G88" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H88" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="I88" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J88" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="K88" s="14">
+        <f t="shared" si="742"/>
+        <v>157.3962264150943</v>
+      </c>
+      <c r="L88" s="14">
+        <f t="shared" si="743"/>
+        <v>0.99622641509433962</v>
+      </c>
+      <c r="M88" s="17">
+        <f t="shared" si="744"/>
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="N88" s="6">
+        <v>6.2E-2</v>
+      </c>
+      <c r="O88" s="6">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="P88" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R88" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="S88" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="T88" s="14">
+        <f t="shared" si="745"/>
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="U88" s="14">
+        <f t="shared" si="746"/>
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="V88" s="17">
+        <f t="shared" si="747"/>
+        <v>12.457000000000001</v>
+      </c>
+      <c r="W88" s="22">
+        <f t="shared" si="748"/>
+        <v>6.1609999999999996</v>
+      </c>
+      <c r="X88" s="22">
+        <f t="shared" si="749"/>
+        <v>12.862</v>
+      </c>
+      <c r="Y88" s="22">
+        <f t="shared" si="750"/>
+        <v>12</v>
+      </c>
+      <c r="Z88" s="22">
+        <f t="shared" si="751"/>
+        <v>7.5</v>
+      </c>
+      <c r="AA88" s="35">
+        <f t="shared" si="752"/>
+        <v>5.7140000000000004</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89" s="14">
+        <f t="shared" si="739"/>
+        <v>152.37151515151515</v>
+      </c>
+      <c r="C89" s="14">
+        <f t="shared" si="740"/>
+        <v>1.0003030303030305</v>
+      </c>
+      <c r="D89" s="17">
+        <f t="shared" si="741"/>
+        <v>3.3</v>
+      </c>
+      <c r="E89" s="6">
+        <v>0.372</v>
+      </c>
+      <c r="F89" s="6">
+        <v>2.6059999999999999</v>
+      </c>
+      <c r="G89" s="6">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="H89" s="6">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="I89" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J89" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K89" s="14">
+        <f t="shared" si="742"/>
+        <v>155.05576208178437</v>
+      </c>
+      <c r="L89" s="14">
+        <f t="shared" si="743"/>
+        <v>0.98513011152416352</v>
+      </c>
+      <c r="M89" s="17">
+        <f t="shared" si="744"/>
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="N89" s="6">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="O89" s="6">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="P89" s="6">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R89" s="28">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S89" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="T89" s="14">
+        <f t="shared" si="745"/>
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="U89" s="14">
+        <f t="shared" si="746"/>
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="V89" s="17">
+        <f t="shared" si="747"/>
+        <v>12.268000000000001</v>
+      </c>
+      <c r="W89" s="22">
+        <f t="shared" si="748"/>
+        <v>6.4139999999999997</v>
+      </c>
+      <c r="X89" s="22">
+        <f t="shared" si="749"/>
+        <v>12.65</v>
+      </c>
+      <c r="Y89" s="22">
+        <f t="shared" si="750"/>
+        <v>11.725</v>
+      </c>
+      <c r="Z89" s="22">
+        <f t="shared" si="751"/>
+        <v>8</v>
+      </c>
+      <c r="AA89" s="35">
+        <f t="shared" si="752"/>
+        <v>5.556</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EB0A6C-952F-41A7-B8A1-9F4587B9AACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F2F80-2B37-4B53-9247-21DC82FFCE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="100">
   <si>
     <t>H23</t>
   </si>
@@ -401,6 +401,10 @@
   </si>
   <si>
     <t>H109</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H110</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -992,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB89"/>
+  <dimension ref="A1:AB90"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="5"/>
@@ -8577,57 +8581,57 @@
       </c>
       <c r="B79" s="29">
         <f t="shared" ref="B79" si="687">D$2/D79</f>
-        <v>152.00302297460703</v>
+        <v>150.36662679425839</v>
       </c>
       <c r="C79" s="29">
         <f t="shared" ref="C79" si="688">D78/D79</f>
-        <v>1.0033252720677146</v>
+        <v>0.99252392344497609</v>
       </c>
       <c r="D79" s="30">
         <f t="shared" ref="D79" si="689">SUM(F79:H79)</f>
-        <v>3.3079999999999998</v>
+        <v>3.3439999999999999</v>
       </c>
       <c r="E79" s="25">
-        <v>0.38800000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="F79" s="26">
-        <v>2.6059999999999999</v>
+        <v>2.6429999999999998</v>
       </c>
       <c r="G79" s="26">
-        <v>0.60299999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H79" s="25">
-        <v>9.9000000000000005E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I79" s="27">
-        <v>0.2</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="J79" s="33" t="s">
         <v>88</v>
       </c>
       <c r="K79" s="29">
         <f t="shared" ref="K79:K80" si="690">M$2/M79</f>
-        <v>155.05576208178437</v>
+        <v>157.3962264150943</v>
       </c>
       <c r="L79" s="29">
         <f t="shared" ref="L79:L80" si="691">M78/M79</f>
-        <v>1.0631970260223049</v>
+        <v>1.0792452830188679</v>
       </c>
       <c r="M79" s="30">
         <f t="shared" si="686"/>
-        <v>0.26900000000000002</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="N79" s="25">
-        <v>6.3E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="O79" s="26">
-        <v>0.20300000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="P79" s="26">
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q79" s="25">
-        <v>1.4E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="R79" s="27">
         <v>3.6999999999999998E-2</v>
@@ -8637,35 +8641,35 @@
       </c>
       <c r="T79" s="29">
         <f t="shared" ref="T79" si="692">ROUND(B79/K79,3)</f>
-        <v>0.98</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="U79" s="29">
         <f t="shared" ref="U79" si="693">ROUND(C79/L79,3)</f>
-        <v>0.94399999999999995</v>
+        <v>0.92</v>
       </c>
       <c r="V79" s="30">
         <f t="shared" ref="V79" si="694">ROUND(D79/M79,3)</f>
-        <v>12.297000000000001</v>
+        <v>12.619</v>
       </c>
       <c r="W79" s="25">
         <f t="shared" ref="W79" si="695">ROUND(E79/N79,3)</f>
-        <v>6.1589999999999998</v>
+        <v>6.7320000000000002</v>
       </c>
       <c r="X79" s="26">
         <f t="shared" ref="X79" si="696">ROUND(F79/O79,3)</f>
-        <v>12.837</v>
+        <v>13.148999999999999</v>
       </c>
       <c r="Y79" s="26">
         <f t="shared" ref="Y79" si="697">ROUND(G79/P79,3)</f>
-        <v>11.596</v>
+        <v>11.654</v>
       </c>
       <c r="Z79" s="25">
         <f t="shared" ref="Z79" si="698">ROUND(H79/Q79,3)</f>
-        <v>7.0709999999999997</v>
+        <v>7.9169999999999998</v>
       </c>
       <c r="AA79" s="27">
         <f t="shared" ref="AA79" si="699">ROUND(I79/R79,3)</f>
-        <v>5.4050000000000002</v>
+        <v>5.4589999999999996</v>
       </c>
     </row>
     <row r="80" spans="1:28" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8674,27 +8678,27 @@
       </c>
       <c r="B80" s="14">
         <f t="shared" ref="B80" si="700">D$2/D80</f>
-        <v>152.04898699727852</v>
+        <v>152.60273141122914</v>
       </c>
       <c r="C80" s="14">
         <f t="shared" ref="C80" si="701">D79/D80</f>
-        <v>1.0003023888720894</v>
+        <v>1.0148710166919575</v>
       </c>
       <c r="D80" s="17">
         <f t="shared" ref="D80" si="702">SUM(F80:H80)</f>
-        <v>3.3069999999999999</v>
+        <v>3.2949999999999999</v>
       </c>
       <c r="E80" s="22">
-        <v>0.38400000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="F80" s="22">
-        <v>2.6080000000000001</v>
+        <v>2.6030000000000002</v>
       </c>
       <c r="G80" s="22">
-        <v>0.59699999999999998</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="H80" s="22">
-        <v>0.10199999999999999</v>
+        <v>9.4E-2</v>
       </c>
       <c r="I80" s="35">
         <v>0.2</v>
@@ -8704,21 +8708,21 @@
       </c>
       <c r="K80" s="14">
         <f t="shared" si="690"/>
-        <v>151.67272727272723</v>
+        <v>157.3962264150943</v>
       </c>
       <c r="L80" s="14">
         <f t="shared" si="691"/>
-        <v>0.97818181818181815</v>
+        <v>1</v>
       </c>
       <c r="M80" s="17">
         <f t="shared" si="686"/>
-        <v>0.27500000000000002</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="N80" s="22">
-        <v>5.6000000000000001E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O80" s="22">
-        <v>0.21099999999999999</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="P80" s="22">
         <v>5.1999999999999998E-2</v>
@@ -8734,31 +8738,31 @@
       </c>
       <c r="T80" s="14">
         <f t="shared" ref="T80:T83" si="703">ROUND(B80/K80,3)</f>
-        <v>1.002</v>
+        <v>0.97</v>
       </c>
       <c r="U80" s="14">
         <f t="shared" ref="U80:U83" si="704">ROUND(C80/L80,3)</f>
-        <v>1.0229999999999999</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="V80" s="17">
         <f t="shared" ref="V80:V83" si="705">ROUND(D80/M80,3)</f>
-        <v>12.025</v>
+        <v>12.433999999999999</v>
       </c>
       <c r="W80" s="22">
         <f t="shared" ref="W80:W83" si="706">ROUND(E80/N80,3)</f>
-        <v>6.8570000000000002</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X80" s="22">
         <f t="shared" ref="X80:X83" si="707">ROUND(F80/O80,3)</f>
-        <v>12.36</v>
+        <v>12.95</v>
       </c>
       <c r="Y80" s="22">
         <f t="shared" ref="Y80:Y83" si="708">ROUND(G80/P80,3)</f>
-        <v>11.481</v>
+        <v>11.5</v>
       </c>
       <c r="Z80" s="22">
         <f t="shared" ref="Z80:Z83" si="709">ROUND(H80/Q80,3)</f>
-        <v>8.5</v>
+        <v>7.8330000000000002</v>
       </c>
       <c r="AA80" s="35">
         <f t="shared" ref="AA80:AA83" si="710">ROUND(I80/R80,3)</f>
@@ -8772,87 +8776,87 @@
       </c>
       <c r="B81" s="14">
         <f t="shared" ref="B81:B83" si="711">D$2/D81</f>
-        <v>151.86529749320445</v>
+        <v>150.86288628862889</v>
       </c>
       <c r="C81" s="14">
         <f t="shared" ref="C81:C83" si="712">D80/D81</f>
-        <v>0.99879190576864985</v>
+        <v>0.98859885988598861</v>
       </c>
       <c r="D81" s="17">
         <f t="shared" ref="D81:D83" si="713">SUM(F81:H81)</f>
-        <v>3.3110000000000004</v>
+        <v>3.3329999999999997</v>
       </c>
       <c r="E81" s="6">
-        <v>0.38100000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="F81" s="6">
-        <v>2.6150000000000002</v>
+        <v>2.6309999999999998</v>
       </c>
       <c r="G81" s="6">
-        <v>0.59899999999999998</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="H81" s="6">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="I81" s="28">
-        <v>0.2</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="J81" s="32" t="s">
         <v>90</v>
       </c>
       <c r="K81" s="14">
         <f t="shared" ref="K81:K86" si="714">M$2/M81</f>
-        <v>153.9114391143911</v>
+        <v>156.21722846441943</v>
       </c>
       <c r="L81" s="14">
         <f t="shared" ref="L81:L86" si="715">M80/M81</f>
-        <v>1.014760147601476</v>
+        <v>0.99250936329588013</v>
       </c>
       <c r="M81" s="17">
         <f t="shared" ref="M81:M86" si="716">SUM(O81:Q81)</f>
-        <v>0.27100000000000002</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="N81" s="6">
-        <v>5.6000000000000001E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O81" s="6">
-        <v>0.20599999999999999</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="P81" s="6">
-        <v>5.2999999999999999E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q81" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R81" s="28">
-        <v>3.6999999999999998E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S81" s="32" t="s">
         <v>90</v>
       </c>
       <c r="T81" s="14">
         <f t="shared" si="703"/>
-        <v>0.98699999999999999</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="U81" s="14">
         <f t="shared" si="704"/>
-        <v>0.98399999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="V81" s="17">
         <f t="shared" si="705"/>
-        <v>12.218</v>
+        <v>12.483000000000001</v>
       </c>
       <c r="W81" s="22">
         <f t="shared" si="706"/>
-        <v>6.8040000000000003</v>
+        <v>6.5439999999999996</v>
       </c>
       <c r="X81" s="22">
         <f t="shared" si="707"/>
-        <v>12.694000000000001</v>
+        <v>12.961</v>
       </c>
       <c r="Y81" s="22">
         <f t="shared" si="708"/>
-        <v>11.302</v>
+        <v>11.635</v>
       </c>
       <c r="Z81" s="22">
         <f t="shared" si="709"/>
@@ -8860,7 +8864,7 @@
       </c>
       <c r="AA81" s="35">
         <f t="shared" si="710"/>
-        <v>5.4050000000000002</v>
+        <v>5.6109999999999998</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8869,30 +8873,30 @@
       </c>
       <c r="B82" s="14">
         <f t="shared" si="711"/>
-        <v>153.16052391105694</v>
+        <v>149.9630181926633</v>
       </c>
       <c r="C82" s="14">
         <f t="shared" si="712"/>
-        <v>1.0085287846481876</v>
+        <v>0.99403519236504623</v>
       </c>
       <c r="D82" s="17">
         <f t="shared" si="713"/>
-        <v>3.2830000000000004</v>
+        <v>3.3529999999999998</v>
       </c>
       <c r="E82" s="6">
-        <v>0.39100000000000001</v>
+        <v>0.376</v>
       </c>
       <c r="F82" s="6">
-        <v>2.5960000000000001</v>
+        <v>2.6549999999999998</v>
       </c>
       <c r="G82" s="6">
-        <v>0.6</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H82" s="6">
-        <v>8.6999999999999994E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="I82" s="28">
-        <v>0.19900000000000001</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="J82" s="32" t="s">
         <v>91</v>
@@ -8903,14 +8907,14 @@
       </c>
       <c r="L82" s="14">
         <f t="shared" si="715"/>
-        <v>1.0265151515151516</v>
+        <v>1.0113636363636365</v>
       </c>
       <c r="M82" s="17">
         <f t="shared" si="716"/>
         <v>0.26400000000000001</v>
       </c>
       <c r="N82" s="6">
-        <v>5.8999999999999997E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="O82" s="6">
         <v>0.20200000000000001</v>
@@ -8929,35 +8933,35 @@
       </c>
       <c r="T82" s="14">
         <f t="shared" si="703"/>
-        <v>0.96899999999999997</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="U82" s="14">
         <f t="shared" si="704"/>
-        <v>0.98199999999999998</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="V82" s="17">
         <f t="shared" si="705"/>
-        <v>12.436</v>
+        <v>12.701000000000001</v>
       </c>
       <c r="W82" s="22">
         <f t="shared" si="706"/>
-        <v>6.6269999999999998</v>
+        <v>6.7140000000000004</v>
       </c>
       <c r="X82" s="22">
         <f t="shared" si="707"/>
-        <v>12.851000000000001</v>
+        <v>13.144</v>
       </c>
       <c r="Y82" s="22">
         <f t="shared" si="708"/>
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="Z82" s="22">
         <f t="shared" si="709"/>
-        <v>7.25</v>
+        <v>7.6669999999999998</v>
       </c>
       <c r="AA82" s="35">
         <f t="shared" si="710"/>
-        <v>5.6859999999999999</v>
+        <v>5.7709999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8966,51 +8970,51 @@
       </c>
       <c r="B83" s="14">
         <f t="shared" si="711"/>
-        <v>152.04898699727852</v>
+        <v>150.63690832834033</v>
       </c>
       <c r="C83" s="14">
         <f t="shared" si="712"/>
-        <v>0.99274266706985193</v>
+        <v>1.0044937088076691</v>
       </c>
       <c r="D83" s="17">
         <f t="shared" si="713"/>
-        <v>3.3069999999999999</v>
+        <v>3.3380000000000001</v>
       </c>
       <c r="E83" s="6">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="F83" s="6">
-        <v>2.6110000000000002</v>
+        <v>2.6320000000000001</v>
       </c>
       <c r="G83" s="6">
-        <v>0.60199999999999998</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H83" s="6">
-        <v>9.4E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I83" s="28">
-        <v>0.2</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="J83" s="32" t="s">
         <v>92</v>
       </c>
       <c r="K83" s="14">
         <f t="shared" si="714"/>
-        <v>157.3962264150943</v>
+        <v>156.21722846441943</v>
       </c>
       <c r="L83" s="14">
         <f t="shared" si="715"/>
-        <v>0.99622641509433962</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="M83" s="17">
         <f t="shared" si="716"/>
-        <v>0.26500000000000001</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="N83" s="6">
-        <v>5.8999999999999997E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O83" s="6">
-        <v>0.20200000000000001</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="P83" s="6">
         <v>5.0999999999999997E-2</v>
@@ -9026,35 +9030,35 @@
       </c>
       <c r="T83" s="14">
         <f t="shared" si="703"/>
-        <v>0.96599999999999997</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="U83" s="14">
         <f t="shared" si="704"/>
-        <v>0.997</v>
+        <v>1.016</v>
       </c>
       <c r="V83" s="17">
         <f t="shared" si="705"/>
-        <v>12.478999999999999</v>
+        <v>12.502000000000001</v>
       </c>
       <c r="W83" s="22">
         <f t="shared" si="706"/>
-        <v>6.3390000000000004</v>
+        <v>6.6139999999999999</v>
       </c>
       <c r="X83" s="22">
         <f t="shared" si="707"/>
-        <v>12.926</v>
+        <v>12.901999999999999</v>
       </c>
       <c r="Y83" s="22">
         <f t="shared" si="708"/>
-        <v>11.804</v>
+        <v>11.843</v>
       </c>
       <c r="Z83" s="22">
         <f t="shared" si="709"/>
-        <v>7.8330000000000002</v>
+        <v>8.5</v>
       </c>
       <c r="AA83" s="35">
         <f t="shared" si="710"/>
-        <v>5.556</v>
+        <v>5.6109999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9063,57 +9067,57 @@
       </c>
       <c r="B84" s="14">
         <f t="shared" ref="B84:B85" si="717">D$2/D84</f>
-        <v>152.9741405536964</v>
+        <v>150.00775656324583</v>
       </c>
       <c r="C84" s="14">
         <f t="shared" ref="C84:C85" si="718">D83/D84</f>
-        <v>1.0060845756008518</v>
+        <v>0.99582338902147982</v>
       </c>
       <c r="D84" s="17">
         <f t="shared" ref="D84:D85" si="719">SUM(F84:H84)</f>
-        <v>3.2869999999999999</v>
+        <v>3.3519999999999999</v>
       </c>
       <c r="E84" s="6">
-        <v>0.373</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="F84" s="6">
-        <v>2.5939999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="G84" s="6">
-        <v>0.59699999999999998</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="H84" s="6">
-        <v>9.6000000000000002E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I84" s="28">
-        <v>0.19800000000000001</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="J84" s="32" t="s">
         <v>93</v>
       </c>
       <c r="K84" s="14">
         <f t="shared" si="714"/>
-        <v>153.34558823529409</v>
+        <v>155.63432835820893</v>
       </c>
       <c r="L84" s="14">
         <f t="shared" si="715"/>
-        <v>0.97426470588235292</v>
+        <v>0.99626865671641796</v>
       </c>
       <c r="M84" s="17">
         <f t="shared" si="716"/>
-        <v>0.27200000000000002</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="N84" s="6">
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="O84" s="6">
-        <v>0.20899999999999999</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="P84" s="6">
-        <v>5.0999999999999997E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q84" s="6">
-        <v>1.2E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R84" s="28">
         <v>3.5999999999999997E-2</v>
@@ -9123,35 +9127,35 @@
       </c>
       <c r="T84" s="14">
         <f t="shared" ref="T84:T85" si="720">ROUND(B84/K84,3)</f>
-        <v>0.998</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="U84" s="14">
         <f t="shared" ref="U84:U85" si="721">ROUND(C84/L84,3)</f>
-        <v>1.0329999999999999</v>
+        <v>1</v>
       </c>
       <c r="V84" s="17">
         <f t="shared" ref="V84:V85" si="722">ROUND(D84/M84,3)</f>
-        <v>12.085000000000001</v>
+        <v>12.507</v>
       </c>
       <c r="W84" s="22">
         <f t="shared" ref="W84:W85" si="723">ROUND(E84/N84,3)</f>
-        <v>6.431</v>
+        <v>7.3970000000000002</v>
       </c>
       <c r="X84" s="22">
         <f t="shared" ref="X84:X85" si="724">ROUND(F84/O84,3)</f>
-        <v>12.411</v>
+        <v>13.054</v>
       </c>
       <c r="Y84" s="22">
         <f t="shared" ref="Y84:Y85" si="725">ROUND(G84/P84,3)</f>
-        <v>11.706</v>
+        <v>11.635</v>
       </c>
       <c r="Z84" s="22">
         <f t="shared" ref="Z84:Z85" si="726">ROUND(H84/Q84,3)</f>
-        <v>8</v>
+        <v>7.4619999999999997</v>
       </c>
       <c r="AA84" s="35">
         <f t="shared" ref="AA84:AA85" si="727">ROUND(I84/R84,3)</f>
-        <v>5.5</v>
+        <v>5.6669999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9160,95 +9164,95 @@
       </c>
       <c r="B85" s="14">
         <f t="shared" si="717"/>
-        <v>153.62847540482738</v>
+        <v>151.72782136391069</v>
       </c>
       <c r="C85" s="14">
         <f t="shared" si="718"/>
-        <v>1.0042774213260006</v>
+        <v>1.0114665057332528</v>
       </c>
       <c r="D85" s="17">
         <f t="shared" si="719"/>
-        <v>3.2730000000000001</v>
+        <v>3.3140000000000001</v>
       </c>
       <c r="E85" s="6">
-        <v>0.379</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F85" s="6">
-        <v>2.5840000000000001</v>
+        <v>2.6120000000000001</v>
       </c>
       <c r="G85" s="6">
-        <v>0.6</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="H85" s="6">
-        <v>8.8999999999999996E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I85" s="28">
-        <v>0.2</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="J85" s="32" t="s">
         <v>94</v>
       </c>
       <c r="K85" s="14">
         <f t="shared" si="714"/>
-        <v>154.48148148148144</v>
+        <v>155.63432835820893</v>
       </c>
       <c r="L85" s="14">
         <f t="shared" si="715"/>
-        <v>1.0074074074074073</v>
+        <v>1</v>
       </c>
       <c r="M85" s="17">
         <f t="shared" si="716"/>
-        <v>0.27</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="N85" s="6">
-        <v>5.8000000000000003E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O85" s="6">
-        <v>0.20799999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="P85" s="6">
-        <v>0.05</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="Q85" s="6">
-        <v>1.2E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R85" s="28">
-        <v>3.5000000000000003E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S85" s="32" t="s">
         <v>94</v>
       </c>
       <c r="T85" s="14">
         <f t="shared" si="720"/>
-        <v>0.99399999999999999</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="U85" s="14">
         <f t="shared" si="721"/>
-        <v>0.997</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="V85" s="17">
         <f t="shared" si="722"/>
-        <v>12.122</v>
+        <v>12.366</v>
       </c>
       <c r="W85" s="22">
         <f t="shared" si="723"/>
-        <v>6.5339999999999998</v>
+        <v>6.8769999999999998</v>
       </c>
       <c r="X85" s="22">
         <f t="shared" si="724"/>
-        <v>12.423</v>
+        <v>12.804</v>
       </c>
       <c r="Y85" s="22">
         <f t="shared" si="725"/>
-        <v>12</v>
+        <v>11.804</v>
       </c>
       <c r="Z85" s="22">
         <f t="shared" si="726"/>
-        <v>7.4169999999999998</v>
+        <v>7.6920000000000002</v>
       </c>
       <c r="AA85" s="35">
         <f t="shared" si="727"/>
-        <v>5.7140000000000004</v>
+        <v>5.5830000000000002</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9257,51 +9261,51 @@
       </c>
       <c r="B86" s="14">
         <f t="shared" ref="B86" si="728">D$2/D86</f>
-        <v>152.41770233404063</v>
+        <v>150.54670658682636</v>
       </c>
       <c r="C86" s="14">
         <f t="shared" ref="C86" si="729">D85/D86</f>
-        <v>0.99211882388602612</v>
+        <v>0.99221556886227547</v>
       </c>
       <c r="D86" s="17">
         <f t="shared" ref="D86" si="730">SUM(F86:H86)</f>
-        <v>3.2989999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="E86" s="6">
-        <v>0.39300000000000002</v>
+        <v>0.38</v>
       </c>
       <c r="F86" s="6">
-        <v>2.605</v>
+        <v>2.633</v>
       </c>
       <c r="G86" s="6">
-        <v>0.60099999999999998</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="H86" s="6">
-        <v>9.2999999999999999E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I86" s="28">
-        <v>0.2</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="J86" s="32" t="s">
         <v>95</v>
       </c>
       <c r="K86" s="14">
         <f t="shared" si="714"/>
-        <v>157.99242424242422</v>
+        <v>151.12318840579707</v>
       </c>
       <c r="L86" s="14">
         <f t="shared" si="715"/>
-        <v>1.0227272727272727</v>
+        <v>0.97101449275362317</v>
       </c>
       <c r="M86" s="17">
         <f t="shared" si="716"/>
-        <v>0.26400000000000001</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="N86" s="6">
-        <v>7.0000000000000007E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="O86" s="6">
-        <v>0.2</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="P86" s="6">
         <v>5.1999999999999998E-2</v>
@@ -9317,35 +9321,35 @@
       </c>
       <c r="T86" s="14">
         <f t="shared" ref="T86" si="731">ROUND(B86/K86,3)</f>
-        <v>0.96499999999999997</v>
+        <v>0.996</v>
       </c>
       <c r="U86" s="14">
         <f t="shared" ref="U86" si="732">ROUND(C86/L86,3)</f>
-        <v>0.97</v>
+        <v>1.022</v>
       </c>
       <c r="V86" s="17">
         <f t="shared" ref="V86" si="733">ROUND(D86/M86,3)</f>
-        <v>12.496</v>
+        <v>12.101000000000001</v>
       </c>
       <c r="W86" s="22">
         <f t="shared" ref="W86" si="734">ROUND(E86/N86,3)</f>
-        <v>5.6139999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="X86" s="22">
         <f t="shared" ref="X86" si="735">ROUND(F86/O86,3)</f>
-        <v>13.025</v>
+        <v>12.42</v>
       </c>
       <c r="Y86" s="22">
         <f t="shared" ref="Y86" si="736">ROUND(G86/P86,3)</f>
-        <v>11.558</v>
+        <v>11.635</v>
       </c>
       <c r="Z86" s="22">
         <f t="shared" ref="Z86" si="737">ROUND(H86/Q86,3)</f>
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA86" s="35">
         <f t="shared" ref="AA86" si="738">ROUND(I86/R86,3)</f>
-        <v>5.556</v>
+        <v>5.6109999999999998</v>
       </c>
     </row>
     <row r="87" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9353,88 +9357,88 @@
         <v>96</v>
       </c>
       <c r="B87" s="14">
-        <f t="shared" ref="B87:B89" si="739">D$2/D87</f>
-        <v>151.81944444444446</v>
+        <f t="shared" ref="B87:B90" si="739">D$2/D87</f>
+        <v>147.62947739283618</v>
       </c>
       <c r="C87" s="14">
-        <f t="shared" ref="C87:C89" si="740">D86/D87</f>
-        <v>0.99607487922705318</v>
+        <f t="shared" ref="C87:C90" si="740">D86/D87</f>
+        <v>0.9806224310041104</v>
       </c>
       <c r="D87" s="17">
-        <f t="shared" ref="D87:D89" si="741">SUM(F87:H87)</f>
-        <v>3.3119999999999998</v>
+        <f t="shared" ref="D87:D90" si="741">SUM(F87:H87)</f>
+        <v>3.4059999999999997</v>
       </c>
       <c r="E87" s="6">
-        <v>0.38</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="F87" s="6">
-        <v>2.609</v>
+        <v>2.698</v>
       </c>
       <c r="G87" s="6">
-        <v>0.60099999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H87" s="6">
         <v>0.10199999999999999</v>
       </c>
       <c r="I87" s="28">
-        <v>0.20100000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="J87" s="32" t="s">
         <v>96</v>
       </c>
       <c r="K87" s="14">
         <f t="shared" ref="K87:K89" si="742">M$2/M87</f>
-        <v>157.99242424242422</v>
+        <v>150.57761732851981</v>
       </c>
       <c r="L87" s="14">
         <f t="shared" ref="L87:L89" si="743">M86/M87</f>
-        <v>1</v>
+        <v>0.99638989169675085</v>
       </c>
       <c r="M87" s="17">
         <f t="shared" ref="M87:M89" si="744">SUM(O87:Q87)</f>
-        <v>0.26400000000000001</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="N87" s="6">
-        <v>5.8000000000000003E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O87" s="6">
-        <v>0.20200000000000001</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="P87" s="6">
-        <v>0.05</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q87" s="6">
         <v>1.2E-2</v>
       </c>
       <c r="R87" s="28">
-        <v>3.5999999999999997E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="S87" s="32" t="s">
         <v>96</v>
       </c>
       <c r="T87" s="14">
         <f t="shared" ref="T87:T89" si="745">ROUND(B87/K87,3)</f>
-        <v>0.96099999999999997</v>
+        <v>0.98</v>
       </c>
       <c r="U87" s="14">
         <f t="shared" ref="U87:U89" si="746">ROUND(C87/L87,3)</f>
-        <v>0.996</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="V87" s="17">
         <f t="shared" ref="V87:V89" si="747">ROUND(D87/M87,3)</f>
-        <v>12.545</v>
+        <v>12.295999999999999</v>
       </c>
       <c r="W87" s="22">
         <f t="shared" ref="W87:W89" si="748">ROUND(E87/N87,3)</f>
-        <v>6.5519999999999996</v>
+        <v>6.7539999999999996</v>
       </c>
       <c r="X87" s="22">
         <f t="shared" ref="X87:X89" si="749">ROUND(F87/O87,3)</f>
-        <v>12.916</v>
+        <v>12.667</v>
       </c>
       <c r="Y87" s="22">
         <f t="shared" ref="Y87:Y89" si="750">ROUND(G87/P87,3)</f>
-        <v>12.02</v>
+        <v>11.654</v>
       </c>
       <c r="Z87" s="22">
         <f t="shared" ref="Z87:Z89" si="751">ROUND(H87/Q87,3)</f>
@@ -9442,7 +9446,7 @@
       </c>
       <c r="AA87" s="35">
         <f t="shared" ref="AA87:AA89" si="752">ROUND(I87/R87,3)</f>
-        <v>5.5830000000000002</v>
+        <v>5.3419999999999996</v>
       </c>
     </row>
     <row r="88" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9451,27 +9455,27 @@
       </c>
       <c r="B88" s="14">
         <f t="shared" si="739"/>
-        <v>152.3253559527416</v>
+        <v>151.36243226971703</v>
       </c>
       <c r="C88" s="14">
         <f t="shared" si="740"/>
-        <v>1.0033323235383216</v>
+        <v>1.0252859723058398</v>
       </c>
       <c r="D88" s="17">
         <f t="shared" si="741"/>
-        <v>3.3010000000000002</v>
+        <v>3.3220000000000001</v>
       </c>
       <c r="E88" s="6">
-        <v>0.38200000000000001</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="F88" s="6">
-        <v>2.6110000000000002</v>
+        <v>2.621</v>
       </c>
       <c r="G88" s="6">
-        <v>0.6</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="H88" s="6">
-        <v>0.09</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I88" s="28">
         <v>0.2</v>
@@ -9481,65 +9485,65 @@
       </c>
       <c r="K88" s="14">
         <f t="shared" si="742"/>
-        <v>157.3962264150943</v>
+        <v>155.63432835820893</v>
       </c>
       <c r="L88" s="14">
         <f t="shared" si="743"/>
-        <v>0.99622641509433962</v>
+        <v>1.0335820895522387</v>
       </c>
       <c r="M88" s="17">
         <f t="shared" si="744"/>
-        <v>0.26500000000000001</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="N88" s="6">
-        <v>6.2E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="O88" s="6">
-        <v>0.20300000000000001</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="P88" s="6">
-        <v>0.05</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="Q88" s="6">
-        <v>1.2E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R88" s="28">
-        <v>3.5000000000000003E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="S88" s="32" t="s">
         <v>97</v>
       </c>
       <c r="T88" s="14">
         <f t="shared" si="745"/>
-        <v>0.96799999999999997</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="U88" s="14">
         <f t="shared" si="746"/>
-        <v>1.0069999999999999</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="V88" s="17">
         <f t="shared" si="747"/>
-        <v>12.457000000000001</v>
+        <v>12.396000000000001</v>
       </c>
       <c r="W88" s="22">
         <f t="shared" si="748"/>
-        <v>6.1609999999999996</v>
+        <v>7.2359999999999998</v>
       </c>
       <c r="X88" s="22">
         <f t="shared" si="749"/>
-        <v>12.862</v>
+        <v>12.848000000000001</v>
       </c>
       <c r="Y88" s="22">
         <f t="shared" si="750"/>
-        <v>12</v>
+        <v>11.824</v>
       </c>
       <c r="Z88" s="22">
         <f t="shared" si="751"/>
-        <v>7.5</v>
+        <v>7.5380000000000003</v>
       </c>
       <c r="AA88" s="35">
         <f t="shared" si="752"/>
-        <v>5.7140000000000004</v>
+        <v>5.556</v>
       </c>
     </row>
     <row r="89" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9548,45 +9552,45 @@
       </c>
       <c r="B89" s="14">
         <f t="shared" si="739"/>
-        <v>152.37151515151515</v>
+        <v>148.94135071090048</v>
       </c>
       <c r="C89" s="14">
         <f t="shared" si="740"/>
-        <v>1.0003030303030305</v>
+        <v>0.9840047393364928</v>
       </c>
       <c r="D89" s="17">
         <f t="shared" si="741"/>
-        <v>3.3</v>
+        <v>3.3760000000000003</v>
       </c>
       <c r="E89" s="6">
-        <v>0.372</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F89" s="6">
-        <v>2.6059999999999999</v>
+        <v>2.6760000000000002</v>
       </c>
       <c r="G89" s="6">
-        <v>0.59799999999999998</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H89" s="6">
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="I89" s="28">
-        <v>0.2</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="J89" s="32" t="s">
         <v>98</v>
       </c>
       <c r="K89" s="14">
         <f t="shared" si="742"/>
-        <v>155.05576208178437</v>
+        <v>154.48148148148144</v>
       </c>
       <c r="L89" s="14">
         <f t="shared" si="743"/>
-        <v>0.98513011152416352</v>
+        <v>0.99259259259259258</v>
       </c>
       <c r="M89" s="17">
         <f t="shared" si="744"/>
-        <v>0.26900000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="N89" s="6">
         <v>5.8000000000000003E-2</v>
@@ -9595,7 +9599,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="P89" s="6">
-        <v>5.0999999999999997E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="Q89" s="6">
         <v>1.2E-2</v>
@@ -9608,27 +9612,27 @@
       </c>
       <c r="T89" s="14">
         <f t="shared" si="745"/>
-        <v>0.98299999999999998</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="U89" s="14">
         <f t="shared" si="746"/>
-        <v>1.0149999999999999</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="V89" s="17">
         <f t="shared" si="747"/>
-        <v>12.268000000000001</v>
+        <v>12.504</v>
       </c>
       <c r="W89" s="22">
         <f t="shared" si="748"/>
-        <v>6.4139999999999997</v>
+        <v>6.5860000000000003</v>
       </c>
       <c r="X89" s="22">
         <f t="shared" si="749"/>
-        <v>12.65</v>
+        <v>12.99</v>
       </c>
       <c r="Y89" s="22">
         <f t="shared" si="750"/>
-        <v>11.725</v>
+        <v>11.615</v>
       </c>
       <c r="Z89" s="22">
         <f t="shared" si="751"/>
@@ -9636,7 +9640,104 @@
       </c>
       <c r="AA89" s="35">
         <f t="shared" si="752"/>
-        <v>5.556</v>
+        <v>5.6669999999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="14">
+        <f t="shared" si="739"/>
+        <v>149.47265160523187</v>
+      </c>
+      <c r="C90" s="14">
+        <f t="shared" si="740"/>
+        <v>1.0035671819262784</v>
+      </c>
+      <c r="D90" s="17">
+        <f t="shared" si="741"/>
+        <v>3.3639999999999999</v>
+      </c>
+      <c r="E90" s="6">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="F90" s="6">
+        <v>2.657</v>
+      </c>
+      <c r="G90" s="6">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="H90" s="6">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I90" s="28">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J90" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="K90" s="14">
+        <f t="shared" ref="K90" si="753">M$2/M90</f>
+        <v>152.22627737226273</v>
+      </c>
+      <c r="L90" s="14">
+        <f t="shared" ref="L90" si="754">M89/M90</f>
+        <v>0.98540145985401462</v>
+      </c>
+      <c r="M90" s="17">
+        <f t="shared" ref="M90" si="755">SUM(O90:Q90)</f>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="N90" s="6">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="O90" s="6">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="P90" s="6">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R90" s="28">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="S90" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="T90" s="14">
+        <f t="shared" ref="T90" si="756">ROUND(B90/K90,3)</f>
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="U90" s="14">
+        <f t="shared" ref="U90" si="757">ROUND(C90/L90,3)</f>
+        <v>1.018</v>
+      </c>
+      <c r="V90" s="17">
+        <f t="shared" ref="V90" si="758">ROUND(D90/M90,3)</f>
+        <v>12.276999999999999</v>
+      </c>
+      <c r="W90" s="22">
+        <f t="shared" ref="W90" si="759">ROUND(E90/N90,3)</f>
+        <v>6.7190000000000003</v>
+      </c>
+      <c r="X90" s="22">
+        <f t="shared" ref="X90" si="760">ROUND(F90/O90,3)</f>
+        <v>12.592000000000001</v>
+      </c>
+      <c r="Y90" s="22">
+        <f t="shared" ref="Y90" si="761">ROUND(G90/P90,3)</f>
+        <v>11.882</v>
+      </c>
+      <c r="Z90" s="22">
+        <f t="shared" ref="Z90" si="762">ROUND(H90/Q90,3)</f>
+        <v>8.4169999999999998</v>
+      </c>
+      <c r="AA90" s="35">
+        <f t="shared" ref="AA90" si="763">ROUND(I90/R90,3)</f>
+        <v>5.7220000000000004</v>
       </c>
     </row>
   </sheetData>
